--- a/data/output/workbook/2026-06-27.xlsx
+++ b/data/output/workbook/2026-06-27.xlsx
@@ -371,7 +371,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="8782050"/>
+    <ext cx="10125075" cy="9134475"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -551,7 +551,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="9896475"/>
+    <ext cx="10125075" cy="9477375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -581,7 +581,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="9810750"/>
+    <ext cx="10125075" cy="9401175"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -954,7 +954,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-06-27 06:08</t>
+          <t>2026-06-27 08:12</t>
         </is>
       </c>
     </row>
@@ -4530,7 +4530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q77"/>
+  <dimension ref="A1:Q75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4547,823 +4547,823 @@
         </is>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" s="29" t="inlineStr">
+        <is>
+          <t>Arizona Diamondbacks offense vs Tampa Bay Rays defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B62" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C62" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D62" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E62" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F62" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G62" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H62" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I62" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J62" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K62" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L62" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M62" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N62" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O62" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P62" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q62" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
     <row r="63">
-      <c r="A63" s="29" t="inlineStr">
-        <is>
-          <t>Arizona Diamondbacks offense vs Tampa Bay Rays defense</t>
+      <c r="A63" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B63" s="32" t="n">
+        <v>4.976</v>
+      </c>
+      <c r="C63" s="32" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="D63" s="32" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="E63" s="32" t="n">
+        <v>4.467</v>
+      </c>
+      <c r="F63" s="32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="G63" s="32" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H63" s="36" t="inlineStr">
+        <is>
+          <t>25th</t>
+        </is>
+      </c>
+      <c r="I63" s="32" t="inlineStr"/>
+      <c r="J63" s="36" t="inlineStr">
+        <is>
+          <t>26th</t>
+        </is>
+      </c>
+      <c r="K63" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="L63" s="32" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="M63" s="32" t="n">
+        <v>4.867</v>
+      </c>
+      <c r="N63" s="32" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O63" s="32" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="P63" s="32" t="n">
+        <v>4.234</v>
+      </c>
+      <c r="Q63" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B64" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C64" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D64" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E64" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F64" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G64" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H64" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I64" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J64" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K64" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L64" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M64" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N64" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O64" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P64" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q64" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A64" s="31" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B64" s="32" t="n">
+        <v>8.688000000000001</v>
+      </c>
+      <c r="C64" s="32" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="D64" s="32" t="n">
+        <v>8.85</v>
+      </c>
+      <c r="E64" s="32" t="n">
+        <v>9</v>
+      </c>
+      <c r="F64" s="32" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="G64" s="32" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="H64" s="34" t="inlineStr">
+        <is>
+          <t>12th</t>
+        </is>
+      </c>
+      <c r="I64" s="32" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="J64" s="34" t="inlineStr">
+        <is>
+          <t>17th</t>
+        </is>
+      </c>
+      <c r="K64" s="32" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="L64" s="32" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="M64" s="32" t="n">
+        <v>8.067</v>
+      </c>
+      <c r="N64" s="32" t="n">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="O64" s="32" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="P64" s="32" t="n">
+        <v>7.868</v>
+      </c>
+      <c r="Q64" s="35" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B65" s="32" t="n">
-        <v>4.976</v>
+        <v>1.329</v>
       </c>
       <c r="C65" s="32" t="n">
-        <v>4.7</v>
+        <v>1.033</v>
       </c>
       <c r="D65" s="32" t="n">
-        <v>4.45</v>
+        <v>0.85</v>
       </c>
       <c r="E65" s="32" t="n">
-        <v>4.467</v>
+        <v>1</v>
       </c>
       <c r="F65" s="32" t="n">
-        <v>3.4</v>
+        <v>0.9</v>
       </c>
       <c r="G65" s="32" t="n">
-        <v>2.6</v>
+        <v>0.8</v>
       </c>
       <c r="H65" s="36" t="inlineStr">
         <is>
-          <t>25th</t>
+          <t>22nd</t>
         </is>
       </c>
       <c r="I65" s="32" t="inlineStr"/>
-      <c r="J65" s="36" t="inlineStr">
-        <is>
-          <t>26th</t>
-        </is>
-      </c>
-      <c r="K65" s="32" t="n">
-        <v>6</v>
-      </c>
-      <c r="L65" s="32" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="M65" s="32" t="n">
-        <v>4.867</v>
-      </c>
-      <c r="N65" s="32" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="O65" s="32" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="P65" s="32" t="n">
-        <v>4.234</v>
+      <c r="J65" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K65" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L65" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M65" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N65" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O65" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P65" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Q65" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B66" s="32" t="n">
-        <v>8.688000000000001</v>
+        <v>8.265000000000001</v>
       </c>
       <c r="C66" s="32" t="n">
+        <v>8.467000000000001</v>
+      </c>
+      <c r="D66" s="32" t="n">
+        <v>8.35</v>
+      </c>
+      <c r="E66" s="32" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="F66" s="32" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="G66" s="32" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="H66" s="36" t="inlineStr">
+        <is>
+          <t>23rd</t>
+        </is>
+      </c>
+      <c r="I66" s="32" t="inlineStr"/>
+      <c r="J66" s="34" t="inlineStr">
+        <is>
+          <t>15th</t>
+        </is>
+      </c>
+      <c r="K66" s="32" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="L66" s="32" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="D66" s="32" t="n">
-        <v>8.85</v>
-      </c>
-      <c r="E66" s="32" t="n">
-        <v>9</v>
-      </c>
-      <c r="F66" s="32" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="G66" s="32" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="H66" s="34" t="inlineStr">
-        <is>
-          <t>12th</t>
-        </is>
-      </c>
-      <c r="I66" s="32" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J66" s="34" t="inlineStr">
-        <is>
-          <t>17th</t>
-        </is>
-      </c>
-      <c r="K66" s="32" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="L66" s="32" t="n">
-        <v>8.4</v>
-      </c>
       <c r="M66" s="32" t="n">
-        <v>8.067</v>
+        <v>8.333</v>
       </c>
       <c r="N66" s="32" t="n">
-        <v>8.050000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O66" s="32" t="n">
-        <v>7.8</v>
+        <v>9.5</v>
       </c>
       <c r="P66" s="32" t="n">
-        <v>7.868</v>
+        <v>8.737</v>
       </c>
       <c r="Q66" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B67" s="32" t="n">
-        <v>1.329</v>
+        <v>0.612</v>
       </c>
       <c r="C67" s="32" t="n">
-        <v>1.033</v>
+        <v>0.467</v>
       </c>
       <c r="D67" s="32" t="n">
-        <v>0.85</v>
+        <v>0.5</v>
       </c>
       <c r="E67" s="32" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="F67" s="32" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="G67" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H67" s="33" t="inlineStr">
+        <is>
+          <t>10th</t>
+        </is>
+      </c>
+      <c r="I67" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J67" s="36" t="inlineStr">
+        <is>
+          <t>25th</t>
+        </is>
+      </c>
+      <c r="K67" s="32" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L67" s="32" t="n">
         <v>0.8</v>
       </c>
-      <c r="H67" s="36" t="inlineStr">
-        <is>
-          <t>22nd</t>
-        </is>
-      </c>
-      <c r="I67" s="32" t="inlineStr"/>
-      <c r="J67" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K67" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L67" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M67" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N67" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O67" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P67" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="M67" s="32" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="N67" s="32" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="O67" s="32" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="P67" s="32" t="n">
+        <v>0.473</v>
       </c>
       <c r="Q67" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="31" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B68" s="32" t="n">
-        <v>8.265000000000001</v>
-      </c>
-      <c r="C68" s="32" t="n">
-        <v>8.467000000000001</v>
-      </c>
-      <c r="D68" s="32" t="n">
-        <v>8.35</v>
-      </c>
-      <c r="E68" s="32" t="n">
+          <t>Opp 1st Inn R/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="29" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays offense vs Arizona Diamondbacks defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B70" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C70" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D70" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E70" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F70" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G70" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H70" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I70" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J70" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K70" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L70" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M70" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N70" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O70" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P70" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q70" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B71" s="32" t="n">
+        <v>4.437</v>
+      </c>
+      <c r="C71" s="32" t="n">
+        <v>4.033</v>
+      </c>
+      <c r="D71" s="32" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="E71" s="32" t="n">
+        <v>3.667</v>
+      </c>
+      <c r="F71" s="32" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="G71" s="32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H71" s="34" t="inlineStr">
+        <is>
+          <t>14th</t>
+        </is>
+      </c>
+      <c r="I71" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J71" s="36" t="inlineStr">
+        <is>
+          <t>30th</t>
+        </is>
+      </c>
+      <c r="K71" s="32" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="L71" s="32" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="M71" s="32" t="n">
+        <v>5.333</v>
+      </c>
+      <c r="N71" s="32" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="O71" s="32" t="n">
+        <v>4.767</v>
+      </c>
+      <c r="P71" s="32" t="n">
+        <v>4.847</v>
+      </c>
+      <c r="Q71" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="31" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B72" s="32" t="n">
+        <v>8.521000000000001</v>
+      </c>
+      <c r="C72" s="32" t="n">
         <v>8.4</v>
       </c>
-      <c r="F68" s="32" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="G68" s="32" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="H68" s="36" t="inlineStr">
-        <is>
-          <t>23rd</t>
-        </is>
-      </c>
-      <c r="I68" s="32" t="inlineStr"/>
-      <c r="J68" s="34" t="inlineStr">
-        <is>
-          <t>15th</t>
-        </is>
-      </c>
-      <c r="K68" s="32" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="L68" s="32" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="M68" s="32" t="n">
-        <v>8.333</v>
-      </c>
-      <c r="N68" s="32" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="O68" s="32" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="P68" s="32" t="n">
-        <v>8.737</v>
-      </c>
-      <c r="Q68" s="35" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B69" s="32" t="n">
-        <v>0.612</v>
-      </c>
-      <c r="C69" s="32" t="n">
-        <v>0.467</v>
-      </c>
-      <c r="D69" s="32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E69" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="F69" s="32" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="G69" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H69" s="33" t="inlineStr">
-        <is>
-          <t>10th</t>
-        </is>
-      </c>
-      <c r="I69" s="32" t="inlineStr">
+      <c r="D72" s="32" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="E72" s="32" t="n">
+        <v>8.667</v>
+      </c>
+      <c r="F72" s="32" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G72" s="32" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="H72" s="33" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="I72" s="32" t="inlineStr">
         <is>
           <t>★★★</t>
         </is>
       </c>
-      <c r="J69" s="36" t="inlineStr">
-        <is>
-          <t>25th</t>
-        </is>
-      </c>
-      <c r="K69" s="32" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="L69" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="M69" s="32" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="N69" s="32" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="O69" s="32" t="n">
-        <v>0.467</v>
-      </c>
-      <c r="P69" s="32" t="n">
-        <v>0.473</v>
-      </c>
-      <c r="Q69" s="35" t="inlineStr">
-        <is>
-          <t>Opp 1st Inn R/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="29" t="inlineStr">
-        <is>
-          <t>Tampa Bay Rays offense vs Arizona Diamondbacks defense</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B72" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C72" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D72" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E72" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F72" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G72" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H72" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I72" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J72" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K72" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L72" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M72" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N72" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O72" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P72" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q72" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="J72" s="36" t="inlineStr">
+        <is>
+          <t>27th</t>
+        </is>
+      </c>
+      <c r="K72" s="32" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="L72" s="32" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="M72" s="32" t="n">
+        <v>9.132999999999999</v>
+      </c>
+      <c r="N72" s="32" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="O72" s="32" t="n">
+        <v>8.567</v>
+      </c>
+      <c r="P72" s="32" t="n">
+        <v>8.840999999999999</v>
+      </c>
+      <c r="Q72" s="35" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B73" s="32" t="n">
-        <v>4.437</v>
+        <v>1.114</v>
       </c>
       <c r="C73" s="32" t="n">
-        <v>4.033</v>
+        <v>1.133</v>
       </c>
       <c r="D73" s="32" t="n">
-        <v>3.55</v>
+        <v>1.15</v>
       </c>
       <c r="E73" s="32" t="n">
-        <v>3.667</v>
+        <v>1</v>
       </c>
       <c r="F73" s="32" t="n">
-        <v>3.9</v>
+        <v>1</v>
       </c>
       <c r="G73" s="32" t="n">
-        <v>3.6</v>
+        <v>1</v>
       </c>
       <c r="H73" s="34" t="inlineStr">
         <is>
-          <t>14th</t>
-        </is>
-      </c>
-      <c r="I73" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J73" s="36" t="inlineStr">
-        <is>
-          <t>30th</t>
-        </is>
-      </c>
-      <c r="K73" s="32" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="L73" s="32" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="M73" s="32" t="n">
-        <v>5.333</v>
-      </c>
-      <c r="N73" s="32" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="O73" s="32" t="n">
-        <v>4.767</v>
-      </c>
-      <c r="P73" s="32" t="n">
-        <v>4.847</v>
+          <t>17th</t>
+        </is>
+      </c>
+      <c r="I73" s="32" t="inlineStr"/>
+      <c r="J73" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Q73" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B74" s="32" t="n">
-        <v>8.521000000000001</v>
+        <v>8.611000000000001</v>
       </c>
       <c r="C74" s="32" t="n">
-        <v>8.4</v>
+        <v>8.967000000000001</v>
       </c>
       <c r="D74" s="32" t="n">
-        <v>8.300000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="E74" s="32" t="n">
-        <v>8.667</v>
+        <v>9.667</v>
       </c>
       <c r="F74" s="32" t="n">
-        <v>8.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G74" s="32" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="H74" s="33" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="I74" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J74" s="36" t="inlineStr">
-        <is>
-          <t>27th</t>
+        <v>10.2</v>
+      </c>
+      <c r="H74" s="34" t="inlineStr">
+        <is>
+          <t>18th</t>
+        </is>
+      </c>
+      <c r="I74" s="32" t="inlineStr"/>
+      <c r="J74" s="34" t="inlineStr">
+        <is>
+          <t>16th</t>
         </is>
       </c>
       <c r="K74" s="32" t="n">
-        <v>10.4</v>
+        <v>9.4</v>
       </c>
       <c r="L74" s="32" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="M74" s="32" t="n">
-        <v>9.132999999999999</v>
+        <v>8.333</v>
       </c>
       <c r="N74" s="32" t="n">
-        <v>8.75</v>
+        <v>7.9</v>
       </c>
       <c r="O74" s="32" t="n">
-        <v>8.567</v>
+        <v>7.8</v>
       </c>
       <c r="P74" s="32" t="n">
-        <v>8.840999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q74" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B75" s="32" t="n">
-        <v>1.114</v>
+        <v>0.587</v>
       </c>
       <c r="C75" s="32" t="n">
-        <v>1.133</v>
+        <v>0.867</v>
       </c>
       <c r="D75" s="32" t="n">
-        <v>1.15</v>
+        <v>0.7</v>
       </c>
       <c r="E75" s="32" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="F75" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G75" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H75" s="34" t="inlineStr">
+        <is>
+          <t>16th</t>
+        </is>
+      </c>
+      <c r="I75" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J75" s="36" t="inlineStr">
+        <is>
+          <t>29th</t>
+        </is>
+      </c>
+      <c r="K75" s="32" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L75" s="32" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M75" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="F75" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="G75" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="H75" s="34" t="inlineStr">
-        <is>
-          <t>17th</t>
-        </is>
-      </c>
-      <c r="I75" s="32" t="inlineStr"/>
-      <c r="J75" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="N75" s="32" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="O75" s="32" t="n">
+        <v>0.733</v>
+      </c>
+      <c r="P75" s="32" t="n">
+        <v>0.641</v>
       </c>
       <c r="Q75" s="35" t="inlineStr">
-        <is>
-          <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="31" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B76" s="32" t="n">
-        <v>8.611000000000001</v>
-      </c>
-      <c r="C76" s="32" t="n">
-        <v>8.967000000000001</v>
-      </c>
-      <c r="D76" s="32" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="E76" s="32" t="n">
-        <v>9.667</v>
-      </c>
-      <c r="F76" s="32" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="G76" s="32" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="H76" s="34" t="inlineStr">
-        <is>
-          <t>18th</t>
-        </is>
-      </c>
-      <c r="I76" s="32" t="inlineStr"/>
-      <c r="J76" s="34" t="inlineStr">
-        <is>
-          <t>16th</t>
-        </is>
-      </c>
-      <c r="K76" s="32" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="L76" s="32" t="n">
-        <v>9</v>
-      </c>
-      <c r="M76" s="32" t="n">
-        <v>8.333</v>
-      </c>
-      <c r="N76" s="32" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="O76" s="32" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="P76" s="32" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Q76" s="35" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B77" s="32" t="n">
-        <v>0.587</v>
-      </c>
-      <c r="C77" s="32" t="n">
-        <v>0.867</v>
-      </c>
-      <c r="D77" s="32" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E77" s="32" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="F77" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="G77" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H77" s="34" t="inlineStr">
-        <is>
-          <t>16th</t>
-        </is>
-      </c>
-      <c r="I77" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J77" s="36" t="inlineStr">
-        <is>
-          <t>29th</t>
-        </is>
-      </c>
-      <c r="K77" s="32" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="L77" s="32" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="M77" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="N77" s="32" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="O77" s="32" t="n">
-        <v>0.733</v>
-      </c>
-      <c r="P77" s="32" t="n">
-        <v>0.641</v>
-      </c>
-      <c r="Q77" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -5382,7 +5382,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q77"/>
+  <dimension ref="A1:Q74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5399,815 +5399,815 @@
         </is>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" s="29" t="inlineStr">
+        <is>
+          <t>Washington Nationals offense vs Baltimore Orioles defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B61" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C61" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D61" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E61" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F61" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G61" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H61" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I61" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J61" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K61" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L61" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M61" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N61" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O61" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P61" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q61" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B62" s="32" t="n">
+        <v>4.205</v>
+      </c>
+      <c r="C62" s="32" t="n">
+        <v>4.133</v>
+      </c>
+      <c r="D62" s="32" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="E62" s="32" t="n">
+        <v>3.667</v>
+      </c>
+      <c r="F62" s="32" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="G62" s="32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H62" s="33" t="inlineStr">
+        <is>
+          <t>10th</t>
+        </is>
+      </c>
+      <c r="I62" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J62" s="36" t="inlineStr">
+        <is>
+          <t>23rd</t>
+        </is>
+      </c>
+      <c r="K62" s="32" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L62" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="M62" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="N62" s="32" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="O62" s="32" t="n">
+        <v>4.667</v>
+      </c>
+      <c r="P62" s="32" t="n">
+        <v>4.886</v>
+      </c>
+      <c r="Q62" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
+        </is>
+      </c>
+    </row>
     <row r="63">
-      <c r="A63" s="29" t="inlineStr">
-        <is>
-          <t>Washington Nationals offense vs Baltimore Orioles defense</t>
+      <c r="A63" s="31" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B63" s="32" t="n">
+        <v>8.054</v>
+      </c>
+      <c r="C63" s="32" t="n">
+        <v>7.833</v>
+      </c>
+      <c r="D63" s="32" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="E63" s="32" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="F63" s="32" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="G63" s="32" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="H63" s="34" t="inlineStr">
+        <is>
+          <t>13th</t>
+        </is>
+      </c>
+      <c r="I63" s="32" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="J63" s="36" t="inlineStr">
+        <is>
+          <t>24th</t>
+        </is>
+      </c>
+      <c r="K63" s="32" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="L63" s="32" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="M63" s="32" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="N63" s="32" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="O63" s="32" t="n">
+        <v>8.567</v>
+      </c>
+      <c r="P63" s="32" t="n">
+        <v>8.837</v>
+      </c>
+      <c r="Q63" s="35" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B64" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C64" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D64" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E64" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F64" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G64" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H64" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I64" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J64" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K64" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L64" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M64" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N64" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O64" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P64" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q64" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A64" s="31" t="inlineStr">
+        <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B64" s="32" t="n">
+        <v>0.976</v>
+      </c>
+      <c r="C64" s="32" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D64" s="32" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="E64" s="32" t="n">
+        <v>1.267</v>
+      </c>
+      <c r="F64" s="32" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G64" s="32" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H64" s="33" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="I64" s="32" t="inlineStr"/>
+      <c r="J64" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K64" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L64" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M64" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N64" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O64" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P64" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q64" s="35" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B65" s="32" t="n">
-        <v>4.205</v>
+        <v>8.372999999999999</v>
       </c>
       <c r="C65" s="32" t="n">
-        <v>4.133</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D65" s="32" t="n">
-        <v>4.3</v>
+        <v>10</v>
       </c>
       <c r="E65" s="32" t="n">
-        <v>3.667</v>
+        <v>10.733</v>
       </c>
       <c r="F65" s="32" t="n">
-        <v>4.4</v>
+        <v>11</v>
       </c>
       <c r="G65" s="32" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H65" s="33" t="inlineStr">
-        <is>
-          <t>10th</t>
-        </is>
-      </c>
-      <c r="I65" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="H65" s="36" t="inlineStr">
+        <is>
+          <t>25th</t>
+        </is>
+      </c>
+      <c r="I65" s="32" t="inlineStr"/>
       <c r="J65" s="36" t="inlineStr">
         <is>
-          <t>23rd</t>
+          <t>22nd</t>
         </is>
       </c>
       <c r="K65" s="32" t="n">
-        <v>5.6</v>
+        <v>8.6</v>
       </c>
       <c r="L65" s="32" t="n">
-        <v>5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="M65" s="32" t="n">
-        <v>5</v>
+        <v>9.467000000000001</v>
       </c>
       <c r="N65" s="32" t="n">
-        <v>4.55</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="O65" s="32" t="n">
-        <v>4.667</v>
+        <v>8.733000000000001</v>
       </c>
       <c r="P65" s="32" t="n">
-        <v>4.886</v>
+        <v>8.398</v>
       </c>
       <c r="Q65" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="31" t="inlineStr">
         <is>
+          <t>1st Inn R/G</t>
+        </is>
+      </c>
+      <c r="B66" s="32" t="n">
+        <v>0.584</v>
+      </c>
+      <c r="C66" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D66" s="32" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E66" s="32" t="n">
+        <v>0.267</v>
+      </c>
+      <c r="F66" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G66" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H66" s="34" t="inlineStr">
+        <is>
+          <t>18th</t>
+        </is>
+      </c>
+      <c r="I66" s="32" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="J66" s="36" t="inlineStr">
+        <is>
+          <t>24th</t>
+        </is>
+      </c>
+      <c r="K66" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="L66" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="M66" s="32" t="n">
+        <v>0.867</v>
+      </c>
+      <c r="N66" s="32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="O66" s="32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P66" s="32" t="n">
+        <v>0.657</v>
+      </c>
+      <c r="Q66" s="35" t="inlineStr">
+        <is>
+          <t>Opp 1st Inn R/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="29" t="inlineStr">
+        <is>
+          <t>Baltimore Orioles offense vs Washington Nationals defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B69" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C69" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D69" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E69" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F69" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G69" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H69" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I69" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J69" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K69" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L69" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M69" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N69" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O69" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P69" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q69" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B70" s="32" t="n">
+        <v>4.181</v>
+      </c>
+      <c r="C70" s="32" t="n">
+        <v>3.567</v>
+      </c>
+      <c r="D70" s="32" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="E70" s="32" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F70" s="32" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="G70" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="H70" s="36" t="inlineStr">
+        <is>
+          <t>22nd</t>
+        </is>
+      </c>
+      <c r="I70" s="32" t="inlineStr"/>
+      <c r="J70" s="36" t="inlineStr">
+        <is>
+          <t>24th</t>
+        </is>
+      </c>
+      <c r="K70" s="32" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="L70" s="32" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M70" s="32" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="N70" s="32" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="O70" s="32" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="P70" s="32" t="n">
+        <v>5.566</v>
+      </c>
+      <c r="Q70" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="31" t="inlineStr">
+        <is>
           <t>Hits/G</t>
         </is>
       </c>
-      <c r="B66" s="32" t="n">
-        <v>8.054</v>
-      </c>
-      <c r="C66" s="32" t="n">
-        <v>7.833</v>
-      </c>
-      <c r="D66" s="32" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="E66" s="32" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="F66" s="32" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="G66" s="32" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="H66" s="34" t="inlineStr">
-        <is>
-          <t>13th</t>
-        </is>
-      </c>
-      <c r="I66" s="32" t="inlineStr">
-        <is>
-          <t>★★</t>
-        </is>
-      </c>
-      <c r="J66" s="36" t="inlineStr">
-        <is>
-          <t>24th</t>
-        </is>
-      </c>
-      <c r="K66" s="32" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="L66" s="32" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="M66" s="32" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="N66" s="32" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="O66" s="32" t="n">
-        <v>8.567</v>
-      </c>
-      <c r="P66" s="32" t="n">
-        <v>8.837</v>
-      </c>
-      <c r="Q66" s="35" t="inlineStr">
+      <c r="B71" s="32" t="n">
+        <v>7.861</v>
+      </c>
+      <c r="C71" s="32" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="D71" s="32" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="E71" s="32" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="F71" s="32" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="G71" s="32" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="H71" s="36" t="inlineStr">
+        <is>
+          <t>29th</t>
+        </is>
+      </c>
+      <c r="I71" s="32" t="inlineStr"/>
+      <c r="J71" s="36" t="inlineStr">
+        <is>
+          <t>21st</t>
+        </is>
+      </c>
+      <c r="K71" s="32" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="L71" s="32" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="M71" s="32" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="N71" s="32" t="n">
+        <v>10.05</v>
+      </c>
+      <c r="O71" s="32" t="n">
+        <v>9</v>
+      </c>
+      <c r="P71" s="32" t="n">
+        <v>9.259</v>
+      </c>
+      <c r="Q71" s="35" t="inlineStr">
         <is>
           <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="31" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="31" t="inlineStr">
         <is>
           <t>HR/G</t>
         </is>
       </c>
-      <c r="B67" s="32" t="n">
-        <v>0.976</v>
-      </c>
-      <c r="C67" s="32" t="n">
+      <c r="B72" s="32" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="C72" s="32" t="n">
+        <v>1.067</v>
+      </c>
+      <c r="D72" s="32" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="E72" s="32" t="n">
         <v>1.2</v>
       </c>
-      <c r="D67" s="32" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="E67" s="32" t="n">
-        <v>1.267</v>
-      </c>
-      <c r="F67" s="32" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="G67" s="32" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="H67" s="33" t="inlineStr">
-        <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="I67" s="32" t="inlineStr"/>
-      <c r="J67" s="35" t="inlineStr">
+      <c r="F72" s="32" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G72" s="32" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H72" s="33" t="inlineStr">
+        <is>
+          <t>8th</t>
+        </is>
+      </c>
+      <c r="I72" s="32" t="inlineStr"/>
+      <c r="J72" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K67" s="32" t="inlineStr">
+      <c r="K72" s="32" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L67" s="32" t="inlineStr">
+      <c r="L72" s="32" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M67" s="32" t="inlineStr">
+      <c r="M72" s="32" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N67" s="32" t="inlineStr">
+      <c r="N72" s="32" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="O67" s="32" t="inlineStr">
+      <c r="O72" s="32" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P67" s="32" t="inlineStr">
+      <c r="P72" s="32" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Q67" s="35" t="inlineStr">
+      <c r="Q72" s="35" t="inlineStr">
         <is>
           <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="31" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B68" s="32" t="n">
-        <v>8.372999999999999</v>
-      </c>
-      <c r="C68" s="32" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="D68" s="32" t="n">
-        <v>10</v>
-      </c>
-      <c r="E68" s="32" t="n">
-        <v>10.733</v>
-      </c>
-      <c r="F68" s="32" t="n">
-        <v>11</v>
-      </c>
-      <c r="G68" s="32" t="n">
-        <v>11</v>
-      </c>
-      <c r="H68" s="36" t="inlineStr">
-        <is>
-          <t>25th</t>
-        </is>
-      </c>
-      <c r="I68" s="32" t="inlineStr"/>
-      <c r="J68" s="36" t="inlineStr">
-        <is>
-          <t>22nd</t>
-        </is>
-      </c>
-      <c r="K68" s="32" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="L68" s="32" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="M68" s="32" t="n">
-        <v>9.467000000000001</v>
-      </c>
-      <c r="N68" s="32" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="O68" s="32" t="n">
-        <v>8.733000000000001</v>
-      </c>
-      <c r="P68" s="32" t="n">
-        <v>8.398</v>
-      </c>
-      <c r="Q68" s="35" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B69" s="32" t="n">
-        <v>0.584</v>
-      </c>
-      <c r="C69" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="D69" s="32" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="E69" s="32" t="n">
-        <v>0.267</v>
-      </c>
-      <c r="F69" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G69" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H69" s="34" t="inlineStr">
-        <is>
-          <t>18th</t>
-        </is>
-      </c>
-      <c r="I69" s="32" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J69" s="36" t="inlineStr">
-        <is>
-          <t>24th</t>
-        </is>
-      </c>
-      <c r="K69" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="L69" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="M69" s="32" t="n">
-        <v>0.867</v>
-      </c>
-      <c r="N69" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="O69" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="P69" s="32" t="n">
-        <v>0.657</v>
-      </c>
-      <c r="Q69" s="35" t="inlineStr">
-        <is>
-          <t>Opp 1st Inn R/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="29" t="inlineStr">
-        <is>
-          <t>Baltimore Orioles offense vs Washington Nationals defense</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B72" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C72" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D72" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E72" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F72" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G72" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H72" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I72" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J72" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K72" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L72" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M72" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N72" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O72" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P72" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q72" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B73" s="32" t="n">
-        <v>4.181</v>
+        <v>9.048</v>
       </c>
       <c r="C73" s="32" t="n">
-        <v>3.567</v>
+        <v>10.333</v>
       </c>
       <c r="D73" s="32" t="n">
-        <v>2.95</v>
+        <v>10.35</v>
       </c>
       <c r="E73" s="32" t="n">
-        <v>3.2</v>
+        <v>10</v>
       </c>
       <c r="F73" s="32" t="n">
-        <v>2.7</v>
+        <v>10.3</v>
       </c>
       <c r="G73" s="32" t="n">
-        <v>3</v>
-      </c>
-      <c r="H73" s="36" t="inlineStr">
-        <is>
-          <t>22nd</t>
+        <v>10.2</v>
+      </c>
+      <c r="H73" s="34" t="inlineStr">
+        <is>
+          <t>20th</t>
         </is>
       </c>
       <c r="I73" s="32" t="inlineStr"/>
-      <c r="J73" s="36" t="inlineStr">
-        <is>
-          <t>24th</t>
+      <c r="J73" s="34" t="inlineStr">
+        <is>
+          <t>13th</t>
         </is>
       </c>
       <c r="K73" s="32" t="n">
-        <v>5.8</v>
+        <v>9.6</v>
       </c>
       <c r="L73" s="32" t="n">
-        <v>6.6</v>
+        <v>9</v>
       </c>
       <c r="M73" s="32" t="n">
-        <v>6.4</v>
+        <v>8.333</v>
       </c>
       <c r="N73" s="32" t="n">
-        <v>6.3</v>
+        <v>7.75</v>
       </c>
       <c r="O73" s="32" t="n">
-        <v>5.8</v>
+        <v>8.233000000000001</v>
       </c>
       <c r="P73" s="32" t="n">
-        <v>5.566</v>
+        <v>7.729</v>
       </c>
       <c r="Q73" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B74" s="32" t="n">
-        <v>7.861</v>
+        <v>0.428</v>
       </c>
       <c r="C74" s="32" t="n">
-        <v>6.9</v>
+        <v>0.333</v>
       </c>
       <c r="D74" s="32" t="n">
-        <v>6.2</v>
+        <v>0.35</v>
       </c>
       <c r="E74" s="32" t="n">
-        <v>6.2</v>
+        <v>0.333</v>
       </c>
       <c r="F74" s="32" t="n">
-        <v>5.2</v>
+        <v>0.2</v>
       </c>
       <c r="G74" s="32" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="H74" s="36" t="inlineStr">
         <is>
-          <t>29th</t>
+          <t>27th</t>
         </is>
       </c>
       <c r="I74" s="32" t="inlineStr"/>
       <c r="J74" s="36" t="inlineStr">
         <is>
-          <t>21st</t>
+          <t>26th</t>
         </is>
       </c>
       <c r="K74" s="32" t="n">
-        <v>8.800000000000001</v>
+        <v>1.2</v>
       </c>
       <c r="L74" s="32" t="n">
-        <v>10.6</v>
+        <v>0.8</v>
       </c>
       <c r="M74" s="32" t="n">
-        <v>10.2</v>
+        <v>0.733</v>
       </c>
       <c r="N74" s="32" t="n">
-        <v>10.05</v>
+        <v>0.65</v>
       </c>
       <c r="O74" s="32" t="n">
-        <v>9</v>
+        <v>0.8</v>
       </c>
       <c r="P74" s="32" t="n">
-        <v>9.259</v>
+        <v>0.717</v>
       </c>
       <c r="Q74" s="35" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="31" t="inlineStr">
-        <is>
-          <t>HR/G</t>
-        </is>
-      </c>
-      <c r="B75" s="32" t="n">
-        <v>1.175</v>
-      </c>
-      <c r="C75" s="32" t="n">
-        <v>1.067</v>
-      </c>
-      <c r="D75" s="32" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="E75" s="32" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="F75" s="32" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="G75" s="32" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="H75" s="33" t="inlineStr">
-        <is>
-          <t>8th</t>
-        </is>
-      </c>
-      <c r="I75" s="32" t="inlineStr"/>
-      <c r="J75" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q75" s="35" t="inlineStr">
-        <is>
-          <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="31" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B76" s="32" t="n">
-        <v>9.048</v>
-      </c>
-      <c r="C76" s="32" t="n">
-        <v>10.333</v>
-      </c>
-      <c r="D76" s="32" t="n">
-        <v>10.35</v>
-      </c>
-      <c r="E76" s="32" t="n">
-        <v>10</v>
-      </c>
-      <c r="F76" s="32" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="G76" s="32" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="H76" s="34" t="inlineStr">
-        <is>
-          <t>20th</t>
-        </is>
-      </c>
-      <c r="I76" s="32" t="inlineStr"/>
-      <c r="J76" s="34" t="inlineStr">
-        <is>
-          <t>13th</t>
-        </is>
-      </c>
-      <c r="K76" s="32" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="L76" s="32" t="n">
-        <v>9</v>
-      </c>
-      <c r="M76" s="32" t="n">
-        <v>8.333</v>
-      </c>
-      <c r="N76" s="32" t="n">
-        <v>7.75</v>
-      </c>
-      <c r="O76" s="32" t="n">
-        <v>8.233000000000001</v>
-      </c>
-      <c r="P76" s="32" t="n">
-        <v>7.729</v>
-      </c>
-      <c r="Q76" s="35" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B77" s="32" t="n">
-        <v>0.428</v>
-      </c>
-      <c r="C77" s="32" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="D77" s="32" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="E77" s="32" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="F77" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G77" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H77" s="36" t="inlineStr">
-        <is>
-          <t>27th</t>
-        </is>
-      </c>
-      <c r="I77" s="32" t="inlineStr"/>
-      <c r="J77" s="36" t="inlineStr">
-        <is>
-          <t>26th</t>
-        </is>
-      </c>
-      <c r="K77" s="32" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="L77" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="M77" s="32" t="n">
-        <v>0.733</v>
-      </c>
-      <c r="N77" s="32" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="O77" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="P77" s="32" t="n">
-        <v>0.717</v>
-      </c>
-      <c r="Q77" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -7074,7 +7074,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q71"/>
+  <dimension ref="A1:Q73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7091,807 +7091,807 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="29" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="29" t="inlineStr">
         <is>
           <t>Colorado Rockies offense vs Minnesota Twins defense</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="30" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B58" s="30" t="inlineStr">
+      <c r="B60" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C58" s="30" t="inlineStr">
+      <c r="C60" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D58" s="30" t="inlineStr">
+      <c r="D60" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E58" s="30" t="inlineStr">
+      <c r="E60" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F58" s="30" t="inlineStr">
+      <c r="F60" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G58" s="30" t="inlineStr">
+      <c r="G60" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H58" s="30" t="inlineStr">
+      <c r="H60" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I58" s="30" t="inlineStr">
+      <c r="I60" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J58" s="30" t="inlineStr">
+      <c r="J60" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K58" s="30" t="inlineStr">
+      <c r="K60" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L58" s="30" t="inlineStr">
+      <c r="L60" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M58" s="30" t="inlineStr">
+      <c r="M60" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N58" s="30" t="inlineStr">
+      <c r="N60" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O58" s="30" t="inlineStr">
+      <c r="O60" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P58" s="30" t="inlineStr">
+      <c r="P60" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q58" s="30" t="inlineStr">
+      <c r="Q60" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B59" s="32" t="n">
-        <v>3.728</v>
-      </c>
-      <c r="C59" s="32" t="n">
-        <v>3.333</v>
-      </c>
-      <c r="D59" s="32" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="E59" s="32" t="n">
-        <v>3.467</v>
-      </c>
-      <c r="F59" s="32" t="n">
-        <v>3</v>
-      </c>
-      <c r="G59" s="32" t="n">
-        <v>2</v>
-      </c>
-      <c r="H59" s="36" t="inlineStr">
-        <is>
-          <t>29th</t>
-        </is>
-      </c>
-      <c r="I59" s="32" t="inlineStr"/>
-      <c r="J59" s="33" t="inlineStr">
-        <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="K59" s="32" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="L59" s="32" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="M59" s="32" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="N59" s="32" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="O59" s="32" t="n">
-        <v>5.467</v>
-      </c>
-      <c r="P59" s="32" t="n">
-        <v>4.713</v>
-      </c>
-      <c r="Q59" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="31" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B60" s="32" t="n">
-        <v>7.899</v>
-      </c>
-      <c r="C60" s="32" t="n">
-        <v>7.567</v>
-      </c>
-      <c r="D60" s="32" t="n">
-        <v>6.35</v>
-      </c>
-      <c r="E60" s="32" t="n">
-        <v>7.267</v>
-      </c>
-      <c r="F60" s="32" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G60" s="32" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="H60" s="36" t="inlineStr">
-        <is>
-          <t>28th</t>
-        </is>
-      </c>
-      <c r="I60" s="32" t="inlineStr"/>
-      <c r="J60" s="33" t="inlineStr">
-        <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="K60" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="L60" s="32" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="M60" s="32" t="n">
-        <v>7.333</v>
-      </c>
-      <c r="N60" s="32" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="O60" s="32" t="n">
-        <v>8.733000000000001</v>
-      </c>
-      <c r="P60" s="32" t="n">
-        <v>8.749000000000001</v>
-      </c>
-      <c r="Q60" s="35" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B61" s="32" t="n">
-        <v>1.006</v>
+        <v>3.728</v>
       </c>
       <c r="C61" s="32" t="n">
-        <v>0.867</v>
+        <v>3.333</v>
       </c>
       <c r="D61" s="32" t="n">
-        <v>0.85</v>
+        <v>2.8</v>
       </c>
       <c r="E61" s="32" t="n">
-        <v>1.067</v>
+        <v>3.467</v>
       </c>
       <c r="F61" s="32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G61" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="H61" s="34" t="inlineStr">
-        <is>
-          <t>19th</t>
+        <v>2</v>
+      </c>
+      <c r="H61" s="36" t="inlineStr">
+        <is>
+          <t>29th</t>
         </is>
       </c>
       <c r="I61" s="32" t="inlineStr"/>
-      <c r="J61" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K61" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L61" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M61" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N61" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O61" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P61" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J61" s="33" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="K61" s="32" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L61" s="32" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="M61" s="32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N61" s="32" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="O61" s="32" t="n">
+        <v>5.467</v>
+      </c>
+      <c r="P61" s="32" t="n">
+        <v>4.713</v>
       </c>
       <c r="Q61" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B62" s="32" t="n">
-        <v>9.526999999999999</v>
+        <v>7.899</v>
       </c>
       <c r="C62" s="32" t="n">
-        <v>10.1</v>
+        <v>7.567</v>
       </c>
       <c r="D62" s="32" t="n">
-        <v>10.65</v>
+        <v>6.35</v>
       </c>
       <c r="E62" s="32" t="n">
-        <v>9.933</v>
+        <v>7.267</v>
       </c>
       <c r="F62" s="32" t="n">
-        <v>10.1</v>
+        <v>6.5</v>
       </c>
       <c r="G62" s="32" t="n">
-        <v>11.6</v>
+        <v>5.6</v>
       </c>
       <c r="H62" s="36" t="inlineStr">
         <is>
-          <t>29th</t>
+          <t>28th</t>
         </is>
       </c>
       <c r="I62" s="32" t="inlineStr"/>
       <c r="J62" s="33" t="inlineStr">
         <is>
-          <t>4th</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="K62" s="32" t="n">
-        <v>11.2</v>
+        <v>5</v>
       </c>
       <c r="L62" s="32" t="n">
-        <v>9.4</v>
+        <v>6.1</v>
       </c>
       <c r="M62" s="32" t="n">
-        <v>9.667</v>
+        <v>7.333</v>
       </c>
       <c r="N62" s="32" t="n">
-        <v>9.15</v>
+        <v>7.7</v>
       </c>
       <c r="O62" s="32" t="n">
-        <v>8.967000000000001</v>
+        <v>8.733000000000001</v>
       </c>
       <c r="P62" s="32" t="n">
-        <v>8.707000000000001</v>
+        <v>8.749000000000001</v>
       </c>
       <c r="Q62" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="31" t="inlineStr">
         <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B63" s="32" t="n">
+        <v>1.006</v>
+      </c>
+      <c r="C63" s="32" t="n">
+        <v>0.867</v>
+      </c>
+      <c r="D63" s="32" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="E63" s="32" t="n">
+        <v>1.067</v>
+      </c>
+      <c r="F63" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G63" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="H63" s="34" t="inlineStr">
+        <is>
+          <t>19th</t>
+        </is>
+      </c>
+      <c r="I63" s="32" t="inlineStr"/>
+      <c r="J63" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K63" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L63" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M63" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N63" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O63" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P63" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q63" s="35" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="31" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B64" s="32" t="n">
+        <v>9.526999999999999</v>
+      </c>
+      <c r="C64" s="32" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="D64" s="32" t="n">
+        <v>10.65</v>
+      </c>
+      <c r="E64" s="32" t="n">
+        <v>9.933</v>
+      </c>
+      <c r="F64" s="32" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="G64" s="32" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="H64" s="36" t="inlineStr">
+        <is>
+          <t>29th</t>
+        </is>
+      </c>
+      <c r="I64" s="32" t="inlineStr"/>
+      <c r="J64" s="33" t="inlineStr">
+        <is>
+          <t>4th</t>
+        </is>
+      </c>
+      <c r="K64" s="32" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="L64" s="32" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="M64" s="32" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="N64" s="32" t="n">
+        <v>9.15</v>
+      </c>
+      <c r="O64" s="32" t="n">
+        <v>8.967000000000001</v>
+      </c>
+      <c r="P64" s="32" t="n">
+        <v>8.707000000000001</v>
+      </c>
+      <c r="Q64" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B63" s="32" t="n">
+      <c r="B65" s="32" t="n">
         <v>0.325</v>
       </c>
-      <c r="C63" s="32" t="n">
+      <c r="C65" s="32" t="n">
         <v>0.133</v>
       </c>
-      <c r="D63" s="32" t="n">
+      <c r="D65" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="E63" s="32" t="n">
+      <c r="E65" s="32" t="n">
         <v>0.267</v>
       </c>
-      <c r="F63" s="32" t="n">
+      <c r="F65" s="32" t="n">
         <v>0.3</v>
       </c>
-      <c r="G63" s="32" t="n">
+      <c r="G65" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="H63" s="36" t="inlineStr">
+      <c r="H65" s="36" t="inlineStr">
         <is>
           <t>23rd</t>
         </is>
       </c>
-      <c r="I63" s="32" t="inlineStr"/>
-      <c r="J63" s="33" t="inlineStr">
+      <c r="I65" s="32" t="inlineStr"/>
+      <c r="J65" s="33" t="inlineStr">
         <is>
           <t>9th</t>
         </is>
       </c>
-      <c r="K63" s="32" t="n">
+      <c r="K65" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="L63" s="32" t="n">
+      <c r="L65" s="32" t="n">
         <v>0.7</v>
       </c>
-      <c r="M63" s="32" t="n">
+      <c r="M65" s="32" t="n">
         <v>0.667</v>
       </c>
-      <c r="N63" s="32" t="n">
+      <c r="N65" s="32" t="n">
         <v>0.7</v>
       </c>
-      <c r="O63" s="32" t="n">
+      <c r="O65" s="32" t="n">
         <v>0.633</v>
       </c>
-      <c r="P63" s="32" t="n">
+      <c r="P65" s="32" t="n">
         <v>0.5629999999999999</v>
       </c>
-      <c r="Q63" s="35" t="inlineStr">
+      <c r="Q65" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="29" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="29" t="inlineStr">
         <is>
           <t>Minnesota Twins offense vs Colorado Rockies defense</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="30" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B66" s="30" t="inlineStr">
+      <c r="B68" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C66" s="30" t="inlineStr">
+      <c r="C68" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D66" s="30" t="inlineStr">
+      <c r="D68" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E66" s="30" t="inlineStr">
+      <c r="E68" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F66" s="30" t="inlineStr">
+      <c r="F68" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G66" s="30" t="inlineStr">
+      <c r="G68" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H66" s="30" t="inlineStr">
+      <c r="H68" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I66" s="30" t="inlineStr">
+      <c r="I68" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J66" s="30" t="inlineStr">
+      <c r="J68" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K66" s="30" t="inlineStr">
+      <c r="K68" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L66" s="30" t="inlineStr">
+      <c r="L68" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M66" s="30" t="inlineStr">
+      <c r="M68" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N66" s="30" t="inlineStr">
+      <c r="N68" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O66" s="30" t="inlineStr">
+      <c r="O68" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P66" s="30" t="inlineStr">
+      <c r="P68" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q66" s="30" t="inlineStr">
+      <c r="Q68" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B67" s="32" t="n">
-        <v>4.234</v>
-      </c>
-      <c r="C67" s="32" t="n">
-        <v>4.333</v>
-      </c>
-      <c r="D67" s="32" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="E67" s="32" t="n">
-        <v>3.467</v>
-      </c>
-      <c r="F67" s="32" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="G67" s="32" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="H67" s="36" t="inlineStr">
-        <is>
-          <t>26th</t>
-        </is>
-      </c>
-      <c r="I67" s="32" t="inlineStr"/>
-      <c r="J67" s="36" t="inlineStr">
-        <is>
-          <t>25th</t>
-        </is>
-      </c>
-      <c r="K67" s="32" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="L67" s="32" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="M67" s="32" t="n">
-        <v>5.867</v>
-      </c>
-      <c r="N67" s="32" t="n">
-        <v>5.85</v>
-      </c>
-      <c r="O67" s="32" t="n">
-        <v>6</v>
-      </c>
-      <c r="P67" s="32" t="n">
-        <v>6.213</v>
-      </c>
-      <c r="Q67" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="31" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B68" s="32" t="n">
-        <v>8.246</v>
-      </c>
-      <c r="C68" s="32" t="n">
-        <v>8.266999999999999</v>
-      </c>
-      <c r="D68" s="32" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="E68" s="32" t="n">
-        <v>7.533</v>
-      </c>
-      <c r="F68" s="32" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="G68" s="32" t="n">
-        <v>7</v>
-      </c>
-      <c r="H68" s="34" t="inlineStr">
-        <is>
-          <t>17th</t>
-        </is>
-      </c>
-      <c r="I68" s="32" t="inlineStr"/>
-      <c r="J68" s="34" t="inlineStr">
-        <is>
-          <t>19th</t>
-        </is>
-      </c>
-      <c r="K68" s="32" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="L68" s="32" t="n">
-        <v>8</v>
-      </c>
-      <c r="M68" s="32" t="n">
-        <v>8.867000000000001</v>
-      </c>
-      <c r="N68" s="32" t="n">
-        <v>9.050000000000001</v>
-      </c>
-      <c r="O68" s="32" t="n">
-        <v>9.433</v>
-      </c>
-      <c r="P68" s="32" t="n">
-        <v>10.325</v>
-      </c>
-      <c r="Q68" s="35" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B69" s="32" t="n">
-        <v>1.168</v>
+        <v>4.234</v>
       </c>
       <c r="C69" s="32" t="n">
-        <v>1.167</v>
+        <v>4.333</v>
       </c>
       <c r="D69" s="32" t="n">
-        <v>1.25</v>
+        <v>4.15</v>
       </c>
       <c r="E69" s="32" t="n">
-        <v>1</v>
+        <v>3.467</v>
       </c>
       <c r="F69" s="32" t="n">
-        <v>0.9</v>
+        <v>2.5</v>
       </c>
       <c r="G69" s="32" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="H69" s="33" t="inlineStr">
-        <is>
-          <t>10th</t>
+        <v>2.6</v>
+      </c>
+      <c r="H69" s="36" t="inlineStr">
+        <is>
+          <t>26th</t>
         </is>
       </c>
       <c r="I69" s="32" t="inlineStr"/>
-      <c r="J69" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J69" s="36" t="inlineStr">
+        <is>
+          <t>25th</t>
+        </is>
+      </c>
+      <c r="K69" s="32" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="L69" s="32" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="M69" s="32" t="n">
+        <v>5.867</v>
+      </c>
+      <c r="N69" s="32" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="O69" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="P69" s="32" t="n">
+        <v>6.213</v>
       </c>
       <c r="Q69" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B70" s="32" t="n">
-        <v>8.467000000000001</v>
+        <v>8.246</v>
       </c>
       <c r="C70" s="32" t="n">
-        <v>9.199999999999999</v>
+        <v>8.266999999999999</v>
       </c>
       <c r="D70" s="32" t="n">
-        <v>10</v>
+        <v>7.9</v>
       </c>
       <c r="E70" s="32" t="n">
-        <v>10</v>
+        <v>7.533</v>
       </c>
       <c r="F70" s="32" t="n">
-        <v>11</v>
+        <v>6.7</v>
       </c>
       <c r="G70" s="32" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="H70" s="36" t="inlineStr">
-        <is>
-          <t>28th</t>
+        <v>7</v>
+      </c>
+      <c r="H70" s="34" t="inlineStr">
+        <is>
+          <t>17th</t>
         </is>
       </c>
       <c r="I70" s="32" t="inlineStr"/>
-      <c r="J70" s="36" t="inlineStr">
-        <is>
-          <t>29th</t>
+      <c r="J70" s="34" t="inlineStr">
+        <is>
+          <t>19th</t>
         </is>
       </c>
       <c r="K70" s="32" t="n">
-        <v>6.2</v>
+        <v>8.4</v>
       </c>
       <c r="L70" s="32" t="n">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="M70" s="32" t="n">
-        <v>7.2</v>
+        <v>8.867000000000001</v>
       </c>
       <c r="N70" s="32" t="n">
-        <v>7.1</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="O70" s="32" t="n">
-        <v>7.233</v>
+        <v>9.433</v>
       </c>
       <c r="P70" s="32" t="n">
-        <v>6.876</v>
+        <v>10.325</v>
       </c>
       <c r="Q70" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B71" s="32" t="n">
+        <v>1.168</v>
+      </c>
+      <c r="C71" s="32" t="n">
+        <v>1.167</v>
+      </c>
+      <c r="D71" s="32" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E71" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="F71" s="32" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G71" s="32" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H71" s="33" t="inlineStr">
+        <is>
+          <t>10th</t>
+        </is>
+      </c>
+      <c r="I71" s="32" t="inlineStr"/>
+      <c r="J71" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q71" s="35" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="31" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B72" s="32" t="n">
+        <v>8.467000000000001</v>
+      </c>
+      <c r="C72" s="32" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="D72" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="E72" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="F72" s="32" t="n">
+        <v>11</v>
+      </c>
+      <c r="G72" s="32" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="H72" s="36" t="inlineStr">
+        <is>
+          <t>28th</t>
+        </is>
+      </c>
+      <c r="I72" s="32" t="inlineStr"/>
+      <c r="J72" s="36" t="inlineStr">
+        <is>
+          <t>29th</t>
+        </is>
+      </c>
+      <c r="K72" s="32" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="L72" s="32" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="M72" s="32" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="N72" s="32" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="O72" s="32" t="n">
+        <v>7.233</v>
+      </c>
+      <c r="P72" s="32" t="n">
+        <v>6.876</v>
+      </c>
+      <c r="Q72" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B71" s="32" t="n">
+      <c r="B73" s="32" t="n">
         <v>0.395</v>
       </c>
-      <c r="C71" s="32" t="n">
+      <c r="C73" s="32" t="n">
         <v>0.3</v>
       </c>
-      <c r="D71" s="32" t="n">
+      <c r="D73" s="32" t="n">
         <v>0.25</v>
       </c>
-      <c r="E71" s="32" t="n">
+      <c r="E73" s="32" t="n">
         <v>0.267</v>
       </c>
-      <c r="F71" s="32" t="n">
+      <c r="F73" s="32" t="n">
         <v>0.3</v>
       </c>
-      <c r="G71" s="32" t="n">
+      <c r="G73" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="H71" s="34" t="inlineStr">
+      <c r="H73" s="34" t="inlineStr">
         <is>
           <t>11th</t>
         </is>
       </c>
-      <c r="I71" s="32" t="inlineStr">
+      <c r="I73" s="32" t="inlineStr">
         <is>
           <t>★★★</t>
         </is>
       </c>
-      <c r="J71" s="36" t="inlineStr">
+      <c r="J73" s="36" t="inlineStr">
         <is>
           <t>27th</t>
         </is>
       </c>
-      <c r="K71" s="32" t="n">
+      <c r="K73" s="32" t="n">
         <v>1.2</v>
       </c>
-      <c r="L71" s="32" t="n">
+      <c r="L73" s="32" t="n">
         <v>0.7</v>
       </c>
-      <c r="M71" s="32" t="n">
+      <c r="M73" s="32" t="n">
         <v>0.8</v>
       </c>
-      <c r="N71" s="32" t="n">
+      <c r="N73" s="32" t="n">
         <v>0.7</v>
       </c>
-      <c r="O71" s="32" t="n">
+      <c r="O73" s="32" t="n">
         <v>0.7</v>
       </c>
-      <c r="P71" s="32" t="n">
+      <c r="P73" s="32" t="n">
         <v>0.882</v>
       </c>
-      <c r="Q71" s="35" t="inlineStr">
+      <c r="Q73" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.6547000000000001</v>
+        <v>0.6546634615384614</v>
       </c>
       <c r="G6" s="14" t="n">
         <v>-190</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -8387,22 +8387,22 @@
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>Over 8</t>
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.5507582938388624</v>
+        <v>0.5875902439024391</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>-123</v>
+        <v>-142</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>111</v>
+        <v>-105</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -8426,7 +8426,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 55.1% (fair -123). Your call.</t>
+          <t>Model 58.8% (fair -142). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -8453,22 +8453,22 @@
       </c>
       <c r="D10" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates +1.5</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.6929203125</v>
+        <v>0.5514423076923077</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-226</v>
+        <v>-123</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>-156</v>
+        <v>108</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -8492,7 +8492,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 69.3% (fair -226). Your call.</t>
+          <t>Model 55.1% (fair -123). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -8504,37 +8504,37 @@
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>Texas Rangers @ Toronto Blue Jays</t>
+          <t>Cincinnati Reds @ Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>Texas Rangers</t>
+          <t>Pittsburgh Pirates +1.5</t>
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.4795278969957081</v>
+        <v>0.6956106870229007</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>109</v>
+        <v>-229</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>133</v>
+        <v>-162</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -8558,7 +8558,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 48.0% (fair +109). Your call.</t>
+          <t>Model 69.6% (fair -229). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -8575,12 +8575,12 @@
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>Washington Nationals @ Baltimore Orioles</t>
+          <t>Texas Rangers @ Toronto Blue Jays</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -8590,17 +8590,17 @@
       </c>
       <c r="E12" s="20" t="inlineStr">
         <is>
-          <t>Baltimore Orioles</t>
+          <t>Texas Rangers</t>
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.6771374999999999</v>
+        <v>0.4795278969957081</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>-210</v>
+        <v>109</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>-156</v>
+        <v>133</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -8624,7 +8624,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 67.7% (fair -210). Your call.</t>
+          <t>Model 48.0% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -8636,17 +8636,17 @@
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks @ Tampa Bay Rays</t>
+          <t>Washington Nationals @ Baltimore Orioles</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>22:10</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
@@ -8656,17 +8656,17 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks</t>
+          <t>Baltimore Orioles</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.4629583333333334</v>
+        <v>0.6771374999999999</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>116</v>
+        <v>-210</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>140</v>
+        <v>-156</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -8690,7 +8690,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 46.3% (fair +116). Your call.</t>
+          <t>Model 67.7% (fair -210). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -8773,32 +8773,32 @@
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Kansas City Royals @ Chicago White Sox</t>
+          <t>Arizona Diamondbacks @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>22:10</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox -1.5</t>
+          <t>Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.4277734375</v>
+        <v>0.4639915966386555</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>134</v>
+        <v>116</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -8822,7 +8822,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 42.8% (fair +134). Your call.</t>
+          <t>Model 46.4% (fair +116). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -8839,12 +8839,12 @@
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks @ Tampa Bay Rays</t>
+          <t>Kansas City Royals @ Chicago White Sox</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>22:10</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -8854,17 +8854,17 @@
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks +1.5</t>
+          <t>Chicago White Sox -1.5</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.6456692307692308</v>
+        <v>0.4277734375</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>-182</v>
+        <v>134</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>-147</v>
+        <v>156</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -8888,7 +8888,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 64.6% (fair -182). Your call.</t>
+          <t>Model 42.8% (fair +134). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -8905,32 +8905,32 @@
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Seattle Mariners @ Cleveland Guardians</t>
+          <t>Arizona Diamondbacks @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>22:10</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Seattle Mariners</t>
+          <t>Arizona Diamondbacks +1.5</t>
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.6167660944206009</v>
+        <v>0.6475</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>-161</v>
+        <v>-184</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>-133</v>
+        <v>-148</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 61.7% (fair -161). Your call.</t>
+          <t>Model 64.8% (fair -184). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -8966,37 +8966,37 @@
     <row r="18">
       <c r="A18" s="20" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies @ New York Mets</t>
+          <t>Chicago Cubs @ Milwaukee Brewers</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies</t>
+          <t>Milwaukee Brewers -1.5</t>
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.5818188940092165</v>
+        <v>0.4558898305084745</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>-139</v>
+        <v>119</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>-117</v>
+        <v>136</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -9020,7 +9020,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 58.2% (fair -139). Your call.</t>
+          <t>Model 45.6% (fair +119). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -9032,17 +9032,17 @@
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Kansas City Royals @ Chicago White Sox</t>
+          <t>Seattle Mariners @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -9052,17 +9052,17 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox</t>
+          <t>Seattle Mariners</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.5913702702702703</v>
+        <v>0.6175531914893617</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>-145</v>
+        <v>-161</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>-122</v>
+        <v>-135</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -9086,7 +9086,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 59.1% (fair -145). Your call.</t>
+          <t>Model 61.8% (fair -161). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -9098,17 +9098,17 @@
     <row r="20">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies @ New York Mets</t>
+          <t>Kansas City Royals @ Chicago White Sox</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -9118,17 +9118,17 @@
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies</t>
+          <t>Chicago White Sox</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.4710132158590308</v>
+        <v>0.5886225225225225</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>112</v>
+        <v>-143</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>127</v>
+        <v>-122</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -9152,7 +9152,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 47.1% (fair +112). Your call.</t>
+          <t>Model 58.9% (fair -143). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -9188,13 +9188,13 @@
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.5614985915492957</v>
+        <v>0.5604184834123221</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>-128</v>
+        <v>-127</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>-113</v>
+        <v>-111</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -9218,7 +9218,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 56.1% (fair -128). Your call.</t>
+          <t>Model 56.0% (fair -127). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -9235,32 +9235,32 @@
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>Texas Rangers @ Toronto Blue Jays</t>
+          <t>Philadelphia Phillies @ New York Mets</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>19:07</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>Under 8</t>
+          <t>Philadelphia Phillies</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.4968075117370893</v>
+        <v>0.4754260089686099</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -9284,7 +9284,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 49.7% (fair +101). Your call.</t>
+          <t>Model 47.5% (fair +110). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -9311,22 +9311,22 @@
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers -1.5</t>
+          <t>Milwaukee Brewers</t>
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.4590434782608696</v>
+        <v>0.6343800000000001</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>118</v>
+        <v>-174</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>130</v>
+        <v>-150</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -9350,7 +9350,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 45.9% (fair +118). Your call.</t>
+          <t>Model 63.4% (fair -174). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -9386,13 +9386,13 @@
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.6574295880149813</v>
+        <v>0.6558248120300751</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>-192</v>
+        <v>-191</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>-167</v>
+        <v>-166</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -9416,7 +9416,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 65.7% (fair -192). Your call.</t>
+          <t>Model 65.6% (fair -191). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -9428,17 +9428,17 @@
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>Chicago Cubs @ Milwaukee Brewers</t>
+          <t>Houston Astros @ Detroit Tigers</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
@@ -9448,17 +9448,17 @@
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers</t>
+          <t>Detroit Tigers</t>
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.6387823529411765</v>
+        <v>0.4730630630630631</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>-177</v>
+        <v>111</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>-155</v>
+        <v>122</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -9482,7 +9482,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 63.9% (fair -177). Your call.</t>
+          <t>Model 47.3% (fair +111). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -9494,17 +9494,17 @@
     <row r="26">
       <c r="A26" s="20" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>Houston Astros @ Detroit Tigers</t>
+          <t>Phoenix Mercury @ Toronto Tempo</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -9514,17 +9514,17 @@
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
-          <t>Detroit Tigers</t>
+          <t>Phoenix Mercury</t>
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.4730630630630631</v>
+        <v>0.3501013513513513</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>111</v>
+        <v>186</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>122</v>
+        <v>196</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 47.3% (fair +111). Your call.</t>
+          <t>Model 35.0% (fair +186). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -9560,17 +9560,17 @@
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>Phoenix Mercury @ Toronto Tempo</t>
+          <t>Chicago Cubs @ Milwaukee Brewers</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>Phoenix Mercury</t>
+          <t>Milwaukee Brewers</t>
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.3555102040816326</v>
+        <v>0.61746</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>181</v>
+        <v>-161</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>194</v>
+        <v>-150</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -9614,7 +9614,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 35.6% (fair +181). Your call.</t>
+          <t>Model 61.7% (fair -161). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -9626,17 +9626,17 @@
     <row r="28">
       <c r="A28" s="20" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>Chicago Cubs @ Milwaukee Brewers</t>
+          <t>Texas Rangers @ Toronto Blue Jays</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:07</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -9646,17 +9646,17 @@
       </c>
       <c r="E28" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers</t>
+          <t>Texas Rangers</t>
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.6204000000000001</v>
+        <v>0.3753649635036496</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>-163</v>
+        <v>166</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>-150</v>
+        <v>174</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -9680,7 +9680,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 62.0% (fair -163). Your call.</t>
+          <t>Model 37.5% (fair +166). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -9697,12 +9697,12 @@
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>Texas Rangers @ Toronto Blue Jays</t>
+          <t>Atlanta Dream @ Seattle Storm</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>19:07</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
@@ -9712,17 +9712,17 @@
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>Texas Rangers</t>
+          <t>Seattle Storm</t>
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.3753649635036496</v>
+        <v>0.2252087912087912</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>166</v>
+        <v>344</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>174</v>
+        <v>355</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 37.5% (fair +166). Your call.</t>
+          <t>Model 22.5% (fair +344). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -9923,13 +9923,13 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.4508715596330276</v>
+        <v>0.4476576576576577</v>
       </c>
       <c r="G5" s="14" t="n">
+        <v>123</v>
+      </c>
+      <c r="H5" s="15" t="n">
         <v>122</v>
-      </c>
-      <c r="H5" s="15" t="n">
-        <v>118</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -9953,7 +9953,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 45.1% (fair +122). Your call.</t>
+          <t>Model 44.8% (fair +123). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -9989,13 +9989,13 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.5491636363636363</v>
+        <v>0.5523522522522523</v>
       </c>
       <c r="G6" s="14" t="n">
+        <v>-123</v>
+      </c>
+      <c r="H6" s="15" t="n">
         <v>-122</v>
-      </c>
-      <c r="H6" s="15" t="n">
-        <v>-120</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -10019,7 +10019,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 54.9% (fair -122). Your call.</t>
+          <t>Model 55.2% (fair -123). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -10523,7 +10523,7 @@
         <v>143</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -10847,13 +10847,13 @@
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.5031804878048781</v>
+        <v>0.4846</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>-101</v>
+        <v>106</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>-105</v>
+        <v>101</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -10877,7 +10877,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 50.3% (fair -101). Your call.</t>
+          <t>Model 48.5% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -10913,10 +10913,10 @@
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.4968075117370893</v>
+        <v>0.5154000000000001</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>101</v>
+        <v>-106</v>
       </c>
       <c r="H20" s="15" t="n">
         <v>113</v>
@@ -10943,7 +10943,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 49.7% (fair +101). Your call.</t>
+          <t>Model 51.5% (fair -106). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -10979,10 +10979,10 @@
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.4312556053811659</v>
+        <v>0.4321076233183856</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H21" s="15" t="n">
         <v>123</v>
@@ -11009,7 +11009,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 43.1% (fair +132). Your call.</t>
+          <t>Model 43.2% (fair +131). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.5687585903083701</v>
+        <v>0.5678888888888889</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-132</v>
+        <v>-131</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>-127</v>
+        <v>-125</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -11075,7 +11075,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 56.9% (fair -132). Your call.</t>
+          <t>Model 56.8% (fair -131). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -11111,13 +11111,13 @@
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.4492384615384615</v>
+        <v>0.4485380952380952</v>
       </c>
       <c r="G23" s="14" t="n">
         <v>123</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>-108</v>
+        <v>-110</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -11177,13 +11177,13 @@
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.5507582938388624</v>
+        <v>0.5514423076923077</v>
       </c>
       <c r="G24" s="14" t="n">
         <v>-123</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -11243,13 +11243,13 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.6534</v>
+        <v>0.5875902439024391</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>-189</v>
+        <v>-142</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>102</v>
+        <v>-105</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -11273,7 +11273,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 65.3% (fair -189). Your call.</t>
+          <t>Model 58.8% (fair -142). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -11309,10 +11309,10 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.3466</v>
+        <v>0.4123943661971831</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>189</v>
+        <v>142</v>
       </c>
       <c r="H26" s="15" t="n">
         <v>113</v>
@@ -11339,7 +11339,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 34.7% (fair +189). Your call.</t>
+          <t>Model 41.2% (fair +142). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -11375,13 +11375,13 @@
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.6929203125</v>
+        <v>0.6956106870229007</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>-226</v>
+        <v>-229</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>-156</v>
+        <v>-162</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -11405,7 +11405,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 69.3% (fair -226). Your call.</t>
+          <t>Model 69.6% (fair -229). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -11441,13 +11441,13 @@
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.3070866141732284</v>
+        <v>0.3044140625</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -11471,7 +11471,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 30.7% (fair +226). Your call.</t>
+          <t>Model 30.4% (fair +228). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -11507,13 +11507,13 @@
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.4710132158590308</v>
+        <v>0.4754260089686099</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -11537,7 +11537,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 47.1% (fair +112). Your call.</t>
+          <t>Model 47.5% (fair +110). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -11573,13 +11573,13 @@
         </is>
       </c>
       <c r="F30" s="13" t="n">
-        <v>0.5289801762114538</v>
+        <v>0.5246</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>-112</v>
+        <v>-110</v>
       </c>
       <c r="H30" s="15" t="n">
-        <v>-127</v>
+        <v>-122</v>
       </c>
       <c r="I30" s="13">
         <f>IF($H$30="","",IF($H$30&lt;0,-$H$30/(-$H$30+100),100/($H$30+100)))</f>
@@ -11603,7 +11603,7 @@
       </c>
       <c r="N30" s="19" t="inlineStr">
         <is>
-          <t>Model 52.9% (fair -112). Your call.</t>
+          <t>Model 52.5% (fair -110). Your call.</t>
         </is>
       </c>
       <c r="O30" s="15" t="n"/>
@@ -11639,13 +11639,13 @@
         </is>
       </c>
       <c r="F31" s="13" t="n">
-        <v>0.4968549019607843</v>
+        <v>0.4962773399014778</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H31" s="15" t="n">
-        <v>-104</v>
+        <v>-103</v>
       </c>
       <c r="I31" s="13">
         <f>IF($H$31="","",IF($H$31&lt;0,-$H$31/(-$H$31+100),100/($H$31+100)))</f>
@@ -11669,7 +11669,7 @@
       </c>
       <c r="N31" s="19" t="inlineStr">
         <is>
-          <t>Model 49.7% (fair +101). Your call.</t>
+          <t>Model 49.6% (fair +102). Your call.</t>
         </is>
       </c>
       <c r="O31" s="15" t="n"/>
@@ -11705,7 +11705,7 @@
         </is>
       </c>
       <c r="F32" s="13" t="n">
-        <v>0.5031188118811881</v>
+        <v>0.5037128712871287</v>
       </c>
       <c r="G32" s="14" t="n">
         <v>-101</v>
@@ -11735,7 +11735,7 @@
       </c>
       <c r="N32" s="19" t="inlineStr">
         <is>
-          <t>Model 50.3% (fair -101). Your call.</t>
+          <t>Model 50.4% (fair -101). Your call.</t>
         </is>
       </c>
       <c r="O32" s="15" t="n"/>
@@ -11771,13 +11771,13 @@
         </is>
       </c>
       <c r="F33" s="13" t="n">
-        <v>0.3425855513307985</v>
+        <v>0.3441923076923077</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H33" s="15" t="n">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="I33" s="13">
         <f>IF($H$33="","",IF($H$33&lt;0,-$H$33/(-$H$33+100),100/($H$33+100)))</f>
@@ -11801,7 +11801,7 @@
       </c>
       <c r="N33" s="19" t="inlineStr">
         <is>
-          <t>Model 34.3% (fair +192). Your call.</t>
+          <t>Model 34.4% (fair +191). Your call.</t>
         </is>
       </c>
       <c r="O33" s="15" t="n"/>
@@ -11837,13 +11837,13 @@
         </is>
       </c>
       <c r="F34" s="13" t="n">
-        <v>0.6574295880149813</v>
+        <v>0.6558248120300751</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>-192</v>
+        <v>-191</v>
       </c>
       <c r="H34" s="15" t="n">
-        <v>-167</v>
+        <v>-166</v>
       </c>
       <c r="I34" s="13">
         <f>IF($H$34="","",IF($H$34&lt;0,-$H$34/(-$H$34+100),100/($H$34+100)))</f>
@@ -11867,7 +11867,7 @@
       </c>
       <c r="N34" s="19" t="inlineStr">
         <is>
-          <t>Model 65.7% (fair -192). Your call.</t>
+          <t>Model 65.6% (fair -191). Your call.</t>
         </is>
       </c>
       <c r="O34" s="15" t="n"/>
@@ -12107,7 +12107,7 @@
         <v>196</v>
       </c>
       <c r="H38" s="15" t="n">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="I38" s="13">
         <f>IF($H$38="","",IF($H$38&lt;0,-$H$38/(-$H$38+100),100/($H$38+100)))</f>
@@ -12299,13 +12299,13 @@
         </is>
       </c>
       <c r="F41" s="13" t="n">
-        <v>0.4629583333333334</v>
+        <v>0.4639915966386555</v>
       </c>
       <c r="G41" s="14" t="n">
         <v>116</v>
       </c>
       <c r="H41" s="15" t="n">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I41" s="13">
         <f>IF($H$41="","",IF($H$41&lt;0,-$H$41/(-$H$41+100),100/($H$41+100)))</f>
@@ -12329,7 +12329,7 @@
       </c>
       <c r="N41" s="19" t="inlineStr">
         <is>
-          <t>Model 46.3% (fair +116). Your call.</t>
+          <t>Model 46.4% (fair +116). Your call.</t>
         </is>
       </c>
       <c r="O41" s="15" t="n"/>
@@ -12365,7 +12365,7 @@
         </is>
       </c>
       <c r="F42" s="13" t="n">
-        <v>0.5370286307053941</v>
+        <v>0.5360340248962655</v>
       </c>
       <c r="G42" s="14" t="n">
         <v>-116</v>
@@ -12395,7 +12395,7 @@
       </c>
       <c r="N42" s="19" t="inlineStr">
         <is>
-          <t>Model 53.7% (fair -116). Your call.</t>
+          <t>Model 53.6% (fair -116). Your call.</t>
         </is>
       </c>
       <c r="O42" s="15" t="n"/>
@@ -12503,7 +12503,7 @@
         <v>101</v>
       </c>
       <c r="H44" s="15" t="n">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="I44" s="13">
         <f>IF($H$44="","",IF($H$44&lt;0,-$H$44/(-$H$44+100),100/($H$44+100)))</f>
@@ -12563,13 +12563,13 @@
         </is>
       </c>
       <c r="F45" s="13" t="n">
-        <v>0.3543032786885246</v>
+        <v>0.3525101214574899</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="H45" s="15" t="n">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="I45" s="13">
         <f>IF($H$45="","",IF($H$45&lt;0,-$H$45/(-$H$45+100),100/($H$45+100)))</f>
@@ -12593,7 +12593,7 @@
       </c>
       <c r="N45" s="19" t="inlineStr">
         <is>
-          <t>Model 35.4% (fair +182). Your call.</t>
+          <t>Model 35.3% (fair +184). Your call.</t>
         </is>
       </c>
       <c r="O45" s="15" t="n"/>
@@ -12629,13 +12629,13 @@
         </is>
       </c>
       <c r="F46" s="13" t="n">
-        <v>0.6456692307692308</v>
+        <v>0.6475</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>-182</v>
+        <v>-184</v>
       </c>
       <c r="H46" s="15" t="n">
-        <v>-147</v>
+        <v>-148</v>
       </c>
       <c r="I46" s="13">
         <f>IF($H$46="","",IF($H$46&lt;0,-$H$46/(-$H$46+100),100/($H$46+100)))</f>
@@ -12659,7 +12659,7 @@
       </c>
       <c r="N46" s="19" t="inlineStr">
         <is>
-          <t>Model 64.6% (fair -182). Your call.</t>
+          <t>Model 64.8% (fair -184). Your call.</t>
         </is>
       </c>
       <c r="O46" s="15" t="n"/>
@@ -12695,10 +12695,10 @@
         </is>
       </c>
       <c r="F47" s="13" t="n">
-        <v>0.4385308056872037</v>
+        <v>0.4395734597156397</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H47" s="15" t="n">
         <v>111</v>
@@ -12725,7 +12725,7 @@
       </c>
       <c r="N47" s="19" t="inlineStr">
         <is>
-          <t>Model 43.9% (fair +128). Your call.</t>
+          <t>Model 44.0% (fair +127). Your call.</t>
         </is>
       </c>
       <c r="O47" s="15" t="n"/>
@@ -12761,13 +12761,13 @@
         </is>
       </c>
       <c r="F48" s="13" t="n">
-        <v>0.5614985915492957</v>
+        <v>0.5604184834123221</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>-128</v>
+        <v>-127</v>
       </c>
       <c r="H48" s="15" t="n">
-        <v>-113</v>
+        <v>-111</v>
       </c>
       <c r="I48" s="13">
         <f>IF($H$48="","",IF($H$48&lt;0,-$H$48/(-$H$48+100),100/($H$48+100)))</f>
@@ -12791,7 +12791,7 @@
       </c>
       <c r="N48" s="19" t="inlineStr">
         <is>
-          <t>Model 56.1% (fair -128). Your call.</t>
+          <t>Model 56.0% (fair -127). Your call.</t>
         </is>
       </c>
       <c r="O48" s="15" t="n"/>
@@ -12833,7 +12833,7 @@
         <v>-146</v>
       </c>
       <c r="H49" s="15" t="n">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="I49" s="13">
         <f>IF($H$49="","",IF($H$49&lt;0,-$H$49/(-$H$49+100),100/($H$49+100)))</f>
@@ -13091,13 +13091,13 @@
         </is>
       </c>
       <c r="F53" s="13" t="n">
-        <v>0.6167660944206009</v>
+        <v>0.6175531914893617</v>
       </c>
       <c r="G53" s="14" t="n">
         <v>-161</v>
       </c>
       <c r="H53" s="15" t="n">
-        <v>-133</v>
+        <v>-135</v>
       </c>
       <c r="I53" s="13">
         <f>IF($H$53="","",IF($H$53&lt;0,-$H$53/(-$H$53+100),100/($H$53+100)))</f>
@@ -13121,7 +13121,7 @@
       </c>
       <c r="N53" s="19" t="inlineStr">
         <is>
-          <t>Model 61.7% (fair -161). Your call.</t>
+          <t>Model 61.8% (fair -161). Your call.</t>
         </is>
       </c>
       <c r="O53" s="15" t="n"/>
@@ -13157,7 +13157,7 @@
         </is>
       </c>
       <c r="F54" s="13" t="n">
-        <v>0.3832618025751073</v>
+        <v>0.3824463519313305</v>
       </c>
       <c r="G54" s="14" t="n">
         <v>161</v>
@@ -13187,7 +13187,7 @@
       </c>
       <c r="N54" s="19" t="inlineStr">
         <is>
-          <t>Model 38.3% (fair +161). Your call.</t>
+          <t>Model 38.2% (fair +161). Your call.</t>
         </is>
       </c>
       <c r="O54" s="15" t="n"/>
@@ -13229,7 +13229,7 @@
         <v>129</v>
       </c>
       <c r="H55" s="15" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I55" s="13">
         <f>IF($H$55="","",IF($H$55&lt;0,-$H$55/(-$H$55+100),100/($H$55+100)))</f>
@@ -13615,13 +13615,13 @@
         </is>
       </c>
       <c r="F61" s="13" t="n">
-        <v>0.3612109375</v>
+        <v>0.3656</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H61" s="15" t="n">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="I61" s="13">
         <f>IF($H$61="","",IF($H$61&lt;0,-$H$61/(-$H$61+100),100/($H$61+100)))</f>
@@ -13645,7 +13645,7 @@
       </c>
       <c r="N61" s="19" t="inlineStr">
         <is>
-          <t>Model 36.1% (fair +177). Your call.</t>
+          <t>Model 36.6% (fair +174). Your call.</t>
         </is>
       </c>
       <c r="O61" s="15" t="n"/>
@@ -13681,13 +13681,13 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>0.6387823529411765</v>
+        <v>0.6343800000000001</v>
       </c>
       <c r="G62" s="14" t="n">
-        <v>-177</v>
+        <v>-174</v>
       </c>
       <c r="H62" s="15" t="n">
-        <v>-155</v>
+        <v>-150</v>
       </c>
       <c r="I62" s="13">
         <f>IF($H$62="","",IF($H$62&lt;0,-$H$62/(-$H$62+100),100/($H$62+100)))</f>
@@ -13711,7 +13711,7 @@
       </c>
       <c r="N62" s="19" t="inlineStr">
         <is>
-          <t>Model 63.9% (fair -177). Your call.</t>
+          <t>Model 63.4% (fair -174). Your call.</t>
         </is>
       </c>
       <c r="O62" s="15" t="n"/>
@@ -13753,7 +13753,7 @@
         <v>-167</v>
       </c>
       <c r="H63" s="15" t="n">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="I63" s="13">
         <f>IF($H$63="","",IF($H$63&lt;0,-$H$63/(-$H$63+100),100/($H$63+100)))</f>
@@ -13819,7 +13819,7 @@
         <v>167</v>
       </c>
       <c r="H64" s="15" t="n">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="I64" s="13">
         <f>IF($H$64="","",IF($H$64&lt;0,-$H$64/(-$H$64+100),100/($H$64+100)))</f>
@@ -13879,13 +13879,13 @@
         </is>
       </c>
       <c r="F65" s="13" t="n">
-        <v>0.4590434782608696</v>
+        <v>0.4558898305084745</v>
       </c>
       <c r="G65" s="14" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H65" s="15" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="I65" s="13">
         <f>IF($H$65="","",IF($H$65&lt;0,-$H$65/(-$H$65+100),100/($H$65+100)))</f>
@@ -13909,7 +13909,7 @@
       </c>
       <c r="N65" s="19" t="inlineStr">
         <is>
-          <t>Model 45.9% (fair +118). Your call.</t>
+          <t>Model 45.6% (fair +119). Your call.</t>
         </is>
       </c>
       <c r="O65" s="15" t="n"/>
@@ -13945,10 +13945,10 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>0.5409618025751073</v>
+        <v>0.5441012875536481</v>
       </c>
       <c r="G66" s="14" t="n">
-        <v>-118</v>
+        <v>-119</v>
       </c>
       <c r="H66" s="15" t="n">
         <v>-133</v>
@@ -13975,7 +13975,7 @@
       </c>
       <c r="N66" s="19" t="inlineStr">
         <is>
-          <t>Model 54.1% (fair -118). Your call.</t>
+          <t>Model 54.4% (fair -119). Your call.</t>
         </is>
       </c>
       <c r="O66" s="15" t="n"/>
@@ -15183,10 +15183,10 @@
         </is>
       </c>
       <c r="F85" s="13" t="n">
-        <v>0.4052049180327869</v>
+        <v>0.4032377049180328</v>
       </c>
       <c r="G85" s="14" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H85" s="15" t="n">
         <v>144</v>
@@ -15213,7 +15213,7 @@
       </c>
       <c r="N85" s="19" t="inlineStr">
         <is>
-          <t>Model 40.5% (fair +147). Your call.</t>
+          <t>Model 40.3% (fair +148). Your call.</t>
         </is>
       </c>
       <c r="O85" s="15" t="n"/>
@@ -15249,13 +15249,13 @@
         </is>
       </c>
       <c r="F86" s="13" t="n">
-        <v>0.5947672131147541</v>
+        <v>0.5967600000000001</v>
       </c>
       <c r="G86" s="14" t="n">
-        <v>-147</v>
+        <v>-148</v>
       </c>
       <c r="H86" s="15" t="n">
-        <v>-144</v>
+        <v>-150</v>
       </c>
       <c r="I86" s="13">
         <f>IF($H$86="","",IF($H$86&lt;0,-$H$86/(-$H$86+100),100/($H$86+100)))</f>
@@ -15279,7 +15279,7 @@
       </c>
       <c r="N86" s="19" t="inlineStr">
         <is>
-          <t>Model 59.5% (fair -147). Your call.</t>
+          <t>Model 59.7% (fair -148). Your call.</t>
         </is>
       </c>
       <c r="O86" s="15" t="n"/>
@@ -15315,10 +15315,10 @@
         </is>
       </c>
       <c r="F87" s="13" t="n">
-        <v>0.5818188940092165</v>
+        <v>0.6188</v>
       </c>
       <c r="G87" s="14" t="n">
-        <v>-139</v>
+        <v>-162</v>
       </c>
       <c r="H87" s="15" t="n">
         <v>-117</v>
@@ -15345,7 +15345,7 @@
       </c>
       <c r="N87" s="19" t="inlineStr">
         <is>
-          <t>Model 58.2% (fair -139). Your call.</t>
+          <t>Model 61.9% (fair -162). Your call.</t>
         </is>
       </c>
       <c r="O87" s="15" t="n"/>
@@ -15381,13 +15381,13 @@
         </is>
       </c>
       <c r="F88" s="13" t="n">
-        <v>0.4181981981981983</v>
+        <v>0.3812</v>
       </c>
       <c r="G88" s="14" t="n">
-        <v>139</v>
+        <v>162</v>
       </c>
       <c r="H88" s="15" t="n">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="I88" s="13">
         <f>IF($H$88="","",IF($H$88&lt;0,-$H$88/(-$H$88+100),100/($H$88+100)))</f>
@@ -15411,7 +15411,7 @@
       </c>
       <c r="N88" s="19" t="inlineStr">
         <is>
-          <t>Model 41.8% (fair +139). Your call.</t>
+          <t>Model 38.1% (fair +162). Your call.</t>
         </is>
       </c>
       <c r="O88" s="15" t="n"/>
@@ -15579,13 +15579,13 @@
         </is>
       </c>
       <c r="F91" s="13" t="n">
-        <v>0.4086343612334802</v>
+        <v>0.4113963963963965</v>
       </c>
       <c r="G91" s="14" t="n">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="H91" s="15" t="n">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="I91" s="13">
         <f>IF($H$91="","",IF($H$91&lt;0,-$H$91/(-$H$91+100),100/($H$91+100)))</f>
@@ -15609,7 +15609,7 @@
       </c>
       <c r="N91" s="19" t="inlineStr">
         <is>
-          <t>Model 40.9% (fair +145). Your call.</t>
+          <t>Model 41.1% (fair +143). Your call.</t>
         </is>
       </c>
       <c r="O91" s="15" t="n"/>
@@ -15645,10 +15645,10 @@
         </is>
       </c>
       <c r="F92" s="13" t="n">
-        <v>0.5913702702702703</v>
+        <v>0.5886225225225225</v>
       </c>
       <c r="G92" s="14" t="n">
-        <v>-145</v>
+        <v>-143</v>
       </c>
       <c r="H92" s="15" t="n">
         <v>-122</v>
@@ -15675,7 +15675,7 @@
       </c>
       <c r="N92" s="19" t="inlineStr">
         <is>
-          <t>Model 59.1% (fair -145). Your call.</t>
+          <t>Model 58.9% (fair -143). Your call.</t>
         </is>
       </c>
       <c r="O92" s="15" t="n"/>
@@ -15711,13 +15711,13 @@
         </is>
       </c>
       <c r="F93" s="13" t="n">
-        <v>0.3796</v>
+        <v>0.3825409836065574</v>
       </c>
       <c r="G93" s="14" t="n">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="H93" s="15" t="n">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="I93" s="13">
         <f>IF($H$93="","",IF($H$93&lt;0,-$H$93/(-$H$93+100),100/($H$93+100)))</f>
@@ -15741,7 +15741,7 @@
       </c>
       <c r="N93" s="19" t="inlineStr">
         <is>
-          <t>Model 38.0% (fair +163). Your call.</t>
+          <t>Model 38.3% (fair +161). Your call.</t>
         </is>
       </c>
       <c r="O93" s="15" t="n"/>
@@ -15777,10 +15777,10 @@
         </is>
       </c>
       <c r="F94" s="13" t="n">
-        <v>0.6204000000000001</v>
+        <v>0.61746</v>
       </c>
       <c r="G94" s="14" t="n">
-        <v>-163</v>
+        <v>-161</v>
       </c>
       <c r="H94" s="15" t="n">
         <v>-150</v>
@@ -15807,7 +15807,7 @@
       </c>
       <c r="N94" s="19" t="inlineStr">
         <is>
-          <t>Model 62.0% (fair -163). Your call.</t>
+          <t>Model 61.7% (fair -161). Your call.</t>
         </is>
       </c>
       <c r="O94" s="15" t="n"/>
@@ -16626,13 +16626,13 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.3555102040816326</v>
+        <v>0.3501013513513513</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -16656,7 +16656,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 35.6% (fair +181). Your call.</t>
+          <t>Model 35.0% (fair +186). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -16692,13 +16692,13 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.6444642857142857</v>
+        <v>0.6498679867986799</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>-181</v>
+        <v>-186</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>-180</v>
+        <v>-203</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -16722,7 +16722,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 64.4% (fair -181). Your call.</t>
+          <t>Model 65.0% (fair -186). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.6547000000000001</v>
+        <v>0.6546634615384614</v>
       </c>
       <c r="G7" s="14" t="n">
         <v>-190</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -16830,7 +16830,7 @@
         <v>190</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -16896,7 +16896,7 @@
         <v>129</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -16962,7 +16962,7 @@
         <v>-129</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -17022,13 +17022,13 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.2905428571428571</v>
+        <v>0.291025641025641</v>
       </c>
       <c r="G11" s="14" t="n">
         <v>244</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -17088,13 +17088,13 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.7094563421828909</v>
+        <v>0.7090057057057058</v>
       </c>
       <c r="G12" s="14" t="n">
         <v>-244</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>-239</v>
+        <v>-233</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -17282,17 +17282,17 @@
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Indiana Fever -6.5</t>
+          <t>Indiana Fever -7.5</t>
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.50645</v>
+        <v>0.4757</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>-103</v>
+        <v>110</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -17316,7 +17316,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 50.6% (fair -103). Your call.</t>
+          <t>Model 47.6% (fair +110). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -17348,17 +17348,17 @@
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Sparks +6.5</t>
+          <t>Los Angeles Sparks +7.5</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.4935643564356436</v>
+        <v>0.5243</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>103</v>
+        <v>-110</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -17382,7 +17382,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 49.4% (fair +103). Your call.</t>
+          <t>Model 52.4% (fair -110). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -17418,13 +17418,13 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.7759285714285714</v>
+        <v>0.7748126436781609</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>-346</v>
+        <v>-344</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>-355</v>
+        <v>-335</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -17448,7 +17448,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 77.6% (fair -346). Your call.</t>
+          <t>Model 77.5% (fair -344). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -17484,10 +17484,10 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.2240879120879121</v>
+        <v>0.2252087912087912</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="H18" s="15" t="n">
         <v>355</v>
@@ -17514,7 +17514,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 22.4% (fair +346). Your call.</t>
+          <t>Model 22.5% (fair +344). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -17550,13 +17550,13 @@
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.30575</v>
+        <v>0.3057211538461538</v>
       </c>
       <c r="G19" s="14" t="n">
         <v>227</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -17622,7 +17622,7 @@
         <v>-227</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>

--- a/data/output/workbook/2026-06-27.xlsx
+++ b/data/output/workbook/2026-06-27.xlsx
@@ -551,7 +551,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="9477375"/>
+    <ext cx="10125075" cy="9896475"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -581,7 +581,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="9401175"/>
+    <ext cx="10125075" cy="9810750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -954,7 +954,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-06-27 08:12</t>
+          <t>2026-06-27 10:31</t>
         </is>
       </c>
     </row>
@@ -4530,7 +4530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q75"/>
+  <dimension ref="A1:Q77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4547,823 +4547,823 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="29" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="29" t="inlineStr">
         <is>
           <t>Arizona Diamondbacks offense vs Tampa Bay Rays defense</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="30" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B62" s="30" t="inlineStr">
+      <c r="B64" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C62" s="30" t="inlineStr">
+      <c r="C64" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D62" s="30" t="inlineStr">
+      <c r="D64" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E62" s="30" t="inlineStr">
+      <c r="E64" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F62" s="30" t="inlineStr">
+      <c r="F64" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G62" s="30" t="inlineStr">
+      <c r="G64" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H62" s="30" t="inlineStr">
+      <c r="H64" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I62" s="30" t="inlineStr">
+      <c r="I64" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J62" s="30" t="inlineStr">
+      <c r="J64" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K62" s="30" t="inlineStr">
+      <c r="K64" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L62" s="30" t="inlineStr">
+      <c r="L64" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M62" s="30" t="inlineStr">
+      <c r="M64" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N62" s="30" t="inlineStr">
+      <c r="N64" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O62" s="30" t="inlineStr">
+      <c r="O64" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P62" s="30" t="inlineStr">
+      <c r="P64" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q62" s="30" t="inlineStr">
+      <c r="Q64" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B63" s="32" t="n">
-        <v>4.976</v>
-      </c>
-      <c r="C63" s="32" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="D63" s="32" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="E63" s="32" t="n">
-        <v>4.467</v>
-      </c>
-      <c r="F63" s="32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="G63" s="32" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="H63" s="36" t="inlineStr">
-        <is>
-          <t>25th</t>
-        </is>
-      </c>
-      <c r="I63" s="32" t="inlineStr"/>
-      <c r="J63" s="36" t="inlineStr">
-        <is>
-          <t>26th</t>
-        </is>
-      </c>
-      <c r="K63" s="32" t="n">
-        <v>6</v>
-      </c>
-      <c r="L63" s="32" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="M63" s="32" t="n">
-        <v>4.867</v>
-      </c>
-      <c r="N63" s="32" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="O63" s="32" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="P63" s="32" t="n">
-        <v>4.234</v>
-      </c>
-      <c r="Q63" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="31" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B64" s="32" t="n">
-        <v>8.688000000000001</v>
-      </c>
-      <c r="C64" s="32" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="D64" s="32" t="n">
-        <v>8.85</v>
-      </c>
-      <c r="E64" s="32" t="n">
-        <v>9</v>
-      </c>
-      <c r="F64" s="32" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="G64" s="32" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="H64" s="34" t="inlineStr">
-        <is>
-          <t>12th</t>
-        </is>
-      </c>
-      <c r="I64" s="32" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J64" s="34" t="inlineStr">
-        <is>
-          <t>17th</t>
-        </is>
-      </c>
-      <c r="K64" s="32" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="L64" s="32" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="M64" s="32" t="n">
-        <v>8.067</v>
-      </c>
-      <c r="N64" s="32" t="n">
-        <v>8.050000000000001</v>
-      </c>
-      <c r="O64" s="32" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="P64" s="32" t="n">
-        <v>7.868</v>
-      </c>
-      <c r="Q64" s="35" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B65" s="32" t="n">
-        <v>1.329</v>
+        <v>4.976</v>
       </c>
       <c r="C65" s="32" t="n">
-        <v>1.033</v>
+        <v>4.7</v>
       </c>
       <c r="D65" s="32" t="n">
-        <v>0.85</v>
+        <v>4.45</v>
       </c>
       <c r="E65" s="32" t="n">
-        <v>1</v>
+        <v>4.467</v>
       </c>
       <c r="F65" s="32" t="n">
-        <v>0.9</v>
+        <v>3.4</v>
       </c>
       <c r="G65" s="32" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="H65" s="36" t="inlineStr">
         <is>
-          <t>22nd</t>
+          <t>25th</t>
         </is>
       </c>
       <c r="I65" s="32" t="inlineStr"/>
-      <c r="J65" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K65" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L65" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M65" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N65" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O65" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P65" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J65" s="36" t="inlineStr">
+        <is>
+          <t>26th</t>
+        </is>
+      </c>
+      <c r="K65" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="L65" s="32" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="M65" s="32" t="n">
+        <v>4.867</v>
+      </c>
+      <c r="N65" s="32" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O65" s="32" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="P65" s="32" t="n">
+        <v>4.234</v>
       </c>
       <c r="Q65" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B66" s="32" t="n">
-        <v>8.265000000000001</v>
+        <v>8.688000000000001</v>
       </c>
       <c r="C66" s="32" t="n">
-        <v>8.467000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D66" s="32" t="n">
-        <v>8.35</v>
+        <v>8.85</v>
       </c>
       <c r="E66" s="32" t="n">
+        <v>9</v>
+      </c>
+      <c r="F66" s="32" t="n">
         <v>8.4</v>
       </c>
-      <c r="F66" s="32" t="n">
-        <v>8.6</v>
-      </c>
       <c r="G66" s="32" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="H66" s="36" t="inlineStr">
-        <is>
-          <t>23rd</t>
-        </is>
-      </c>
-      <c r="I66" s="32" t="inlineStr"/>
+        <v>7.6</v>
+      </c>
+      <c r="H66" s="34" t="inlineStr">
+        <is>
+          <t>12th</t>
+        </is>
+      </c>
+      <c r="I66" s="32" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
       <c r="J66" s="34" t="inlineStr">
         <is>
-          <t>15th</t>
+          <t>17th</t>
         </is>
       </c>
       <c r="K66" s="32" t="n">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L66" s="32" t="n">
-        <v>8.699999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="M66" s="32" t="n">
-        <v>8.333</v>
+        <v>8.067</v>
       </c>
       <c r="N66" s="32" t="n">
-        <v>8.800000000000001</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="O66" s="32" t="n">
-        <v>9.5</v>
+        <v>7.8</v>
       </c>
       <c r="P66" s="32" t="n">
-        <v>8.737</v>
+        <v>7.868</v>
       </c>
       <c r="Q66" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="31" t="inlineStr">
         <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B67" s="32" t="n">
+        <v>1.329</v>
+      </c>
+      <c r="C67" s="32" t="n">
+        <v>1.033</v>
+      </c>
+      <c r="D67" s="32" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="E67" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="F67" s="32" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G67" s="32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H67" s="36" t="inlineStr">
+        <is>
+          <t>22nd</t>
+        </is>
+      </c>
+      <c r="I67" s="32" t="inlineStr"/>
+      <c r="J67" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K67" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L67" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M67" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N67" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O67" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P67" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q67" s="35" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="31" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B68" s="32" t="n">
+        <v>8.265000000000001</v>
+      </c>
+      <c r="C68" s="32" t="n">
+        <v>8.467000000000001</v>
+      </c>
+      <c r="D68" s="32" t="n">
+        <v>8.35</v>
+      </c>
+      <c r="E68" s="32" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="F68" s="32" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="G68" s="32" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="H68" s="36" t="inlineStr">
+        <is>
+          <t>23rd</t>
+        </is>
+      </c>
+      <c r="I68" s="32" t="inlineStr"/>
+      <c r="J68" s="34" t="inlineStr">
+        <is>
+          <t>15th</t>
+        </is>
+      </c>
+      <c r="K68" s="32" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="L68" s="32" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M68" s="32" t="n">
+        <v>8.333</v>
+      </c>
+      <c r="N68" s="32" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="O68" s="32" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="P68" s="32" t="n">
+        <v>8.737</v>
+      </c>
+      <c r="Q68" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B67" s="32" t="n">
+      <c r="B69" s="32" t="n">
         <v>0.612</v>
       </c>
-      <c r="C67" s="32" t="n">
+      <c r="C69" s="32" t="n">
         <v>0.467</v>
       </c>
-      <c r="D67" s="32" t="n">
+      <c r="D69" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="E67" s="32" t="n">
+      <c r="E69" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="F67" s="32" t="n">
+      <c r="F69" s="32" t="n">
         <v>0.7</v>
       </c>
-      <c r="G67" s="32" t="n">
+      <c r="G69" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="H67" s="33" t="inlineStr">
+      <c r="H69" s="33" t="inlineStr">
         <is>
           <t>10th</t>
         </is>
       </c>
-      <c r="I67" s="32" t="inlineStr">
+      <c r="I69" s="32" t="inlineStr">
         <is>
           <t>★★★</t>
         </is>
       </c>
-      <c r="J67" s="36" t="inlineStr">
+      <c r="J69" s="36" t="inlineStr">
         <is>
           <t>25th</t>
         </is>
       </c>
-      <c r="K67" s="32" t="n">
+      <c r="K69" s="32" t="n">
         <v>1.2</v>
       </c>
-      <c r="L67" s="32" t="n">
+      <c r="L69" s="32" t="n">
         <v>0.8</v>
       </c>
-      <c r="M67" s="32" t="n">
+      <c r="M69" s="32" t="n">
         <v>0.667</v>
       </c>
-      <c r="N67" s="32" t="n">
+      <c r="N69" s="32" t="n">
         <v>0.65</v>
       </c>
-      <c r="O67" s="32" t="n">
+      <c r="O69" s="32" t="n">
         <v>0.467</v>
       </c>
-      <c r="P67" s="32" t="n">
+      <c r="P69" s="32" t="n">
         <v>0.473</v>
       </c>
-      <c r="Q67" s="35" t="inlineStr">
+      <c r="Q69" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="29" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="29" t="inlineStr">
         <is>
           <t>Tampa Bay Rays offense vs Arizona Diamondbacks defense</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="30" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B70" s="30" t="inlineStr">
+      <c r="B72" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C70" s="30" t="inlineStr">
+      <c r="C72" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D70" s="30" t="inlineStr">
+      <c r="D72" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E70" s="30" t="inlineStr">
+      <c r="E72" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F70" s="30" t="inlineStr">
+      <c r="F72" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G70" s="30" t="inlineStr">
+      <c r="G72" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H70" s="30" t="inlineStr">
+      <c r="H72" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I70" s="30" t="inlineStr">
+      <c r="I72" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J70" s="30" t="inlineStr">
+      <c r="J72" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K70" s="30" t="inlineStr">
+      <c r="K72" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L70" s="30" t="inlineStr">
+      <c r="L72" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M70" s="30" t="inlineStr">
+      <c r="M72" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N70" s="30" t="inlineStr">
+      <c r="N72" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O70" s="30" t="inlineStr">
+      <c r="O72" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P70" s="30" t="inlineStr">
+      <c r="P72" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q70" s="30" t="inlineStr">
+      <c r="Q72" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B71" s="32" t="n">
-        <v>4.437</v>
-      </c>
-      <c r="C71" s="32" t="n">
-        <v>4.033</v>
-      </c>
-      <c r="D71" s="32" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="E71" s="32" t="n">
-        <v>3.667</v>
-      </c>
-      <c r="F71" s="32" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="G71" s="32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="H71" s="34" t="inlineStr">
-        <is>
-          <t>14th</t>
-        </is>
-      </c>
-      <c r="I71" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J71" s="36" t="inlineStr">
-        <is>
-          <t>30th</t>
-        </is>
-      </c>
-      <c r="K71" s="32" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="L71" s="32" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="M71" s="32" t="n">
-        <v>5.333</v>
-      </c>
-      <c r="N71" s="32" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="O71" s="32" t="n">
-        <v>4.767</v>
-      </c>
-      <c r="P71" s="32" t="n">
-        <v>4.847</v>
-      </c>
-      <c r="Q71" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="31" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B72" s="32" t="n">
-        <v>8.521000000000001</v>
-      </c>
-      <c r="C72" s="32" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="D72" s="32" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="E72" s="32" t="n">
-        <v>8.667</v>
-      </c>
-      <c r="F72" s="32" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="G72" s="32" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="H72" s="33" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="I72" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J72" s="36" t="inlineStr">
-        <is>
-          <t>27th</t>
-        </is>
-      </c>
-      <c r="K72" s="32" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="L72" s="32" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="M72" s="32" t="n">
-        <v>9.132999999999999</v>
-      </c>
-      <c r="N72" s="32" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="O72" s="32" t="n">
-        <v>8.567</v>
-      </c>
-      <c r="P72" s="32" t="n">
-        <v>8.840999999999999</v>
-      </c>
-      <c r="Q72" s="35" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B73" s="32" t="n">
-        <v>1.114</v>
+        <v>4.437</v>
       </c>
       <c r="C73" s="32" t="n">
-        <v>1.133</v>
+        <v>4.033</v>
       </c>
       <c r="D73" s="32" t="n">
-        <v>1.15</v>
+        <v>3.55</v>
       </c>
       <c r="E73" s="32" t="n">
-        <v>1</v>
+        <v>3.667</v>
       </c>
       <c r="F73" s="32" t="n">
-        <v>1</v>
+        <v>3.9</v>
       </c>
       <c r="G73" s="32" t="n">
-        <v>1</v>
+        <v>3.6</v>
       </c>
       <c r="H73" s="34" t="inlineStr">
         <is>
-          <t>17th</t>
-        </is>
-      </c>
-      <c r="I73" s="32" t="inlineStr"/>
-      <c r="J73" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>14th</t>
+        </is>
+      </c>
+      <c r="I73" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J73" s="36" t="inlineStr">
+        <is>
+          <t>30th</t>
+        </is>
+      </c>
+      <c r="K73" s="32" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="L73" s="32" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="M73" s="32" t="n">
+        <v>5.333</v>
+      </c>
+      <c r="N73" s="32" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="O73" s="32" t="n">
+        <v>4.767</v>
+      </c>
+      <c r="P73" s="32" t="n">
+        <v>4.847</v>
       </c>
       <c r="Q73" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B74" s="32" t="n">
-        <v>8.611000000000001</v>
+        <v>8.521000000000001</v>
       </c>
       <c r="C74" s="32" t="n">
-        <v>8.967000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="D74" s="32" t="n">
-        <v>9.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E74" s="32" t="n">
-        <v>9.667</v>
+        <v>8.667</v>
       </c>
       <c r="F74" s="32" t="n">
-        <v>9.199999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="G74" s="32" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="H74" s="34" t="inlineStr">
-        <is>
-          <t>18th</t>
-        </is>
-      </c>
-      <c r="I74" s="32" t="inlineStr"/>
-      <c r="J74" s="34" t="inlineStr">
-        <is>
-          <t>16th</t>
+        <v>9.6</v>
+      </c>
+      <c r="H74" s="33" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="I74" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J74" s="36" t="inlineStr">
+        <is>
+          <t>27th</t>
         </is>
       </c>
       <c r="K74" s="32" t="n">
-        <v>9.4</v>
+        <v>10.4</v>
       </c>
       <c r="L74" s="32" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="M74" s="32" t="n">
-        <v>8.333</v>
+        <v>9.132999999999999</v>
       </c>
       <c r="N74" s="32" t="n">
-        <v>7.9</v>
+        <v>8.75</v>
       </c>
       <c r="O74" s="32" t="n">
-        <v>7.8</v>
+        <v>8.567</v>
       </c>
       <c r="P74" s="32" t="n">
-        <v>8.199999999999999</v>
+        <v>8.840999999999999</v>
       </c>
       <c r="Q74" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="31" t="inlineStr">
         <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B75" s="32" t="n">
+        <v>1.114</v>
+      </c>
+      <c r="C75" s="32" t="n">
+        <v>1.133</v>
+      </c>
+      <c r="D75" s="32" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="E75" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="F75" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="H75" s="34" t="inlineStr">
+        <is>
+          <t>17th</t>
+        </is>
+      </c>
+      <c r="I75" s="32" t="inlineStr"/>
+      <c r="J75" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q75" s="35" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="31" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B76" s="32" t="n">
+        <v>8.611000000000001</v>
+      </c>
+      <c r="C76" s="32" t="n">
+        <v>8.967000000000001</v>
+      </c>
+      <c r="D76" s="32" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="E76" s="32" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="F76" s="32" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="G76" s="32" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="H76" s="34" t="inlineStr">
+        <is>
+          <t>18th</t>
+        </is>
+      </c>
+      <c r="I76" s="32" t="inlineStr"/>
+      <c r="J76" s="34" t="inlineStr">
+        <is>
+          <t>16th</t>
+        </is>
+      </c>
+      <c r="K76" s="32" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="L76" s="32" t="n">
+        <v>9</v>
+      </c>
+      <c r="M76" s="32" t="n">
+        <v>8.333</v>
+      </c>
+      <c r="N76" s="32" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="O76" s="32" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="P76" s="32" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Q76" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B75" s="32" t="n">
+      <c r="B77" s="32" t="n">
         <v>0.587</v>
       </c>
-      <c r="C75" s="32" t="n">
+      <c r="C77" s="32" t="n">
         <v>0.867</v>
       </c>
-      <c r="D75" s="32" t="n">
+      <c r="D77" s="32" t="n">
         <v>0.7</v>
       </c>
-      <c r="E75" s="32" t="n">
+      <c r="E77" s="32" t="n">
         <v>0.667</v>
       </c>
-      <c r="F75" s="32" t="n">
+      <c r="F77" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="G75" s="32" t="n">
+      <c r="G77" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="H75" s="34" t="inlineStr">
+      <c r="H77" s="34" t="inlineStr">
         <is>
           <t>16th</t>
         </is>
       </c>
-      <c r="I75" s="32" t="inlineStr">
+      <c r="I77" s="32" t="inlineStr">
         <is>
           <t>★★★</t>
         </is>
       </c>
-      <c r="J75" s="36" t="inlineStr">
+      <c r="J77" s="36" t="inlineStr">
         <is>
           <t>29th</t>
         </is>
       </c>
-      <c r="K75" s="32" t="n">
+      <c r="K77" s="32" t="n">
         <v>1.8</v>
       </c>
-      <c r="L75" s="32" t="n">
+      <c r="L77" s="32" t="n">
         <v>1.1</v>
       </c>
-      <c r="M75" s="32" t="n">
+      <c r="M77" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="N75" s="32" t="n">
+      <c r="N77" s="32" t="n">
         <v>0.9</v>
       </c>
-      <c r="O75" s="32" t="n">
+      <c r="O77" s="32" t="n">
         <v>0.733</v>
       </c>
-      <c r="P75" s="32" t="n">
+      <c r="P77" s="32" t="n">
         <v>0.641</v>
       </c>
-      <c r="Q75" s="35" t="inlineStr">
+      <c r="Q77" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -5382,7 +5382,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q74"/>
+  <dimension ref="A1:Q77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5399,815 +5399,815 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="29" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="29" t="inlineStr">
         <is>
           <t>Washington Nationals offense vs Baltimore Orioles defense</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="30" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B61" s="30" t="inlineStr">
+      <c r="B64" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C61" s="30" t="inlineStr">
+      <c r="C64" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D61" s="30" t="inlineStr">
+      <c r="D64" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E61" s="30" t="inlineStr">
+      <c r="E64" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F61" s="30" t="inlineStr">
+      <c r="F64" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G61" s="30" t="inlineStr">
+      <c r="G64" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H61" s="30" t="inlineStr">
+      <c r="H64" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I61" s="30" t="inlineStr">
+      <c r="I64" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J61" s="30" t="inlineStr">
+      <c r="J64" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K61" s="30" t="inlineStr">
+      <c r="K64" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L61" s="30" t="inlineStr">
+      <c r="L64" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M61" s="30" t="inlineStr">
+      <c r="M64" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N61" s="30" t="inlineStr">
+      <c r="N64" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O61" s="30" t="inlineStr">
+      <c r="O64" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P61" s="30" t="inlineStr">
+      <c r="P64" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q61" s="30" t="inlineStr">
+      <c r="Q64" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B62" s="32" t="n">
-        <v>4.205</v>
-      </c>
-      <c r="C62" s="32" t="n">
-        <v>4.133</v>
-      </c>
-      <c r="D62" s="32" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="E62" s="32" t="n">
-        <v>3.667</v>
-      </c>
-      <c r="F62" s="32" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="G62" s="32" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H62" s="33" t="inlineStr">
-        <is>
-          <t>10th</t>
-        </is>
-      </c>
-      <c r="I62" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J62" s="36" t="inlineStr">
-        <is>
-          <t>23rd</t>
-        </is>
-      </c>
-      <c r="K62" s="32" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="L62" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="M62" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="N62" s="32" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="O62" s="32" t="n">
-        <v>4.667</v>
-      </c>
-      <c r="P62" s="32" t="n">
-        <v>4.886</v>
-      </c>
-      <c r="Q62" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="31" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B63" s="32" t="n">
-        <v>8.054</v>
-      </c>
-      <c r="C63" s="32" t="n">
-        <v>7.833</v>
-      </c>
-      <c r="D63" s="32" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="E63" s="32" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="F63" s="32" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="G63" s="32" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="H63" s="34" t="inlineStr">
-        <is>
-          <t>13th</t>
-        </is>
-      </c>
-      <c r="I63" s="32" t="inlineStr">
-        <is>
-          <t>★★</t>
-        </is>
-      </c>
-      <c r="J63" s="36" t="inlineStr">
-        <is>
-          <t>24th</t>
-        </is>
-      </c>
-      <c r="K63" s="32" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="L63" s="32" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="M63" s="32" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="N63" s="32" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="O63" s="32" t="n">
-        <v>8.567</v>
-      </c>
-      <c r="P63" s="32" t="n">
-        <v>8.837</v>
-      </c>
-      <c r="Q63" s="35" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="31" t="inlineStr">
-        <is>
-          <t>HR/G</t>
-        </is>
-      </c>
-      <c r="B64" s="32" t="n">
-        <v>0.976</v>
-      </c>
-      <c r="C64" s="32" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="D64" s="32" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="E64" s="32" t="n">
-        <v>1.267</v>
-      </c>
-      <c r="F64" s="32" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="G64" s="32" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="H64" s="33" t="inlineStr">
-        <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="I64" s="32" t="inlineStr"/>
-      <c r="J64" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K64" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L64" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M64" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N64" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O64" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P64" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q64" s="35" t="inlineStr">
-        <is>
-          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B65" s="32" t="n">
-        <v>8.372999999999999</v>
+        <v>4.205</v>
       </c>
       <c r="C65" s="32" t="n">
-        <v>9.800000000000001</v>
+        <v>4.133</v>
       </c>
       <c r="D65" s="32" t="n">
-        <v>10</v>
+        <v>4.3</v>
       </c>
       <c r="E65" s="32" t="n">
-        <v>10.733</v>
+        <v>3.667</v>
       </c>
       <c r="F65" s="32" t="n">
-        <v>11</v>
+        <v>4.4</v>
       </c>
       <c r="G65" s="32" t="n">
-        <v>11</v>
-      </c>
-      <c r="H65" s="36" t="inlineStr">
-        <is>
-          <t>25th</t>
-        </is>
-      </c>
-      <c r="I65" s="32" t="inlineStr"/>
+        <v>4.2</v>
+      </c>
+      <c r="H65" s="33" t="inlineStr">
+        <is>
+          <t>10th</t>
+        </is>
+      </c>
+      <c r="I65" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
       <c r="J65" s="36" t="inlineStr">
         <is>
-          <t>22nd</t>
+          <t>23rd</t>
         </is>
       </c>
       <c r="K65" s="32" t="n">
-        <v>8.6</v>
+        <v>5.6</v>
       </c>
       <c r="L65" s="32" t="n">
-        <v>9.800000000000001</v>
+        <v>5</v>
       </c>
       <c r="M65" s="32" t="n">
-        <v>9.467000000000001</v>
+        <v>5</v>
       </c>
       <c r="N65" s="32" t="n">
-        <v>9.300000000000001</v>
+        <v>4.55</v>
       </c>
       <c r="O65" s="32" t="n">
-        <v>8.733000000000001</v>
+        <v>4.667</v>
       </c>
       <c r="P65" s="32" t="n">
-        <v>8.398</v>
+        <v>4.886</v>
       </c>
       <c r="Q65" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="31" t="inlineStr">
         <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B66" s="32" t="n">
+        <v>8.054</v>
+      </c>
+      <c r="C66" s="32" t="n">
+        <v>7.833</v>
+      </c>
+      <c r="D66" s="32" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="E66" s="32" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="F66" s="32" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="G66" s="32" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="H66" s="34" t="inlineStr">
+        <is>
+          <t>13th</t>
+        </is>
+      </c>
+      <c r="I66" s="32" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="J66" s="36" t="inlineStr">
+        <is>
+          <t>24th</t>
+        </is>
+      </c>
+      <c r="K66" s="32" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="L66" s="32" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="M66" s="32" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="N66" s="32" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="O66" s="32" t="n">
+        <v>8.567</v>
+      </c>
+      <c r="P66" s="32" t="n">
+        <v>8.837</v>
+      </c>
+      <c r="Q66" s="35" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="31" t="inlineStr">
+        <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B67" s="32" t="n">
+        <v>0.976</v>
+      </c>
+      <c r="C67" s="32" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D67" s="32" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="E67" s="32" t="n">
+        <v>1.267</v>
+      </c>
+      <c r="F67" s="32" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G67" s="32" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H67" s="33" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="I67" s="32" t="inlineStr"/>
+      <c r="J67" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K67" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L67" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M67" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N67" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O67" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P67" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q67" s="35" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="31" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B68" s="32" t="n">
+        <v>8.372999999999999</v>
+      </c>
+      <c r="C68" s="32" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="D68" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="E68" s="32" t="n">
+        <v>10.733</v>
+      </c>
+      <c r="F68" s="32" t="n">
+        <v>11</v>
+      </c>
+      <c r="G68" s="32" t="n">
+        <v>11</v>
+      </c>
+      <c r="H68" s="36" t="inlineStr">
+        <is>
+          <t>25th</t>
+        </is>
+      </c>
+      <c r="I68" s="32" t="inlineStr"/>
+      <c r="J68" s="36" t="inlineStr">
+        <is>
+          <t>22nd</t>
+        </is>
+      </c>
+      <c r="K68" s="32" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="L68" s="32" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="M68" s="32" t="n">
+        <v>9.467000000000001</v>
+      </c>
+      <c r="N68" s="32" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="O68" s="32" t="n">
+        <v>8.733000000000001</v>
+      </c>
+      <c r="P68" s="32" t="n">
+        <v>8.398</v>
+      </c>
+      <c r="Q68" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B66" s="32" t="n">
+      <c r="B69" s="32" t="n">
         <v>0.584</v>
       </c>
-      <c r="C66" s="32" t="n">
+      <c r="C69" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="D66" s="32" t="n">
+      <c r="D69" s="32" t="n">
         <v>0.35</v>
       </c>
-      <c r="E66" s="32" t="n">
+      <c r="E69" s="32" t="n">
         <v>0.267</v>
       </c>
-      <c r="F66" s="32" t="n">
+      <c r="F69" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="G66" s="32" t="n">
+      <c r="G69" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="H66" s="34" t="inlineStr">
+      <c r="H69" s="34" t="inlineStr">
         <is>
           <t>18th</t>
         </is>
       </c>
-      <c r="I66" s="32" t="inlineStr">
+      <c r="I69" s="32" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="J66" s="36" t="inlineStr">
+      <c r="J69" s="36" t="inlineStr">
         <is>
           <t>24th</t>
         </is>
       </c>
-      <c r="K66" s="32" t="n">
+      <c r="K69" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="L66" s="32" t="n">
+      <c r="L69" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="M66" s="32" t="n">
+      <c r="M69" s="32" t="n">
         <v>0.867</v>
       </c>
-      <c r="N66" s="32" t="n">
+      <c r="N69" s="32" t="n">
         <v>0.8</v>
       </c>
-      <c r="O66" s="32" t="n">
+      <c r="O69" s="32" t="n">
         <v>0.8</v>
       </c>
-      <c r="P66" s="32" t="n">
+      <c r="P69" s="32" t="n">
         <v>0.657</v>
       </c>
-      <c r="Q66" s="35" t="inlineStr">
+      <c r="Q69" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="29" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="29" t="inlineStr">
         <is>
           <t>Baltimore Orioles offense vs Washington Nationals defense</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="30" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B69" s="30" t="inlineStr">
+      <c r="B72" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C69" s="30" t="inlineStr">
+      <c r="C72" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D69" s="30" t="inlineStr">
+      <c r="D72" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E69" s="30" t="inlineStr">
+      <c r="E72" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F69" s="30" t="inlineStr">
+      <c r="F72" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G69" s="30" t="inlineStr">
+      <c r="G72" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H69" s="30" t="inlineStr">
+      <c r="H72" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I69" s="30" t="inlineStr">
+      <c r="I72" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J69" s="30" t="inlineStr">
+      <c r="J72" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K69" s="30" t="inlineStr">
+      <c r="K72" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L69" s="30" t="inlineStr">
+      <c r="L72" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M69" s="30" t="inlineStr">
+      <c r="M72" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N69" s="30" t="inlineStr">
+      <c r="N72" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O69" s="30" t="inlineStr">
+      <c r="O72" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P69" s="30" t="inlineStr">
+      <c r="P72" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q69" s="30" t="inlineStr">
+      <c r="Q72" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B70" s="32" t="n">
-        <v>4.181</v>
-      </c>
-      <c r="C70" s="32" t="n">
-        <v>3.567</v>
-      </c>
-      <c r="D70" s="32" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="E70" s="32" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="F70" s="32" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="G70" s="32" t="n">
-        <v>3</v>
-      </c>
-      <c r="H70" s="36" t="inlineStr">
-        <is>
-          <t>22nd</t>
-        </is>
-      </c>
-      <c r="I70" s="32" t="inlineStr"/>
-      <c r="J70" s="36" t="inlineStr">
-        <is>
-          <t>24th</t>
-        </is>
-      </c>
-      <c r="K70" s="32" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="L70" s="32" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="M70" s="32" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="N70" s="32" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="O70" s="32" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="P70" s="32" t="n">
-        <v>5.566</v>
-      </c>
-      <c r="Q70" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="31" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B71" s="32" t="n">
-        <v>7.861</v>
-      </c>
-      <c r="C71" s="32" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="D71" s="32" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="E71" s="32" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="F71" s="32" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="G71" s="32" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="H71" s="36" t="inlineStr">
-        <is>
-          <t>29th</t>
-        </is>
-      </c>
-      <c r="I71" s="32" t="inlineStr"/>
-      <c r="J71" s="36" t="inlineStr">
-        <is>
-          <t>21st</t>
-        </is>
-      </c>
-      <c r="K71" s="32" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="L71" s="32" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="M71" s="32" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="N71" s="32" t="n">
-        <v>10.05</v>
-      </c>
-      <c r="O71" s="32" t="n">
-        <v>9</v>
-      </c>
-      <c r="P71" s="32" t="n">
-        <v>9.259</v>
-      </c>
-      <c r="Q71" s="35" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="31" t="inlineStr">
-        <is>
-          <t>HR/G</t>
-        </is>
-      </c>
-      <c r="B72" s="32" t="n">
-        <v>1.175</v>
-      </c>
-      <c r="C72" s="32" t="n">
-        <v>1.067</v>
-      </c>
-      <c r="D72" s="32" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="E72" s="32" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="F72" s="32" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="G72" s="32" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="H72" s="33" t="inlineStr">
-        <is>
-          <t>8th</t>
-        </is>
-      </c>
-      <c r="I72" s="32" t="inlineStr"/>
-      <c r="J72" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q72" s="35" t="inlineStr">
-        <is>
-          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B73" s="32" t="n">
-        <v>9.048</v>
+        <v>4.181</v>
       </c>
       <c r="C73" s="32" t="n">
-        <v>10.333</v>
+        <v>3.567</v>
       </c>
       <c r="D73" s="32" t="n">
-        <v>10.35</v>
+        <v>2.95</v>
       </c>
       <c r="E73" s="32" t="n">
-        <v>10</v>
+        <v>3.2</v>
       </c>
       <c r="F73" s="32" t="n">
-        <v>10.3</v>
+        <v>2.7</v>
       </c>
       <c r="G73" s="32" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="H73" s="34" t="inlineStr">
-        <is>
-          <t>20th</t>
+        <v>3</v>
+      </c>
+      <c r="H73" s="36" t="inlineStr">
+        <is>
+          <t>22nd</t>
         </is>
       </c>
       <c r="I73" s="32" t="inlineStr"/>
-      <c r="J73" s="34" t="inlineStr">
-        <is>
-          <t>13th</t>
+      <c r="J73" s="36" t="inlineStr">
+        <is>
+          <t>24th</t>
         </is>
       </c>
       <c r="K73" s="32" t="n">
-        <v>9.6</v>
+        <v>5.8</v>
       </c>
       <c r="L73" s="32" t="n">
-        <v>9</v>
+        <v>6.6</v>
       </c>
       <c r="M73" s="32" t="n">
-        <v>8.333</v>
+        <v>6.4</v>
       </c>
       <c r="N73" s="32" t="n">
-        <v>7.75</v>
+        <v>6.3</v>
       </c>
       <c r="O73" s="32" t="n">
-        <v>8.233000000000001</v>
+        <v>5.8</v>
       </c>
       <c r="P73" s="32" t="n">
-        <v>7.729</v>
+        <v>5.566</v>
       </c>
       <c r="Q73" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="31" t="inlineStr">
         <is>
-          <t>1st Inn R/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B74" s="32" t="n">
-        <v>0.428</v>
+        <v>7.861</v>
       </c>
       <c r="C74" s="32" t="n">
-        <v>0.333</v>
+        <v>6.9</v>
       </c>
       <c r="D74" s="32" t="n">
-        <v>0.35</v>
+        <v>6.2</v>
       </c>
       <c r="E74" s="32" t="n">
-        <v>0.333</v>
+        <v>6.2</v>
       </c>
       <c r="F74" s="32" t="n">
-        <v>0.2</v>
+        <v>5.2</v>
       </c>
       <c r="G74" s="32" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="H74" s="36" t="inlineStr">
         <is>
-          <t>27th</t>
+          <t>29th</t>
         </is>
       </c>
       <c r="I74" s="32" t="inlineStr"/>
       <c r="J74" s="36" t="inlineStr">
         <is>
+          <t>21st</t>
+        </is>
+      </c>
+      <c r="K74" s="32" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="L74" s="32" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="M74" s="32" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="N74" s="32" t="n">
+        <v>10.05</v>
+      </c>
+      <c r="O74" s="32" t="n">
+        <v>9</v>
+      </c>
+      <c r="P74" s="32" t="n">
+        <v>9.259</v>
+      </c>
+      <c r="Q74" s="35" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="31" t="inlineStr">
+        <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B75" s="32" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="C75" s="32" t="n">
+        <v>1.067</v>
+      </c>
+      <c r="D75" s="32" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="E75" s="32" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F75" s="32" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G75" s="32" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H75" s="33" t="inlineStr">
+        <is>
+          <t>8th</t>
+        </is>
+      </c>
+      <c r="I75" s="32" t="inlineStr"/>
+      <c r="J75" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q75" s="35" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="31" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B76" s="32" t="n">
+        <v>9.048</v>
+      </c>
+      <c r="C76" s="32" t="n">
+        <v>10.333</v>
+      </c>
+      <c r="D76" s="32" t="n">
+        <v>10.35</v>
+      </c>
+      <c r="E76" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="F76" s="32" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="G76" s="32" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="H76" s="34" t="inlineStr">
+        <is>
+          <t>20th</t>
+        </is>
+      </c>
+      <c r="I76" s="32" t="inlineStr"/>
+      <c r="J76" s="34" t="inlineStr">
+        <is>
+          <t>13th</t>
+        </is>
+      </c>
+      <c r="K76" s="32" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="L76" s="32" t="n">
+        <v>9</v>
+      </c>
+      <c r="M76" s="32" t="n">
+        <v>8.333</v>
+      </c>
+      <c r="N76" s="32" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="O76" s="32" t="n">
+        <v>8.233000000000001</v>
+      </c>
+      <c r="P76" s="32" t="n">
+        <v>7.729</v>
+      </c>
+      <c r="Q76" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="31" t="inlineStr">
+        <is>
+          <t>1st Inn R/G</t>
+        </is>
+      </c>
+      <c r="B77" s="32" t="n">
+        <v>0.428</v>
+      </c>
+      <c r="C77" s="32" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="D77" s="32" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E77" s="32" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="F77" s="32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G77" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" s="36" t="inlineStr">
+        <is>
+          <t>27th</t>
+        </is>
+      </c>
+      <c r="I77" s="32" t="inlineStr"/>
+      <c r="J77" s="36" t="inlineStr">
+        <is>
           <t>26th</t>
         </is>
       </c>
-      <c r="K74" s="32" t="n">
+      <c r="K77" s="32" t="n">
         <v>1.2</v>
       </c>
-      <c r="L74" s="32" t="n">
+      <c r="L77" s="32" t="n">
         <v>0.8</v>
       </c>
-      <c r="M74" s="32" t="n">
+      <c r="M77" s="32" t="n">
         <v>0.733</v>
       </c>
-      <c r="N74" s="32" t="n">
+      <c r="N77" s="32" t="n">
         <v>0.65</v>
       </c>
-      <c r="O74" s="32" t="n">
+      <c r="O77" s="32" t="n">
         <v>0.8</v>
       </c>
-      <c r="P74" s="32" t="n">
+      <c r="P77" s="32" t="n">
         <v>0.717</v>
       </c>
-      <c r="Q74" s="35" t="inlineStr">
+      <c r="Q77" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -8132,13 +8132,13 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.715</v>
+        <v>0.7150000000000001</v>
       </c>
       <c r="G5" s="14" t="n">
         <v>-251</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>-104</v>
+        <v>104</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -8194,17 +8194,17 @@
       </c>
       <c r="E6" s="20" t="inlineStr">
         <is>
-          <t>Over 177.5</t>
+          <t>Over 176.5</t>
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.6546634615384614</v>
+        <v>0.6789058823529411</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>-190</v>
+        <v>-211</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>108</v>
+        <v>-104</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -8228,7 +8228,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 65.5% (fair -190). Your call.</t>
+          <t>Model 67.9% (fair -211). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -8264,10 +8264,10 @@
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.666252995391705</v>
+        <v>0.6690566820276497</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-200</v>
+        <v>-202</v>
       </c>
       <c r="H7" s="15" t="n">
         <v>-117</v>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 66.6% (fair -200). Your call.</t>
+          <t>Model 66.9% (fair -202). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -8311,32 +8311,32 @@
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>Houston Astros @ Detroit Tigers</t>
+          <t>Cincinnati Reds @ Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.5704901960784313</v>
+        <v>0.5525480769230769</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>-133</v>
+        <v>-123</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 57.0% (fair -133). Your call.</t>
+          <t>Model 55.3% (fair -123). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -8387,22 +8387,22 @@
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Over 8</t>
+          <t>Pittsburgh Pirates +1.5</t>
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.5875902439024391</v>
+        <v>0.6929203125</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>-142</v>
+        <v>-226</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>-105</v>
+        <v>-156</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -8426,7 +8426,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 58.8% (fair -142). Your call.</t>
+          <t>Model 69.3% (fair -226). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -8438,17 +8438,17 @@
     <row r="10">
       <c r="A10" s="20" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>Cincinnati Reds @ Pittsburgh Pirates</t>
+          <t>Seattle Mariners @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -8458,17 +8458,17 @@
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>Seattle Mariners</t>
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.5514423076923077</v>
+        <v>0.5615</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-123</v>
+        <v>-128</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -8492,7 +8492,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 55.1% (fair -123). Your call.</t>
+          <t>Model 56.1% (fair -128). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -8504,37 +8504,37 @@
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>Cincinnati Reds @ Pittsburgh Pirates</t>
+          <t>Washington Nationals @ Baltimore Orioles</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates +1.5</t>
+          <t>Baltimore Orioles</t>
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.6956106870229007</v>
+        <v>0.6803671875</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>-229</v>
+        <v>-213</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>-162</v>
+        <v>-156</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -8558,7 +8558,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 69.6% (fair -229). Your call.</t>
+          <t>Model 68.0% (fair -213). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -8570,17 +8570,17 @@
     <row r="12">
       <c r="A12" s="20" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>Texas Rangers @ Toronto Blue Jays</t>
+          <t>Arizona Diamondbacks @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>22:10</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -8590,17 +8590,17 @@
       </c>
       <c r="E12" s="20" t="inlineStr">
         <is>
-          <t>Texas Rangers</t>
+          <t>Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.4795278969957081</v>
+        <v>0.4650840336134454</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -8624,7 +8624,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 48.0% (fair +109). Your call.</t>
+          <t>Model 46.5% (fair +115). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -8636,37 +8636,37 @@
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Washington Nationals @ Baltimore Orioles</t>
+          <t>Kansas City Royals @ Chicago White Sox</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Baltimore Orioles</t>
+          <t>Chicago White Sox -1.5</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.6771374999999999</v>
+        <v>0.423923076923077</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>-210</v>
+        <v>136</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>-156</v>
+        <v>160</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -8690,7 +8690,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 67.7% (fair -210). Your call.</t>
+          <t>Model 42.4% (fair +136). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -8702,37 +8702,37 @@
     <row r="14">
       <c r="A14" s="20" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>Seattle Mariners @ Cleveland Guardians</t>
+          <t>Chicago Cubs @ Milwaukee Brewers</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Seattle Mariners</t>
+          <t>Milwaukee Brewers -1.5</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.5639450980392157</v>
+        <v>0.4519166666666667</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>-129</v>
+        <v>121</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>-104</v>
+        <v>140</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -8756,7 +8756,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 56.4% (fair -129). Your call.</t>
+          <t>Model 45.2% (fair +121). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -8773,12 +8773,12 @@
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks @ Tampa Bay Rays</t>
+          <t>Seattle Mariners @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>22:10</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
@@ -8788,17 +8788,17 @@
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks</t>
+          <t>Seattle Mariners</t>
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.4639915966386555</v>
+        <v>0.6167660944206009</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>116</v>
+        <v>-161</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>138</v>
+        <v>-133</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -8822,7 +8822,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 46.4% (fair +116). Your call.</t>
+          <t>Model 61.7% (fair -161). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -8839,12 +8839,12 @@
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>Kansas City Royals @ Chicago White Sox</t>
+          <t>Arizona Diamondbacks @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>22:10</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -8854,17 +8854,17 @@
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>Chicago White Sox -1.5</t>
+          <t>Arizona Diamondbacks +1.5</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.4277734375</v>
+        <v>0.6481200000000001</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>134</v>
+        <v>-184</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>156</v>
+        <v>-150</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -8888,7 +8888,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 42.8% (fair +134). Your call.</t>
+          <t>Model 64.8% (fair -184). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -8900,37 +8900,37 @@
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks @ Tampa Bay Rays</t>
+          <t>Texas Rangers @ Toronto Blue Jays</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>22:10</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks +1.5</t>
+          <t>Texas Rangers</t>
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.6475</v>
+        <v>0.4636051502145923</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>-184</v>
+        <v>116</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>-148</v>
+        <v>133</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 64.8% (fair -184). Your call.</t>
+          <t>Model 46.4% (fair +116). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -8966,37 +8966,37 @@
     <row r="18">
       <c r="A18" s="20" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>Chicago Cubs @ Milwaukee Brewers</t>
+          <t>Kansas City Royals @ Chicago White Sox</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers -1.5</t>
+          <t>Chicago White Sox</t>
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.4558898305084745</v>
+        <v>0.5913702702702703</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>119</v>
+        <v>-145</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>136</v>
+        <v>-122</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -9020,7 +9020,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 45.6% (fair +119). Your call.</t>
+          <t>Model 59.1% (fair -145). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Seattle Mariners @ Cleveland Guardians</t>
+          <t>Washington Nationals @ Baltimore Orioles</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>23:05</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -9052,17 +9052,17 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Seattle Mariners</t>
+          <t>Baltimore Orioles</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.6175531914893617</v>
+        <v>0.5570307692307692</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>-161</v>
+        <v>-126</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>-135</v>
+        <v>-108</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -9086,7 +9086,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 61.8% (fair -161). Your call.</t>
+          <t>Model 55.7% (fair -126). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -9098,17 +9098,17 @@
     <row r="20">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>Kansas City Royals @ Chicago White Sox</t>
+          <t>Phoenix Mercury @ Toronto Tempo</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -9118,17 +9118,17 @@
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Chicago White Sox</t>
+          <t>Phoenix Mercury</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.5886225225225225</v>
+        <v>0.3422364217252396</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>-143</v>
+        <v>192</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>-122</v>
+        <v>213</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -9152,7 +9152,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 58.9% (fair -143). Your call.</t>
+          <t>Model 34.2% (fair +192). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -9169,12 +9169,12 @@
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Washington Nationals @ Baltimore Orioles</t>
+          <t>Chicago Cubs @ Milwaukee Brewers</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>23:05</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -9184,17 +9184,17 @@
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Baltimore Orioles</t>
+          <t>Milwaukee Brewers</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.5604184834123221</v>
+        <v>0.6334093117408908</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>-127</v>
+        <v>-173</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>-111</v>
+        <v>-147</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -9218,7 +9218,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 56.0% (fair -127). Your call.</t>
+          <t>Model 63.3% (fair -173). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -9254,13 +9254,13 @@
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.4754260089686099</v>
+        <v>0.476891891891892</v>
       </c>
       <c r="G22" s="14" t="n">
         <v>110</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -9284,7 +9284,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 47.5% (fair +110). Your call.</t>
+          <t>Model 47.7% (fair +110). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -9301,32 +9301,32 @@
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>Chicago Cubs @ Milwaukee Brewers</t>
+          <t>Philadelphia Phillies @ New York Mets</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers</t>
+          <t>Philadelphia Phillies +1.5</t>
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.6343800000000001</v>
+        <v>0.6622795620437956</v>
       </c>
       <c r="G23" s="14" t="n">
+        <v>-196</v>
+      </c>
+      <c r="H23" s="15" t="n">
         <v>-174</v>
-      </c>
-      <c r="H23" s="15" t="n">
-        <v>-150</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -9350,7 +9350,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 63.4% (fair -174). Your call.</t>
+          <t>Model 66.2% (fair -196). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -9367,32 +9367,32 @@
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies @ New York Mets</t>
+          <t>New York Yankees @ Boston Red Sox</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies +1.5</t>
+          <t>New York Yankees</t>
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.6558248120300751</v>
+        <v>0.5405711538461537</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>-191</v>
+        <v>-118</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>-166</v>
+        <v>-108</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -9416,7 +9416,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 65.6% (fair -191). Your call.</t>
+          <t>Model 54.1% (fair -118). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -9452,10 +9452,10 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.4730630630630631</v>
+        <v>0.4686936936936937</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="H25" s="15" t="n">
         <v>122</v>
@@ -9482,7 +9482,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 47.3% (fair +111). Your call.</t>
+          <t>Model 46.9% (fair +113). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -9499,32 +9499,32 @@
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>Phoenix Mercury @ Toronto Tempo</t>
+          <t>Los Angeles Sparks @ Indiana Fever</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
-          <t>Phoenix Mercury</t>
+          <t>Los Angeles Sparks +7.5</t>
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.3501013513513513</v>
+        <v>0.5121287128712871</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>186</v>
+        <v>-105</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>196</v>
+        <v>102</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 35.0% (fair +186). Your call.</t>
+          <t>Model 51.2% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -9560,37 +9560,37 @@
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>Chicago Cubs @ Milwaukee Brewers</t>
+          <t>Texas Rangers @ Toronto Blue Jays</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:07</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers</t>
+          <t>Texas Rangers +1.5</t>
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.61746</v>
+        <v>0.5665306306306306</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>-161</v>
+        <v>-131</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>-150</v>
+        <v>-122</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -9614,7 +9614,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 61.7% (fair -161). Your call.</t>
+          <t>Model 56.7% (fair -131). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -9626,17 +9626,17 @@
     <row r="28">
       <c r="A28" s="20" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>Texas Rangers @ Toronto Blue Jays</t>
+          <t>Chicago Cubs @ Milwaukee Brewers</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
         <is>
-          <t>19:07</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -9646,17 +9646,17 @@
       </c>
       <c r="E28" s="20" t="inlineStr">
         <is>
-          <t>Texas Rangers</t>
+          <t>Milwaukee Brewers</t>
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.3753649635036496</v>
+        <v>0.61746</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>166</v>
+        <v>-161</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>174</v>
+        <v>-150</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -9680,7 +9680,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 37.5% (fair +166). Your call.</t>
+          <t>Model 61.7% (fair -161). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -9712,17 +9712,17 @@
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>Seattle Storm</t>
+          <t>Atlanta Dream</t>
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.2252087912087912</v>
+        <v>0.7559532467532468</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>344</v>
+        <v>-310</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>355</v>
+        <v>-285</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 22.5% (fair +344). Your call.</t>
+          <t>Model 75.6% (fair -310). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -10051,17 +10051,17 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Over 9</t>
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.5704901960784313</v>
+        <v>0.5043</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-133</v>
+        <v>-102</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -10085,7 +10085,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 57.0% (fair -133). Your call.</t>
+          <t>Model 50.4% (fair -102). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -10117,17 +10117,17 @@
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>Under 9</t>
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.4295076923076923</v>
+        <v>0.4957</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>133</v>
+        <v>102</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>-108</v>
+        <v>104</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -10151,7 +10151,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 43.0% (fair +133). Your call.</t>
+          <t>Model 49.6% (fair +102). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -10187,13 +10187,13 @@
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.3759090909090909</v>
+        <v>0.3750375939849624</v>
       </c>
       <c r="G9" s="14" t="n">
+        <v>167</v>
+      </c>
+      <c r="H9" s="15" t="n">
         <v>166</v>
-      </c>
-      <c r="H9" s="15" t="n">
-        <v>164</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -10217,7 +10217,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 37.6% (fair +166). Your call.</t>
+          <t>Model 37.5% (fair +167). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -10253,10 +10253,10 @@
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.6240888888888888</v>
+        <v>0.6249703703703704</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-166</v>
+        <v>-167</v>
       </c>
       <c r="H10" s="15" t="n">
         <v>-170</v>
@@ -10283,7 +10283,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 62.4% (fair -166). Your call.</t>
+          <t>Model 62.5% (fair -167). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -10319,13 +10319,13 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.5432488262910798</v>
+        <v>0.5405711538461537</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>-119</v>
+        <v>-118</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>-113</v>
+        <v>-108</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -10349,7 +10349,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 54.3% (fair -119). Your call.</t>
+          <t>Model 54.1% (fair -118). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -10385,10 +10385,10 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.4567605633802817</v>
+        <v>0.4594366197183099</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H12" s="15" t="n">
         <v>113</v>
@@ -10415,7 +10415,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 45.7% (fair +119). Your call.</t>
+          <t>Model 45.9% (fair +118). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -10457,7 +10457,7 @@
         <v>-143</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -10523,7 +10523,7 @@
         <v>143</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -10589,7 +10589,7 @@
         <v>272</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -10655,7 +10655,7 @@
         <v>-272</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -10715,13 +10715,13 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.3753649635036496</v>
+        <v>0.3770740740740741</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -10745,7 +10745,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 37.5% (fair +166). Your call.</t>
+          <t>Model 37.7% (fair +165). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -10781,10 +10781,10 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.6246555555555555</v>
+        <v>0.6228925925925926</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>-166</v>
+        <v>-165</v>
       </c>
       <c r="H18" s="15" t="n">
         <v>-170</v>
@@ -10811,7 +10811,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 62.5% (fair -166). Your call.</t>
+          <t>Model 62.3% (fair -165). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -10979,7 +10979,7 @@
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.4321076233183856</v>
+        <v>0.4334529147982063</v>
       </c>
       <c r="G21" s="14" t="n">
         <v>131</v>
@@ -11009,7 +11009,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 43.2% (fair +131). Your call.</t>
+          <t>Model 43.3% (fair +131). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.5678888888888889</v>
+        <v>0.5665306306306306</v>
       </c>
       <c r="G22" s="14" t="n">
         <v>-131</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>-125</v>
+        <v>-122</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -11075,7 +11075,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 56.8% (fair -131). Your call.</t>
+          <t>Model 56.7% (fair -131). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -11111,13 +11111,13 @@
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.4485380952380952</v>
+        <v>0.4474730769230769</v>
       </c>
       <c r="G23" s="14" t="n">
         <v>123</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>-110</v>
+        <v>-108</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -11141,7 +11141,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 44.9% (fair +123). Your call.</t>
+          <t>Model 44.7% (fair +123). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -11177,7 +11177,7 @@
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.5514423076923077</v>
+        <v>0.5525480769230769</v>
       </c>
       <c r="G24" s="14" t="n">
         <v>-123</v>
@@ -11207,7 +11207,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 55.1% (fair -123). Your call.</t>
+          <t>Model 55.3% (fair -123). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -11243,13 +11243,13 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.5875902439024391</v>
+        <v>0.6534</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>-142</v>
+        <v>-189</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>-105</v>
+        <v>102</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -11273,7 +11273,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 58.8% (fair -142). Your call.</t>
+          <t>Model 65.3% (fair -189). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -11309,10 +11309,10 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.4123943661971831</v>
+        <v>0.3466</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>142</v>
+        <v>189</v>
       </c>
       <c r="H26" s="15" t="n">
         <v>113</v>
@@ -11339,7 +11339,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 41.2% (fair +142). Your call.</t>
+          <t>Model 34.7% (fair +189). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -11375,13 +11375,13 @@
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.6956106870229007</v>
+        <v>0.6929203125</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>-229</v>
+        <v>-226</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>-162</v>
+        <v>-156</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -11405,7 +11405,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 69.6% (fair -229). Your call.</t>
+          <t>Model 69.3% (fair -226). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -11441,13 +11441,13 @@
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.3044140625</v>
+        <v>0.3070866141732284</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -11471,7 +11471,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 30.4% (fair +228). Your call.</t>
+          <t>Model 30.7% (fair +226). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -11507,13 +11507,13 @@
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.4754260089686099</v>
+        <v>0.476891891891892</v>
       </c>
       <c r="G29" s="14" t="n">
         <v>110</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -11537,7 +11537,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 47.5% (fair +110). Your call.</t>
+          <t>Model 47.7% (fair +110). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -11573,13 +11573,13 @@
         </is>
       </c>
       <c r="F30" s="13" t="n">
-        <v>0.5246</v>
+        <v>0.5230909090909091</v>
       </c>
       <c r="G30" s="14" t="n">
         <v>-110</v>
       </c>
       <c r="H30" s="15" t="n">
-        <v>-122</v>
+        <v>-120</v>
       </c>
       <c r="I30" s="13">
         <f>IF($H$30="","",IF($H$30&lt;0,-$H$30/(-$H$30+100),100/($H$30+100)))</f>
@@ -11603,7 +11603,7 @@
       </c>
       <c r="N30" s="19" t="inlineStr">
         <is>
-          <t>Model 52.5% (fair -110). Your call.</t>
+          <t>Model 52.3% (fair -110). Your call.</t>
         </is>
       </c>
       <c r="O30" s="15" t="n"/>
@@ -11635,17 +11635,17 @@
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Over 9</t>
         </is>
       </c>
       <c r="F31" s="13" t="n">
-        <v>0.4962773399014778</v>
+        <v>0.3286</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>102</v>
+        <v>204</v>
       </c>
       <c r="H31" s="15" t="n">
-        <v>-103</v>
+        <v>112</v>
       </c>
       <c r="I31" s="13">
         <f>IF($H$31="","",IF($H$31&lt;0,-$H$31/(-$H$31+100),100/($H$31+100)))</f>
@@ -11669,7 +11669,7 @@
       </c>
       <c r="N31" s="19" t="inlineStr">
         <is>
-          <t>Model 49.6% (fair +102). Your call.</t>
+          <t>Model 32.9% (fair +204). Your call.</t>
         </is>
       </c>
       <c r="O31" s="15" t="n"/>
@@ -11701,17 +11701,17 @@
       </c>
       <c r="E32" s="20" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>Under 9</t>
         </is>
       </c>
       <c r="F32" s="13" t="n">
-        <v>0.5037128712871287</v>
+        <v>0.6714</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>-101</v>
+        <v>-204</v>
       </c>
       <c r="H32" s="15" t="n">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="I32" s="13">
         <f>IF($H$32="","",IF($H$32&lt;0,-$H$32/(-$H$32+100),100/($H$32+100)))</f>
@@ -11735,7 +11735,7 @@
       </c>
       <c r="N32" s="19" t="inlineStr">
         <is>
-          <t>Model 50.4% (fair -101). Your call.</t>
+          <t>Model 67.1% (fair -204). Your call.</t>
         </is>
       </c>
       <c r="O32" s="15" t="n"/>
@@ -11771,13 +11771,13 @@
         </is>
       </c>
       <c r="F33" s="13" t="n">
-        <v>0.3441923076923077</v>
+        <v>0.3377407407407407</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="H33" s="15" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="I33" s="13">
         <f>IF($H$33="","",IF($H$33&lt;0,-$H$33/(-$H$33+100),100/($H$33+100)))</f>
@@ -11801,7 +11801,7 @@
       </c>
       <c r="N33" s="19" t="inlineStr">
         <is>
-          <t>Model 34.4% (fair +191). Your call.</t>
+          <t>Model 33.8% (fair +196). Your call.</t>
         </is>
       </c>
       <c r="O33" s="15" t="n"/>
@@ -11837,13 +11837,13 @@
         </is>
       </c>
       <c r="F34" s="13" t="n">
-        <v>0.6558248120300751</v>
+        <v>0.6622795620437956</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>-191</v>
+        <v>-196</v>
       </c>
       <c r="H34" s="15" t="n">
-        <v>-166</v>
+        <v>-174</v>
       </c>
       <c r="I34" s="13">
         <f>IF($H$34="","",IF($H$34&lt;0,-$H$34/(-$H$34+100),100/($H$34+100)))</f>
@@ -11867,7 +11867,7 @@
       </c>
       <c r="N34" s="19" t="inlineStr">
         <is>
-          <t>Model 65.6% (fair -191). Your call.</t>
+          <t>Model 66.2% (fair -196). Your call.</t>
         </is>
       </c>
       <c r="O34" s="15" t="n"/>
@@ -11909,7 +11909,7 @@
         <v>186</v>
       </c>
       <c r="H35" s="15" t="n">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="I35" s="13">
         <f>IF($H$35="","",IF($H$35&lt;0,-$H$35/(-$H$35+100),100/($H$35+100)))</f>
@@ -12041,7 +12041,7 @@
         <v>-196</v>
       </c>
       <c r="H37" s="15" t="n">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="I37" s="13">
         <f>IF($H$37="","",IF($H$37&lt;0,-$H$37/(-$H$37+100),100/($H$37+100)))</f>
@@ -12107,7 +12107,7 @@
         <v>196</v>
       </c>
       <c r="H38" s="15" t="n">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="I38" s="13">
         <f>IF($H$38="","",IF($H$38&lt;0,-$H$38/(-$H$38+100),100/($H$38+100)))</f>
@@ -12167,13 +12167,13 @@
         </is>
       </c>
       <c r="F39" s="13" t="n">
-        <v>0.4277734375</v>
+        <v>0.423923076923077</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H39" s="15" t="n">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="I39" s="13">
         <f>IF($H$39="","",IF($H$39&lt;0,-$H$39/(-$H$39+100),100/($H$39+100)))</f>
@@ -12197,7 +12197,7 @@
       </c>
       <c r="N39" s="19" t="inlineStr">
         <is>
-          <t>Model 42.8% (fair +134). Your call.</t>
+          <t>Model 42.4% (fair +136). Your call.</t>
         </is>
       </c>
       <c r="O39" s="15" t="n"/>
@@ -12233,13 +12233,13 @@
         </is>
       </c>
       <c r="F40" s="13" t="n">
-        <v>0.5722640625000001</v>
+        <v>0.5760779467680608</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>-134</v>
+        <v>-136</v>
       </c>
       <c r="H40" s="15" t="n">
-        <v>-156</v>
+        <v>-163</v>
       </c>
       <c r="I40" s="13">
         <f>IF($H$40="","",IF($H$40&lt;0,-$H$40/(-$H$40+100),100/($H$40+100)))</f>
@@ -12263,7 +12263,7 @@
       </c>
       <c r="N40" s="19" t="inlineStr">
         <is>
-          <t>Model 57.2% (fair -134). Your call.</t>
+          <t>Model 57.6% (fair -136). Your call.</t>
         </is>
       </c>
       <c r="O40" s="15" t="n"/>
@@ -12299,10 +12299,10 @@
         </is>
       </c>
       <c r="F41" s="13" t="n">
-        <v>0.4639915966386555</v>
+        <v>0.4650840336134454</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H41" s="15" t="n">
         <v>138</v>
@@ -12329,7 +12329,7 @@
       </c>
       <c r="N41" s="19" t="inlineStr">
         <is>
-          <t>Model 46.4% (fair +116). Your call.</t>
+          <t>Model 46.5% (fair +115). Your call.</t>
         </is>
       </c>
       <c r="O41" s="15" t="n"/>
@@ -12365,13 +12365,13 @@
         </is>
       </c>
       <c r="F42" s="13" t="n">
-        <v>0.5360340248962655</v>
+        <v>0.5348949579831932</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>-116</v>
+        <v>-115</v>
       </c>
       <c r="H42" s="15" t="n">
-        <v>-141</v>
+        <v>-138</v>
       </c>
       <c r="I42" s="13">
         <f>IF($H$42="","",IF($H$42&lt;0,-$H$42/(-$H$42+100),100/($H$42+100)))</f>
@@ -12395,7 +12395,7 @@
       </c>
       <c r="N42" s="19" t="inlineStr">
         <is>
-          <t>Model 53.6% (fair -116). Your call.</t>
+          <t>Model 53.5% (fair -115). Your call.</t>
         </is>
       </c>
       <c r="O42" s="15" t="n"/>
@@ -12503,7 +12503,7 @@
         <v>101</v>
       </c>
       <c r="H44" s="15" t="n">
-        <v>113</v>
+        <v>-104</v>
       </c>
       <c r="I44" s="13">
         <f>IF($H$44="","",IF($H$44&lt;0,-$H$44/(-$H$44+100),100/($H$44+100)))</f>
@@ -12563,7 +12563,7 @@
         </is>
       </c>
       <c r="F45" s="13" t="n">
-        <v>0.3525101214574899</v>
+        <v>0.3518623481781377</v>
       </c>
       <c r="G45" s="14" t="n">
         <v>184</v>
@@ -12593,7 +12593,7 @@
       </c>
       <c r="N45" s="19" t="inlineStr">
         <is>
-          <t>Model 35.3% (fair +184). Your call.</t>
+          <t>Model 35.2% (fair +184). Your call.</t>
         </is>
       </c>
       <c r="O45" s="15" t="n"/>
@@ -12629,13 +12629,13 @@
         </is>
       </c>
       <c r="F46" s="13" t="n">
-        <v>0.6475</v>
+        <v>0.6481200000000001</v>
       </c>
       <c r="G46" s="14" t="n">
         <v>-184</v>
       </c>
       <c r="H46" s="15" t="n">
-        <v>-148</v>
+        <v>-150</v>
       </c>
       <c r="I46" s="13">
         <f>IF($H$46="","",IF($H$46&lt;0,-$H$46/(-$H$46+100),100/($H$46+100)))</f>
@@ -12695,13 +12695,13 @@
         </is>
       </c>
       <c r="F47" s="13" t="n">
-        <v>0.4395734597156397</v>
+        <v>0.4429807692307692</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H47" s="15" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I47" s="13">
         <f>IF($H$47="","",IF($H$47&lt;0,-$H$47/(-$H$47+100),100/($H$47+100)))</f>
@@ -12725,7 +12725,7 @@
       </c>
       <c r="N47" s="19" t="inlineStr">
         <is>
-          <t>Model 44.0% (fair +127). Your call.</t>
+          <t>Model 44.3% (fair +126). Your call.</t>
         </is>
       </c>
       <c r="O47" s="15" t="n"/>
@@ -12761,13 +12761,13 @@
         </is>
       </c>
       <c r="F48" s="13" t="n">
-        <v>0.5604184834123221</v>
+        <v>0.5570307692307692</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>-127</v>
+        <v>-126</v>
       </c>
       <c r="H48" s="15" t="n">
-        <v>-111</v>
+        <v>-108</v>
       </c>
       <c r="I48" s="13">
         <f>IF($H$48="","",IF($H$48&lt;0,-$H$48/(-$H$48+100),100/($H$48+100)))</f>
@@ -12791,7 +12791,7 @@
       </c>
       <c r="N48" s="19" t="inlineStr">
         <is>
-          <t>Model 56.0% (fair -127). Your call.</t>
+          <t>Model 55.7% (fair -126). Your call.</t>
         </is>
       </c>
       <c r="O48" s="15" t="n"/>
@@ -12833,7 +12833,7 @@
         <v>-146</v>
       </c>
       <c r="H49" s="15" t="n">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="I49" s="13">
         <f>IF($H$49="","",IF($H$49&lt;0,-$H$49/(-$H$49+100),100/($H$49+100)))</f>
@@ -13091,13 +13091,13 @@
         </is>
       </c>
       <c r="F53" s="13" t="n">
-        <v>0.6175531914893617</v>
+        <v>0.6167660944206009</v>
       </c>
       <c r="G53" s="14" t="n">
         <v>-161</v>
       </c>
       <c r="H53" s="15" t="n">
-        <v>-135</v>
+        <v>-133</v>
       </c>
       <c r="I53" s="13">
         <f>IF($H$53="","",IF($H$53&lt;0,-$H$53/(-$H$53+100),100/($H$53+100)))</f>
@@ -13121,7 +13121,7 @@
       </c>
       <c r="N53" s="19" t="inlineStr">
         <is>
-          <t>Model 61.8% (fair -161). Your call.</t>
+          <t>Model 61.7% (fair -161). Your call.</t>
         </is>
       </c>
       <c r="O53" s="15" t="n"/>
@@ -13157,7 +13157,7 @@
         </is>
       </c>
       <c r="F54" s="13" t="n">
-        <v>0.3824463519313305</v>
+        <v>0.3832618025751073</v>
       </c>
       <c r="G54" s="14" t="n">
         <v>161</v>
@@ -13187,7 +13187,7 @@
       </c>
       <c r="N54" s="19" t="inlineStr">
         <is>
-          <t>Model 38.2% (fair +161). Your call.</t>
+          <t>Model 38.3% (fair +161). Your call.</t>
         </is>
       </c>
       <c r="O54" s="15" t="n"/>
@@ -13229,7 +13229,7 @@
         <v>129</v>
       </c>
       <c r="H55" s="15" t="n">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="I55" s="13">
         <f>IF($H$55="","",IF($H$55&lt;0,-$H$55/(-$H$55+100),100/($H$55+100)))</f>
@@ -13295,7 +13295,7 @@
         <v>-129</v>
       </c>
       <c r="H56" s="15" t="n">
-        <v>104</v>
+        <v>-108</v>
       </c>
       <c r="I56" s="13">
         <f>IF($H$56="","",IF($H$56&lt;0,-$H$56/(-$H$56+100),100/($H$56+100)))</f>
@@ -13355,10 +13355,10 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>0.5482819383259911</v>
+        <v>0.5499044052863437</v>
       </c>
       <c r="G57" s="14" t="n">
-        <v>-121</v>
+        <v>-122</v>
       </c>
       <c r="H57" s="15" t="n">
         <v>-127</v>
@@ -13385,7 +13385,7 @@
       </c>
       <c r="N57" s="19" t="inlineStr">
         <is>
-          <t>Model 54.8% (fair -121). Your call.</t>
+          <t>Model 55.0% (fair -122). Your call.</t>
         </is>
       </c>
       <c r="O57" s="15" t="n"/>
@@ -13421,13 +13421,13 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>0.4517488789237669</v>
+        <v>0.4500884955752213</v>
       </c>
       <c r="G58" s="14" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H58" s="15" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="I58" s="13">
         <f>IF($H$58="","",IF($H$58&lt;0,-$H$58/(-$H$58+100),100/($H$58+100)))</f>
@@ -13451,7 +13451,7 @@
       </c>
       <c r="N58" s="19" t="inlineStr">
         <is>
-          <t>Model 45.2% (fair +121). Your call.</t>
+          <t>Model 45.0% (fair +122). Your call.</t>
         </is>
       </c>
       <c r="O58" s="15" t="n"/>
@@ -13615,10 +13615,10 @@
         </is>
       </c>
       <c r="F61" s="13" t="n">
-        <v>0.3656</v>
+        <v>0.36656</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H61" s="15" t="n">
         <v>150</v>
@@ -13645,7 +13645,7 @@
       </c>
       <c r="N61" s="19" t="inlineStr">
         <is>
-          <t>Model 36.6% (fair +174). Your call.</t>
+          <t>Model 36.7% (fair +173). Your call.</t>
         </is>
       </c>
       <c r="O61" s="15" t="n"/>
@@ -13681,13 +13681,13 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>0.6343800000000001</v>
+        <v>0.6334093117408908</v>
       </c>
       <c r="G62" s="14" t="n">
-        <v>-174</v>
+        <v>-173</v>
       </c>
       <c r="H62" s="15" t="n">
-        <v>-150</v>
+        <v>-147</v>
       </c>
       <c r="I62" s="13">
         <f>IF($H$62="","",IF($H$62&lt;0,-$H$62/(-$H$62+100),100/($H$62+100)))</f>
@@ -13711,7 +13711,7 @@
       </c>
       <c r="N62" s="19" t="inlineStr">
         <is>
-          <t>Model 63.4% (fair -174). Your call.</t>
+          <t>Model 63.3% (fair -173). Your call.</t>
         </is>
       </c>
       <c r="O62" s="15" t="n"/>
@@ -13753,7 +13753,7 @@
         <v>-167</v>
       </c>
       <c r="H63" s="15" t="n">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="I63" s="13">
         <f>IF($H$63="","",IF($H$63&lt;0,-$H$63/(-$H$63+100),100/($H$63+100)))</f>
@@ -13819,7 +13819,7 @@
         <v>167</v>
       </c>
       <c r="H64" s="15" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="I64" s="13">
         <f>IF($H$64="","",IF($H$64&lt;0,-$H$64/(-$H$64+100),100/($H$64+100)))</f>
@@ -13879,13 +13879,13 @@
         </is>
       </c>
       <c r="F65" s="13" t="n">
-        <v>0.4558898305084745</v>
+        <v>0.4519166666666667</v>
       </c>
       <c r="G65" s="14" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="H65" s="15" t="n">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="I65" s="13">
         <f>IF($H$65="","",IF($H$65&lt;0,-$H$65/(-$H$65+100),100/($H$65+100)))</f>
@@ -13909,7 +13909,7 @@
       </c>
       <c r="N65" s="19" t="inlineStr">
         <is>
-          <t>Model 45.6% (fair +119). Your call.</t>
+          <t>Model 45.2% (fair +121). Your call.</t>
         </is>
       </c>
       <c r="O65" s="15" t="n"/>
@@ -13945,13 +13945,13 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>0.5441012875536481</v>
+        <v>0.5480571428571428</v>
       </c>
       <c r="G66" s="14" t="n">
-        <v>-119</v>
+        <v>-121</v>
       </c>
       <c r="H66" s="15" t="n">
-        <v>-133</v>
+        <v>-138</v>
       </c>
       <c r="I66" s="13">
         <f>IF($H$66="","",IF($H$66&lt;0,-$H$66/(-$H$66+100),100/($H$66+100)))</f>
@@ -13975,7 +13975,7 @@
       </c>
       <c r="N66" s="19" t="inlineStr">
         <is>
-          <t>Model 54.4% (fair -119). Your call.</t>
+          <t>Model 54.8% (fair -121). Your call.</t>
         </is>
       </c>
       <c r="O66" s="15" t="n"/>
@@ -14523,13 +14523,13 @@
         </is>
       </c>
       <c r="F75" s="13" t="n">
-        <v>0.3228515625</v>
+        <v>0.3196577946768061</v>
       </c>
       <c r="G75" s="14" t="n">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="H75" s="15" t="n">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="I75" s="13">
         <f>IF($H$75="","",IF($H$75&lt;0,-$H$75/(-$H$75+100),100/($H$75+100)))</f>
@@ -14553,7 +14553,7 @@
       </c>
       <c r="N75" s="19" t="inlineStr">
         <is>
-          <t>Model 32.3% (fair +210). Your call.</t>
+          <t>Model 32.0% (fair +213). Your call.</t>
         </is>
       </c>
       <c r="O75" s="15" t="n"/>
@@ -14589,10 +14589,10 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>0.6771374999999999</v>
+        <v>0.6803671875</v>
       </c>
       <c r="G76" s="14" t="n">
-        <v>-210</v>
+        <v>-213</v>
       </c>
       <c r="H76" s="15" t="n">
         <v>-156</v>
@@ -14619,7 +14619,7 @@
       </c>
       <c r="N76" s="19" t="inlineStr">
         <is>
-          <t>Model 67.7% (fair -210). Your call.</t>
+          <t>Model 68.0% (fair -213). Your call.</t>
         </is>
       </c>
       <c r="O76" s="15" t="n"/>
@@ -14655,13 +14655,13 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>0.333778801843318</v>
+        <v>0.330945945945946</v>
       </c>
       <c r="G77" s="14" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="H77" s="15" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="I77" s="13">
         <f>IF($H$77="","",IF($H$77&lt;0,-$H$77/(-$H$77+100),100/($H$77+100)))</f>
@@ -14685,7 +14685,7 @@
       </c>
       <c r="N77" s="19" t="inlineStr">
         <is>
-          <t>Model 33.4% (fair +200). Your call.</t>
+          <t>Model 33.1% (fair +202). Your call.</t>
         </is>
       </c>
       <c r="O77" s="15" t="n"/>
@@ -14721,10 +14721,10 @@
         </is>
       </c>
       <c r="F78" s="13" t="n">
-        <v>0.666252995391705</v>
+        <v>0.6690566820276497</v>
       </c>
       <c r="G78" s="14" t="n">
-        <v>-200</v>
+        <v>-202</v>
       </c>
       <c r="H78" s="15" t="n">
         <v>-117</v>
@@ -14751,7 +14751,7 @@
       </c>
       <c r="N78" s="19" t="inlineStr">
         <is>
-          <t>Model 66.6% (fair -200). Your call.</t>
+          <t>Model 66.9% (fair -202). Your call.</t>
         </is>
       </c>
       <c r="O78" s="15" t="n"/>
@@ -14787,10 +14787,10 @@
         </is>
       </c>
       <c r="F79" s="13" t="n">
-        <v>0.4795278969957081</v>
+        <v>0.4636051502145923</v>
       </c>
       <c r="G79" s="14" t="n">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="H79" s="15" t="n">
         <v>133</v>
@@ -14817,7 +14817,7 @@
       </c>
       <c r="N79" s="19" t="inlineStr">
         <is>
-          <t>Model 48.0% (fair +109). Your call.</t>
+          <t>Model 46.4% (fair +116). Your call.</t>
         </is>
       </c>
       <c r="O79" s="15" t="n"/>
@@ -14853,10 +14853,10 @@
         </is>
       </c>
       <c r="F80" s="13" t="n">
-        <v>0.5204571428571428</v>
+        <v>0.5364025210084034</v>
       </c>
       <c r="G80" s="14" t="n">
-        <v>-109</v>
+        <v>-116</v>
       </c>
       <c r="H80" s="15" t="n">
         <v>-138</v>
@@ -14883,7 +14883,7 @@
       </c>
       <c r="N80" s="19" t="inlineStr">
         <is>
-          <t>Model 52.0% (fair -109). Your call.</t>
+          <t>Model 53.6% (fair -116). Your call.</t>
         </is>
       </c>
       <c r="O80" s="15" t="n"/>
@@ -14919,13 +14919,13 @@
         </is>
       </c>
       <c r="F81" s="13" t="n">
-        <v>0.5269619718309859</v>
+        <v>0.5313045045045045</v>
       </c>
       <c r="G81" s="14" t="n">
-        <v>-111</v>
+        <v>-113</v>
       </c>
       <c r="H81" s="15" t="n">
-        <v>-113</v>
+        <v>-122</v>
       </c>
       <c r="I81" s="13">
         <f>IF($H$81="","",IF($H$81&lt;0,-$H$81/(-$H$81+100),100/($H$81+100)))</f>
@@ -14949,7 +14949,7 @@
       </c>
       <c r="N81" s="19" t="inlineStr">
         <is>
-          <t>Model 52.7% (fair -111). Your call.</t>
+          <t>Model 53.1% (fair -113). Your call.</t>
         </is>
       </c>
       <c r="O81" s="15" t="n"/>
@@ -14985,10 +14985,10 @@
         </is>
       </c>
       <c r="F82" s="13" t="n">
-        <v>0.4730630630630631</v>
+        <v>0.4686936936936937</v>
       </c>
       <c r="G82" s="14" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="H82" s="15" t="n">
         <v>122</v>
@@ -15015,7 +15015,7 @@
       </c>
       <c r="N82" s="19" t="inlineStr">
         <is>
-          <t>Model 47.3% (fair +111). Your call.</t>
+          <t>Model 46.9% (fair +113). Your call.</t>
         </is>
       </c>
       <c r="O82" s="15" t="n"/>
@@ -15051,13 +15051,13 @@
         </is>
       </c>
       <c r="F83" s="13" t="n">
-        <v>0.5639450980392157</v>
+        <v>0.5615</v>
       </c>
       <c r="G83" s="14" t="n">
-        <v>-129</v>
+        <v>-128</v>
       </c>
       <c r="H83" s="15" t="n">
-        <v>-104</v>
+        <v>100</v>
       </c>
       <c r="I83" s="13">
         <f>IF($H$83="","",IF($H$83&lt;0,-$H$83/(-$H$83+100),100/($H$83+100)))</f>
@@ -15081,7 +15081,7 @@
       </c>
       <c r="N83" s="19" t="inlineStr">
         <is>
-          <t>Model 56.4% (fair -129). Your call.</t>
+          <t>Model 56.1% (fair -128). Your call.</t>
         </is>
       </c>
       <c r="O83" s="15" t="n"/>
@@ -15117,10 +15117,10 @@
         </is>
       </c>
       <c r="F84" s="13" t="n">
-        <v>0.43605</v>
+        <v>0.4385</v>
       </c>
       <c r="G84" s="14" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H84" s="15" t="n">
         <v>100</v>
@@ -15147,7 +15147,7 @@
       </c>
       <c r="N84" s="19" t="inlineStr">
         <is>
-          <t>Model 43.6% (fair +129). Your call.</t>
+          <t>Model 43.9% (fair +128). Your call.</t>
         </is>
       </c>
       <c r="O84" s="15" t="n"/>
@@ -15183,10 +15183,10 @@
         </is>
       </c>
       <c r="F85" s="13" t="n">
-        <v>0.4032377049180328</v>
+        <v>0.4052049180327869</v>
       </c>
       <c r="G85" s="14" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H85" s="15" t="n">
         <v>144</v>
@@ -15213,7 +15213,7 @@
       </c>
       <c r="N85" s="19" t="inlineStr">
         <is>
-          <t>Model 40.3% (fair +148). Your call.</t>
+          <t>Model 40.5% (fair +147). Your call.</t>
         </is>
       </c>
       <c r="O85" s="15" t="n"/>
@@ -15249,13 +15249,13 @@
         </is>
       </c>
       <c r="F86" s="13" t="n">
-        <v>0.5967600000000001</v>
+        <v>0.5947672131147541</v>
       </c>
       <c r="G86" s="14" t="n">
-        <v>-148</v>
+        <v>-147</v>
       </c>
       <c r="H86" s="15" t="n">
-        <v>-150</v>
+        <v>-144</v>
       </c>
       <c r="I86" s="13">
         <f>IF($H$86="","",IF($H$86&lt;0,-$H$86/(-$H$86+100),100/($H$86+100)))</f>
@@ -15279,7 +15279,7 @@
       </c>
       <c r="N86" s="19" t="inlineStr">
         <is>
-          <t>Model 59.7% (fair -148). Your call.</t>
+          <t>Model 59.5% (fair -147). Your call.</t>
         </is>
       </c>
       <c r="O86" s="15" t="n"/>
@@ -15579,13 +15579,13 @@
         </is>
       </c>
       <c r="F91" s="13" t="n">
-        <v>0.4113963963963965</v>
+        <v>0.4086343612334802</v>
       </c>
       <c r="G91" s="14" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H91" s="15" t="n">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="I91" s="13">
         <f>IF($H$91="","",IF($H$91&lt;0,-$H$91/(-$H$91+100),100/($H$91+100)))</f>
@@ -15609,7 +15609,7 @@
       </c>
       <c r="N91" s="19" t="inlineStr">
         <is>
-          <t>Model 41.1% (fair +143). Your call.</t>
+          <t>Model 40.9% (fair +145). Your call.</t>
         </is>
       </c>
       <c r="O91" s="15" t="n"/>
@@ -15645,10 +15645,10 @@
         </is>
       </c>
       <c r="F92" s="13" t="n">
-        <v>0.5886225225225225</v>
+        <v>0.5913702702702703</v>
       </c>
       <c r="G92" s="14" t="n">
-        <v>-143</v>
+        <v>-145</v>
       </c>
       <c r="H92" s="15" t="n">
         <v>-122</v>
@@ -15675,7 +15675,7 @@
       </c>
       <c r="N92" s="19" t="inlineStr">
         <is>
-          <t>Model 58.9% (fair -143). Your call.</t>
+          <t>Model 59.1% (fair -145). Your call.</t>
         </is>
       </c>
       <c r="O92" s="15" t="n"/>
@@ -16626,13 +16626,13 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.3501013513513513</v>
+        <v>0.3422364217252396</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -16656,7 +16656,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 35.0% (fair +186). Your call.</t>
+          <t>Model 34.2% (fair +192). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -16692,13 +16692,13 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.6498679867986799</v>
+        <v>0.657782108626198</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>-186</v>
+        <v>-192</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>-203</v>
+        <v>-213</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -16722,7 +16722,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 65.0% (fair -186). Your call.</t>
+          <t>Model 65.8% (fair -192). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -16754,17 +16754,17 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Over 177.5</t>
+          <t>Over 176.5</t>
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.6546634615384614</v>
+        <v>0.6789058823529411</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-190</v>
+        <v>-211</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>108</v>
+        <v>-104</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -16788,7 +16788,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 65.5% (fair -190). Your call.</t>
+          <t>Model 67.9% (fair -211). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -16820,17 +16820,17 @@
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>Under 177.5</t>
+          <t>Under 176.5</t>
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.3453000000000001</v>
+        <v>0.3211000000000001</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>190</v>
+        <v>211</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>108</v>
+        <v>-104</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -16854,7 +16854,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 34.5% (fair +190). Your call.</t>
+          <t>Model 32.1% (fair +211). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -16896,7 +16896,7 @@
         <v>129</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -16962,7 +16962,7 @@
         <v>-129</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -17022,10 +17022,10 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.291025641025641</v>
+        <v>0.2901139601139601</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H11" s="15" t="n">
         <v>251</v>
@@ -17052,7 +17052,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 29.1% (fair +244). Your call.</t>
+          <t>Model 29.0% (fair +245). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -17088,13 +17088,13 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.7090057057057058</v>
+        <v>0.7099058823529412</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>-244</v>
+        <v>-245</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>-233</v>
+        <v>-240</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -17118,7 +17118,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 70.9% (fair -244). Your call.</t>
+          <t>Model 71.0% (fair -245). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -17154,13 +17154,13 @@
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.715</v>
+        <v>0.7150000000000001</v>
       </c>
       <c r="G13" s="14" t="n">
         <v>-251</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>-104</v>
+        <v>104</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -17226,7 +17226,7 @@
         <v>251</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>-104</v>
+        <v>104</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -17286,13 +17286,13 @@
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.4757</v>
+        <v>0.4878712871287129</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -17316,7 +17316,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 47.6% (fair +110). Your call.</t>
+          <t>Model 48.8% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -17352,13 +17352,13 @@
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.5243</v>
+        <v>0.5121287128712871</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>-110</v>
+        <v>-105</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -17382,7 +17382,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 52.4% (fair -110). Your call.</t>
+          <t>Model 51.2% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -17418,13 +17418,13 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.7748126436781609</v>
+        <v>0.7559532467532468</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>-344</v>
+        <v>-310</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>-335</v>
+        <v>-285</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -17448,7 +17448,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 77.5% (fair -344). Your call.</t>
+          <t>Model 75.6% (fair -310). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -17484,13 +17484,13 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.2252087912087912</v>
+        <v>0.2440779220779221</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>344</v>
+        <v>310</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>355</v>
+        <v>285</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -17514,7 +17514,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 22.5% (fair +344). Your call.</t>
+          <t>Model 24.4% (fair +310). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -17546,17 +17546,17 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Over 177.5</t>
+          <t>Over 176.5</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.3057211538461538</v>
+        <v>0.3294862745098039</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>227</v>
+        <v>204</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>108</v>
+        <v>-104</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -17580,7 +17580,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 30.6% (fair +227). Your call.</t>
+          <t>Model 32.9% (fair +204). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -17612,17 +17612,17 @@
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Under 177.5</t>
+          <t>Under 176.5</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.6942999999999999</v>
+        <v>0.6705</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>-227</v>
+        <v>-203</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>108</v>
+        <v>-104</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -17646,7 +17646,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 69.4% (fair -227). Your call.</t>
+          <t>Model 67.0% (fair -203). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -17678,17 +17678,17 @@
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Seattle Storm +7.5</t>
+          <t>Seattle Storm -4</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.5591</v>
+        <v>0.1973</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>-127</v>
+        <v>407</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>108</v>
+        <v>410</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -17712,7 +17712,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 55.9% (fair -127). Your call.</t>
+          <t>Model 19.7% (fair +407). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -17744,17 +17744,17 @@
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>Atlanta Dream -7.5</t>
+          <t>Atlanta Dream +4</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.4409</v>
+        <v>0.8027</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>127</v>
+        <v>-407</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>500</v>
+        <v>113</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -17778,7 +17778,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 44.1% (fair +127). Your call.</t>
+          <t>Model 80.3% (fair -407). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>

--- a/data/output/workbook/2026-06-27.xlsx
+++ b/data/output/workbook/2026-06-27.xlsx
@@ -491,7 +491,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="9429750"/>
+    <ext cx="10125075" cy="9048750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -954,7 +954,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-06-27 10:31</t>
+          <t>2026-06-27 12:06</t>
         </is>
       </c>
     </row>
@@ -2846,7 +2846,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q75"/>
+  <dimension ref="A1:Q72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2863,807 +2863,807 @@
         </is>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" s="29" t="inlineStr">
+        <is>
+          <t>Philadelphia Phillies offense vs New York Mets defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B59" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C59" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D59" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E59" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F59" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G59" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H59" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I59" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J59" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K59" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L59" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M59" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N59" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O59" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P59" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q59" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B60" s="32" t="n">
+        <v>4.802</v>
+      </c>
+      <c r="C60" s="32" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="D60" s="32" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E60" s="32" t="n">
+        <v>3.933</v>
+      </c>
+      <c r="F60" s="32" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="G60" s="32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H60" s="34" t="inlineStr">
+        <is>
+          <t>17th</t>
+        </is>
+      </c>
+      <c r="I60" s="32" t="inlineStr"/>
+      <c r="J60" s="34" t="inlineStr">
+        <is>
+          <t>18th</t>
+        </is>
+      </c>
+      <c r="K60" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="L60" s="32" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="M60" s="32" t="n">
+        <v>4.667</v>
+      </c>
+      <c r="N60" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="O60" s="32" t="n">
+        <v>5.367</v>
+      </c>
+      <c r="P60" s="32" t="n">
+        <v>4.386</v>
+      </c>
+      <c r="Q60" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
+        </is>
+      </c>
+    </row>
     <row r="61">
-      <c r="A61" s="29" t="inlineStr">
-        <is>
-          <t>Philadelphia Phillies offense vs New York Mets defense</t>
+      <c r="A61" s="31" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B61" s="32" t="n">
+        <v>8.802</v>
+      </c>
+      <c r="C61" s="32" t="n">
+        <v>8.766999999999999</v>
+      </c>
+      <c r="D61" s="32" t="n">
+        <v>8.15</v>
+      </c>
+      <c r="E61" s="32" t="n">
+        <v>7.733</v>
+      </c>
+      <c r="F61" s="32" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="G61" s="32" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="H61" s="36" t="inlineStr">
+        <is>
+          <t>23rd</t>
+        </is>
+      </c>
+      <c r="I61" s="32" t="inlineStr"/>
+      <c r="J61" s="33" t="inlineStr">
+        <is>
+          <t>9th</t>
+        </is>
+      </c>
+      <c r="K61" s="32" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="L61" s="32" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="M61" s="32" t="n">
+        <v>8.333</v>
+      </c>
+      <c r="N61" s="32" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="O61" s="32" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="P61" s="32" t="n">
+        <v>8.211</v>
+      </c>
+      <c r="Q61" s="35" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B62" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C62" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D62" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E62" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F62" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G62" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H62" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I62" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J62" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K62" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L62" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M62" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N62" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O62" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P62" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q62" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A62" s="31" t="inlineStr">
+        <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B62" s="32" t="n">
+        <v>1.285</v>
+      </c>
+      <c r="C62" s="32" t="n">
+        <v>1.533</v>
+      </c>
+      <c r="D62" s="32" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E62" s="32" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F62" s="32" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G62" s="32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H62" s="36" t="inlineStr">
+        <is>
+          <t>21st</t>
+        </is>
+      </c>
+      <c r="I62" s="32" t="inlineStr"/>
+      <c r="J62" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K62" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L62" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M62" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N62" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O62" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P62" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q62" s="35" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B63" s="32" t="n">
-        <v>4.802</v>
+        <v>8.273</v>
       </c>
       <c r="C63" s="32" t="n">
-        <v>4.8</v>
+        <v>9.5</v>
       </c>
       <c r="D63" s="32" t="n">
-        <v>4.5</v>
+        <v>9.6</v>
       </c>
       <c r="E63" s="32" t="n">
-        <v>3.933</v>
+        <v>9.933</v>
       </c>
       <c r="F63" s="32" t="n">
-        <v>3.7</v>
+        <v>10.4</v>
       </c>
       <c r="G63" s="32" t="n">
-        <v>3.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H63" s="34" t="inlineStr">
         <is>
-          <t>17th</t>
-        </is>
-      </c>
-      <c r="I63" s="32" t="inlineStr"/>
-      <c r="J63" s="34" t="inlineStr">
-        <is>
-          <t>18th</t>
+          <t>15th</t>
+        </is>
+      </c>
+      <c r="I63" s="32" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="J63" s="36" t="inlineStr">
+        <is>
+          <t>26th</t>
         </is>
       </c>
       <c r="K63" s="32" t="n">
-        <v>5</v>
+        <v>7.4</v>
       </c>
       <c r="L63" s="32" t="n">
-        <v>4.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="M63" s="32" t="n">
-        <v>4.667</v>
+        <v>7.933</v>
       </c>
       <c r="N63" s="32" t="n">
-        <v>5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="O63" s="32" t="n">
-        <v>5.367</v>
+        <v>8.433</v>
       </c>
       <c r="P63" s="32" t="n">
-        <v>4.386</v>
+        <v>8.645</v>
       </c>
       <c r="Q63" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B64" s="32" t="n">
-        <v>8.802</v>
+        <v>0.605</v>
       </c>
       <c r="C64" s="32" t="n">
-        <v>8.766999999999999</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="D64" s="32" t="n">
-        <v>8.15</v>
+        <v>0.5</v>
       </c>
       <c r="E64" s="32" t="n">
-        <v>7.733</v>
+        <v>0.333</v>
       </c>
       <c r="F64" s="32" t="n">
-        <v>7.4</v>
+        <v>0.3</v>
       </c>
       <c r="G64" s="32" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="H64" s="36" t="inlineStr">
         <is>
-          <t>23rd</t>
+          <t>24th</t>
         </is>
       </c>
       <c r="I64" s="32" t="inlineStr"/>
       <c r="J64" s="33" t="inlineStr">
         <is>
-          <t>9th</t>
+          <t>4th</t>
         </is>
       </c>
       <c r="K64" s="32" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="L64" s="32" t="n">
-        <v>7.6</v>
+        <v>0.3</v>
       </c>
       <c r="M64" s="32" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="N64" s="32" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O64" s="32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P64" s="32" t="n">
+        <v>0.416</v>
+      </c>
+      <c r="Q64" s="35" t="inlineStr">
+        <is>
+          <t>Opp 1st Inn R/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="29" t="inlineStr">
+        <is>
+          <t>New York Mets offense vs Philadelphia Phillies defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B67" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C67" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D67" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E67" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F67" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G67" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H67" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I67" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J67" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K67" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L67" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M67" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N67" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O67" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P67" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q67" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B68" s="32" t="n">
+        <v>4.789</v>
+      </c>
+      <c r="C68" s="32" t="n">
+        <v>5.133</v>
+      </c>
+      <c r="D68" s="32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E68" s="32" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="F68" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="G68" s="32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H68" s="34" t="inlineStr">
+        <is>
+          <t>15th</t>
+        </is>
+      </c>
+      <c r="I68" s="32" t="inlineStr"/>
+      <c r="J68" s="33" t="inlineStr">
+        <is>
+          <t>4th</t>
+        </is>
+      </c>
+      <c r="K68" s="32" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="L68" s="32" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="M68" s="32" t="n">
+        <v>3.533</v>
+      </c>
+      <c r="N68" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="O68" s="32" t="n">
+        <v>3.767</v>
+      </c>
+      <c r="P68" s="32" t="n">
+        <v>4.052</v>
+      </c>
+      <c r="Q68" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="31" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B69" s="32" t="n">
+        <v>8.44</v>
+      </c>
+      <c r="C69" s="32" t="n">
+        <v>8.667</v>
+      </c>
+      <c r="D69" s="32" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="E69" s="32" t="n">
         <v>8.333</v>
       </c>
-      <c r="N64" s="32" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="O64" s="32" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="P64" s="32" t="n">
-        <v>8.211</v>
-      </c>
-      <c r="Q64" s="35" t="inlineStr">
+      <c r="F69" s="32" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="G69" s="32" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="H69" s="34" t="inlineStr">
+        <is>
+          <t>18th</t>
+        </is>
+      </c>
+      <c r="I69" s="32" t="inlineStr"/>
+      <c r="J69" s="33" t="inlineStr">
+        <is>
+          <t>4th</t>
+        </is>
+      </c>
+      <c r="K69" s="32" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="L69" s="32" t="n">
+        <v>7</v>
+      </c>
+      <c r="M69" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="N69" s="32" t="n">
+        <v>8.15</v>
+      </c>
+      <c r="O69" s="32" t="n">
+        <v>7.933</v>
+      </c>
+      <c r="P69" s="32" t="n">
+        <v>8.266999999999999</v>
+      </c>
+      <c r="Q69" s="35" t="inlineStr">
         <is>
           <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="31" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="31" t="inlineStr">
         <is>
           <t>HR/G</t>
         </is>
       </c>
-      <c r="B65" s="32" t="n">
-        <v>1.285</v>
-      </c>
-      <c r="C65" s="32" t="n">
-        <v>1.533</v>
-      </c>
-      <c r="D65" s="32" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="E65" s="32" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="F65" s="32" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G65" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="H65" s="36" t="inlineStr">
-        <is>
-          <t>21st</t>
-        </is>
-      </c>
-      <c r="I65" s="32" t="inlineStr"/>
-      <c r="J65" s="35" t="inlineStr">
+      <c r="B70" s="32" t="n">
+        <v>1.392</v>
+      </c>
+      <c r="C70" s="32" t="n">
+        <v>1.567</v>
+      </c>
+      <c r="D70" s="32" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="E70" s="32" t="n">
+        <v>1.667</v>
+      </c>
+      <c r="F70" s="32" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G70" s="32" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H70" s="34" t="inlineStr">
+        <is>
+          <t>13th</t>
+        </is>
+      </c>
+      <c r="I70" s="32" t="inlineStr"/>
+      <c r="J70" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K65" s="32" t="inlineStr">
+      <c r="K70" s="32" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L65" s="32" t="inlineStr">
+      <c r="L70" s="32" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M65" s="32" t="inlineStr">
+      <c r="M70" s="32" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N65" s="32" t="inlineStr">
+      <c r="N70" s="32" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="O65" s="32" t="inlineStr">
+      <c r="O70" s="32" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P65" s="32" t="inlineStr">
+      <c r="P70" s="32" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Q65" s="35" t="inlineStr">
+      <c r="Q70" s="35" t="inlineStr">
         <is>
           <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="31" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B66" s="32" t="n">
-        <v>8.273</v>
-      </c>
-      <c r="C66" s="32" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="D66" s="32" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="E66" s="32" t="n">
-        <v>9.933</v>
-      </c>
-      <c r="F66" s="32" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="G66" s="32" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="H66" s="34" t="inlineStr">
-        <is>
-          <t>15th</t>
-        </is>
-      </c>
-      <c r="I66" s="32" t="inlineStr">
-        <is>
-          <t>★★</t>
-        </is>
-      </c>
-      <c r="J66" s="36" t="inlineStr">
-        <is>
-          <t>26th</t>
-        </is>
-      </c>
-      <c r="K66" s="32" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="L66" s="32" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="M66" s="32" t="n">
-        <v>7.933</v>
-      </c>
-      <c r="N66" s="32" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="O66" s="32" t="n">
-        <v>8.433</v>
-      </c>
-      <c r="P66" s="32" t="n">
-        <v>8.645</v>
-      </c>
-      <c r="Q66" s="35" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B67" s="32" t="n">
-        <v>0.605</v>
-      </c>
-      <c r="C67" s="32" t="n">
-        <v>0.5669999999999999</v>
-      </c>
-      <c r="D67" s="32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E67" s="32" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="F67" s="32" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G67" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H67" s="36" t="inlineStr">
-        <is>
-          <t>24th</t>
-        </is>
-      </c>
-      <c r="I67" s="32" t="inlineStr"/>
-      <c r="J67" s="33" t="inlineStr">
-        <is>
-          <t>4th</t>
-        </is>
-      </c>
-      <c r="K67" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L67" s="32" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="M67" s="32" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="N67" s="32" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="O67" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="P67" s="32" t="n">
-        <v>0.416</v>
-      </c>
-      <c r="Q67" s="35" t="inlineStr">
-        <is>
-          <t>Opp 1st Inn R/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="29" t="inlineStr">
-        <is>
-          <t>New York Mets offense vs Philadelphia Phillies defense</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B70" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C70" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D70" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E70" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F70" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G70" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H70" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I70" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J70" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K70" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L70" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M70" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N70" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O70" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P70" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q70" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>4.789</v>
+        <v>8.199</v>
       </c>
       <c r="C71" s="32" t="n">
-        <v>5.133</v>
+        <v>8.9</v>
       </c>
       <c r="D71" s="32" t="n">
-        <v>4.2</v>
+        <v>9.6</v>
       </c>
       <c r="E71" s="32" t="n">
-        <v>4.8</v>
+        <v>8.867000000000001</v>
       </c>
       <c r="F71" s="32" t="n">
-        <v>5</v>
+        <v>8.6</v>
       </c>
       <c r="G71" s="32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="H71" s="34" t="inlineStr">
-        <is>
-          <t>15th</t>
+        <v>8.800000000000001</v>
+      </c>
+      <c r="H71" s="33" t="inlineStr">
+        <is>
+          <t>7th</t>
         </is>
       </c>
       <c r="I71" s="32" t="inlineStr"/>
       <c r="J71" s="33" t="inlineStr">
         <is>
-          <t>4th</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="K71" s="32" t="n">
-        <v>2.8</v>
+        <v>11.4</v>
       </c>
       <c r="L71" s="32" t="n">
-        <v>2.7</v>
+        <v>10.6</v>
       </c>
       <c r="M71" s="32" t="n">
-        <v>3.533</v>
+        <v>9.067</v>
       </c>
       <c r="N71" s="32" t="n">
-        <v>4</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="O71" s="32" t="n">
-        <v>3.767</v>
+        <v>8.867000000000001</v>
       </c>
       <c r="P71" s="32" t="n">
-        <v>4.052</v>
+        <v>9.058</v>
       </c>
       <c r="Q71" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B72" s="32" t="n">
-        <v>8.44</v>
+        <v>0.578</v>
       </c>
       <c r="C72" s="32" t="n">
-        <v>8.667</v>
+        <v>1</v>
       </c>
       <c r="D72" s="32" t="n">
-        <v>7.75</v>
+        <v>0.9</v>
       </c>
       <c r="E72" s="32" t="n">
-        <v>8.333</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="F72" s="32" t="n">
-        <v>8.300000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="G72" s="32" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="H72" s="34" t="inlineStr">
-        <is>
-          <t>18th</t>
+        <v>1</v>
+      </c>
+      <c r="H72" s="33" t="inlineStr">
+        <is>
+          <t>4th</t>
         </is>
       </c>
       <c r="I72" s="32" t="inlineStr"/>
       <c r="J72" s="33" t="inlineStr">
         <is>
-          <t>4th</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="K72" s="32" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="L72" s="32" t="n">
-        <v>7</v>
+        <v>0.1</v>
       </c>
       <c r="M72" s="32" t="n">
-        <v>8</v>
+        <v>0.333</v>
       </c>
       <c r="N72" s="32" t="n">
-        <v>8.15</v>
+        <v>0.65</v>
       </c>
       <c r="O72" s="32" t="n">
-        <v>7.933</v>
+        <v>0.833</v>
       </c>
       <c r="P72" s="32" t="n">
-        <v>8.266999999999999</v>
+        <v>0.407</v>
       </c>
       <c r="Q72" s="35" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="31" t="inlineStr">
-        <is>
-          <t>HR/G</t>
-        </is>
-      </c>
-      <c r="B73" s="32" t="n">
-        <v>1.392</v>
-      </c>
-      <c r="C73" s="32" t="n">
-        <v>1.567</v>
-      </c>
-      <c r="D73" s="32" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="E73" s="32" t="n">
-        <v>1.667</v>
-      </c>
-      <c r="F73" s="32" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="G73" s="32" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="H73" s="34" t="inlineStr">
-        <is>
-          <t>13th</t>
-        </is>
-      </c>
-      <c r="I73" s="32" t="inlineStr"/>
-      <c r="J73" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q73" s="35" t="inlineStr">
-        <is>
-          <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="31" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B74" s="32" t="n">
-        <v>8.199</v>
-      </c>
-      <c r="C74" s="32" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="D74" s="32" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="E74" s="32" t="n">
-        <v>8.867000000000001</v>
-      </c>
-      <c r="F74" s="32" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="G74" s="32" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="H74" s="33" t="inlineStr">
-        <is>
-          <t>7th</t>
-        </is>
-      </c>
-      <c r="I74" s="32" t="inlineStr"/>
-      <c r="J74" s="33" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="K74" s="32" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="L74" s="32" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="M74" s="32" t="n">
-        <v>9.067</v>
-      </c>
-      <c r="N74" s="32" t="n">
-        <v>8.949999999999999</v>
-      </c>
-      <c r="O74" s="32" t="n">
-        <v>8.867000000000001</v>
-      </c>
-      <c r="P74" s="32" t="n">
-        <v>9.058</v>
-      </c>
-      <c r="Q74" s="35" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B75" s="32" t="n">
-        <v>0.578</v>
-      </c>
-      <c r="C75" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="D75" s="32" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E75" s="32" t="n">
-        <v>0.9330000000000001</v>
-      </c>
-      <c r="F75" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="G75" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="H75" s="33" t="inlineStr">
-        <is>
-          <t>4th</t>
-        </is>
-      </c>
-      <c r="I75" s="32" t="inlineStr"/>
-      <c r="J75" s="33" t="inlineStr">
-        <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="K75" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L75" s="32" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="M75" s="32" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="N75" s="32" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="O75" s="32" t="n">
-        <v>0.833</v>
-      </c>
-      <c r="P75" s="32" t="n">
-        <v>0.407</v>
-      </c>
-      <c r="Q75" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -8132,13 +8132,13 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.7150000000000001</v>
+        <v>0.715</v>
       </c>
       <c r="G5" s="14" t="n">
         <v>-251</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -8194,17 +8194,17 @@
       </c>
       <c r="E6" s="20" t="inlineStr">
         <is>
-          <t>Over 176.5</t>
+          <t>Over 178</t>
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.6789058823529411</v>
+        <v>0.6423267326732672</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>-211</v>
+        <v>-180</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>-104</v>
+        <v>102</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -8228,7 +8228,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 67.9% (fair -211). Your call.</t>
+          <t>Model 64.2% (fair -180). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -8306,37 +8306,37 @@
     <row r="8">
       <c r="A8" s="20" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>Cincinnati Reds @ Pittsburgh Pirates</t>
+          <t>Portland Fire @ Washington Mystics</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>Over 164.5</t>
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.5525480769230769</v>
+        <v>0.6287809523809523</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>-123</v>
+        <v>-169</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>108</v>
+        <v>-110</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 55.3% (fair -123). Your call.</t>
+          <t>Model 62.9% (fair -169). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -8387,22 +8387,22 @@
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates +1.5</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.6929203125</v>
+        <v>0.5490995260663507</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>-226</v>
+        <v>-122</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>-156</v>
+        <v>111</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -8426,7 +8426,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 69.3% (fair -226). Your call.</t>
+          <t>Model 54.9% (fair -122). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -8438,37 +8438,37 @@
     <row r="10">
       <c r="A10" s="20" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>Seattle Mariners @ Cleveland Guardians</t>
+          <t>Houston Astros @ Detroit Tigers</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>Seattle Mariners</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.5615</v>
+        <v>0.5861388349514564</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-128</v>
+        <v>-142</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>100</v>
+        <v>-106</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -8492,7 +8492,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 56.1% (fair -128). Your call.</t>
+          <t>Model 58.6% (fair -142). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -8509,12 +8509,12 @@
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>Washington Nationals @ Baltimore Orioles</t>
+          <t>New York Liberty @ Golden State Valkyries</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
@@ -8524,17 +8524,17 @@
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>Baltimore Orioles</t>
+          <t>Golden State Valkyries</t>
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.6803671875</v>
+        <v>0.56855</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>-213</v>
+        <v>-132</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>-156</v>
+        <v>100</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -8558,7 +8558,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 68.0% (fair -213). Your call.</t>
+          <t>Model 56.9% (fair -132). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -8575,32 +8575,32 @@
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks @ Tampa Bay Rays</t>
+          <t>Cincinnati Reds @ Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>22:10</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks</t>
+          <t>Pittsburgh Pirates +1.5</t>
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.4650840336134454</v>
+        <v>0.6929203125</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>115</v>
+        <v>-226</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>138</v>
+        <v>-156</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -8624,7 +8624,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 46.5% (fair +115). Your call.</t>
+          <t>Model 69.3% (fair -226). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -8636,37 +8636,37 @@
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Kansas City Royals @ Chicago White Sox</t>
+          <t>Seattle Mariners @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox -1.5</t>
+          <t>Seattle Mariners</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.423923076923077</v>
+        <v>0.55905</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>136</v>
+        <v>-127</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -8690,7 +8690,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 42.4% (fair +136). Your call.</t>
+          <t>Model 55.9% (fair -127). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -8702,37 +8702,37 @@
     <row r="14">
       <c r="A14" s="20" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>Chicago Cubs @ Milwaukee Brewers</t>
+          <t>Washington Nationals @ Baltimore Orioles</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers -1.5</t>
+          <t>Baltimore Orioles</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.4519166666666667</v>
+        <v>0.6803671875</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>121</v>
+        <v>-213</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>140</v>
+        <v>-156</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -8756,7 +8756,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 45.2% (fair +121). Your call.</t>
+          <t>Model 68.0% (fair -213). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -8768,37 +8768,37 @@
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Seattle Mariners @ Cleveland Guardians</t>
+          <t>Las Vegas Aces @ Chicago Sky</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Seattle Mariners</t>
+          <t>Chicago Sky +7.5</t>
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.6167660944206009</v>
+        <v>0.5767615384615384</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>-161</v>
+        <v>-136</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>-133</v>
+        <v>-108</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -8822,7 +8822,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 61.7% (fair -161). Your call.</t>
+          <t>Model 57.7% (fair -136). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -8834,37 +8834,37 @@
     <row r="16">
       <c r="A16" s="20" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks @ Tampa Bay Rays</t>
+          <t>New York Liberty @ Golden State Valkyries</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>22:10</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks +1.5</t>
+          <t>Over 163.5</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.6481200000000001</v>
+        <v>0.5769238095238095</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>-184</v>
+        <v>-136</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>-150</v>
+        <v>-110</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -8888,7 +8888,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 64.8% (fair -184). Your call.</t>
+          <t>Model 57.7% (fair -136). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -8900,37 +8900,37 @@
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Texas Rangers @ Toronto Blue Jays</t>
+          <t>Seattle Mariners @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Texas Rangers</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.4636051502145923</v>
+        <v>0.5116509433962264</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>116</v>
+        <v>-105</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>133</v>
+        <v>112</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 46.4% (fair +116). Your call.</t>
+          <t>Model 51.2% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -8971,12 +8971,12 @@
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>Kansas City Royals @ Chicago White Sox</t>
+          <t>Texas Rangers @ Toronto Blue Jays</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -8986,17 +8986,17 @@
       </c>
       <c r="E18" s="20" t="inlineStr">
         <is>
-          <t>Chicago White Sox</t>
+          <t>Texas Rangers</t>
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.5913702702702703</v>
+        <v>0.4655364806866953</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>-145</v>
+        <v>115</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>-122</v>
+        <v>133</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -9020,7 +9020,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 59.1% (fair -145). Your call.</t>
+          <t>Model 46.6% (fair +115). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Washington Nationals @ Baltimore Orioles</t>
+          <t>Arizona Diamondbacks @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>23:05</t>
+          <t>22:10</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -9052,17 +9052,17 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Baltimore Orioles</t>
+          <t>Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.5570307692307692</v>
+        <v>0.4715652173913044</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>-126</v>
+        <v>112</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>-108</v>
+        <v>130</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -9086,7 +9086,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 55.7% (fair -126). Your call.</t>
+          <t>Model 47.2% (fair +112). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -9103,12 +9103,12 @@
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>Phoenix Mercury @ Toronto Tempo</t>
+          <t>Washington Nationals @ Baltimore Orioles</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>23:05</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -9118,17 +9118,17 @@
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Phoenix Mercury</t>
+          <t>Baltimore Orioles</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.3422364217252396</v>
+        <v>0.5523215686274509</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>192</v>
+        <v>-123</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>213</v>
+        <v>-104</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -9152,7 +9152,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 34.2% (fair +192). Your call.</t>
+          <t>Model 55.2% (fair -123). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -9179,22 +9179,22 @@
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers</t>
+          <t>Milwaukee Brewers -1.5</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.6334093117408908</v>
+        <v>0.4529411764705883</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>-173</v>
+        <v>121</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>-147</v>
+        <v>138</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -9218,7 +9218,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 63.3% (fair -173). Your call.</t>
+          <t>Model 45.3% (fair +121). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -9235,12 +9235,12 @@
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies @ New York Mets</t>
+          <t>Seattle Mariners @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -9250,17 +9250,17 @@
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies</t>
+          <t>Seattle Mariners</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.476891891891892</v>
+        <v>0.6171444444444445</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>110</v>
+        <v>-161</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>122</v>
+        <v>-134</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -9284,7 +9284,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 47.7% (fair +110). Your call.</t>
+          <t>Model 61.7% (fair -161). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -9296,37 +9296,37 @@
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies @ New York Mets</t>
+          <t>Kansas City Royals @ Chicago White Sox</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies +1.5</t>
+          <t>Chicago White Sox</t>
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.6622795620437956</v>
+        <v>0.5913702702702703</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>-196</v>
+        <v>-145</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>-174</v>
+        <v>-122</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -9350,7 +9350,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 66.2% (fair -196). Your call.</t>
+          <t>Model 59.1% (fair -145). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -9362,37 +9362,37 @@
     <row r="24">
       <c r="A24" s="20" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>New York Yankees @ Boston Red Sox</t>
+          <t>New York Liberty @ Golden State Valkyries</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
         <is>
-          <t>New York Yankees</t>
+          <t>Golden State Valkyries +1</t>
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.5405711538461537</v>
+        <v>0.5743046511627908</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>-118</v>
+        <v>-135</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>-108</v>
+        <v>-115</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -9416,7 +9416,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 54.1% (fair -118). Your call.</t>
+          <t>Model 57.4% (fair -135). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -9428,37 +9428,37 @@
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>Houston Astros @ Detroit Tigers</t>
+          <t>Arizona Diamondbacks @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>22:10</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Detroit Tigers</t>
+          <t>Arizona Diamondbacks +1.5</t>
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.4686936936936937</v>
+        <v>0.6537984375</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>113</v>
+        <v>-189</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>122</v>
+        <v>-156</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -9482,7 +9482,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 46.9% (fair +113). Your call.</t>
+          <t>Model 65.4% (fair -189). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -9494,37 +9494,37 @@
     <row r="26">
       <c r="A26" s="20" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Sparks @ Indiana Fever</t>
+          <t>Philadelphia Phillies @ New York Mets</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Sparks +7.5</t>
+          <t>Philadelphia Phillies</t>
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.5121287128712871</v>
+        <v>0.5869189189189189</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>-105</v>
+        <v>-142</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>102</v>
+        <v>-122</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 51.2% (fair -105). Your call.</t>
+          <t>Model 58.7% (fair -142). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -9565,32 +9565,32 @@
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>Texas Rangers @ Toronto Blue Jays</t>
+          <t>Chicago Cubs @ Milwaukee Brewers</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>19:07</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>Texas Rangers +1.5</t>
+          <t>Milwaukee Brewers</t>
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.5665306306306306</v>
+        <v>0.6330821138211382</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>-131</v>
+        <v>-173</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>-122</v>
+        <v>-146</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -9614,7 +9614,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 56.7% (fair -131). Your call.</t>
+          <t>Model 63.3% (fair -173). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -9626,17 +9626,17 @@
     <row r="28">
       <c r="A28" s="20" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>Chicago Cubs @ Milwaukee Brewers</t>
+          <t>Philadelphia Phillies @ New York Mets</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -9646,17 +9646,17 @@
       </c>
       <c r="E28" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers</t>
+          <t>Philadelphia Phillies</t>
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.61746</v>
+        <v>0.4770909090909091</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>-161</v>
+        <v>110</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>-150</v>
+        <v>120</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -9680,7 +9680,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 61.7% (fair -161). Your call.</t>
+          <t>Model 47.7% (fair +110). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -9697,32 +9697,32 @@
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>Atlanta Dream @ Seattle Storm</t>
+          <t>Philadelphia Phillies @ New York Mets</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>Atlanta Dream</t>
+          <t>Philadelphia Phillies +1.5</t>
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.7559532467532468</v>
+        <v>0.6617573529411764</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>-310</v>
+        <v>-196</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>-285</v>
+        <v>-172</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 75.6% (fair -310). Your call.</t>
+          <t>Model 66.2% (fair -196). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -10051,17 +10051,17 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Over 9</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.5043</v>
+        <v>0.5861388349514564</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-102</v>
+        <v>-142</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>120</v>
+        <v>-106</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -10085,7 +10085,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 50.4% (fair -102). Your call.</t>
+          <t>Model 58.6% (fair -142). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -10117,17 +10117,17 @@
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>Under 9</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.4957</v>
+        <v>0.4138461538461539</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>102</v>
+        <v>142</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -10151,7 +10151,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 49.6% (fair +102). Your call.</t>
+          <t>Model 41.4% (fair +142). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -10187,13 +10187,13 @@
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.3750375939849624</v>
+        <v>0.3746067415730337</v>
       </c>
       <c r="G9" s="14" t="n">
         <v>167</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -10253,7 +10253,7 @@
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.6249703703703704</v>
+        <v>0.625411111111111</v>
       </c>
       <c r="G10" s="14" t="n">
         <v>-167</v>
@@ -10319,13 +10319,13 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.5405711538461537</v>
+        <v>0.5340650485436893</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>-118</v>
+        <v>-115</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>-108</v>
+        <v>-106</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -10349,7 +10349,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 54.1% (fair -118). Your call.</t>
+          <t>Model 53.4% (fair -115). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -10385,13 +10385,13 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.4594366197183099</v>
+        <v>0.4659313725490196</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -10415,7 +10415,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 45.9% (fair +118). Your call.</t>
+          <t>Model 46.6% (fair +115). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -10523,7 +10523,7 @@
         <v>143</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -10589,7 +10589,7 @@
         <v>272</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>160</v>
+        <v>178</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -10655,7 +10655,7 @@
         <v>-272</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -10843,7 +10843,7 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Over 8</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
@@ -10853,7 +10853,7 @@
         <v>106</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -10909,7 +10909,7 @@
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Under 8</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
@@ -10979,13 +10979,13 @@
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.4334529147982063</v>
+        <v>0.4351363636363636</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -11009,7 +11009,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 43.3% (fair +131). Your call.</t>
+          <t>Model 43.5% (fair +130). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -11045,10 +11045,10 @@
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.5665306306306306</v>
+        <v>0.564827027027027</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-131</v>
+        <v>-130</v>
       </c>
       <c r="H22" s="15" t="n">
         <v>-122</v>
@@ -11075,7 +11075,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 56.7% (fair -131). Your call.</t>
+          <t>Model 56.5% (fair -130). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -11111,13 +11111,13 @@
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.4474730769230769</v>
+        <v>0.4508914691943128</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>-108</v>
+        <v>-111</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -11141,7 +11141,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 44.7% (fair +123). Your call.</t>
+          <t>Model 45.1% (fair +122). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -11177,13 +11177,13 @@
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.5525480769230769</v>
+        <v>0.5490995260663507</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>-123</v>
+        <v>-122</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -11207,7 +11207,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 55.3% (fair -123). Your call.</t>
+          <t>Model 54.9% (fair -122). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -11239,7 +11239,7 @@
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Over 8</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F25" s="13" t="n">
@@ -11249,7 +11249,7 @@
         <v>-189</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -11305,7 +11305,7 @@
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
-          <t>Under 8</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F26" s="13" t="n">
@@ -11507,13 +11507,13 @@
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.476891891891892</v>
+        <v>0.4770909090909091</v>
       </c>
       <c r="G29" s="14" t="n">
         <v>110</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -11573,13 +11573,13 @@
         </is>
       </c>
       <c r="F30" s="13" t="n">
-        <v>0.5230909090909091</v>
+        <v>0.5228963963963964</v>
       </c>
       <c r="G30" s="14" t="n">
         <v>-110</v>
       </c>
       <c r="H30" s="15" t="n">
-        <v>-120</v>
+        <v>-122</v>
       </c>
       <c r="I30" s="13">
         <f>IF($H$30="","",IF($H$30&lt;0,-$H$30/(-$H$30+100),100/($H$30+100)))</f>
@@ -11771,7 +11771,7 @@
         </is>
       </c>
       <c r="F33" s="13" t="n">
-        <v>0.3377407407407407</v>
+        <v>0.3382222222222222</v>
       </c>
       <c r="G33" s="14" t="n">
         <v>196</v>
@@ -11837,13 +11837,13 @@
         </is>
       </c>
       <c r="F34" s="13" t="n">
-        <v>0.6622795620437956</v>
+        <v>0.6617573529411764</v>
       </c>
       <c r="G34" s="14" t="n">
         <v>-196</v>
       </c>
       <c r="H34" s="15" t="n">
-        <v>-174</v>
+        <v>-172</v>
       </c>
       <c r="I34" s="13">
         <f>IF($H$34="","",IF($H$34&lt;0,-$H$34/(-$H$34+100),100/($H$34+100)))</f>
@@ -11909,7 +11909,7 @@
         <v>186</v>
       </c>
       <c r="H35" s="15" t="n">
-        <v>130</v>
+        <v>117</v>
       </c>
       <c r="I35" s="13">
         <f>IF($H$35="","",IF($H$35&lt;0,-$H$35/(-$H$35+100),100/($H$35+100)))</f>
@@ -11975,7 +11975,7 @@
         <v>-186</v>
       </c>
       <c r="H36" s="15" t="n">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="I36" s="13">
         <f>IF($H$36="","",IF($H$36&lt;0,-$H$36/(-$H$36+100),100/($H$36+100)))</f>
@@ -12107,7 +12107,7 @@
         <v>196</v>
       </c>
       <c r="H38" s="15" t="n">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="I38" s="13">
         <f>IF($H$38="","",IF($H$38&lt;0,-$H$38/(-$H$38+100),100/($H$38+100)))</f>
@@ -12167,13 +12167,13 @@
         </is>
       </c>
       <c r="F39" s="13" t="n">
-        <v>0.423923076923077</v>
+        <v>0.4649</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>136</v>
+        <v>115</v>
       </c>
       <c r="H39" s="15" t="n">
-        <v>160</v>
+        <v>178</v>
       </c>
       <c r="I39" s="13">
         <f>IF($H$39="","",IF($H$39&lt;0,-$H$39/(-$H$39+100),100/($H$39+100)))</f>
@@ -12197,7 +12197,7 @@
       </c>
       <c r="N39" s="19" t="inlineStr">
         <is>
-          <t>Model 42.4% (fair +136). Your call.</t>
+          <t>Model 46.5% (fair +115). Your call.</t>
         </is>
       </c>
       <c r="O39" s="15" t="n"/>
@@ -12233,13 +12233,13 @@
         </is>
       </c>
       <c r="F40" s="13" t="n">
-        <v>0.5760779467680608</v>
+        <v>0.5351</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>-136</v>
+        <v>-115</v>
       </c>
       <c r="H40" s="15" t="n">
-        <v>-163</v>
+        <v>176</v>
       </c>
       <c r="I40" s="13">
         <f>IF($H$40="","",IF($H$40&lt;0,-$H$40/(-$H$40+100),100/($H$40+100)))</f>
@@ -12263,7 +12263,7 @@
       </c>
       <c r="N40" s="19" t="inlineStr">
         <is>
-          <t>Model 57.6% (fair -136). Your call.</t>
+          <t>Model 53.5% (fair -115). Your call.</t>
         </is>
       </c>
       <c r="O40" s="15" t="n"/>
@@ -12299,13 +12299,13 @@
         </is>
       </c>
       <c r="F41" s="13" t="n">
-        <v>0.4650840336134454</v>
+        <v>0.4715652173913044</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="H41" s="15" t="n">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="I41" s="13">
         <f>IF($H$41="","",IF($H$41&lt;0,-$H$41/(-$H$41+100),100/($H$41+100)))</f>
@@ -12329,7 +12329,7 @@
       </c>
       <c r="N41" s="19" t="inlineStr">
         <is>
-          <t>Model 46.5% (fair +115). Your call.</t>
+          <t>Model 47.2% (fair +112). Your call.</t>
         </is>
       </c>
       <c r="O41" s="15" t="n"/>
@@ -12365,13 +12365,13 @@
         </is>
       </c>
       <c r="F42" s="13" t="n">
-        <v>0.5348949579831932</v>
+        <v>0.528398275862069</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>-115</v>
+        <v>-112</v>
       </c>
       <c r="H42" s="15" t="n">
-        <v>-138</v>
+        <v>-132</v>
       </c>
       <c r="I42" s="13">
         <f>IF($H$42="","",IF($H$42&lt;0,-$H$42/(-$H$42+100),100/($H$42+100)))</f>
@@ -12395,7 +12395,7 @@
       </c>
       <c r="N42" s="19" t="inlineStr">
         <is>
-          <t>Model 53.5% (fair -115). Your call.</t>
+          <t>Model 52.8% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O42" s="15" t="n"/>
@@ -12437,7 +12437,7 @@
         <v>-101</v>
       </c>
       <c r="H43" s="15" t="n">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="I43" s="13">
         <f>IF($H$43="","",IF($H$43&lt;0,-$H$43/(-$H$43+100),100/($H$43+100)))</f>
@@ -12503,7 +12503,7 @@
         <v>101</v>
       </c>
       <c r="H44" s="15" t="n">
-        <v>-104</v>
+        <v>124</v>
       </c>
       <c r="I44" s="13">
         <f>IF($H$44="","",IF($H$44&lt;0,-$H$44/(-$H$44+100),100/($H$44+100)))</f>
@@ -12563,13 +12563,13 @@
         </is>
       </c>
       <c r="F45" s="13" t="n">
-        <v>0.3518623481781377</v>
+        <v>0.3461960784313726</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="H45" s="15" t="n">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="I45" s="13">
         <f>IF($H$45="","",IF($H$45&lt;0,-$H$45/(-$H$45+100),100/($H$45+100)))</f>
@@ -12593,7 +12593,7 @@
       </c>
       <c r="N45" s="19" t="inlineStr">
         <is>
-          <t>Model 35.2% (fair +184). Your call.</t>
+          <t>Model 34.6% (fair +189). Your call.</t>
         </is>
       </c>
       <c r="O45" s="15" t="n"/>
@@ -12629,13 +12629,13 @@
         </is>
       </c>
       <c r="F46" s="13" t="n">
-        <v>0.6481200000000001</v>
+        <v>0.6537984375</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>-184</v>
+        <v>-189</v>
       </c>
       <c r="H46" s="15" t="n">
-        <v>-150</v>
+        <v>-156</v>
       </c>
       <c r="I46" s="13">
         <f>IF($H$46="","",IF($H$46&lt;0,-$H$46/(-$H$46+100),100/($H$46+100)))</f>
@@ -12659,7 +12659,7 @@
       </c>
       <c r="N46" s="19" t="inlineStr">
         <is>
-          <t>Model 64.8% (fair -184). Your call.</t>
+          <t>Model 65.4% (fair -189). Your call.</t>
         </is>
       </c>
       <c r="O46" s="15" t="n"/>
@@ -12695,13 +12695,13 @@
         </is>
       </c>
       <c r="F47" s="13" t="n">
-        <v>0.4429807692307692</v>
+        <v>0.4476960784313725</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="H47" s="15" t="n">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="I47" s="13">
         <f>IF($H$47="","",IF($H$47&lt;0,-$H$47/(-$H$47+100),100/($H$47+100)))</f>
@@ -12725,7 +12725,7 @@
       </c>
       <c r="N47" s="19" t="inlineStr">
         <is>
-          <t>Model 44.3% (fair +126). Your call.</t>
+          <t>Model 44.8% (fair +123). Your call.</t>
         </is>
       </c>
       <c r="O47" s="15" t="n"/>
@@ -12761,13 +12761,13 @@
         </is>
       </c>
       <c r="F48" s="13" t="n">
-        <v>0.5570307692307692</v>
+        <v>0.5523215686274509</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>-126</v>
+        <v>-123</v>
       </c>
       <c r="H48" s="15" t="n">
-        <v>-108</v>
+        <v>-104</v>
       </c>
       <c r="I48" s="13">
         <f>IF($H$48="","",IF($H$48&lt;0,-$H$48/(-$H$48+100),100/($H$48+100)))</f>
@@ -12791,7 +12791,7 @@
       </c>
       <c r="N48" s="19" t="inlineStr">
         <is>
-          <t>Model 55.7% (fair -126). Your call.</t>
+          <t>Model 55.2% (fair -123). Your call.</t>
         </is>
       </c>
       <c r="O48" s="15" t="n"/>
@@ -12833,7 +12833,7 @@
         <v>-146</v>
       </c>
       <c r="H49" s="15" t="n">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="I49" s="13">
         <f>IF($H$49="","",IF($H$49&lt;0,-$H$49/(-$H$49+100),100/($H$49+100)))</f>
@@ -13031,7 +13031,7 @@
         <v>-138</v>
       </c>
       <c r="H52" s="15" t="n">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="I52" s="13">
         <f>IF($H$52="","",IF($H$52&lt;0,-$H$52/(-$H$52+100),100/($H$52+100)))</f>
@@ -13091,13 +13091,13 @@
         </is>
       </c>
       <c r="F53" s="13" t="n">
-        <v>0.6167660944206009</v>
+        <v>0.6171444444444445</v>
       </c>
       <c r="G53" s="14" t="n">
         <v>-161</v>
       </c>
       <c r="H53" s="15" t="n">
-        <v>-133</v>
+        <v>-134</v>
       </c>
       <c r="I53" s="13">
         <f>IF($H$53="","",IF($H$53&lt;0,-$H$53/(-$H$53+100),100/($H$53+100)))</f>
@@ -13157,7 +13157,7 @@
         </is>
       </c>
       <c r="F54" s="13" t="n">
-        <v>0.3832618025751073</v>
+        <v>0.3828326180257511</v>
       </c>
       <c r="G54" s="14" t="n">
         <v>161</v>
@@ -13219,17 +13219,17 @@
       </c>
       <c r="E55" s="12" t="inlineStr">
         <is>
-          <t>Over 8</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F55" s="13" t="n">
-        <v>0.4363</v>
+        <v>0.5116509433962264</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>129</v>
+        <v>-105</v>
       </c>
       <c r="H55" s="15" t="n">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="I55" s="13">
         <f>IF($H$55="","",IF($H$55&lt;0,-$H$55/(-$H$55+100),100/($H$55+100)))</f>
@@ -13253,7 +13253,7 @@
       </c>
       <c r="N55" s="19" t="inlineStr">
         <is>
-          <t>Model 43.6% (fair +129). Your call.</t>
+          <t>Model 51.2% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O55" s="15" t="n"/>
@@ -13285,14 +13285,14 @@
       </c>
       <c r="E56" s="20" t="inlineStr">
         <is>
-          <t>Under 8</t>
+          <t>Under 7.5</t>
         </is>
       </c>
       <c r="F56" s="13" t="n">
-        <v>0.5637</v>
+        <v>0.4883365384615385</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>-129</v>
+        <v>105</v>
       </c>
       <c r="H56" s="15" t="n">
         <v>-108</v>
@@ -13319,7 +13319,7 @@
       </c>
       <c r="N56" s="19" t="inlineStr">
         <is>
-          <t>Model 56.4% (fair -129). Your call.</t>
+          <t>Model 48.8% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O56" s="15" t="n"/>
@@ -13615,7 +13615,7 @@
         </is>
       </c>
       <c r="F61" s="13" t="n">
-        <v>0.36656</v>
+        <v>0.36692</v>
       </c>
       <c r="G61" s="14" t="n">
         <v>173</v>
@@ -13681,13 +13681,13 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>0.6334093117408908</v>
+        <v>0.6330821138211382</v>
       </c>
       <c r="G62" s="14" t="n">
         <v>-173</v>
       </c>
       <c r="H62" s="15" t="n">
-        <v>-147</v>
+        <v>-146</v>
       </c>
       <c r="I62" s="13">
         <f>IF($H$62="","",IF($H$62&lt;0,-$H$62/(-$H$62+100),100/($H$62+100)))</f>
@@ -13819,7 +13819,7 @@
         <v>167</v>
       </c>
       <c r="H64" s="15" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="I64" s="13">
         <f>IF($H$64="","",IF($H$64&lt;0,-$H$64/(-$H$64+100),100/($H$64+100)))</f>
@@ -13879,13 +13879,13 @@
         </is>
       </c>
       <c r="F65" s="13" t="n">
-        <v>0.4519166666666667</v>
+        <v>0.4529411764705883</v>
       </c>
       <c r="G65" s="14" t="n">
         <v>121</v>
       </c>
       <c r="H65" s="15" t="n">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I65" s="13">
         <f>IF($H$65="","",IF($H$65&lt;0,-$H$65/(-$H$65+100),100/($H$65+100)))</f>
@@ -13909,7 +13909,7 @@
       </c>
       <c r="N65" s="19" t="inlineStr">
         <is>
-          <t>Model 45.2% (fair +121). Your call.</t>
+          <t>Model 45.3% (fair +121). Your call.</t>
         </is>
       </c>
       <c r="O65" s="15" t="n"/>
@@ -13945,7 +13945,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>0.5480571428571428</v>
+        <v>0.5470714285714285</v>
       </c>
       <c r="G66" s="14" t="n">
         <v>-121</v>
@@ -13975,7 +13975,7 @@
       </c>
       <c r="N66" s="19" t="inlineStr">
         <is>
-          <t>Model 54.8% (fair -121). Your call.</t>
+          <t>Model 54.7% (fair -121). Your call.</t>
         </is>
       </c>
       <c r="O66" s="15" t="n"/>
@@ -14787,10 +14787,10 @@
         </is>
       </c>
       <c r="F79" s="13" t="n">
-        <v>0.4636051502145923</v>
+        <v>0.4655364806866953</v>
       </c>
       <c r="G79" s="14" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H79" s="15" t="n">
         <v>133</v>
@@ -14817,7 +14817,7 @@
       </c>
       <c r="N79" s="19" t="inlineStr">
         <is>
-          <t>Model 46.4% (fair +116). Your call.</t>
+          <t>Model 46.6% (fair +115). Your call.</t>
         </is>
       </c>
       <c r="O79" s="15" t="n"/>
@@ -14853,13 +14853,13 @@
         </is>
       </c>
       <c r="F80" s="13" t="n">
-        <v>0.5364025210084034</v>
+        <v>0.5344545064377683</v>
       </c>
       <c r="G80" s="14" t="n">
-        <v>-116</v>
+        <v>-115</v>
       </c>
       <c r="H80" s="15" t="n">
-        <v>-138</v>
+        <v>-133</v>
       </c>
       <c r="I80" s="13">
         <f>IF($H$80="","",IF($H$80&lt;0,-$H$80/(-$H$80+100),100/($H$80+100)))</f>
@@ -14883,7 +14883,7 @@
       </c>
       <c r="N80" s="19" t="inlineStr">
         <is>
-          <t>Model 53.6% (fair -116). Your call.</t>
+          <t>Model 53.4% (fair -115). Your call.</t>
         </is>
       </c>
       <c r="O80" s="15" t="n"/>
@@ -14919,13 +14919,13 @@
         </is>
       </c>
       <c r="F81" s="13" t="n">
-        <v>0.5313045045045045</v>
+        <v>0.5364207373271889</v>
       </c>
       <c r="G81" s="14" t="n">
-        <v>-113</v>
+        <v>-116</v>
       </c>
       <c r="H81" s="15" t="n">
-        <v>-122</v>
+        <v>-117</v>
       </c>
       <c r="I81" s="13">
         <f>IF($H$81="","",IF($H$81&lt;0,-$H$81/(-$H$81+100),100/($H$81+100)))</f>
@@ -14949,7 +14949,7 @@
       </c>
       <c r="N81" s="19" t="inlineStr">
         <is>
-          <t>Model 53.1% (fair -113). Your call.</t>
+          <t>Model 53.6% (fair -116). Your call.</t>
         </is>
       </c>
       <c r="O81" s="15" t="n"/>
@@ -14985,10 +14985,10 @@
         </is>
       </c>
       <c r="F82" s="13" t="n">
-        <v>0.4686936936936937</v>
+        <v>0.4636036036036036</v>
       </c>
       <c r="G82" s="14" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="H82" s="15" t="n">
         <v>122</v>
@@ -15015,7 +15015,7 @@
       </c>
       <c r="N82" s="19" t="inlineStr">
         <is>
-          <t>Model 46.9% (fair +113). Your call.</t>
+          <t>Model 46.4% (fair +116). Your call.</t>
         </is>
       </c>
       <c r="O82" s="15" t="n"/>
@@ -15051,10 +15051,10 @@
         </is>
       </c>
       <c r="F83" s="13" t="n">
-        <v>0.5615</v>
+        <v>0.55905</v>
       </c>
       <c r="G83" s="14" t="n">
-        <v>-128</v>
+        <v>-127</v>
       </c>
       <c r="H83" s="15" t="n">
         <v>100</v>
@@ -15081,7 +15081,7 @@
       </c>
       <c r="N83" s="19" t="inlineStr">
         <is>
-          <t>Model 56.1% (fair -128). Your call.</t>
+          <t>Model 55.9% (fair -127). Your call.</t>
         </is>
       </c>
       <c r="O83" s="15" t="n"/>
@@ -15117,13 +15117,13 @@
         </is>
       </c>
       <c r="F84" s="13" t="n">
-        <v>0.4385</v>
+        <v>0.4409294117647058</v>
       </c>
       <c r="G84" s="14" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H84" s="15" t="n">
-        <v>100</v>
+        <v>-104</v>
       </c>
       <c r="I84" s="13">
         <f>IF($H$84="","",IF($H$84&lt;0,-$H$84/(-$H$84+100),100/($H$84+100)))</f>
@@ -15147,7 +15147,7 @@
       </c>
       <c r="N84" s="19" t="inlineStr">
         <is>
-          <t>Model 43.9% (fair +128). Your call.</t>
+          <t>Model 44.1% (fair +127). Your call.</t>
         </is>
       </c>
       <c r="O84" s="15" t="n"/>
@@ -15315,13 +15315,13 @@
         </is>
       </c>
       <c r="F87" s="13" t="n">
-        <v>0.6188</v>
+        <v>0.5869189189189189</v>
       </c>
       <c r="G87" s="14" t="n">
-        <v>-162</v>
+        <v>-142</v>
       </c>
       <c r="H87" s="15" t="n">
-        <v>-117</v>
+        <v>-122</v>
       </c>
       <c r="I87" s="13">
         <f>IF($H$87="","",IF($H$87&lt;0,-$H$87/(-$H$87+100),100/($H$87+100)))</f>
@@ -15345,7 +15345,7 @@
       </c>
       <c r="N87" s="19" t="inlineStr">
         <is>
-          <t>Model 61.9% (fair -162). Your call.</t>
+          <t>Model 58.7% (fair -142). Your call.</t>
         </is>
       </c>
       <c r="O87" s="15" t="n"/>
@@ -15381,10 +15381,10 @@
         </is>
       </c>
       <c r="F88" s="13" t="n">
-        <v>0.3812</v>
+        <v>0.4130837004405286</v>
       </c>
       <c r="G88" s="14" t="n">
-        <v>162</v>
+        <v>142</v>
       </c>
       <c r="H88" s="15" t="n">
         <v>127</v>
@@ -15411,7 +15411,7 @@
       </c>
       <c r="N88" s="19" t="inlineStr">
         <is>
-          <t>Model 38.1% (fair +162). Your call.</t>
+          <t>Model 41.3% (fair +142). Your call.</t>
         </is>
       </c>
       <c r="O88" s="15" t="n"/>
@@ -15447,13 +15447,13 @@
         </is>
       </c>
       <c r="F89" s="13" t="n">
-        <v>0.4251072961373391</v>
+        <v>0.4225210084033614</v>
       </c>
       <c r="G89" s="14" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H89" s="15" t="n">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="I89" s="13">
         <f>IF($H$89="","",IF($H$89&lt;0,-$H$89/(-$H$89+100),100/($H$89+100)))</f>
@@ -15477,7 +15477,7 @@
       </c>
       <c r="N89" s="19" t="inlineStr">
         <is>
-          <t>Model 42.5% (fair +135). Your call.</t>
+          <t>Model 42.3% (fair +137). Your call.</t>
         </is>
       </c>
       <c r="O89" s="15" t="n"/>
@@ -15513,10 +15513,10 @@
         </is>
       </c>
       <c r="F90" s="13" t="n">
-        <v>0.5749033613445378</v>
+        <v>0.5774546218487394</v>
       </c>
       <c r="G90" s="14" t="n">
-        <v>-135</v>
+        <v>-137</v>
       </c>
       <c r="H90" s="15" t="n">
         <v>-138</v>
@@ -15543,7 +15543,7 @@
       </c>
       <c r="N90" s="19" t="inlineStr">
         <is>
-          <t>Model 57.5% (fair -135). Your call.</t>
+          <t>Model 57.7% (fair -137). Your call.</t>
         </is>
       </c>
       <c r="O90" s="15" t="n"/>
@@ -15711,13 +15711,13 @@
         </is>
       </c>
       <c r="F93" s="13" t="n">
-        <v>0.3825409836065574</v>
+        <v>0.3796</v>
       </c>
       <c r="G93" s="14" t="n">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="H93" s="15" t="n">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="I93" s="13">
         <f>IF($H$93="","",IF($H$93&lt;0,-$H$93/(-$H$93+100),100/($H$93+100)))</f>
@@ -15741,7 +15741,7 @@
       </c>
       <c r="N93" s="19" t="inlineStr">
         <is>
-          <t>Model 38.3% (fair +161). Your call.</t>
+          <t>Model 38.0% (fair +163). Your call.</t>
         </is>
       </c>
       <c r="O93" s="15" t="n"/>
@@ -15777,10 +15777,10 @@
         </is>
       </c>
       <c r="F94" s="13" t="n">
-        <v>0.61746</v>
+        <v>0.6204000000000001</v>
       </c>
       <c r="G94" s="14" t="n">
-        <v>-161</v>
+        <v>-163</v>
       </c>
       <c r="H94" s="15" t="n">
         <v>-150</v>
@@ -15807,7 +15807,7 @@
       </c>
       <c r="N94" s="19" t="inlineStr">
         <is>
-          <t>Model 61.7% (fair -161). Your call.</t>
+          <t>Model 62.0% (fair -163). Your call.</t>
         </is>
       </c>
       <c r="O94" s="15" t="n"/>
@@ -16482,7 +16482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P22"/>
+  <dimension ref="A1:P46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -16626,13 +16626,13 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.3422364217252396</v>
+        <v>0.3525850340136054</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>213</v>
+        <v>194</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -16656,7 +16656,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 34.2% (fair +192). Your call.</t>
+          <t>Model 35.3% (fair +184). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -16692,13 +16692,13 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.657782108626198</v>
+        <v>0.6474585034013606</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>-192</v>
+        <v>-184</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>-213</v>
+        <v>-194</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -16722,7 +16722,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 65.8% (fair -192). Your call.</t>
+          <t>Model 64.7% (fair -184). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -16754,17 +16754,17 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Over 176.5</t>
+          <t>Over 178</t>
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.6789058823529411</v>
+        <v>0.6423267326732672</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-211</v>
+        <v>-180</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>-104</v>
+        <v>102</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -16788,7 +16788,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 67.9% (fair -211). Your call.</t>
+          <t>Model 64.2% (fair -180). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -16820,17 +16820,17 @@
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>Under 176.5</t>
+          <t>Under 178</t>
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.3211000000000001</v>
+        <v>0.3577</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>211</v>
+        <v>180</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>-104</v>
+        <v>102</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -16854,7 +16854,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 32.1% (fair +211). Your call.</t>
+          <t>Model 35.8% (fair +180). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -16896,7 +16896,7 @@
         <v>129</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -16962,7 +16962,7 @@
         <v>-129</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -17022,13 +17022,13 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.2901139601139601</v>
+        <v>0.2918840579710145</v>
       </c>
       <c r="G11" s="14" t="n">
+        <v>243</v>
+      </c>
+      <c r="H11" s="15" t="n">
         <v>245</v>
-      </c>
-      <c r="H11" s="15" t="n">
-        <v>251</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -17052,7 +17052,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 29.0% (fair +245). Your call.</t>
+          <t>Model 29.2% (fair +243). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -17088,10 +17088,10 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.7099058823529412</v>
+        <v>0.7080705882352941</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>-245</v>
+        <v>-243</v>
       </c>
       <c r="H12" s="15" t="n">
         <v>-240</v>
@@ -17118,7 +17118,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 71.0% (fair -245). Your call.</t>
+          <t>Model 70.8% (fair -243). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -17154,13 +17154,13 @@
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.7150000000000001</v>
+        <v>0.715</v>
       </c>
       <c r="G13" s="14" t="n">
         <v>-251</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -17226,7 +17226,7 @@
         <v>251</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -17282,17 +17282,17 @@
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Indiana Fever -7.5</t>
+          <t>Indiana Fever -6.5</t>
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.4878712871287129</v>
+        <v>0.5101098039215686</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>105</v>
+        <v>-104</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>102</v>
+        <v>-104</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -17316,7 +17316,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 48.8% (fair +105). Your call.</t>
+          <t>Model 51.0% (fair -104). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -17348,17 +17348,17 @@
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Sparks +7.5</t>
+          <t>Los Angeles Sparks +6.5</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.5121287128712871</v>
+        <v>0.4899019607843137</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>-105</v>
+        <v>104</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -17382,7 +17382,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 51.2% (fair -105). Your call.</t>
+          <t>Model 49.0% (fair +104). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -17418,13 +17418,13 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.7559532467532468</v>
+        <v>0.7488246575342467</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>-310</v>
+        <v>-298</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>-285</v>
+        <v>-265</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -17448,7 +17448,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 75.6% (fair -310). Your call.</t>
+          <t>Model 74.9% (fair -298). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -17484,13 +17484,13 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.2440779220779221</v>
+        <v>0.2511780821917808</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>310</v>
+        <v>298</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>285</v>
+        <v>265</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -17514,7 +17514,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 24.4% (fair +310). Your call.</t>
+          <t>Model 25.1% (fair +298). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -17546,17 +17546,17 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Over 176.5</t>
+          <t>Over 178</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.3294862745098039</v>
+        <v>0.2941584158415842</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>204</v>
+        <v>240</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>-104</v>
+        <v>102</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -17580,7 +17580,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 32.9% (fair +204). Your call.</t>
+          <t>Model 29.4% (fair +240). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -17612,17 +17612,17 @@
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Under 176.5</t>
+          <t>Under 178</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.6705</v>
+        <v>0.7059</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>-203</v>
+        <v>-240</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>-104</v>
+        <v>102</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -17646,7 +17646,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 67.0% (fair -203). Your call.</t>
+          <t>Model 70.6% (fair -240). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -17678,17 +17678,17 @@
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Seattle Storm -4</t>
+          <t>Seattle Storm -4.5</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.1973</v>
+        <v>0.1855</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>407</v>
+        <v>439</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>410</v>
+        <v>370</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -17712,7 +17712,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 19.7% (fair +407). Your call.</t>
+          <t>Model 18.6% (fair +439). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -17744,17 +17744,17 @@
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>Atlanta Dream +4</t>
+          <t>Atlanta Dream +4.5</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.8027</v>
+        <v>0.8145</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-407</v>
+        <v>-439</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -17778,7 +17778,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 80.3% (fair -407). Your call.</t>
+          <t>Model 81.5% (fair -439). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -17787,9 +17787,1593 @@
         <v/>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>Minnesota Lynx @ Dallas Wings</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E23" s="12" t="inlineStr">
+        <is>
+          <t>Minnesota Lynx</t>
+        </is>
+      </c>
+      <c r="F23" s="13" t="n">
+        <v>0.6240117647058824</v>
+      </c>
+      <c r="G23" s="14" t="n">
+        <v>-166</v>
+      </c>
+      <c r="H23" s="15" t="n">
+        <v>-155</v>
+      </c>
+      <c r="I23" s="13">
+        <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
+        <v/>
+      </c>
+      <c r="J23" s="16">
+        <f>IF($H$23="","",$F$23*IF($H$23&lt;0,-100/$H$23,$H$23/100)-(1-$F$23))</f>
+        <v/>
+      </c>
+      <c r="K23" s="17">
+        <f>IF($H$23="","",MAX(0,($F$23*IF($H$23&lt;0,-100/$H$23,$H$23/100)-(1-$F$23))/IF($H$23&lt;0,-100/$H$23,$H$23/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L23" s="18">
+        <f>IF($H$23="","",ROUND(MIN($K$23,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M23" s="12">
+        <f>IF($J$23="","",IF($J$23&lt;0,"Pass",IF($J$23&lt;'Settings'!$B$4,"Thin",IF($J$23&lt;0.06,"✅ Sharp band",IF($J$23&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N23" s="19" t="inlineStr">
+        <is>
+          <t>Model 62.4% (fair -166). Your call.</t>
+        </is>
+      </c>
+      <c r="O23" s="15" t="n"/>
+      <c r="P23" s="16">
+        <f>IF(OR($H$23="",$O$23=""),"",(1+IF($H$23&lt;0,-100/$H$23,$H$23/100))/(1+IF($O$23&lt;0,-100/$O$23,$O$23/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>Minnesota Lynx @ Dallas Wings</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E24" s="20" t="inlineStr">
+        <is>
+          <t>Dallas Wings</t>
+        </is>
+      </c>
+      <c r="F24" s="13" t="n">
+        <v>0.376015625</v>
+      </c>
+      <c r="G24" s="14" t="n">
+        <v>166</v>
+      </c>
+      <c r="H24" s="15" t="n">
+        <v>156</v>
+      </c>
+      <c r="I24" s="13">
+        <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
+        <v/>
+      </c>
+      <c r="J24" s="16">
+        <f>IF($H$24="","",$F$24*IF($H$24&lt;0,-100/$H$24,$H$24/100)-(1-$F$24))</f>
+        <v/>
+      </c>
+      <c r="K24" s="17">
+        <f>IF($H$24="","",MAX(0,($F$24*IF($H$24&lt;0,-100/$H$24,$H$24/100)-(1-$F$24))/IF($H$24&lt;0,-100/$H$24,$H$24/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L24" s="18">
+        <f>IF($H$24="","",ROUND(MIN($K$24,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M24" s="12">
+        <f>IF($J$24="","",IF($J$24&lt;0,"Pass",IF($J$24&lt;'Settings'!$B$4,"Thin",IF($J$24&lt;0.06,"✅ Sharp band",IF($J$24&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N24" s="19" t="inlineStr">
+        <is>
+          <t>Model 37.6% (fair +166). Your call.</t>
+        </is>
+      </c>
+      <c r="O24" s="15" t="n"/>
+      <c r="P24" s="16">
+        <f>IF(OR($H$24="",$O$24=""),"",(1+IF($H$24&lt;0,-100/$H$24,$H$24/100))/(1+IF($O$24&lt;0,-100/$O$24,$O$24/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>Minnesota Lynx @ Dallas Wings</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E25" s="12" t="inlineStr">
+        <is>
+          <t>Over 178.5</t>
+        </is>
+      </c>
+      <c r="F25" s="13" t="n">
+        <v>0.3843921568627451</v>
+      </c>
+      <c r="G25" s="14" t="n">
+        <v>160</v>
+      </c>
+      <c r="H25" s="15" t="n">
+        <v>-104</v>
+      </c>
+      <c r="I25" s="13">
+        <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
+        <v/>
+      </c>
+      <c r="J25" s="16">
+        <f>IF($H$25="","",$F$25*IF($H$25&lt;0,-100/$H$25,$H$25/100)-(1-$F$25))</f>
+        <v/>
+      </c>
+      <c r="K25" s="17">
+        <f>IF($H$25="","",MAX(0,($F$25*IF($H$25&lt;0,-100/$H$25,$H$25/100)-(1-$F$25))/IF($H$25&lt;0,-100/$H$25,$H$25/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L25" s="18">
+        <f>IF($H$25="","",ROUND(MIN($K$25,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M25" s="12">
+        <f>IF($J$25="","",IF($J$25&lt;0,"Pass",IF($J$25&lt;'Settings'!$B$4,"Thin",IF($J$25&lt;0.06,"✅ Sharp band",IF($J$25&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N25" s="19" t="inlineStr">
+        <is>
+          <t>Model 38.4% (fair +160). Your call.</t>
+        </is>
+      </c>
+      <c r="O25" s="15" t="n"/>
+      <c r="P25" s="16">
+        <f>IF(OR($H$25="",$O$25=""),"",(1+IF($H$25&lt;0,-100/$H$25,$H$25/100))/(1+IF($O$25&lt;0,-100/$O$25,$O$25/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
+        <is>
+          <t>Minnesota Lynx @ Dallas Wings</t>
+        </is>
+      </c>
+      <c r="C26" s="20" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="D26" s="20" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E26" s="20" t="inlineStr">
+        <is>
+          <t>Under 178.5</t>
+        </is>
+      </c>
+      <c r="F26" s="13" t="n">
+        <v>0.6155999999999999</v>
+      </c>
+      <c r="G26" s="14" t="n">
+        <v>-160</v>
+      </c>
+      <c r="H26" s="15" t="n">
+        <v>-104</v>
+      </c>
+      <c r="I26" s="13">
+        <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
+        <v/>
+      </c>
+      <c r="J26" s="16">
+        <f>IF($H$26="","",$F$26*IF($H$26&lt;0,-100/$H$26,$H$26/100)-(1-$F$26))</f>
+        <v/>
+      </c>
+      <c r="K26" s="17">
+        <f>IF($H$26="","",MAX(0,($F$26*IF($H$26&lt;0,-100/$H$26,$H$26/100)-(1-$F$26))/IF($H$26&lt;0,-100/$H$26,$H$26/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L26" s="18">
+        <f>IF($H$26="","",ROUND(MIN($K$26,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M26" s="12">
+        <f>IF($J$26="","",IF($J$26&lt;0,"Pass",IF($J$26&lt;'Settings'!$B$4,"Thin",IF($J$26&lt;0.06,"✅ Sharp band",IF($J$26&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N26" s="19" t="inlineStr">
+        <is>
+          <t>Model 61.6% (fair -160). Your call.</t>
+        </is>
+      </c>
+      <c r="O26" s="15" t="n"/>
+      <c r="P26" s="16">
+        <f>IF(OR($H$26="",$O$26=""),"",(1+IF($H$26&lt;0,-100/$H$26,$H$26/100))/(1+IF($O$26&lt;0,-100/$O$26,$O$26/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>Minnesota Lynx @ Dallas Wings</t>
+        </is>
+      </c>
+      <c r="C27" s="12" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E27" s="12" t="inlineStr">
+        <is>
+          <t>Dallas Wings +3.5</t>
+        </is>
+      </c>
+      <c r="F27" s="13" t="n">
+        <v>0.5042</v>
+      </c>
+      <c r="G27" s="14" t="n">
+        <v>-102</v>
+      </c>
+      <c r="H27" s="15" t="n">
+        <v>-104</v>
+      </c>
+      <c r="I27" s="13">
+        <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
+        <v/>
+      </c>
+      <c r="J27" s="16">
+        <f>IF($H$27="","",$F$27*IF($H$27&lt;0,-100/$H$27,$H$27/100)-(1-$F$27))</f>
+        <v/>
+      </c>
+      <c r="K27" s="17">
+        <f>IF($H$27="","",MAX(0,($F$27*IF($H$27&lt;0,-100/$H$27,$H$27/100)-(1-$F$27))/IF($H$27&lt;0,-100/$H$27,$H$27/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L27" s="18">
+        <f>IF($H$27="","",ROUND(MIN($K$27,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M27" s="12">
+        <f>IF($J$27="","",IF($J$27&lt;0,"Pass",IF($J$27&lt;'Settings'!$B$4,"Thin",IF($J$27&lt;0.06,"✅ Sharp band",IF($J$27&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N27" s="19" t="inlineStr">
+        <is>
+          <t>Model 50.4% (fair -102). Your call.</t>
+        </is>
+      </c>
+      <c r="O27" s="15" t="n"/>
+      <c r="P27" s="16">
+        <f>IF(OR($H$27="",$O$27=""),"",(1+IF($H$27&lt;0,-100/$H$27,$H$27/100))/(1+IF($O$27&lt;0,-100/$O$27,$O$27/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
+        <is>
+          <t>Minnesota Lynx @ Dallas Wings</t>
+        </is>
+      </c>
+      <c r="C28" s="20" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="D28" s="20" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E28" s="20" t="inlineStr">
+        <is>
+          <t>Minnesota Lynx -3.5</t>
+        </is>
+      </c>
+      <c r="F28" s="13" t="n">
+        <v>0.4958</v>
+      </c>
+      <c r="G28" s="14" t="n">
+        <v>102</v>
+      </c>
+      <c r="H28" s="15" t="n">
+        <v>122</v>
+      </c>
+      <c r="I28" s="13">
+        <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
+        <v/>
+      </c>
+      <c r="J28" s="16">
+        <f>IF($H$28="","",$F$28*IF($H$28&lt;0,-100/$H$28,$H$28/100)-(1-$F$28))</f>
+        <v/>
+      </c>
+      <c r="K28" s="17">
+        <f>IF($H$28="","",MAX(0,($F$28*IF($H$28&lt;0,-100/$H$28,$H$28/100)-(1-$F$28))/IF($H$28&lt;0,-100/$H$28,$H$28/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L28" s="18">
+        <f>IF($H$28="","",ROUND(MIN($K$28,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M28" s="12">
+        <f>IF($J$28="","",IF($J$28&lt;0,"Pass",IF($J$28&lt;'Settings'!$B$4,"Thin",IF($J$28&lt;0.06,"✅ Sharp band",IF($J$28&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N28" s="19" t="inlineStr">
+        <is>
+          <t>Model 49.6% (fair +102). Your call.</t>
+        </is>
+      </c>
+      <c r="O28" s="15" t="n"/>
+      <c r="P28" s="16">
+        <f>IF(OR($H$28="",$O$28=""),"",(1+IF($H$28&lt;0,-100/$H$28,$H$28/100))/(1+IF($O$28&lt;0,-100/$O$28,$O$28/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B29" s="12" t="inlineStr">
+        <is>
+          <t>Portland Fire @ Washington Mystics</t>
+        </is>
+      </c>
+      <c r="C29" s="12" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="D29" s="12" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E29" s="12" t="inlineStr">
+        <is>
+          <t>Portland Fire</t>
+        </is>
+      </c>
+      <c r="F29" s="13" t="n">
+        <v>0.3086</v>
+      </c>
+      <c r="G29" s="14" t="n">
+        <v>224</v>
+      </c>
+      <c r="H29" s="15" t="n">
+        <v>245</v>
+      </c>
+      <c r="I29" s="13">
+        <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
+        <v/>
+      </c>
+      <c r="J29" s="16">
+        <f>IF($H$29="","",$F$29*IF($H$29&lt;0,-100/$H$29,$H$29/100)-(1-$F$29))</f>
+        <v/>
+      </c>
+      <c r="K29" s="17">
+        <f>IF($H$29="","",MAX(0,($F$29*IF($H$29&lt;0,-100/$H$29,$H$29/100)-(1-$F$29))/IF($H$29&lt;0,-100/$H$29,$H$29/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L29" s="18">
+        <f>IF($H$29="","",ROUND(MIN($K$29,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M29" s="12">
+        <f>IF($J$29="","",IF($J$29&lt;0,"Pass",IF($J$29&lt;'Settings'!$B$4,"Thin",IF($J$29&lt;0.06,"✅ Sharp band",IF($J$29&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N29" s="19" t="inlineStr">
+        <is>
+          <t>Model 30.9% (fair +224). Your call.</t>
+        </is>
+      </c>
+      <c r="O29" s="15" t="n"/>
+      <c r="P29" s="16">
+        <f>IF(OR($H$29="",$O$29=""),"",(1+IF($H$29&lt;0,-100/$H$29,$H$29/100))/(1+IF($O$29&lt;0,-100/$O$29,$O$29/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="inlineStr">
+        <is>
+          <t>Portland Fire @ Washington Mystics</t>
+        </is>
+      </c>
+      <c r="C30" s="20" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="D30" s="20" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E30" s="20" t="inlineStr">
+        <is>
+          <t>Washington Mystics</t>
+        </is>
+      </c>
+      <c r="F30" s="13" t="n">
+        <v>0.6914</v>
+      </c>
+      <c r="G30" s="14" t="n">
+        <v>-224</v>
+      </c>
+      <c r="H30" s="15" t="n">
+        <v>-210</v>
+      </c>
+      <c r="I30" s="13">
+        <f>IF($H$30="","",IF($H$30&lt;0,-$H$30/(-$H$30+100),100/($H$30+100)))</f>
+        <v/>
+      </c>
+      <c r="J30" s="16">
+        <f>IF($H$30="","",$F$30*IF($H$30&lt;0,-100/$H$30,$H$30/100)-(1-$F$30))</f>
+        <v/>
+      </c>
+      <c r="K30" s="17">
+        <f>IF($H$30="","",MAX(0,($F$30*IF($H$30&lt;0,-100/$H$30,$H$30/100)-(1-$F$30))/IF($H$30&lt;0,-100/$H$30,$H$30/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L30" s="18">
+        <f>IF($H$30="","",ROUND(MIN($K$30,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M30" s="12">
+        <f>IF($J$30="","",IF($J$30&lt;0,"Pass",IF($J$30&lt;'Settings'!$B$4,"Thin",IF($J$30&lt;0.06,"✅ Sharp band",IF($J$30&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N30" s="19" t="inlineStr">
+        <is>
+          <t>Model 69.1% (fair -224). Your call.</t>
+        </is>
+      </c>
+      <c r="O30" s="15" t="n"/>
+      <c r="P30" s="16">
+        <f>IF(OR($H$30="",$O$30=""),"",(1+IF($H$30&lt;0,-100/$H$30,$H$30/100))/(1+IF($O$30&lt;0,-100/$O$30,$O$30/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B31" s="12" t="inlineStr">
+        <is>
+          <t>Portland Fire @ Washington Mystics</t>
+        </is>
+      </c>
+      <c r="C31" s="12" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="D31" s="12" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E31" s="12" t="inlineStr">
+        <is>
+          <t>Over 164.5</t>
+        </is>
+      </c>
+      <c r="F31" s="13" t="n">
+        <v>0.6287809523809523</v>
+      </c>
+      <c r="G31" s="14" t="n">
+        <v>-169</v>
+      </c>
+      <c r="H31" s="15" t="n">
+        <v>-110</v>
+      </c>
+      <c r="I31" s="13">
+        <f>IF($H$31="","",IF($H$31&lt;0,-$H$31/(-$H$31+100),100/($H$31+100)))</f>
+        <v/>
+      </c>
+      <c r="J31" s="16">
+        <f>IF($H$31="","",$F$31*IF($H$31&lt;0,-100/$H$31,$H$31/100)-(1-$F$31))</f>
+        <v/>
+      </c>
+      <c r="K31" s="17">
+        <f>IF($H$31="","",MAX(0,($F$31*IF($H$31&lt;0,-100/$H$31,$H$31/100)-(1-$F$31))/IF($H$31&lt;0,-100/$H$31,$H$31/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L31" s="18">
+        <f>IF($H$31="","",ROUND(MIN($K$31,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M31" s="12">
+        <f>IF($J$31="","",IF($J$31&lt;0,"Pass",IF($J$31&lt;'Settings'!$B$4,"Thin",IF($J$31&lt;0.06,"✅ Sharp band",IF($J$31&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N31" s="19" t="inlineStr">
+        <is>
+          <t>Model 62.9% (fair -169). Your call.</t>
+        </is>
+      </c>
+      <c r="O31" s="15" t="n"/>
+      <c r="P31" s="16">
+        <f>IF(OR($H$31="",$O$31=""),"",(1+IF($H$31&lt;0,-100/$H$31,$H$31/100))/(1+IF($O$31&lt;0,-100/$O$31,$O$31/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B32" s="20" t="inlineStr">
+        <is>
+          <t>Portland Fire @ Washington Mystics</t>
+        </is>
+      </c>
+      <c r="C32" s="20" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="D32" s="20" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E32" s="20" t="inlineStr">
+        <is>
+          <t>Under 164.5</t>
+        </is>
+      </c>
+      <c r="F32" s="13" t="n">
+        <v>0.3712</v>
+      </c>
+      <c r="G32" s="14" t="n">
+        <v>169</v>
+      </c>
+      <c r="H32" s="15" t="n">
+        <v>-110</v>
+      </c>
+      <c r="I32" s="13">
+        <f>IF($H$32="","",IF($H$32&lt;0,-$H$32/(-$H$32+100),100/($H$32+100)))</f>
+        <v/>
+      </c>
+      <c r="J32" s="16">
+        <f>IF($H$32="","",$F$32*IF($H$32&lt;0,-100/$H$32,$H$32/100)-(1-$F$32))</f>
+        <v/>
+      </c>
+      <c r="K32" s="17">
+        <f>IF($H$32="","",MAX(0,($F$32*IF($H$32&lt;0,-100/$H$32,$H$32/100)-(1-$F$32))/IF($H$32&lt;0,-100/$H$32,$H$32/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L32" s="18">
+        <f>IF($H$32="","",ROUND(MIN($K$32,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M32" s="12">
+        <f>IF($J$32="","",IF($J$32&lt;0,"Pass",IF($J$32&lt;'Settings'!$B$4,"Thin",IF($J$32&lt;0.06,"✅ Sharp band",IF($J$32&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N32" s="19" t="inlineStr">
+        <is>
+          <t>Model 37.1% (fair +169). Your call.</t>
+        </is>
+      </c>
+      <c r="O32" s="15" t="n"/>
+      <c r="P32" s="16">
+        <f>IF(OR($H$32="",$O$32=""),"",(1+IF($H$32&lt;0,-100/$H$32,$H$32/100))/(1+IF($O$32&lt;0,-100/$O$32,$O$32/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B33" s="12" t="inlineStr">
+        <is>
+          <t>Portland Fire @ Washington Mystics</t>
+        </is>
+      </c>
+      <c r="C33" s="12" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="D33" s="12" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E33" s="12" t="inlineStr">
+        <is>
+          <t>Washington Mystics -5.5</t>
+        </is>
+      </c>
+      <c r="F33" s="13" t="n">
+        <v>0.4964666666666666</v>
+      </c>
+      <c r="G33" s="14" t="n">
+        <v>101</v>
+      </c>
+      <c r="H33" s="15" t="n">
+        <v>-110</v>
+      </c>
+      <c r="I33" s="13">
+        <f>IF($H$33="","",IF($H$33&lt;0,-$H$33/(-$H$33+100),100/($H$33+100)))</f>
+        <v/>
+      </c>
+      <c r="J33" s="16">
+        <f>IF($H$33="","",$F$33*IF($H$33&lt;0,-100/$H$33,$H$33/100)-(1-$F$33))</f>
+        <v/>
+      </c>
+      <c r="K33" s="17">
+        <f>IF($H$33="","",MAX(0,($F$33*IF($H$33&lt;0,-100/$H$33,$H$33/100)-(1-$F$33))/IF($H$33&lt;0,-100/$H$33,$H$33/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L33" s="18">
+        <f>IF($H$33="","",ROUND(MIN($K$33,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M33" s="12">
+        <f>IF($J$33="","",IF($J$33&lt;0,"Pass",IF($J$33&lt;'Settings'!$B$4,"Thin",IF($J$33&lt;0.06,"✅ Sharp band",IF($J$33&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N33" s="19" t="inlineStr">
+        <is>
+          <t>Model 49.6% (fair +101). Your call.</t>
+        </is>
+      </c>
+      <c r="O33" s="15" t="n"/>
+      <c r="P33" s="16">
+        <f>IF(OR($H$33="",$O$33=""),"",(1+IF($H$33&lt;0,-100/$H$33,$H$33/100))/(1+IF($O$33&lt;0,-100/$O$33,$O$33/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B34" s="20" t="inlineStr">
+        <is>
+          <t>Portland Fire @ Washington Mystics</t>
+        </is>
+      </c>
+      <c r="C34" s="20" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="D34" s="20" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E34" s="20" t="inlineStr">
+        <is>
+          <t>Portland Fire +5.5</t>
+        </is>
+      </c>
+      <c r="F34" s="13" t="n">
+        <v>0.5035202898550725</v>
+      </c>
+      <c r="G34" s="14" t="n">
+        <v>-101</v>
+      </c>
+      <c r="H34" s="15" t="n">
+        <v>-107</v>
+      </c>
+      <c r="I34" s="13">
+        <f>IF($H$34="","",IF($H$34&lt;0,-$H$34/(-$H$34+100),100/($H$34+100)))</f>
+        <v/>
+      </c>
+      <c r="J34" s="16">
+        <f>IF($H$34="","",$F$34*IF($H$34&lt;0,-100/$H$34,$H$34/100)-(1-$F$34))</f>
+        <v/>
+      </c>
+      <c r="K34" s="17">
+        <f>IF($H$34="","",MAX(0,($F$34*IF($H$34&lt;0,-100/$H$34,$H$34/100)-(1-$F$34))/IF($H$34&lt;0,-100/$H$34,$H$34/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L34" s="18">
+        <f>IF($H$34="","",ROUND(MIN($K$34,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M34" s="12">
+        <f>IF($J$34="","",IF($J$34&lt;0,"Pass",IF($J$34&lt;'Settings'!$B$4,"Thin",IF($J$34&lt;0.06,"✅ Sharp band",IF($J$34&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N34" s="19" t="inlineStr">
+        <is>
+          <t>Model 50.4% (fair -101). Your call.</t>
+        </is>
+      </c>
+      <c r="O34" s="15" t="n"/>
+      <c r="P34" s="16">
+        <f>IF(OR($H$34="",$O$34=""),"",(1+IF($H$34&lt;0,-100/$H$34,$H$34/100))/(1+IF($O$34&lt;0,-100/$O$34,$O$34/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B35" s="12" t="inlineStr">
+        <is>
+          <t>Las Vegas Aces @ Chicago Sky</t>
+        </is>
+      </c>
+      <c r="C35" s="12" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="D35" s="12" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E35" s="12" t="inlineStr">
+        <is>
+          <t>Las Vegas Aces</t>
+        </is>
+      </c>
+      <c r="F35" s="13" t="n">
+        <v>0.757125</v>
+      </c>
+      <c r="G35" s="14" t="n">
+        <v>-312</v>
+      </c>
+      <c r="H35" s="15" t="n">
+        <v>-300</v>
+      </c>
+      <c r="I35" s="13">
+        <f>IF($H$35="","",IF($H$35&lt;0,-$H$35/(-$H$35+100),100/($H$35+100)))</f>
+        <v/>
+      </c>
+      <c r="J35" s="16">
+        <f>IF($H$35="","",$F$35*IF($H$35&lt;0,-100/$H$35,$H$35/100)-(1-$F$35))</f>
+        <v/>
+      </c>
+      <c r="K35" s="17">
+        <f>IF($H$35="","",MAX(0,($F$35*IF($H$35&lt;0,-100/$H$35,$H$35/100)-(1-$F$35))/IF($H$35&lt;0,-100/$H$35,$H$35/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L35" s="18">
+        <f>IF($H$35="","",ROUND(MIN($K$35,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M35" s="12">
+        <f>IF($J$35="","",IF($J$35&lt;0,"Pass",IF($J$35&lt;'Settings'!$B$4,"Thin",IF($J$35&lt;0.06,"✅ Sharp band",IF($J$35&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N35" s="19" t="inlineStr">
+        <is>
+          <t>Model 75.7% (fair -312). Your call.</t>
+        </is>
+      </c>
+      <c r="O35" s="15" t="n"/>
+      <c r="P35" s="16">
+        <f>IF(OR($H$35="",$O$35=""),"",(1+IF($H$35&lt;0,-100/$H$35,$H$35/100))/(1+IF($O$35&lt;0,-100/$O$35,$O$35/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B36" s="20" t="inlineStr">
+        <is>
+          <t>Las Vegas Aces @ Chicago Sky</t>
+        </is>
+      </c>
+      <c r="C36" s="20" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="D36" s="20" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E36" s="20" t="inlineStr">
+        <is>
+          <t>Chicago Sky</t>
+        </is>
+      </c>
+      <c r="F36" s="13" t="n">
+        <v>0.2428776978417266</v>
+      </c>
+      <c r="G36" s="14" t="n">
+        <v>312</v>
+      </c>
+      <c r="H36" s="15" t="n">
+        <v>317</v>
+      </c>
+      <c r="I36" s="13">
+        <f>IF($H$36="","",IF($H$36&lt;0,-$H$36/(-$H$36+100),100/($H$36+100)))</f>
+        <v/>
+      </c>
+      <c r="J36" s="16">
+        <f>IF($H$36="","",$F$36*IF($H$36&lt;0,-100/$H$36,$H$36/100)-(1-$F$36))</f>
+        <v/>
+      </c>
+      <c r="K36" s="17">
+        <f>IF($H$36="","",MAX(0,($F$36*IF($H$36&lt;0,-100/$H$36,$H$36/100)-(1-$F$36))/IF($H$36&lt;0,-100/$H$36,$H$36/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L36" s="18">
+        <f>IF($H$36="","",ROUND(MIN($K$36,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M36" s="12">
+        <f>IF($J$36="","",IF($J$36&lt;0,"Pass",IF($J$36&lt;'Settings'!$B$4,"Thin",IF($J$36&lt;0.06,"✅ Sharp band",IF($J$36&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N36" s="19" t="inlineStr">
+        <is>
+          <t>Model 24.3% (fair +312). Your call.</t>
+        </is>
+      </c>
+      <c r="O36" s="15" t="n"/>
+      <c r="P36" s="16">
+        <f>IF(OR($H$36="",$O$36=""),"",(1+IF($H$36&lt;0,-100/$H$36,$H$36/100))/(1+IF($O$36&lt;0,-100/$O$36,$O$36/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B37" s="12" t="inlineStr">
+        <is>
+          <t>Las Vegas Aces @ Chicago Sky</t>
+        </is>
+      </c>
+      <c r="C37" s="12" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="D37" s="12" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E37" s="12" t="inlineStr">
+        <is>
+          <t>Over 179.5</t>
+        </is>
+      </c>
+      <c r="F37" s="13" t="n">
+        <v>0.5262923076923077</v>
+      </c>
+      <c r="G37" s="14" t="n">
+        <v>-111</v>
+      </c>
+      <c r="H37" s="15" t="n">
+        <v>-108</v>
+      </c>
+      <c r="I37" s="13">
+        <f>IF($H$37="","",IF($H$37&lt;0,-$H$37/(-$H$37+100),100/($H$37+100)))</f>
+        <v/>
+      </c>
+      <c r="J37" s="16">
+        <f>IF($H$37="","",$F$37*IF($H$37&lt;0,-100/$H$37,$H$37/100)-(1-$F$37))</f>
+        <v/>
+      </c>
+      <c r="K37" s="17">
+        <f>IF($H$37="","",MAX(0,($F$37*IF($H$37&lt;0,-100/$H$37,$H$37/100)-(1-$F$37))/IF($H$37&lt;0,-100/$H$37,$H$37/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L37" s="18">
+        <f>IF($H$37="","",ROUND(MIN($K$37,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M37" s="12">
+        <f>IF($J$37="","",IF($J$37&lt;0,"Pass",IF($J$37&lt;'Settings'!$B$4,"Thin",IF($J$37&lt;0.06,"✅ Sharp band",IF($J$37&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N37" s="19" t="inlineStr">
+        <is>
+          <t>Model 52.6% (fair -111). Your call.</t>
+        </is>
+      </c>
+      <c r="O37" s="15" t="n"/>
+      <c r="P37" s="16">
+        <f>IF(OR($H$37="",$O$37=""),"",(1+IF($H$37&lt;0,-100/$H$37,$H$37/100))/(1+IF($O$37&lt;0,-100/$O$37,$O$37/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B38" s="20" t="inlineStr">
+        <is>
+          <t>Las Vegas Aces @ Chicago Sky</t>
+        </is>
+      </c>
+      <c r="C38" s="20" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="D38" s="20" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E38" s="20" t="inlineStr">
+        <is>
+          <t>Under 179.5</t>
+        </is>
+      </c>
+      <c r="F38" s="13" t="n">
+        <v>0.4737</v>
+      </c>
+      <c r="G38" s="14" t="n">
+        <v>111</v>
+      </c>
+      <c r="H38" s="15" t="n">
+        <v>-108</v>
+      </c>
+      <c r="I38" s="13">
+        <f>IF($H$38="","",IF($H$38&lt;0,-$H$38/(-$H$38+100),100/($H$38+100)))</f>
+        <v/>
+      </c>
+      <c r="J38" s="16">
+        <f>IF($H$38="","",$F$38*IF($H$38&lt;0,-100/$H$38,$H$38/100)-(1-$F$38))</f>
+        <v/>
+      </c>
+      <c r="K38" s="17">
+        <f>IF($H$38="","",MAX(0,($F$38*IF($H$38&lt;0,-100/$H$38,$H$38/100)-(1-$F$38))/IF($H$38&lt;0,-100/$H$38,$H$38/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L38" s="18">
+        <f>IF($H$38="","",ROUND(MIN($K$38,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M38" s="12">
+        <f>IF($J$38="","",IF($J$38&lt;0,"Pass",IF($J$38&lt;'Settings'!$B$4,"Thin",IF($J$38&lt;0.06,"✅ Sharp band",IF($J$38&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N38" s="19" t="inlineStr">
+        <is>
+          <t>Model 47.4% (fair +111). Your call.</t>
+        </is>
+      </c>
+      <c r="O38" s="15" t="n"/>
+      <c r="P38" s="16">
+        <f>IF(OR($H$38="",$O$38=""),"",(1+IF($H$38&lt;0,-100/$H$38,$H$38/100))/(1+IF($O$38&lt;0,-100/$O$38,$O$38/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="12" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B39" s="12" t="inlineStr">
+        <is>
+          <t>Las Vegas Aces @ Chicago Sky</t>
+        </is>
+      </c>
+      <c r="C39" s="12" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="D39" s="12" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E39" s="12" t="inlineStr">
+        <is>
+          <t>Chicago Sky +7.5</t>
+        </is>
+      </c>
+      <c r="F39" s="13" t="n">
+        <v>0.5767615384615384</v>
+      </c>
+      <c r="G39" s="14" t="n">
+        <v>-136</v>
+      </c>
+      <c r="H39" s="15" t="n">
+        <v>-108</v>
+      </c>
+      <c r="I39" s="13">
+        <f>IF($H$39="","",IF($H$39&lt;0,-$H$39/(-$H$39+100),100/($H$39+100)))</f>
+        <v/>
+      </c>
+      <c r="J39" s="16">
+        <f>IF($H$39="","",$F$39*IF($H$39&lt;0,-100/$H$39,$H$39/100)-(1-$F$39))</f>
+        <v/>
+      </c>
+      <c r="K39" s="17">
+        <f>IF($H$39="","",MAX(0,($F$39*IF($H$39&lt;0,-100/$H$39,$H$39/100)-(1-$F$39))/IF($H$39&lt;0,-100/$H$39,$H$39/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L39" s="18">
+        <f>IF($H$39="","",ROUND(MIN($K$39,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M39" s="12">
+        <f>IF($J$39="","",IF($J$39&lt;0,"Pass",IF($J$39&lt;'Settings'!$B$4,"Thin",IF($J$39&lt;0.06,"✅ Sharp band",IF($J$39&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N39" s="19" t="inlineStr">
+        <is>
+          <t>Model 57.7% (fair -136). Your call.</t>
+        </is>
+      </c>
+      <c r="O39" s="15" t="n"/>
+      <c r="P39" s="16">
+        <f>IF(OR($H$39="",$O$39=""),"",(1+IF($H$39&lt;0,-100/$H$39,$H$39/100))/(1+IF($O$39&lt;0,-100/$O$39,$O$39/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B40" s="20" t="inlineStr">
+        <is>
+          <t>Las Vegas Aces @ Chicago Sky</t>
+        </is>
+      </c>
+      <c r="C40" s="20" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="D40" s="20" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E40" s="20" t="inlineStr">
+        <is>
+          <t>Las Vegas Aces -7.5</t>
+        </is>
+      </c>
+      <c r="F40" s="13" t="n">
+        <v>0.4232380952380952</v>
+      </c>
+      <c r="G40" s="14" t="n">
+        <v>136</v>
+      </c>
+      <c r="H40" s="15" t="n">
+        <v>-110</v>
+      </c>
+      <c r="I40" s="13">
+        <f>IF($H$40="","",IF($H$40&lt;0,-$H$40/(-$H$40+100),100/($H$40+100)))</f>
+        <v/>
+      </c>
+      <c r="J40" s="16">
+        <f>IF($H$40="","",$F$40*IF($H$40&lt;0,-100/$H$40,$H$40/100)-(1-$F$40))</f>
+        <v/>
+      </c>
+      <c r="K40" s="17">
+        <f>IF($H$40="","",MAX(0,($F$40*IF($H$40&lt;0,-100/$H$40,$H$40/100)-(1-$F$40))/IF($H$40&lt;0,-100/$H$40,$H$40/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L40" s="18">
+        <f>IF($H$40="","",ROUND(MIN($K$40,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M40" s="12">
+        <f>IF($J$40="","",IF($J$40&lt;0,"Pass",IF($J$40&lt;'Settings'!$B$4,"Thin",IF($J$40&lt;0.06,"✅ Sharp band",IF($J$40&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N40" s="19" t="inlineStr">
+        <is>
+          <t>Model 42.3% (fair +136). Your call.</t>
+        </is>
+      </c>
+      <c r="O40" s="15" t="n"/>
+      <c r="P40" s="16">
+        <f>IF(OR($H$40="",$O$40=""),"",(1+IF($H$40&lt;0,-100/$H$40,$H$40/100))/(1+IF($O$40&lt;0,-100/$O$40,$O$40/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="12" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B41" s="12" t="inlineStr">
+        <is>
+          <t>New York Liberty @ Golden State Valkyries</t>
+        </is>
+      </c>
+      <c r="C41" s="12" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="D41" s="12" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E41" s="12" t="inlineStr">
+        <is>
+          <t>New York Liberty</t>
+        </is>
+      </c>
+      <c r="F41" s="13" t="n">
+        <v>0.4314470588235294</v>
+      </c>
+      <c r="G41" s="14" t="n">
+        <v>132</v>
+      </c>
+      <c r="H41" s="15" t="n">
+        <v>-104</v>
+      </c>
+      <c r="I41" s="13">
+        <f>IF($H$41="","",IF($H$41&lt;0,-$H$41/(-$H$41+100),100/($H$41+100)))</f>
+        <v/>
+      </c>
+      <c r="J41" s="16">
+        <f>IF($H$41="","",$F$41*IF($H$41&lt;0,-100/$H$41,$H$41/100)-(1-$F$41))</f>
+        <v/>
+      </c>
+      <c r="K41" s="17">
+        <f>IF($H$41="","",MAX(0,($F$41*IF($H$41&lt;0,-100/$H$41,$H$41/100)-(1-$F$41))/IF($H$41&lt;0,-100/$H$41,$H$41/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L41" s="18">
+        <f>IF($H$41="","",ROUND(MIN($K$41,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M41" s="12">
+        <f>IF($J$41="","",IF($J$41&lt;0,"Pass",IF($J$41&lt;'Settings'!$B$4,"Thin",IF($J$41&lt;0.06,"✅ Sharp band",IF($J$41&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N41" s="19" t="inlineStr">
+        <is>
+          <t>Model 43.1% (fair +132). Your call.</t>
+        </is>
+      </c>
+      <c r="O41" s="15" t="n"/>
+      <c r="P41" s="16">
+        <f>IF(OR($H$41="",$O$41=""),"",(1+IF($H$41&lt;0,-100/$H$41,$H$41/100))/(1+IF($O$41&lt;0,-100/$O$41,$O$41/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B42" s="20" t="inlineStr">
+        <is>
+          <t>New York Liberty @ Golden State Valkyries</t>
+        </is>
+      </c>
+      <c r="C42" s="20" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="D42" s="20" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E42" s="20" t="inlineStr">
+        <is>
+          <t>Golden State Valkyries</t>
+        </is>
+      </c>
+      <c r="F42" s="13" t="n">
+        <v>0.56855</v>
+      </c>
+      <c r="G42" s="14" t="n">
+        <v>-132</v>
+      </c>
+      <c r="H42" s="15" t="n">
+        <v>100</v>
+      </c>
+      <c r="I42" s="13">
+        <f>IF($H$42="","",IF($H$42&lt;0,-$H$42/(-$H$42+100),100/($H$42+100)))</f>
+        <v/>
+      </c>
+      <c r="J42" s="16">
+        <f>IF($H$42="","",$F$42*IF($H$42&lt;0,-100/$H$42,$H$42/100)-(1-$F$42))</f>
+        <v/>
+      </c>
+      <c r="K42" s="17">
+        <f>IF($H$42="","",MAX(0,($F$42*IF($H$42&lt;0,-100/$H$42,$H$42/100)-(1-$F$42))/IF($H$42&lt;0,-100/$H$42,$H$42/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L42" s="18">
+        <f>IF($H$42="","",ROUND(MIN($K$42,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M42" s="12">
+        <f>IF($J$42="","",IF($J$42&lt;0,"Pass",IF($J$42&lt;'Settings'!$B$4,"Thin",IF($J$42&lt;0.06,"✅ Sharp band",IF($J$42&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N42" s="19" t="inlineStr">
+        <is>
+          <t>Model 56.9% (fair -132). Your call.</t>
+        </is>
+      </c>
+      <c r="O42" s="15" t="n"/>
+      <c r="P42" s="16">
+        <f>IF(OR($H$42="",$O$42=""),"",(1+IF($H$42&lt;0,-100/$H$42,$H$42/100))/(1+IF($O$42&lt;0,-100/$O$42,$O$42/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="12" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B43" s="12" t="inlineStr">
+        <is>
+          <t>New York Liberty @ Golden State Valkyries</t>
+        </is>
+      </c>
+      <c r="C43" s="12" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="D43" s="12" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E43" s="12" t="inlineStr">
+        <is>
+          <t>Over 163.5</t>
+        </is>
+      </c>
+      <c r="F43" s="13" t="n">
+        <v>0.5769238095238095</v>
+      </c>
+      <c r="G43" s="14" t="n">
+        <v>-136</v>
+      </c>
+      <c r="H43" s="15" t="n">
+        <v>-110</v>
+      </c>
+      <c r="I43" s="13">
+        <f>IF($H$43="","",IF($H$43&lt;0,-$H$43/(-$H$43+100),100/($H$43+100)))</f>
+        <v/>
+      </c>
+      <c r="J43" s="16">
+        <f>IF($H$43="","",$F$43*IF($H$43&lt;0,-100/$H$43,$H$43/100)-(1-$F$43))</f>
+        <v/>
+      </c>
+      <c r="K43" s="17">
+        <f>IF($H$43="","",MAX(0,($F$43*IF($H$43&lt;0,-100/$H$43,$H$43/100)-(1-$F$43))/IF($H$43&lt;0,-100/$H$43,$H$43/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L43" s="18">
+        <f>IF($H$43="","",ROUND(MIN($K$43,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M43" s="12">
+        <f>IF($J$43="","",IF($J$43&lt;0,"Pass",IF($J$43&lt;'Settings'!$B$4,"Thin",IF($J$43&lt;0.06,"✅ Sharp band",IF($J$43&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N43" s="19" t="inlineStr">
+        <is>
+          <t>Model 57.7% (fair -136). Your call.</t>
+        </is>
+      </c>
+      <c r="O43" s="15" t="n"/>
+      <c r="P43" s="16">
+        <f>IF(OR($H$43="",$O$43=""),"",(1+IF($H$43&lt;0,-100/$H$43,$H$43/100))/(1+IF($O$43&lt;0,-100/$O$43,$O$43/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B44" s="20" t="inlineStr">
+        <is>
+          <t>New York Liberty @ Golden State Valkyries</t>
+        </is>
+      </c>
+      <c r="C44" s="20" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="D44" s="20" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E44" s="20" t="inlineStr">
+        <is>
+          <t>Under 163.5</t>
+        </is>
+      </c>
+      <c r="F44" s="13" t="n">
+        <v>0.4231</v>
+      </c>
+      <c r="G44" s="14" t="n">
+        <v>136</v>
+      </c>
+      <c r="H44" s="15" t="n">
+        <v>-110</v>
+      </c>
+      <c r="I44" s="13">
+        <f>IF($H$44="","",IF($H$44&lt;0,-$H$44/(-$H$44+100),100/($H$44+100)))</f>
+        <v/>
+      </c>
+      <c r="J44" s="16">
+        <f>IF($H$44="","",$F$44*IF($H$44&lt;0,-100/$H$44,$H$44/100)-(1-$F$44))</f>
+        <v/>
+      </c>
+      <c r="K44" s="17">
+        <f>IF($H$44="","",MAX(0,($F$44*IF($H$44&lt;0,-100/$H$44,$H$44/100)-(1-$F$44))/IF($H$44&lt;0,-100/$H$44,$H$44/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L44" s="18">
+        <f>IF($H$44="","",ROUND(MIN($K$44,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M44" s="12">
+        <f>IF($J$44="","",IF($J$44&lt;0,"Pass",IF($J$44&lt;'Settings'!$B$4,"Thin",IF($J$44&lt;0.06,"✅ Sharp band",IF($J$44&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N44" s="19" t="inlineStr">
+        <is>
+          <t>Model 42.3% (fair +136). Your call.</t>
+        </is>
+      </c>
+      <c r="O44" s="15" t="n"/>
+      <c r="P44" s="16">
+        <f>IF(OR($H$44="",$O$44=""),"",(1+IF($H$44&lt;0,-100/$H$44,$H$44/100))/(1+IF($O$44&lt;0,-100/$O$44,$O$44/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="12" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B45" s="12" t="inlineStr">
+        <is>
+          <t>New York Liberty @ Golden State Valkyries</t>
+        </is>
+      </c>
+      <c r="C45" s="12" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="D45" s="12" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E45" s="12" t="inlineStr">
+        <is>
+          <t>Golden State Valkyries +1</t>
+        </is>
+      </c>
+      <c r="F45" s="13" t="n">
+        <v>0.5743046511627908</v>
+      </c>
+      <c r="G45" s="14" t="n">
+        <v>-135</v>
+      </c>
+      <c r="H45" s="15" t="n">
+        <v>-115</v>
+      </c>
+      <c r="I45" s="13">
+        <f>IF($H$45="","",IF($H$45&lt;0,-$H$45/(-$H$45+100),100/($H$45+100)))</f>
+        <v/>
+      </c>
+      <c r="J45" s="16">
+        <f>IF($H$45="","",$F$45*IF($H$45&lt;0,-100/$H$45,$H$45/100)-(1-$F$45))</f>
+        <v/>
+      </c>
+      <c r="K45" s="17">
+        <f>IF($H$45="","",MAX(0,($F$45*IF($H$45&lt;0,-100/$H$45,$H$45/100)-(1-$F$45))/IF($H$45&lt;0,-100/$H$45,$H$45/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L45" s="18">
+        <f>IF($H$45="","",ROUND(MIN($K$45,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M45" s="12">
+        <f>IF($J$45="","",IF($J$45&lt;0,"Pass",IF($J$45&lt;'Settings'!$B$4,"Thin",IF($J$45&lt;0.06,"✅ Sharp band",IF($J$45&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N45" s="19" t="inlineStr">
+        <is>
+          <t>Model 57.4% (fair -135). Your call.</t>
+        </is>
+      </c>
+      <c r="O45" s="15" t="n"/>
+      <c r="P45" s="16">
+        <f>IF(OR($H$45="",$O$45=""),"",(1+IF($H$45&lt;0,-100/$H$45,$H$45/100))/(1+IF($O$45&lt;0,-100/$O$45,$O$45/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B46" s="20" t="inlineStr">
+        <is>
+          <t>New York Liberty @ Golden State Valkyries</t>
+        </is>
+      </c>
+      <c r="C46" s="20" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="D46" s="20" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E46" s="20" t="inlineStr">
+        <is>
+          <t>New York Liberty -1</t>
+        </is>
+      </c>
+      <c r="F46" s="13" t="n">
+        <v>0.4257</v>
+      </c>
+      <c r="G46" s="14" t="n">
+        <v>135</v>
+      </c>
+      <c r="H46" s="15" t="n">
+        <v>100</v>
+      </c>
+      <c r="I46" s="13">
+        <f>IF($H$46="","",IF($H$46&lt;0,-$H$46/(-$H$46+100),100/($H$46+100)))</f>
+        <v/>
+      </c>
+      <c r="J46" s="16">
+        <f>IF($H$46="","",$F$46*IF($H$46&lt;0,-100/$H$46,$H$46/100)-(1-$F$46))</f>
+        <v/>
+      </c>
+      <c r="K46" s="17">
+        <f>IF($H$46="","",MAX(0,($F$46*IF($H$46&lt;0,-100/$H$46,$H$46/100)-(1-$F$46))/IF($H$46&lt;0,-100/$H$46,$H$46/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L46" s="18">
+        <f>IF($H$46="","",ROUND(MIN($K$46,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M46" s="12">
+        <f>IF($J$46="","",IF($J$46&lt;0,"Pass",IF($J$46&lt;'Settings'!$B$4,"Thin",IF($J$46&lt;0.06,"✅ Sharp band",IF($J$46&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N46" s="19" t="inlineStr">
+        <is>
+          <t>Model 42.6% (fair +135). Your call.</t>
+        </is>
+      </c>
+      <c r="O46" s="15" t="n"/>
+      <c r="P46" s="16">
+        <f>IF(OR($H$46="",$O$46=""),"",(1+IF($H$46&lt;0,-100/$H$46,$H$46/100))/(1+IF($O$46&lt;0,-100/$O$46,$O$46/100))-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="CE4B"/>
-  <conditionalFormatting sqref="J5:J22">
+  <conditionalFormatting sqref="J5:J46">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-0.05"/>

--- a/data/output/workbook/2026-06-27.xlsx
+++ b/data/output/workbook/2026-06-27.xlsx
@@ -521,7 +521,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="9439275"/>
+    <ext cx="10125075" cy="9858375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -551,7 +551,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="9477375"/>
+    <ext cx="10125075" cy="9896475"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -581,7 +581,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="9401175"/>
+    <ext cx="10125075" cy="9810750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -954,7 +954,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-06-27 14:02</t>
+          <t>2026-06-27 15:33</t>
         </is>
       </c>
     </row>
@@ -3682,7 +3682,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q75"/>
+  <dimension ref="A1:Q77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3699,819 +3699,819 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="29" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="29" t="inlineStr">
         <is>
           <t>Kansas City Royals offense vs Chicago White Sox defense</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="30" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B62" s="30" t="inlineStr">
+      <c r="B64" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C62" s="30" t="inlineStr">
+      <c r="C64" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D62" s="30" t="inlineStr">
+      <c r="D64" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E62" s="30" t="inlineStr">
+      <c r="E64" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F62" s="30" t="inlineStr">
+      <c r="F64" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G62" s="30" t="inlineStr">
+      <c r="G64" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H62" s="30" t="inlineStr">
+      <c r="H64" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I62" s="30" t="inlineStr">
+      <c r="I64" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J62" s="30" t="inlineStr">
+      <c r="J64" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K62" s="30" t="inlineStr">
+      <c r="K64" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L62" s="30" t="inlineStr">
+      <c r="L64" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M62" s="30" t="inlineStr">
+      <c r="M64" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N62" s="30" t="inlineStr">
+      <c r="N64" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O62" s="30" t="inlineStr">
+      <c r="O64" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P62" s="30" t="inlineStr">
+      <c r="P64" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q62" s="30" t="inlineStr">
+      <c r="Q64" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B63" s="32" t="n">
-        <v>4.083</v>
-      </c>
-      <c r="C63" s="32" t="n">
-        <v>4.833</v>
-      </c>
-      <c r="D63" s="32" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="E63" s="32" t="n">
-        <v>6.133</v>
-      </c>
-      <c r="F63" s="32" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="G63" s="32" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="H63" s="33" t="inlineStr">
-        <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="I63" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J63" s="36" t="inlineStr">
-        <is>
-          <t>22nd</t>
-        </is>
-      </c>
-      <c r="K63" s="32" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="L63" s="32" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="M63" s="32" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="N63" s="32" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O63" s="32" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="P63" s="32" t="n">
-        <v>4.697</v>
-      </c>
-      <c r="Q63" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="31" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B64" s="32" t="n">
-        <v>8.429</v>
-      </c>
-      <c r="C64" s="32" t="n">
-        <v>8.567</v>
-      </c>
-      <c r="D64" s="32" t="n">
-        <v>9.050000000000001</v>
-      </c>
-      <c r="E64" s="32" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="F64" s="32" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="G64" s="32" t="n">
-        <v>8</v>
-      </c>
-      <c r="H64" s="33" t="inlineStr">
-        <is>
-          <t>9th</t>
-        </is>
-      </c>
-      <c r="I64" s="32" t="inlineStr">
-        <is>
-          <t>★★</t>
-        </is>
-      </c>
-      <c r="J64" s="34" t="inlineStr">
-        <is>
-          <t>18th</t>
-        </is>
-      </c>
-      <c r="K64" s="32" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="L64" s="32" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="M64" s="32" t="n">
-        <v>8.333</v>
-      </c>
-      <c r="N64" s="32" t="n">
-        <v>7.85</v>
-      </c>
-      <c r="O64" s="32" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="P64" s="32" t="n">
-        <v>8.23</v>
-      </c>
-      <c r="Q64" s="35" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B65" s="32" t="n">
-        <v>0.97</v>
+        <v>4.083</v>
       </c>
       <c r="C65" s="32" t="n">
-        <v>1.1</v>
+        <v>4.833</v>
       </c>
       <c r="D65" s="32" t="n">
-        <v>1.05</v>
+        <v>5.05</v>
       </c>
       <c r="E65" s="32" t="n">
-        <v>1.333</v>
+        <v>6.133</v>
       </c>
       <c r="F65" s="32" t="n">
-        <v>1.1</v>
+        <v>6.2</v>
       </c>
       <c r="G65" s="32" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="H65" s="34" t="inlineStr">
-        <is>
-          <t>12th</t>
-        </is>
-      </c>
-      <c r="I65" s="32" t="inlineStr"/>
-      <c r="J65" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K65" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L65" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M65" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N65" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O65" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P65" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>5.4</v>
+      </c>
+      <c r="H65" s="33" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="I65" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J65" s="36" t="inlineStr">
+        <is>
+          <t>22nd</t>
+        </is>
+      </c>
+      <c r="K65" s="32" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L65" s="32" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="M65" s="32" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N65" s="32" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O65" s="32" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="P65" s="32" t="n">
+        <v>4.697</v>
       </c>
       <c r="Q65" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B66" s="32" t="n">
-        <v>6.768</v>
+        <v>8.429</v>
       </c>
       <c r="C66" s="32" t="n">
-        <v>6.533</v>
+        <v>8.567</v>
       </c>
       <c r="D66" s="32" t="n">
-        <v>6.8</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="E66" s="32" t="n">
-        <v>6.667</v>
+        <v>10.2</v>
       </c>
       <c r="F66" s="32" t="n">
-        <v>7</v>
+        <v>10.1</v>
       </c>
       <c r="G66" s="32" t="n">
         <v>8</v>
       </c>
       <c r="H66" s="33" t="inlineStr">
         <is>
-          <t>4th</t>
-        </is>
-      </c>
-      <c r="I66" s="32" t="inlineStr"/>
-      <c r="J66" s="33" t="inlineStr">
-        <is>
-          <t>6th</t>
+          <t>9th</t>
+        </is>
+      </c>
+      <c r="I66" s="32" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="J66" s="34" t="inlineStr">
+        <is>
+          <t>18th</t>
         </is>
       </c>
       <c r="K66" s="32" t="n">
-        <v>10.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L66" s="32" t="n">
-        <v>10.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="M66" s="32" t="n">
-        <v>9.266999999999999</v>
+        <v>8.333</v>
       </c>
       <c r="N66" s="32" t="n">
-        <v>9.300000000000001</v>
+        <v>7.85</v>
       </c>
       <c r="O66" s="32" t="n">
-        <v>9.333</v>
+        <v>8.4</v>
       </c>
       <c r="P66" s="32" t="n">
-        <v>8.029999999999999</v>
+        <v>8.23</v>
       </c>
       <c r="Q66" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="31" t="inlineStr">
         <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B67" s="32" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="C67" s="32" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D67" s="32" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="E67" s="32" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="F67" s="32" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G67" s="32" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H67" s="34" t="inlineStr">
+        <is>
+          <t>12th</t>
+        </is>
+      </c>
+      <c r="I67" s="32" t="inlineStr"/>
+      <c r="J67" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K67" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L67" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M67" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N67" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O67" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P67" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q67" s="35" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="31" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B68" s="32" t="n">
+        <v>6.768</v>
+      </c>
+      <c r="C68" s="32" t="n">
+        <v>6.533</v>
+      </c>
+      <c r="D68" s="32" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="E68" s="32" t="n">
+        <v>6.667</v>
+      </c>
+      <c r="F68" s="32" t="n">
+        <v>7</v>
+      </c>
+      <c r="G68" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="H68" s="33" t="inlineStr">
+        <is>
+          <t>4th</t>
+        </is>
+      </c>
+      <c r="I68" s="32" t="inlineStr"/>
+      <c r="J68" s="33" t="inlineStr">
+        <is>
+          <t>6th</t>
+        </is>
+      </c>
+      <c r="K68" s="32" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="L68" s="32" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="M68" s="32" t="n">
+        <v>9.266999999999999</v>
+      </c>
+      <c r="N68" s="32" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="O68" s="32" t="n">
+        <v>9.333</v>
+      </c>
+      <c r="P68" s="32" t="n">
+        <v>8.029999999999999</v>
+      </c>
+      <c r="Q68" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B67" s="32" t="n">
+      <c r="B69" s="32" t="n">
         <v>0.542</v>
       </c>
-      <c r="C67" s="32" t="n">
+      <c r="C69" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="D67" s="32" t="n">
+      <c r="D69" s="32" t="n">
         <v>1.1</v>
       </c>
-      <c r="E67" s="32" t="n">
+      <c r="E69" s="32" t="n">
         <v>1.267</v>
       </c>
-      <c r="F67" s="32" t="n">
+      <c r="F69" s="32" t="n">
         <v>1.2</v>
       </c>
-      <c r="G67" s="32" t="n">
+      <c r="G69" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="H67" s="33" t="inlineStr">
+      <c r="H69" s="33" t="inlineStr">
         <is>
           <t>9th</t>
         </is>
       </c>
-      <c r="I67" s="32" t="inlineStr">
+      <c r="I69" s="32" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="J67" s="34" t="inlineStr">
+      <c r="J69" s="34" t="inlineStr">
         <is>
           <t>12th</t>
         </is>
       </c>
-      <c r="K67" s="32" t="n">
+      <c r="K69" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="L67" s="32" t="n">
+      <c r="L69" s="32" t="n">
         <v>0.3</v>
       </c>
-      <c r="M67" s="32" t="n">
+      <c r="M69" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="N67" s="32" t="n">
+      <c r="N69" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="O67" s="32" t="n">
+      <c r="O69" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="P67" s="32" t="n">
+      <c r="P69" s="32" t="n">
         <v>0.648</v>
       </c>
-      <c r="Q67" s="35" t="inlineStr">
+      <c r="Q69" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="29" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="29" t="inlineStr">
         <is>
           <t>Chicago White Sox offense vs Kansas City Royals defense</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="30" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B70" s="30" t="inlineStr">
+      <c r="B72" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C70" s="30" t="inlineStr">
+      <c r="C72" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D70" s="30" t="inlineStr">
+      <c r="D72" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E70" s="30" t="inlineStr">
+      <c r="E72" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F70" s="30" t="inlineStr">
+      <c r="F72" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G70" s="30" t="inlineStr">
+      <c r="G72" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H70" s="30" t="inlineStr">
+      <c r="H72" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I70" s="30" t="inlineStr">
+      <c r="I72" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J70" s="30" t="inlineStr">
+      <c r="J72" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K70" s="30" t="inlineStr">
+      <c r="K72" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L70" s="30" t="inlineStr">
+      <c r="L72" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M70" s="30" t="inlineStr">
+      <c r="M72" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N70" s="30" t="inlineStr">
+      <c r="N72" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O70" s="30" t="inlineStr">
+      <c r="O72" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P70" s="30" t="inlineStr">
+      <c r="P72" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q70" s="30" t="inlineStr">
+      <c r="Q72" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B71" s="32" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="C71" s="32" t="n">
-        <v>4.133</v>
-      </c>
-      <c r="D71" s="32" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="E71" s="32" t="n">
-        <v>3.333</v>
-      </c>
-      <c r="F71" s="32" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="G71" s="32" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="H71" s="33" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="I71" s="32" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J71" s="33" t="inlineStr">
-        <is>
-          <t>6th</t>
-        </is>
-      </c>
-      <c r="K71" s="32" t="n">
-        <v>3</v>
-      </c>
-      <c r="L71" s="32" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="M71" s="32" t="n">
-        <v>4.467</v>
-      </c>
-      <c r="N71" s="32" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O71" s="32" t="n">
-        <v>4.033</v>
-      </c>
-      <c r="P71" s="32" t="n">
-        <v>4.012</v>
-      </c>
-      <c r="Q71" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="31" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B72" s="32" t="n">
-        <v>7.782</v>
-      </c>
-      <c r="C72" s="32" t="n">
-        <v>7.567</v>
-      </c>
-      <c r="D72" s="32" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="E72" s="32" t="n">
-        <v>6.533</v>
-      </c>
-      <c r="F72" s="32" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="G72" s="32" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="H72" s="33" t="inlineStr">
-        <is>
-          <t>4th</t>
-        </is>
-      </c>
-      <c r="I72" s="32" t="inlineStr"/>
-      <c r="J72" s="33" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="K72" s="32" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="L72" s="32" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="M72" s="32" t="n">
-        <v>7.867</v>
-      </c>
-      <c r="N72" s="32" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="O72" s="32" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="P72" s="32" t="n">
-        <v>8.185</v>
-      </c>
-      <c r="Q72" s="35" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B73" s="32" t="n">
-        <v>1.018</v>
+        <v>4.03</v>
       </c>
       <c r="C73" s="32" t="n">
-        <v>1.1</v>
+        <v>4.133</v>
       </c>
       <c r="D73" s="32" t="n">
-        <v>0.9</v>
+        <v>3.55</v>
       </c>
       <c r="E73" s="32" t="n">
-        <v>1</v>
+        <v>3.333</v>
       </c>
       <c r="F73" s="32" t="n">
-        <v>1.2</v>
+        <v>3.9</v>
       </c>
       <c r="G73" s="32" t="n">
-        <v>1.6</v>
+        <v>5.4</v>
       </c>
       <c r="H73" s="33" t="inlineStr">
         <is>
-          <t>7th</t>
-        </is>
-      </c>
-      <c r="I73" s="32" t="inlineStr"/>
-      <c r="J73" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="I73" s="32" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="J73" s="33" t="inlineStr">
+        <is>
+          <t>6th</t>
+        </is>
+      </c>
+      <c r="K73" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="L73" s="32" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="M73" s="32" t="n">
+        <v>4.467</v>
+      </c>
+      <c r="N73" s="32" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O73" s="32" t="n">
+        <v>4.033</v>
+      </c>
+      <c r="P73" s="32" t="n">
+        <v>4.012</v>
       </c>
       <c r="Q73" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B74" s="32" t="n">
-        <v>8.442</v>
+        <v>7.782</v>
       </c>
       <c r="C74" s="32" t="n">
-        <v>9.1</v>
+        <v>7.567</v>
       </c>
       <c r="D74" s="32" t="n">
-        <v>9.199999999999999</v>
+        <v>6.65</v>
       </c>
       <c r="E74" s="32" t="n">
-        <v>9.199999999999999</v>
+        <v>6.533</v>
       </c>
       <c r="F74" s="32" t="n">
-        <v>8.300000000000001</v>
+        <v>7.1</v>
       </c>
       <c r="G74" s="32" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="H74" s="33" t="inlineStr">
         <is>
-          <t>10th</t>
+          <t>4th</t>
         </is>
       </c>
       <c r="I74" s="32" t="inlineStr"/>
-      <c r="J74" s="34" t="inlineStr">
-        <is>
-          <t>11th</t>
+      <c r="J74" s="33" t="inlineStr">
+        <is>
+          <t>2nd</t>
         </is>
       </c>
       <c r="K74" s="32" t="n">
-        <v>9.800000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="L74" s="32" t="n">
-        <v>8.5</v>
+        <v>6.3</v>
       </c>
       <c r="M74" s="32" t="n">
-        <v>7.933</v>
+        <v>7.867</v>
       </c>
       <c r="N74" s="32" t="n">
-        <v>8.050000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="O74" s="32" t="n">
-        <v>8.067</v>
+        <v>7.9</v>
       </c>
       <c r="P74" s="32" t="n">
-        <v>7.857</v>
+        <v>8.185</v>
       </c>
       <c r="Q74" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="31" t="inlineStr">
         <is>
-          <t>1st Inn R/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B75" s="32" t="n">
-        <v>0.594</v>
+        <v>1.018</v>
       </c>
       <c r="C75" s="32" t="n">
-        <v>0.633</v>
+        <v>1.1</v>
       </c>
       <c r="D75" s="32" t="n">
         <v>0.9</v>
       </c>
       <c r="E75" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="F75" s="32" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G75" s="32" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H75" s="33" t="inlineStr">
+        <is>
+          <t>7th</t>
+        </is>
+      </c>
+      <c r="I75" s="32" t="inlineStr"/>
+      <c r="J75" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q75" s="35" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="31" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B76" s="32" t="n">
+        <v>8.442</v>
+      </c>
+      <c r="C76" s="32" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="D76" s="32" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="E76" s="32" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="F76" s="32" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="G76" s="32" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="H76" s="33" t="inlineStr">
+        <is>
+          <t>10th</t>
+        </is>
+      </c>
+      <c r="I76" s="32" t="inlineStr"/>
+      <c r="J76" s="34" t="inlineStr">
+        <is>
+          <t>11th</t>
+        </is>
+      </c>
+      <c r="K76" s="32" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="L76" s="32" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="M76" s="32" t="n">
+        <v>7.933</v>
+      </c>
+      <c r="N76" s="32" t="n">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="O76" s="32" t="n">
+        <v>8.067</v>
+      </c>
+      <c r="P76" s="32" t="n">
+        <v>7.857</v>
+      </c>
+      <c r="Q76" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="31" t="inlineStr">
+        <is>
+          <t>1st Inn R/G</t>
+        </is>
+      </c>
+      <c r="B77" s="32" t="n">
+        <v>0.594</v>
+      </c>
+      <c r="C77" s="32" t="n">
+        <v>0.633</v>
+      </c>
+      <c r="D77" s="32" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E77" s="32" t="n">
         <v>0.867</v>
       </c>
-      <c r="F75" s="32" t="n">
+      <c r="F77" s="32" t="n">
         <v>0.9</v>
       </c>
-      <c r="G75" s="32" t="n">
+      <c r="G77" s="32" t="n">
         <v>1.2</v>
       </c>
-      <c r="H75" s="33" t="inlineStr">
+      <c r="H77" s="33" t="inlineStr">
         <is>
           <t>3rd</t>
         </is>
       </c>
-      <c r="I75" s="32" t="inlineStr"/>
-      <c r="J75" s="33" t="inlineStr">
+      <c r="I77" s="32" t="inlineStr"/>
+      <c r="J77" s="33" t="inlineStr">
         <is>
           <t>3rd</t>
         </is>
       </c>
-      <c r="K75" s="32" t="n">
+      <c r="K77" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="L75" s="32" t="n">
+      <c r="L77" s="32" t="n">
         <v>0.1</v>
       </c>
-      <c r="M75" s="32" t="n">
+      <c r="M77" s="32" t="n">
         <v>0.467</v>
       </c>
-      <c r="N75" s="32" t="n">
+      <c r="N77" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="O75" s="32" t="n">
+      <c r="O77" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="P75" s="32" t="n">
+      <c r="P77" s="32" t="n">
         <v>0.399</v>
       </c>
-      <c r="Q75" s="35" t="inlineStr">
+      <c r="Q77" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -4530,7 +4530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q75"/>
+  <dimension ref="A1:Q77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4547,823 +4547,823 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="29" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="29" t="inlineStr">
         <is>
           <t>Arizona Diamondbacks offense vs Tampa Bay Rays defense</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="30" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B62" s="30" t="inlineStr">
+      <c r="B64" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C62" s="30" t="inlineStr">
+      <c r="C64" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D62" s="30" t="inlineStr">
+      <c r="D64" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E62" s="30" t="inlineStr">
+      <c r="E64" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F62" s="30" t="inlineStr">
+      <c r="F64" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G62" s="30" t="inlineStr">
+      <c r="G64" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H62" s="30" t="inlineStr">
+      <c r="H64" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I62" s="30" t="inlineStr">
+      <c r="I64" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J62" s="30" t="inlineStr">
+      <c r="J64" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K62" s="30" t="inlineStr">
+      <c r="K64" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L62" s="30" t="inlineStr">
+      <c r="L64" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M62" s="30" t="inlineStr">
+      <c r="M64" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N62" s="30" t="inlineStr">
+      <c r="N64" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O62" s="30" t="inlineStr">
+      <c r="O64" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P62" s="30" t="inlineStr">
+      <c r="P64" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q62" s="30" t="inlineStr">
+      <c r="Q64" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B63" s="32" t="n">
-        <v>4.976</v>
-      </c>
-      <c r="C63" s="32" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="D63" s="32" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="E63" s="32" t="n">
-        <v>4.467</v>
-      </c>
-      <c r="F63" s="32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="G63" s="32" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="H63" s="36" t="inlineStr">
-        <is>
-          <t>25th</t>
-        </is>
-      </c>
-      <c r="I63" s="32" t="inlineStr"/>
-      <c r="J63" s="36" t="inlineStr">
-        <is>
-          <t>26th</t>
-        </is>
-      </c>
-      <c r="K63" s="32" t="n">
-        <v>6</v>
-      </c>
-      <c r="L63" s="32" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="M63" s="32" t="n">
-        <v>4.867</v>
-      </c>
-      <c r="N63" s="32" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="O63" s="32" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="P63" s="32" t="n">
-        <v>4.234</v>
-      </c>
-      <c r="Q63" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="31" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B64" s="32" t="n">
-        <v>8.688000000000001</v>
-      </c>
-      <c r="C64" s="32" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="D64" s="32" t="n">
-        <v>8.85</v>
-      </c>
-      <c r="E64" s="32" t="n">
-        <v>9</v>
-      </c>
-      <c r="F64" s="32" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="G64" s="32" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="H64" s="34" t="inlineStr">
-        <is>
-          <t>12th</t>
-        </is>
-      </c>
-      <c r="I64" s="32" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J64" s="34" t="inlineStr">
-        <is>
-          <t>17th</t>
-        </is>
-      </c>
-      <c r="K64" s="32" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="L64" s="32" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="M64" s="32" t="n">
-        <v>8.067</v>
-      </c>
-      <c r="N64" s="32" t="n">
-        <v>8.050000000000001</v>
-      </c>
-      <c r="O64" s="32" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="P64" s="32" t="n">
-        <v>7.868</v>
-      </c>
-      <c r="Q64" s="35" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B65" s="32" t="n">
-        <v>1.329</v>
+        <v>4.976</v>
       </c>
       <c r="C65" s="32" t="n">
-        <v>1.033</v>
+        <v>4.7</v>
       </c>
       <c r="D65" s="32" t="n">
-        <v>0.85</v>
+        <v>4.45</v>
       </c>
       <c r="E65" s="32" t="n">
-        <v>1</v>
+        <v>4.467</v>
       </c>
       <c r="F65" s="32" t="n">
-        <v>0.9</v>
+        <v>3.4</v>
       </c>
       <c r="G65" s="32" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="H65" s="36" t="inlineStr">
         <is>
-          <t>22nd</t>
+          <t>25th</t>
         </is>
       </c>
       <c r="I65" s="32" t="inlineStr"/>
-      <c r="J65" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K65" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L65" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M65" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N65" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O65" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P65" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J65" s="36" t="inlineStr">
+        <is>
+          <t>26th</t>
+        </is>
+      </c>
+      <c r="K65" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="L65" s="32" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="M65" s="32" t="n">
+        <v>4.867</v>
+      </c>
+      <c r="N65" s="32" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O65" s="32" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="P65" s="32" t="n">
+        <v>4.234</v>
       </c>
       <c r="Q65" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B66" s="32" t="n">
-        <v>8.265000000000001</v>
+        <v>8.688000000000001</v>
       </c>
       <c r="C66" s="32" t="n">
-        <v>8.467000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D66" s="32" t="n">
-        <v>8.35</v>
+        <v>8.85</v>
       </c>
       <c r="E66" s="32" t="n">
+        <v>9</v>
+      </c>
+      <c r="F66" s="32" t="n">
         <v>8.4</v>
       </c>
-      <c r="F66" s="32" t="n">
-        <v>8.6</v>
-      </c>
       <c r="G66" s="32" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="H66" s="36" t="inlineStr">
-        <is>
-          <t>23rd</t>
-        </is>
-      </c>
-      <c r="I66" s="32" t="inlineStr"/>
+        <v>7.6</v>
+      </c>
+      <c r="H66" s="34" t="inlineStr">
+        <is>
+          <t>12th</t>
+        </is>
+      </c>
+      <c r="I66" s="32" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
       <c r="J66" s="34" t="inlineStr">
         <is>
-          <t>15th</t>
+          <t>17th</t>
         </is>
       </c>
       <c r="K66" s="32" t="n">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L66" s="32" t="n">
-        <v>8.699999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="M66" s="32" t="n">
-        <v>8.333</v>
+        <v>8.067</v>
       </c>
       <c r="N66" s="32" t="n">
-        <v>8.800000000000001</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="O66" s="32" t="n">
-        <v>9.5</v>
+        <v>7.8</v>
       </c>
       <c r="P66" s="32" t="n">
-        <v>8.737</v>
+        <v>7.868</v>
       </c>
       <c r="Q66" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="31" t="inlineStr">
         <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B67" s="32" t="n">
+        <v>1.329</v>
+      </c>
+      <c r="C67" s="32" t="n">
+        <v>1.033</v>
+      </c>
+      <c r="D67" s="32" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="E67" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="F67" s="32" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G67" s="32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H67" s="36" t="inlineStr">
+        <is>
+          <t>22nd</t>
+        </is>
+      </c>
+      <c r="I67" s="32" t="inlineStr"/>
+      <c r="J67" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K67" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L67" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M67" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N67" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O67" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P67" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q67" s="35" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="31" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B68" s="32" t="n">
+        <v>8.265000000000001</v>
+      </c>
+      <c r="C68" s="32" t="n">
+        <v>8.467000000000001</v>
+      </c>
+      <c r="D68" s="32" t="n">
+        <v>8.35</v>
+      </c>
+      <c r="E68" s="32" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="F68" s="32" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="G68" s="32" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="H68" s="36" t="inlineStr">
+        <is>
+          <t>23rd</t>
+        </is>
+      </c>
+      <c r="I68" s="32" t="inlineStr"/>
+      <c r="J68" s="34" t="inlineStr">
+        <is>
+          <t>15th</t>
+        </is>
+      </c>
+      <c r="K68" s="32" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="L68" s="32" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M68" s="32" t="n">
+        <v>8.333</v>
+      </c>
+      <c r="N68" s="32" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="O68" s="32" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="P68" s="32" t="n">
+        <v>8.737</v>
+      </c>
+      <c r="Q68" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B67" s="32" t="n">
+      <c r="B69" s="32" t="n">
         <v>0.612</v>
       </c>
-      <c r="C67" s="32" t="n">
+      <c r="C69" s="32" t="n">
         <v>0.467</v>
       </c>
-      <c r="D67" s="32" t="n">
+      <c r="D69" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="E67" s="32" t="n">
+      <c r="E69" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="F67" s="32" t="n">
+      <c r="F69" s="32" t="n">
         <v>0.7</v>
       </c>
-      <c r="G67" s="32" t="n">
+      <c r="G69" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="H67" s="33" t="inlineStr">
+      <c r="H69" s="33" t="inlineStr">
         <is>
           <t>10th</t>
         </is>
       </c>
-      <c r="I67" s="32" t="inlineStr">
+      <c r="I69" s="32" t="inlineStr">
         <is>
           <t>★★★</t>
         </is>
       </c>
-      <c r="J67" s="36" t="inlineStr">
+      <c r="J69" s="36" t="inlineStr">
         <is>
           <t>25th</t>
         </is>
       </c>
-      <c r="K67" s="32" t="n">
+      <c r="K69" s="32" t="n">
         <v>1.2</v>
       </c>
-      <c r="L67" s="32" t="n">
+      <c r="L69" s="32" t="n">
         <v>0.8</v>
       </c>
-      <c r="M67" s="32" t="n">
+      <c r="M69" s="32" t="n">
         <v>0.667</v>
       </c>
-      <c r="N67" s="32" t="n">
+      <c r="N69" s="32" t="n">
         <v>0.65</v>
       </c>
-      <c r="O67" s="32" t="n">
+      <c r="O69" s="32" t="n">
         <v>0.467</v>
       </c>
-      <c r="P67" s="32" t="n">
+      <c r="P69" s="32" t="n">
         <v>0.473</v>
       </c>
-      <c r="Q67" s="35" t="inlineStr">
+      <c r="Q69" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="29" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="29" t="inlineStr">
         <is>
           <t>Tampa Bay Rays offense vs Arizona Diamondbacks defense</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="30" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B70" s="30" t="inlineStr">
+      <c r="B72" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C70" s="30" t="inlineStr">
+      <c r="C72" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D70" s="30" t="inlineStr">
+      <c r="D72" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E70" s="30" t="inlineStr">
+      <c r="E72" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F70" s="30" t="inlineStr">
+      <c r="F72" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G70" s="30" t="inlineStr">
+      <c r="G72" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H70" s="30" t="inlineStr">
+      <c r="H72" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I70" s="30" t="inlineStr">
+      <c r="I72" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J70" s="30" t="inlineStr">
+      <c r="J72" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K70" s="30" t="inlineStr">
+      <c r="K72" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L70" s="30" t="inlineStr">
+      <c r="L72" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M70" s="30" t="inlineStr">
+      <c r="M72" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N70" s="30" t="inlineStr">
+      <c r="N72" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O70" s="30" t="inlineStr">
+      <c r="O72" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P70" s="30" t="inlineStr">
+      <c r="P72" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q70" s="30" t="inlineStr">
+      <c r="Q72" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B71" s="32" t="n">
-        <v>4.437</v>
-      </c>
-      <c r="C71" s="32" t="n">
-        <v>4.033</v>
-      </c>
-      <c r="D71" s="32" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="E71" s="32" t="n">
-        <v>3.667</v>
-      </c>
-      <c r="F71" s="32" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="G71" s="32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="H71" s="34" t="inlineStr">
-        <is>
-          <t>14th</t>
-        </is>
-      </c>
-      <c r="I71" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J71" s="36" t="inlineStr">
-        <is>
-          <t>30th</t>
-        </is>
-      </c>
-      <c r="K71" s="32" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="L71" s="32" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="M71" s="32" t="n">
-        <v>5.333</v>
-      </c>
-      <c r="N71" s="32" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="O71" s="32" t="n">
-        <v>4.767</v>
-      </c>
-      <c r="P71" s="32" t="n">
-        <v>4.847</v>
-      </c>
-      <c r="Q71" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="31" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B72" s="32" t="n">
-        <v>8.521000000000001</v>
-      </c>
-      <c r="C72" s="32" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="D72" s="32" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="E72" s="32" t="n">
-        <v>8.667</v>
-      </c>
-      <c r="F72" s="32" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="G72" s="32" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="H72" s="33" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="I72" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J72" s="36" t="inlineStr">
-        <is>
-          <t>27th</t>
-        </is>
-      </c>
-      <c r="K72" s="32" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="L72" s="32" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="M72" s="32" t="n">
-        <v>9.132999999999999</v>
-      </c>
-      <c r="N72" s="32" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="O72" s="32" t="n">
-        <v>8.567</v>
-      </c>
-      <c r="P72" s="32" t="n">
-        <v>8.840999999999999</v>
-      </c>
-      <c r="Q72" s="35" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B73" s="32" t="n">
-        <v>1.114</v>
+        <v>4.437</v>
       </c>
       <c r="C73" s="32" t="n">
-        <v>1.133</v>
+        <v>4.033</v>
       </c>
       <c r="D73" s="32" t="n">
-        <v>1.15</v>
+        <v>3.55</v>
       </c>
       <c r="E73" s="32" t="n">
-        <v>1</v>
+        <v>3.667</v>
       </c>
       <c r="F73" s="32" t="n">
-        <v>1</v>
+        <v>3.9</v>
       </c>
       <c r="G73" s="32" t="n">
-        <v>1</v>
+        <v>3.6</v>
       </c>
       <c r="H73" s="34" t="inlineStr">
         <is>
-          <t>17th</t>
-        </is>
-      </c>
-      <c r="I73" s="32" t="inlineStr"/>
-      <c r="J73" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>14th</t>
+        </is>
+      </c>
+      <c r="I73" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J73" s="36" t="inlineStr">
+        <is>
+          <t>30th</t>
+        </is>
+      </c>
+      <c r="K73" s="32" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="L73" s="32" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="M73" s="32" t="n">
+        <v>5.333</v>
+      </c>
+      <c r="N73" s="32" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="O73" s="32" t="n">
+        <v>4.767</v>
+      </c>
+      <c r="P73" s="32" t="n">
+        <v>4.847</v>
       </c>
       <c r="Q73" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B74" s="32" t="n">
-        <v>8.611000000000001</v>
+        <v>8.521000000000001</v>
       </c>
       <c r="C74" s="32" t="n">
-        <v>8.967000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="D74" s="32" t="n">
-        <v>9.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E74" s="32" t="n">
-        <v>9.667</v>
+        <v>8.667</v>
       </c>
       <c r="F74" s="32" t="n">
-        <v>9.199999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="G74" s="32" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="H74" s="34" t="inlineStr">
-        <is>
-          <t>18th</t>
-        </is>
-      </c>
-      <c r="I74" s="32" t="inlineStr"/>
-      <c r="J74" s="34" t="inlineStr">
-        <is>
-          <t>16th</t>
+        <v>9.6</v>
+      </c>
+      <c r="H74" s="33" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="I74" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J74" s="36" t="inlineStr">
+        <is>
+          <t>27th</t>
         </is>
       </c>
       <c r="K74" s="32" t="n">
-        <v>9.4</v>
+        <v>10.4</v>
       </c>
       <c r="L74" s="32" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="M74" s="32" t="n">
-        <v>8.333</v>
+        <v>9.132999999999999</v>
       </c>
       <c r="N74" s="32" t="n">
-        <v>7.9</v>
+        <v>8.75</v>
       </c>
       <c r="O74" s="32" t="n">
-        <v>7.8</v>
+        <v>8.567</v>
       </c>
       <c r="P74" s="32" t="n">
-        <v>8.199999999999999</v>
+        <v>8.840999999999999</v>
       </c>
       <c r="Q74" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="31" t="inlineStr">
         <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B75" s="32" t="n">
+        <v>1.114</v>
+      </c>
+      <c r="C75" s="32" t="n">
+        <v>1.133</v>
+      </c>
+      <c r="D75" s="32" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="E75" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="F75" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="H75" s="34" t="inlineStr">
+        <is>
+          <t>17th</t>
+        </is>
+      </c>
+      <c r="I75" s="32" t="inlineStr"/>
+      <c r="J75" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q75" s="35" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="31" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B76" s="32" t="n">
+        <v>8.611000000000001</v>
+      </c>
+      <c r="C76" s="32" t="n">
+        <v>8.967000000000001</v>
+      </c>
+      <c r="D76" s="32" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="E76" s="32" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="F76" s="32" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="G76" s="32" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="H76" s="34" t="inlineStr">
+        <is>
+          <t>18th</t>
+        </is>
+      </c>
+      <c r="I76" s="32" t="inlineStr"/>
+      <c r="J76" s="34" t="inlineStr">
+        <is>
+          <t>16th</t>
+        </is>
+      </c>
+      <c r="K76" s="32" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="L76" s="32" t="n">
+        <v>9</v>
+      </c>
+      <c r="M76" s="32" t="n">
+        <v>8.333</v>
+      </c>
+      <c r="N76" s="32" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="O76" s="32" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="P76" s="32" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Q76" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B75" s="32" t="n">
+      <c r="B77" s="32" t="n">
         <v>0.587</v>
       </c>
-      <c r="C75" s="32" t="n">
+      <c r="C77" s="32" t="n">
         <v>0.867</v>
       </c>
-      <c r="D75" s="32" t="n">
+      <c r="D77" s="32" t="n">
         <v>0.7</v>
       </c>
-      <c r="E75" s="32" t="n">
+      <c r="E77" s="32" t="n">
         <v>0.667</v>
       </c>
-      <c r="F75" s="32" t="n">
+      <c r="F77" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="G75" s="32" t="n">
+      <c r="G77" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="H75" s="34" t="inlineStr">
+      <c r="H77" s="34" t="inlineStr">
         <is>
           <t>16th</t>
         </is>
       </c>
-      <c r="I75" s="32" t="inlineStr">
+      <c r="I77" s="32" t="inlineStr">
         <is>
           <t>★★★</t>
         </is>
       </c>
-      <c r="J75" s="36" t="inlineStr">
+      <c r="J77" s="36" t="inlineStr">
         <is>
           <t>29th</t>
         </is>
       </c>
-      <c r="K75" s="32" t="n">
+      <c r="K77" s="32" t="n">
         <v>1.8</v>
       </c>
-      <c r="L75" s="32" t="n">
+      <c r="L77" s="32" t="n">
         <v>1.1</v>
       </c>
-      <c r="M75" s="32" t="n">
+      <c r="M77" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="N75" s="32" t="n">
+      <c r="N77" s="32" t="n">
         <v>0.9</v>
       </c>
-      <c r="O75" s="32" t="n">
+      <c r="O77" s="32" t="n">
         <v>0.733</v>
       </c>
-      <c r="P75" s="32" t="n">
+      <c r="P77" s="32" t="n">
         <v>0.641</v>
       </c>
-      <c r="Q75" s="35" t="inlineStr">
+      <c r="Q77" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -5382,7 +5382,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q74"/>
+  <dimension ref="A1:Q77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5399,815 +5399,815 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="29" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="29" t="inlineStr">
         <is>
           <t>Washington Nationals offense vs Baltimore Orioles defense</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="30" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B61" s="30" t="inlineStr">
+      <c r="B64" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C61" s="30" t="inlineStr">
+      <c r="C64" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D61" s="30" t="inlineStr">
+      <c r="D64" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E61" s="30" t="inlineStr">
+      <c r="E64" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F61" s="30" t="inlineStr">
+      <c r="F64" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G61" s="30" t="inlineStr">
+      <c r="G64" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H61" s="30" t="inlineStr">
+      <c r="H64" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I61" s="30" t="inlineStr">
+      <c r="I64" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J61" s="30" t="inlineStr">
+      <c r="J64" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K61" s="30" t="inlineStr">
+      <c r="K64" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L61" s="30" t="inlineStr">
+      <c r="L64" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M61" s="30" t="inlineStr">
+      <c r="M64" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N61" s="30" t="inlineStr">
+      <c r="N64" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O61" s="30" t="inlineStr">
+      <c r="O64" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P61" s="30" t="inlineStr">
+      <c r="P64" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q61" s="30" t="inlineStr">
+      <c r="Q64" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B62" s="32" t="n">
-        <v>4.205</v>
-      </c>
-      <c r="C62" s="32" t="n">
-        <v>4.133</v>
-      </c>
-      <c r="D62" s="32" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="E62" s="32" t="n">
-        <v>3.667</v>
-      </c>
-      <c r="F62" s="32" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="G62" s="32" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H62" s="33" t="inlineStr">
-        <is>
-          <t>10th</t>
-        </is>
-      </c>
-      <c r="I62" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J62" s="36" t="inlineStr">
-        <is>
-          <t>23rd</t>
-        </is>
-      </c>
-      <c r="K62" s="32" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="L62" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="M62" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="N62" s="32" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="O62" s="32" t="n">
-        <v>4.667</v>
-      </c>
-      <c r="P62" s="32" t="n">
-        <v>4.886</v>
-      </c>
-      <c r="Q62" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="31" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B63" s="32" t="n">
-        <v>8.054</v>
-      </c>
-      <c r="C63" s="32" t="n">
-        <v>7.833</v>
-      </c>
-      <c r="D63" s="32" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="E63" s="32" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="F63" s="32" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="G63" s="32" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="H63" s="34" t="inlineStr">
-        <is>
-          <t>13th</t>
-        </is>
-      </c>
-      <c r="I63" s="32" t="inlineStr">
-        <is>
-          <t>★★</t>
-        </is>
-      </c>
-      <c r="J63" s="36" t="inlineStr">
-        <is>
-          <t>24th</t>
-        </is>
-      </c>
-      <c r="K63" s="32" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="L63" s="32" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="M63" s="32" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="N63" s="32" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="O63" s="32" t="n">
-        <v>8.567</v>
-      </c>
-      <c r="P63" s="32" t="n">
-        <v>8.837</v>
-      </c>
-      <c r="Q63" s="35" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="31" t="inlineStr">
-        <is>
-          <t>HR/G</t>
-        </is>
-      </c>
-      <c r="B64" s="32" t="n">
-        <v>0.976</v>
-      </c>
-      <c r="C64" s="32" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="D64" s="32" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="E64" s="32" t="n">
-        <v>1.267</v>
-      </c>
-      <c r="F64" s="32" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="G64" s="32" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="H64" s="33" t="inlineStr">
-        <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="I64" s="32" t="inlineStr"/>
-      <c r="J64" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K64" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L64" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M64" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N64" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O64" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P64" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q64" s="35" t="inlineStr">
-        <is>
-          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B65" s="32" t="n">
-        <v>8.372999999999999</v>
+        <v>4.205</v>
       </c>
       <c r="C65" s="32" t="n">
-        <v>9.800000000000001</v>
+        <v>4.133</v>
       </c>
       <c r="D65" s="32" t="n">
-        <v>10</v>
+        <v>4.3</v>
       </c>
       <c r="E65" s="32" t="n">
-        <v>10.733</v>
+        <v>3.667</v>
       </c>
       <c r="F65" s="32" t="n">
-        <v>11</v>
+        <v>4.4</v>
       </c>
       <c r="G65" s="32" t="n">
-        <v>11</v>
-      </c>
-      <c r="H65" s="36" t="inlineStr">
-        <is>
-          <t>25th</t>
-        </is>
-      </c>
-      <c r="I65" s="32" t="inlineStr"/>
+        <v>4.2</v>
+      </c>
+      <c r="H65" s="33" t="inlineStr">
+        <is>
+          <t>10th</t>
+        </is>
+      </c>
+      <c r="I65" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
       <c r="J65" s="36" t="inlineStr">
         <is>
-          <t>22nd</t>
+          <t>23rd</t>
         </is>
       </c>
       <c r="K65" s="32" t="n">
-        <v>8.6</v>
+        <v>5.6</v>
       </c>
       <c r="L65" s="32" t="n">
-        <v>9.800000000000001</v>
+        <v>5</v>
       </c>
       <c r="M65" s="32" t="n">
-        <v>9.467000000000001</v>
+        <v>5</v>
       </c>
       <c r="N65" s="32" t="n">
-        <v>9.300000000000001</v>
+        <v>4.55</v>
       </c>
       <c r="O65" s="32" t="n">
-        <v>8.733000000000001</v>
+        <v>4.667</v>
       </c>
       <c r="P65" s="32" t="n">
-        <v>8.398</v>
+        <v>4.886</v>
       </c>
       <c r="Q65" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="31" t="inlineStr">
         <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B66" s="32" t="n">
+        <v>8.054</v>
+      </c>
+      <c r="C66" s="32" t="n">
+        <v>7.833</v>
+      </c>
+      <c r="D66" s="32" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="E66" s="32" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="F66" s="32" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="G66" s="32" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="H66" s="34" t="inlineStr">
+        <is>
+          <t>13th</t>
+        </is>
+      </c>
+      <c r="I66" s="32" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="J66" s="36" t="inlineStr">
+        <is>
+          <t>24th</t>
+        </is>
+      </c>
+      <c r="K66" s="32" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="L66" s="32" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="M66" s="32" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="N66" s="32" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="O66" s="32" t="n">
+        <v>8.567</v>
+      </c>
+      <c r="P66" s="32" t="n">
+        <v>8.837</v>
+      </c>
+      <c r="Q66" s="35" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="31" t="inlineStr">
+        <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B67" s="32" t="n">
+        <v>0.976</v>
+      </c>
+      <c r="C67" s="32" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D67" s="32" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="E67" s="32" t="n">
+        <v>1.267</v>
+      </c>
+      <c r="F67" s="32" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G67" s="32" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H67" s="33" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="I67" s="32" t="inlineStr"/>
+      <c r="J67" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K67" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L67" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M67" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N67" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O67" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P67" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q67" s="35" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="31" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B68" s="32" t="n">
+        <v>8.372999999999999</v>
+      </c>
+      <c r="C68" s="32" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="D68" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="E68" s="32" t="n">
+        <v>10.733</v>
+      </c>
+      <c r="F68" s="32" t="n">
+        <v>11</v>
+      </c>
+      <c r="G68" s="32" t="n">
+        <v>11</v>
+      </c>
+      <c r="H68" s="36" t="inlineStr">
+        <is>
+          <t>25th</t>
+        </is>
+      </c>
+      <c r="I68" s="32" t="inlineStr"/>
+      <c r="J68" s="36" t="inlineStr">
+        <is>
+          <t>22nd</t>
+        </is>
+      </c>
+      <c r="K68" s="32" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="L68" s="32" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="M68" s="32" t="n">
+        <v>9.467000000000001</v>
+      </c>
+      <c r="N68" s="32" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="O68" s="32" t="n">
+        <v>8.733000000000001</v>
+      </c>
+      <c r="P68" s="32" t="n">
+        <v>8.398</v>
+      </c>
+      <c r="Q68" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B66" s="32" t="n">
+      <c r="B69" s="32" t="n">
         <v>0.584</v>
       </c>
-      <c r="C66" s="32" t="n">
+      <c r="C69" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="D66" s="32" t="n">
+      <c r="D69" s="32" t="n">
         <v>0.35</v>
       </c>
-      <c r="E66" s="32" t="n">
+      <c r="E69" s="32" t="n">
         <v>0.267</v>
       </c>
-      <c r="F66" s="32" t="n">
+      <c r="F69" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="G66" s="32" t="n">
+      <c r="G69" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="H66" s="34" t="inlineStr">
+      <c r="H69" s="34" t="inlineStr">
         <is>
           <t>18th</t>
         </is>
       </c>
-      <c r="I66" s="32" t="inlineStr">
+      <c r="I69" s="32" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="J66" s="36" t="inlineStr">
+      <c r="J69" s="36" t="inlineStr">
         <is>
           <t>24th</t>
         </is>
       </c>
-      <c r="K66" s="32" t="n">
+      <c r="K69" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="L66" s="32" t="n">
+      <c r="L69" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="M66" s="32" t="n">
+      <c r="M69" s="32" t="n">
         <v>0.867</v>
       </c>
-      <c r="N66" s="32" t="n">
+      <c r="N69" s="32" t="n">
         <v>0.8</v>
       </c>
-      <c r="O66" s="32" t="n">
+      <c r="O69" s="32" t="n">
         <v>0.8</v>
       </c>
-      <c r="P66" s="32" t="n">
+      <c r="P69" s="32" t="n">
         <v>0.657</v>
       </c>
-      <c r="Q66" s="35" t="inlineStr">
+      <c r="Q69" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="29" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="29" t="inlineStr">
         <is>
           <t>Baltimore Orioles offense vs Washington Nationals defense</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="30" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B69" s="30" t="inlineStr">
+      <c r="B72" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C69" s="30" t="inlineStr">
+      <c r="C72" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D69" s="30" t="inlineStr">
+      <c r="D72" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E69" s="30" t="inlineStr">
+      <c r="E72" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F69" s="30" t="inlineStr">
+      <c r="F72" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G69" s="30" t="inlineStr">
+      <c r="G72" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H69" s="30" t="inlineStr">
+      <c r="H72" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I69" s="30" t="inlineStr">
+      <c r="I72" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J69" s="30" t="inlineStr">
+      <c r="J72" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K69" s="30" t="inlineStr">
+      <c r="K72" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L69" s="30" t="inlineStr">
+      <c r="L72" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M69" s="30" t="inlineStr">
+      <c r="M72" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N69" s="30" t="inlineStr">
+      <c r="N72" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O69" s="30" t="inlineStr">
+      <c r="O72" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P69" s="30" t="inlineStr">
+      <c r="P72" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q69" s="30" t="inlineStr">
+      <c r="Q72" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B70" s="32" t="n">
-        <v>4.181</v>
-      </c>
-      <c r="C70" s="32" t="n">
-        <v>3.567</v>
-      </c>
-      <c r="D70" s="32" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="E70" s="32" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="F70" s="32" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="G70" s="32" t="n">
-        <v>3</v>
-      </c>
-      <c r="H70" s="36" t="inlineStr">
-        <is>
-          <t>22nd</t>
-        </is>
-      </c>
-      <c r="I70" s="32" t="inlineStr"/>
-      <c r="J70" s="36" t="inlineStr">
-        <is>
-          <t>24th</t>
-        </is>
-      </c>
-      <c r="K70" s="32" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="L70" s="32" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="M70" s="32" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="N70" s="32" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="O70" s="32" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="P70" s="32" t="n">
-        <v>5.566</v>
-      </c>
-      <c r="Q70" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="31" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B71" s="32" t="n">
-        <v>7.861</v>
-      </c>
-      <c r="C71" s="32" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="D71" s="32" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="E71" s="32" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="F71" s="32" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="G71" s="32" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="H71" s="36" t="inlineStr">
-        <is>
-          <t>29th</t>
-        </is>
-      </c>
-      <c r="I71" s="32" t="inlineStr"/>
-      <c r="J71" s="36" t="inlineStr">
-        <is>
-          <t>21st</t>
-        </is>
-      </c>
-      <c r="K71" s="32" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="L71" s="32" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="M71" s="32" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="N71" s="32" t="n">
-        <v>10.05</v>
-      </c>
-      <c r="O71" s="32" t="n">
-        <v>9</v>
-      </c>
-      <c r="P71" s="32" t="n">
-        <v>9.259</v>
-      </c>
-      <c r="Q71" s="35" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="31" t="inlineStr">
-        <is>
-          <t>HR/G</t>
-        </is>
-      </c>
-      <c r="B72" s="32" t="n">
-        <v>1.175</v>
-      </c>
-      <c r="C72" s="32" t="n">
-        <v>1.067</v>
-      </c>
-      <c r="D72" s="32" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="E72" s="32" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="F72" s="32" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="G72" s="32" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="H72" s="33" t="inlineStr">
-        <is>
-          <t>8th</t>
-        </is>
-      </c>
-      <c r="I72" s="32" t="inlineStr"/>
-      <c r="J72" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q72" s="35" t="inlineStr">
-        <is>
-          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B73" s="32" t="n">
-        <v>9.048</v>
+        <v>4.181</v>
       </c>
       <c r="C73" s="32" t="n">
-        <v>10.333</v>
+        <v>3.567</v>
       </c>
       <c r="D73" s="32" t="n">
-        <v>10.35</v>
+        <v>2.95</v>
       </c>
       <c r="E73" s="32" t="n">
-        <v>10</v>
+        <v>3.2</v>
       </c>
       <c r="F73" s="32" t="n">
-        <v>10.3</v>
+        <v>2.7</v>
       </c>
       <c r="G73" s="32" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="H73" s="34" t="inlineStr">
-        <is>
-          <t>20th</t>
+        <v>3</v>
+      </c>
+      <c r="H73" s="36" t="inlineStr">
+        <is>
+          <t>22nd</t>
         </is>
       </c>
       <c r="I73" s="32" t="inlineStr"/>
-      <c r="J73" s="34" t="inlineStr">
-        <is>
-          <t>13th</t>
+      <c r="J73" s="36" t="inlineStr">
+        <is>
+          <t>24th</t>
         </is>
       </c>
       <c r="K73" s="32" t="n">
-        <v>9.6</v>
+        <v>5.8</v>
       </c>
       <c r="L73" s="32" t="n">
-        <v>9</v>
+        <v>6.6</v>
       </c>
       <c r="M73" s="32" t="n">
-        <v>8.333</v>
+        <v>6.4</v>
       </c>
       <c r="N73" s="32" t="n">
-        <v>7.75</v>
+        <v>6.3</v>
       </c>
       <c r="O73" s="32" t="n">
-        <v>8.233000000000001</v>
+        <v>5.8</v>
       </c>
       <c r="P73" s="32" t="n">
-        <v>7.729</v>
+        <v>5.566</v>
       </c>
       <c r="Q73" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="31" t="inlineStr">
         <is>
-          <t>1st Inn R/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B74" s="32" t="n">
-        <v>0.428</v>
+        <v>7.861</v>
       </c>
       <c r="C74" s="32" t="n">
-        <v>0.333</v>
+        <v>6.9</v>
       </c>
       <c r="D74" s="32" t="n">
-        <v>0.35</v>
+        <v>6.2</v>
       </c>
       <c r="E74" s="32" t="n">
-        <v>0.333</v>
+        <v>6.2</v>
       </c>
       <c r="F74" s="32" t="n">
-        <v>0.2</v>
+        <v>5.2</v>
       </c>
       <c r="G74" s="32" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="H74" s="36" t="inlineStr">
         <is>
-          <t>27th</t>
+          <t>29th</t>
         </is>
       </c>
       <c r="I74" s="32" t="inlineStr"/>
       <c r="J74" s="36" t="inlineStr">
         <is>
+          <t>21st</t>
+        </is>
+      </c>
+      <c r="K74" s="32" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="L74" s="32" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="M74" s="32" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="N74" s="32" t="n">
+        <v>10.05</v>
+      </c>
+      <c r="O74" s="32" t="n">
+        <v>9</v>
+      </c>
+      <c r="P74" s="32" t="n">
+        <v>9.259</v>
+      </c>
+      <c r="Q74" s="35" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="31" t="inlineStr">
+        <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B75" s="32" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="C75" s="32" t="n">
+        <v>1.067</v>
+      </c>
+      <c r="D75" s="32" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="E75" s="32" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F75" s="32" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G75" s="32" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H75" s="33" t="inlineStr">
+        <is>
+          <t>8th</t>
+        </is>
+      </c>
+      <c r="I75" s="32" t="inlineStr"/>
+      <c r="J75" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q75" s="35" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="31" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B76" s="32" t="n">
+        <v>9.048</v>
+      </c>
+      <c r="C76" s="32" t="n">
+        <v>10.333</v>
+      </c>
+      <c r="D76" s="32" t="n">
+        <v>10.35</v>
+      </c>
+      <c r="E76" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="F76" s="32" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="G76" s="32" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="H76" s="34" t="inlineStr">
+        <is>
+          <t>20th</t>
+        </is>
+      </c>
+      <c r="I76" s="32" t="inlineStr"/>
+      <c r="J76" s="34" t="inlineStr">
+        <is>
+          <t>13th</t>
+        </is>
+      </c>
+      <c r="K76" s="32" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="L76" s="32" t="n">
+        <v>9</v>
+      </c>
+      <c r="M76" s="32" t="n">
+        <v>8.333</v>
+      </c>
+      <c r="N76" s="32" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="O76" s="32" t="n">
+        <v>8.233000000000001</v>
+      </c>
+      <c r="P76" s="32" t="n">
+        <v>7.729</v>
+      </c>
+      <c r="Q76" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="31" t="inlineStr">
+        <is>
+          <t>1st Inn R/G</t>
+        </is>
+      </c>
+      <c r="B77" s="32" t="n">
+        <v>0.428</v>
+      </c>
+      <c r="C77" s="32" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="D77" s="32" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E77" s="32" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="F77" s="32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G77" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" s="36" t="inlineStr">
+        <is>
+          <t>27th</t>
+        </is>
+      </c>
+      <c r="I77" s="32" t="inlineStr"/>
+      <c r="J77" s="36" t="inlineStr">
+        <is>
           <t>26th</t>
         </is>
       </c>
-      <c r="K74" s="32" t="n">
+      <c r="K77" s="32" t="n">
         <v>1.2</v>
       </c>
-      <c r="L74" s="32" t="n">
+      <c r="L77" s="32" t="n">
         <v>0.8</v>
       </c>
-      <c r="M74" s="32" t="n">
+      <c r="M77" s="32" t="n">
         <v>0.733</v>
       </c>
-      <c r="N74" s="32" t="n">
+      <c r="N77" s="32" t="n">
         <v>0.65</v>
       </c>
-      <c r="O74" s="32" t="n">
+      <c r="O77" s="32" t="n">
         <v>0.8</v>
       </c>
-      <c r="P74" s="32" t="n">
+      <c r="P77" s="32" t="n">
         <v>0.717</v>
       </c>
-      <c r="Q74" s="35" t="inlineStr">
+      <c r="Q77" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -8138,7 +8138,7 @@
         <v>-251</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>100</v>
+        <v>-104</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -8198,10 +8198,10 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.4990808823529412</v>
+        <v>0.4966544117647059</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H6" s="15" t="n">
         <v>172</v>
@@ -8228,7 +8228,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 49.9% (fair +100). Your call.</t>
+          <t>Model 49.7% (fair +101). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -8240,17 +8240,17 @@
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>Kansas City Royals @ Chicago White Sox</t>
+          <t>Phoenix Mercury @ Toronto Tempo</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
@@ -8260,17 +8260,17 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Over 8</t>
+          <t>Over 179.5</t>
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.646390243902439</v>
+        <v>0.6043749999999999</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-183</v>
+        <v>-153</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>-105</v>
+        <v>108</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 64.6% (fair -183). Your call.</t>
+          <t>Model 60.4% (fair -153). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -8306,37 +8306,37 @@
     <row r="8">
       <c r="A8" s="20" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>Phoenix Mercury @ Toronto Tempo</t>
+          <t>Cincinnati Reds @ Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>Over 179.5</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.6043749999999999</v>
+        <v>0.6685819819819819</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>-153</v>
+        <v>-202</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>108</v>
+        <v>-122</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 60.4% (fair -153). Your call.</t>
+          <t>Model 66.9% (fair -202). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -8377,32 +8377,32 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>Cincinnati Reds @ Pittsburgh Pirates</t>
+          <t>Portland Fire @ Washington Mystics</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>Over 165.5</t>
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.664206572769953</v>
+        <v>0.6033500000000001</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>-198</v>
+        <v>-152</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>-113</v>
+        <v>100</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -8426,7 +8426,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 66.4% (fair -198). Your call.</t>
+          <t>Model 60.3% (fair -152). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -8443,12 +8443,12 @@
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>Portland Fire @ Washington Mystics</t>
+          <t>Washington Nationals @ Baltimore Orioles</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -8458,17 +8458,17 @@
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>Over 164.5</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.6287809523809523</v>
+        <v>0.5857560975609757</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-169</v>
+        <v>-141</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>-110</v>
+        <v>105</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -8492,7 +8492,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 62.9% (fair -169). Your call.</t>
+          <t>Model 58.6% (fair -141). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -8504,17 +8504,17 @@
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>New York Liberty @ Golden State Valkyries</t>
+          <t>Cincinnati Reds @ Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
@@ -8524,17 +8524,17 @@
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>Golden State Valkyries</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.571</v>
+        <v>0.559656862745098</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>-133</v>
+        <v>-127</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -8558,7 +8558,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 57.1% (fair -133). Your call.</t>
+          <t>Model 56.0% (fair -127). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -8575,12 +8575,12 @@
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>Washington Nationals @ Baltimore Orioles</t>
+          <t>Kansas City Royals @ Chicago White Sox</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -8594,13 +8594,13 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.5946285714285714</v>
+        <v>0.5817512195121951</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>-147</v>
+        <v>-139</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>-110</v>
+        <v>-105</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -8624,7 +8624,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 59.5% (fair -147). Your call.</t>
+          <t>Model 58.2% (fair -139). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -8636,17 +8636,17 @@
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Cincinnati Reds @ Pittsburgh Pirates</t>
+          <t>New York Liberty @ Golden State Valkyries</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
@@ -8656,17 +8656,17 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>Golden State Valkyries</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.5608910891089109</v>
+        <v>0.578321568627451</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>-128</v>
+        <v>-137</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>102</v>
+        <v>-104</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -8690,7 +8690,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 56.1% (fair -128). Your call.</t>
+          <t>Model 57.8% (fair -137). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -8707,32 +8707,32 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>Seattle Mariners @ Cleveland Guardians</t>
+          <t>New York Liberty @ Golden State Valkyries</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Seattle Mariners</t>
+          <t>Golden State Valkyries +1.5</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.5461764705882354</v>
+        <v>0.576435294117647</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>-120</v>
+        <v>-136</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>104</v>
+        <v>-104</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -8756,7 +8756,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 54.6% (fair -120). Your call.</t>
+          <t>Model 57.6% (fair -136). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -8773,32 +8773,32 @@
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Las Vegas Aces @ Chicago Sky</t>
+          <t>Arizona Diamondbacks @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Chicago Sky +7.5</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.5767615384615384</v>
+        <v>0.5958069767441861</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>-136</v>
+        <v>-147</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>-108</v>
+        <v>-115</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -8822,7 +8822,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 57.7% (fair -136). Your call.</t>
+          <t>Model 59.6% (fair -147). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -8839,12 +8839,12 @@
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>Washington Nationals @ Baltimore Orioles</t>
+          <t>Las Vegas Aces @ Chicago Sky</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -8854,17 +8854,17 @@
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>Baltimore Orioles -1.5</t>
+          <t>Chicago Sky +7.5</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.5273809523809523</v>
+        <v>0.5767615384615384</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>-112</v>
+        <v>-136</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>110</v>
+        <v>-108</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -8888,7 +8888,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 52.7% (fair -112). Your call.</t>
+          <t>Model 57.7% (fair -136). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -8905,12 +8905,12 @@
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Kansas City Royals @ Chicago White Sox</t>
+          <t>Washington Nationals @ Baltimore Orioles</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
@@ -8920,17 +8920,17 @@
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox -1.5</t>
+          <t>Baltimore Orioles -1.5</t>
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.4257692307692307</v>
+        <v>0.5273809523809523</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>135</v>
+        <v>-112</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>160</v>
+        <v>110</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 42.6% (fair +135). Your call.</t>
+          <t>Model 52.7% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>New York Liberty @ Golden State Valkyries</t>
+          <t>Las Vegas Aces @ Chicago Sky</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -9052,17 +9052,17 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Over 163.5</t>
+          <t>Over 178.5</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.5769238095238095</v>
+        <v>0.55275</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>-136</v>
+        <v>-124</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>-110</v>
+        <v>100</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -9086,7 +9086,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 57.7% (fair -136). Your call.</t>
+          <t>Model 55.3% (fair -124). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -9103,12 +9103,12 @@
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks @ Tampa Bay Rays</t>
+          <t>New York Liberty @ Golden State Valkyries</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -9118,17 +9118,17 @@
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Over 7.5</t>
+          <t>Over 163.5</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.5879976744186046</v>
+        <v>0.5769238095238095</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>-143</v>
+        <v>-136</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>-115</v>
+        <v>-110</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -9152,7 +9152,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 58.8% (fair -143). Your call.</t>
+          <t>Model 57.7% (fair -136). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -9188,13 +9188,13 @@
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.562726213592233</v>
+        <v>0.5621853658536585</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>-129</v>
+        <v>-128</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>-106</v>
+        <v>-105</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -9218,7 +9218,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 56.3% (fair -129). Your call.</t>
+          <t>Model 56.2% (fair -128). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -9235,32 +9235,32 @@
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>New York Liberty @ Golden State Valkyries</t>
+          <t>Seattle Mariners @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>Golden State Valkyries +1</t>
+          <t>Seattle Mariners</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.5716857142857142</v>
+        <v>0.54865</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-133</v>
+        <v>-122</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>-110</v>
+        <v>100</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -9284,7 +9284,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 57.2% (fair -133). Your call.</t>
+          <t>Model 54.9% (fair -122). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -9301,32 +9301,32 @@
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>Texas Rangers @ Toronto Blue Jays</t>
+          <t>Atlanta Braves @ San Francisco Giants</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Texas Rangers</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.4680257510729613</v>
+        <v>0.5612634146341464</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>114</v>
+        <v>-128</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>133</v>
+        <v>-105</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -9350,7 +9350,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 46.8% (fair +114). Your call.</t>
+          <t>Model 56.1% (fair -128). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -9362,37 +9362,37 @@
     <row r="24">
       <c r="A24" s="20" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>New York Yankees @ Boston Red Sox</t>
+          <t>Washington Nationals @ Baltimore Orioles</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>23:20</t>
+          <t>23:05</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
         <is>
-          <t>Over 8</t>
+          <t>Baltimore Orioles</t>
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.5584463414634147</v>
+        <v>0.5517098039215687</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>-126</v>
+        <v>-123</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>-105</v>
+        <v>-104</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -9416,7 +9416,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 55.8% (fair -126). Your call.</t>
+          <t>Model 55.2% (fair -123). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -9433,12 +9433,12 @@
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>Washington Nationals @ Baltimore Orioles</t>
+          <t>Arizona Diamondbacks @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>23:05</t>
+          <t>22:10</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
@@ -9448,17 +9448,17 @@
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Baltimore Orioles</t>
+          <t>Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.5517098039215687</v>
+        <v>0.4752863436123348</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>-123</v>
+        <v>110</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>-104</v>
+        <v>127</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -9482,7 +9482,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 55.2% (fair -123). Your call.</t>
+          <t>Model 47.5% (fair +110). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -9494,37 +9494,37 @@
     <row r="26">
       <c r="A26" s="20" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>Seattle Mariners @ Cleveland Guardians</t>
+          <t>Kansas City Royals @ Chicago White Sox</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
-          <t>Seattle Mariners</t>
+          <t>Chicago White Sox -1.5</t>
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.6171444444444445</v>
+        <v>0.4223529411764706</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>-161</v>
+        <v>137</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>-134</v>
+        <v>155</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 61.7% (fair -161). Your call.</t>
+          <t>Model 42.2% (fair +137). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -9565,12 +9565,12 @@
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks @ Tampa Bay Rays</t>
+          <t>Seattle Mariners @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>22:10</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks</t>
+          <t>Seattle Mariners</t>
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.4740088105726872</v>
+        <v>0.6186806722689074</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>111</v>
+        <v>-162</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>127</v>
+        <v>-138</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -9614,7 +9614,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 47.4% (fair +111). Your call.</t>
+          <t>Model 61.9% (fair -162). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -9626,37 +9626,37 @@
     <row r="28">
       <c r="A28" s="20" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies @ New York Mets</t>
+          <t>Atlanta Braves @ San Francisco Giants</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies</t>
+          <t>San Francisco Giants +1.5</t>
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.4862272727272727</v>
+        <v>0.6019565217391304</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>106</v>
+        <v>-151</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>120</v>
+        <v>-130</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -9680,7 +9680,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 48.6% (fair +106). Your call.</t>
+          <t>Model 60.2% (fair -151). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -9697,32 +9697,32 @@
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>Las Vegas Aces @ Chicago Sky</t>
+          <t>Kansas City Royals @ Chicago White Sox</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>Over 178.5</t>
+          <t>Chicago White Sox</t>
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.5527730769230769</v>
+        <v>0.5935991189427313</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>-124</v>
+        <v>-146</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>-108</v>
+        <v>-127</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 55.3% (fair -124). Your call.</t>
+          <t>Model 59.4% (fair -146). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -9779,7 +9779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P140"/>
+  <dimension ref="A1:P144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -10589,7 +10589,7 @@
         <v>272</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -10715,13 +10715,13 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.3753649635036496</v>
+        <v>0.3717625899280576</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -10745,7 +10745,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 37.5% (fair +166). Your call.</t>
+          <t>Model 37.2% (fair +169). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -10781,13 +10781,13 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.6246555555555555</v>
+        <v>0.6282503597122302</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>-166</v>
+        <v>-169</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>-170</v>
+        <v>-178</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -10811,7 +10811,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 62.5% (fair -166). Your call.</t>
+          <t>Model 62.8% (fair -169). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -10847,13 +10847,13 @@
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.5031804878048781</v>
+        <v>0.4846</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>-101</v>
+        <v>106</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>-105</v>
+        <v>105</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -10877,7 +10877,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 50.3% (fair -101). Your call.</t>
+          <t>Model 48.5% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -10913,10 +10913,10 @@
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.4968075117370893</v>
+        <v>0.5154000000000001</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>101</v>
+        <v>-106</v>
       </c>
       <c r="H20" s="15" t="n">
         <v>113</v>
@@ -10943,7 +10943,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 49.7% (fair +101). Your call.</t>
+          <t>Model 51.5% (fair -106). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -10979,13 +10979,13 @@
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.4334529147982063</v>
+        <v>0.4176</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -11009,7 +11009,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 43.3% (fair +131). Your call.</t>
+          <t>Model 41.8% (fair +139). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.5665306306306306</v>
+        <v>0.5824</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-131</v>
+        <v>-139</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>-122</v>
+        <v>170</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -11075,7 +11075,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 56.7% (fair -131). Your call.</t>
+          <t>Model 58.2% (fair -139). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -11111,10 +11111,10 @@
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.4391</v>
+        <v>0.44035</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H23" s="15" t="n">
         <v>100</v>
@@ -11141,7 +11141,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 43.9% (fair +128). Your call.</t>
+          <t>Model 44.0% (fair +127). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -11177,13 +11177,13 @@
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.5608910891089109</v>
+        <v>0.559656862745098</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>-128</v>
+        <v>-127</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -11207,7 +11207,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 56.1% (fair -128). Your call.</t>
+          <t>Model 56.0% (fair -127). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -11315,7 +11315,7 @@
         <v>189</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -11375,13 +11375,13 @@
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.4862272727272727</v>
+        <v>0.4883870967741936</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -11405,7 +11405,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 48.6% (fair +106). Your call.</t>
+          <t>Model 48.8% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -11441,13 +11441,13 @@
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.5137846153846154</v>
+        <v>0.5116363636363636</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>-106</v>
+        <v>-105</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>-121</v>
+        <v>-120</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -11471,7 +11471,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 51.4% (fair -106). Your call.</t>
+          <t>Model 51.2% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -11513,7 +11513,7 @@
         <v>217</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -11711,7 +11711,7 @@
         <v>-240</v>
       </c>
       <c r="H32" s="15" t="n">
-        <v>-134</v>
+        <v>-124</v>
       </c>
       <c r="I32" s="13">
         <f>IF($H$32="","",IF($H$32&lt;0,-$H$32/(-$H$32+100),100/($H$32+100)))</f>
@@ -11777,7 +11777,7 @@
         <v>186</v>
       </c>
       <c r="H33" s="15" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I33" s="13">
         <f>IF($H$33="","",IF($H$33&lt;0,-$H$33/(-$H$33+100),100/($H$33+100)))</f>
@@ -12041,7 +12041,7 @@
         <v>115</v>
       </c>
       <c r="H37" s="15" t="n">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I37" s="13">
         <f>IF($H$37="","",IF($H$37&lt;0,-$H$37/(-$H$37+100),100/($H$37+100)))</f>
@@ -12107,7 +12107,7 @@
         <v>-115</v>
       </c>
       <c r="H38" s="15" t="n">
-        <v>-134</v>
+        <v>-126</v>
       </c>
       <c r="I38" s="13">
         <f>IF($H$38="","",IF($H$38&lt;0,-$H$38/(-$H$38+100),100/($H$38+100)))</f>
@@ -12167,10 +12167,10 @@
         </is>
       </c>
       <c r="F39" s="13" t="n">
-        <v>0.4740088105726872</v>
+        <v>0.4752863436123348</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H39" s="15" t="n">
         <v>127</v>
@@ -12197,7 +12197,7 @@
       </c>
       <c r="N39" s="19" t="inlineStr">
         <is>
-          <t>Model 47.4% (fair +111). Your call.</t>
+          <t>Model 47.5% (fair +110). Your call.</t>
         </is>
       </c>
       <c r="O39" s="15" t="n"/>
@@ -12233,13 +12233,13 @@
         </is>
       </c>
       <c r="F40" s="13" t="n">
-        <v>0.5259913043478261</v>
+        <v>0.5247281938325992</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>-111</v>
+        <v>-110</v>
       </c>
       <c r="H40" s="15" t="n">
-        <v>-130</v>
+        <v>-127</v>
       </c>
       <c r="I40" s="13">
         <f>IF($H$40="","",IF($H$40&lt;0,-$H$40/(-$H$40+100),100/($H$40+100)))</f>
@@ -12263,7 +12263,7 @@
       </c>
       <c r="N40" s="19" t="inlineStr">
         <is>
-          <t>Model 52.6% (fair -111). Your call.</t>
+          <t>Model 52.5% (fair -110). Your call.</t>
         </is>
       </c>
       <c r="O40" s="15" t="n"/>
@@ -12299,13 +12299,13 @@
         </is>
       </c>
       <c r="F41" s="13" t="n">
-        <v>0.4916826923076922</v>
+        <v>0.4975490196078431</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H41" s="15" t="n">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="I41" s="13">
         <f>IF($H$41="","",IF($H$41&lt;0,-$H$41/(-$H$41+100),100/($H$41+100)))</f>
@@ -12329,7 +12329,7 @@
       </c>
       <c r="N41" s="19" t="inlineStr">
         <is>
-          <t>Model 49.2% (fair +103). Your call.</t>
+          <t>Model 49.8% (fair +101). Your call.</t>
         </is>
       </c>
       <c r="O41" s="15" t="n"/>
@@ -12365,13 +12365,13 @@
         </is>
       </c>
       <c r="F42" s="13" t="n">
-        <v>0.5083269230769231</v>
+        <v>0.5024257425742574</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>-103</v>
+        <v>-101</v>
       </c>
       <c r="H42" s="15" t="n">
-        <v>-108</v>
+        <v>-102</v>
       </c>
       <c r="I42" s="13">
         <f>IF($H$42="","",IF($H$42&lt;0,-$H$42/(-$H$42+100),100/($H$42+100)))</f>
@@ -12395,7 +12395,7 @@
       </c>
       <c r="N42" s="19" t="inlineStr">
         <is>
-          <t>Model 50.8% (fair -103). Your call.</t>
+          <t>Model 50.2% (fair -101). Your call.</t>
         </is>
       </c>
       <c r="O42" s="15" t="n"/>
@@ -12503,7 +12503,7 @@
         <v>-232</v>
       </c>
       <c r="H44" s="15" t="n">
-        <v>-122</v>
+        <v>-117</v>
       </c>
       <c r="I44" s="13">
         <f>IF($H$44="","",IF($H$44&lt;0,-$H$44/(-$H$44+100),100/($H$44+100)))</f>
@@ -12959,13 +12959,13 @@
         </is>
       </c>
       <c r="F51" s="13" t="n">
-        <v>0.6171444444444445</v>
+        <v>0.6186806722689074</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>-161</v>
+        <v>-162</v>
       </c>
       <c r="H51" s="15" t="n">
-        <v>-134</v>
+        <v>-138</v>
       </c>
       <c r="I51" s="13">
         <f>IF($H$51="","",IF($H$51&lt;0,-$H$51/(-$H$51+100),100/($H$51+100)))</f>
@@ -12989,7 +12989,7 @@
       </c>
       <c r="N51" s="19" t="inlineStr">
         <is>
-          <t>Model 61.7% (fair -161). Your call.</t>
+          <t>Model 61.9% (fair -162). Your call.</t>
         </is>
       </c>
       <c r="O51" s="15" t="n"/>
@@ -13025,10 +13025,10 @@
         </is>
       </c>
       <c r="F52" s="13" t="n">
-        <v>0.3828326180257511</v>
+        <v>0.3813304721030042</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H52" s="15" t="n">
         <v>133</v>
@@ -13055,7 +13055,7 @@
       </c>
       <c r="N52" s="19" t="inlineStr">
         <is>
-          <t>Model 38.3% (fair +161). Your call.</t>
+          <t>Model 38.1% (fair +162). Your call.</t>
         </is>
       </c>
       <c r="O52" s="15" t="n"/>
@@ -13351,10 +13351,10 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>0.36656</v>
+        <v>0.3656</v>
       </c>
       <c r="G57" s="14" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H57" s="15" t="n">
         <v>150</v>
@@ -13381,7 +13381,7 @@
       </c>
       <c r="N57" s="19" t="inlineStr">
         <is>
-          <t>Model 36.7% (fair +173). Your call.</t>
+          <t>Model 36.6% (fair +174). Your call.</t>
         </is>
       </c>
       <c r="O57" s="15" t="n"/>
@@ -13417,13 +13417,13 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>0.6334093117408908</v>
+        <v>0.6343800000000001</v>
       </c>
       <c r="G58" s="14" t="n">
-        <v>-173</v>
+        <v>-174</v>
       </c>
       <c r="H58" s="15" t="n">
-        <v>-147</v>
+        <v>-150</v>
       </c>
       <c r="I58" s="13">
         <f>IF($H$58="","",IF($H$58&lt;0,-$H$58/(-$H$58+100),100/($H$58+100)))</f>
@@ -13447,7 +13447,7 @@
       </c>
       <c r="N58" s="19" t="inlineStr">
         <is>
-          <t>Model 63.3% (fair -173). Your call.</t>
+          <t>Model 63.4% (fair -174). Your call.</t>
         </is>
       </c>
       <c r="O58" s="15" t="n"/>
@@ -13687,7 +13687,7 @@
         <v>-106</v>
       </c>
       <c r="H62" s="15" t="n">
-        <v>-107</v>
+        <v>103</v>
       </c>
       <c r="I62" s="13">
         <f>IF($H$62="","",IF($H$62&lt;0,-$H$62/(-$H$62+100),100/($H$62+100)))</f>
@@ -14387,17 +14387,17 @@
       </c>
       <c r="E73" s="12" t="inlineStr">
         <is>
-          <t>Over 9</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F73" s="13" t="n">
-        <v>0.5946285714285714</v>
+        <v>0.5857560975609757</v>
       </c>
       <c r="G73" s="14" t="n">
-        <v>-147</v>
+        <v>-141</v>
       </c>
       <c r="H73" s="15" t="n">
-        <v>-110</v>
+        <v>105</v>
       </c>
       <c r="I73" s="13">
         <f>IF($H$73="","",IF($H$73&lt;0,-$H$73/(-$H$73+100),100/($H$73+100)))</f>
@@ -14421,7 +14421,7 @@
       </c>
       <c r="N73" s="19" t="inlineStr">
         <is>
-          <t>Model 59.5% (fair -147). Your call.</t>
+          <t>Model 58.6% (fair -141). Your call.</t>
         </is>
       </c>
       <c r="O73" s="15" t="n"/>
@@ -14453,14 +14453,14 @@
       </c>
       <c r="E74" s="20" t="inlineStr">
         <is>
-          <t>Under 9</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F74" s="13" t="n">
-        <v>0.4053512195121951</v>
+        <v>0.4142634146341463</v>
       </c>
       <c r="G74" s="14" t="n">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="H74" s="15" t="n">
         <v>-105</v>
@@ -14487,7 +14487,7 @@
       </c>
       <c r="N74" s="19" t="inlineStr">
         <is>
-          <t>Model 40.5% (fair +147). Your call.</t>
+          <t>Model 41.4% (fair +141). Your call.</t>
         </is>
       </c>
       <c r="O74" s="15" t="n"/>
@@ -14655,10 +14655,10 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>0.3357603686635945</v>
+        <v>0.3313824884792627</v>
       </c>
       <c r="G77" s="14" t="n">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="H77" s="15" t="n">
         <v>117</v>
@@ -14685,7 +14685,7 @@
       </c>
       <c r="N77" s="19" t="inlineStr">
         <is>
-          <t>Model 33.6% (fair +198). Your call.</t>
+          <t>Model 33.1% (fair +202). Your call.</t>
         </is>
       </c>
       <c r="O77" s="15" t="n"/>
@@ -14721,13 +14721,13 @@
         </is>
       </c>
       <c r="F78" s="13" t="n">
-        <v>0.664206572769953</v>
+        <v>0.6685819819819819</v>
       </c>
       <c r="G78" s="14" t="n">
-        <v>-198</v>
+        <v>-202</v>
       </c>
       <c r="H78" s="15" t="n">
-        <v>-113</v>
+        <v>-122</v>
       </c>
       <c r="I78" s="13">
         <f>IF($H$78="","",IF($H$78&lt;0,-$H$78/(-$H$78+100),100/($H$78+100)))</f>
@@ -14751,7 +14751,7 @@
       </c>
       <c r="N78" s="19" t="inlineStr">
         <is>
-          <t>Model 66.4% (fair -198). Your call.</t>
+          <t>Model 66.9% (fair -202). Your call.</t>
         </is>
       </c>
       <c r="O78" s="15" t="n"/>
@@ -14783,17 +14783,17 @@
       </c>
       <c r="E79" s="12" t="inlineStr">
         <is>
-          <t>Over 9</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F79" s="13" t="n">
-        <v>0.5374862745098039</v>
+        <v>0.5817</v>
       </c>
       <c r="G79" s="14" t="n">
-        <v>-116</v>
+        <v>-139</v>
       </c>
       <c r="H79" s="15" t="n">
-        <v>-104</v>
+        <v>104</v>
       </c>
       <c r="I79" s="13">
         <f>IF($H$79="","",IF($H$79&lt;0,-$H$79/(-$H$79+100),100/($H$79+100)))</f>
@@ -14817,7 +14817,7 @@
       </c>
       <c r="N79" s="19" t="inlineStr">
         <is>
-          <t>Model 53.7% (fair -116). Your call.</t>
+          <t>Model 58.2% (fair -139). Your call.</t>
         </is>
       </c>
       <c r="O79" s="15" t="n"/>
@@ -14849,17 +14849,17 @@
       </c>
       <c r="E80" s="20" t="inlineStr">
         <is>
-          <t>Under 9</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F80" s="13" t="n">
-        <v>0.4625238095238095</v>
+        <v>0.4183</v>
       </c>
       <c r="G80" s="14" t="n">
-        <v>116</v>
+        <v>139</v>
       </c>
       <c r="H80" s="15" t="n">
-        <v>-110</v>
+        <v>110</v>
       </c>
       <c r="I80" s="13">
         <f>IF($H$80="","",IF($H$80&lt;0,-$H$80/(-$H$80+100),100/($H$80+100)))</f>
@@ -14883,7 +14883,7 @@
       </c>
       <c r="N80" s="19" t="inlineStr">
         <is>
-          <t>Model 46.3% (fair +116). Your call.</t>
+          <t>Model 41.8% (fair +139). Your call.</t>
         </is>
       </c>
       <c r="O80" s="15" t="n"/>
@@ -14919,10 +14919,10 @@
         </is>
       </c>
       <c r="F81" s="13" t="n">
-        <v>0.4990808823529412</v>
+        <v>0.4966544117647059</v>
       </c>
       <c r="G81" s="14" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H81" s="15" t="n">
         <v>172</v>
@@ -14949,7 +14949,7 @@
       </c>
       <c r="N81" s="19" t="inlineStr">
         <is>
-          <t>Model 49.9% (fair +100). Your call.</t>
+          <t>Model 49.7% (fair +101). Your call.</t>
         </is>
       </c>
       <c r="O81" s="15" t="n"/>
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="F82" s="13" t="n">
-        <v>0.5009333333333332</v>
+        <v>0.5033571428571428</v>
       </c>
       <c r="G82" s="14" t="n">
-        <v>-100</v>
+        <v>-101</v>
       </c>
       <c r="H82" s="15" t="n">
-        <v>-170</v>
+        <v>-180</v>
       </c>
       <c r="I82" s="13">
         <f>IF($H$82="","",IF($H$82&lt;0,-$H$82/(-$H$82+100),100/($H$82+100)))</f>
@@ -15015,7 +15015,7 @@
       </c>
       <c r="N82" s="19" t="inlineStr">
         <is>
-          <t>Model 50.1% (fair -100). Your call.</t>
+          <t>Model 50.3% (fair -101). Your call.</t>
         </is>
       </c>
       <c r="O82" s="15" t="n"/>
@@ -15051,13 +15051,13 @@
         </is>
       </c>
       <c r="F83" s="13" t="n">
-        <v>0.4680257510729613</v>
+        <v>0.4761711711711712</v>
       </c>
       <c r="G83" s="14" t="n">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="H83" s="15" t="n">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="I83" s="13">
         <f>IF($H$83="","",IF($H$83&lt;0,-$H$83/(-$H$83+100),100/($H$83+100)))</f>
@@ -15081,7 +15081,7 @@
       </c>
       <c r="N83" s="19" t="inlineStr">
         <is>
-          <t>Model 46.8% (fair +114). Your call.</t>
+          <t>Model 47.6% (fair +110). Your call.</t>
         </is>
       </c>
       <c r="O83" s="15" t="n"/>
@@ -15117,13 +15117,13 @@
         </is>
       </c>
       <c r="F84" s="13" t="n">
-        <v>0.5320013215859031</v>
+        <v>0.5238306306306306</v>
       </c>
       <c r="G84" s="14" t="n">
-        <v>-114</v>
+        <v>-110</v>
       </c>
       <c r="H84" s="15" t="n">
-        <v>-127</v>
+        <v>-122</v>
       </c>
       <c r="I84" s="13">
         <f>IF($H$84="","",IF($H$84&lt;0,-$H$84/(-$H$84+100),100/($H$84+100)))</f>
@@ -15147,7 +15147,7 @@
       </c>
       <c r="N84" s="19" t="inlineStr">
         <is>
-          <t>Model 53.2% (fair -114). Your call.</t>
+          <t>Model 52.4% (fair -110). Your call.</t>
         </is>
       </c>
       <c r="O84" s="15" t="n"/>
@@ -15183,13 +15183,13 @@
         </is>
       </c>
       <c r="F85" s="13" t="n">
-        <v>0.562726213592233</v>
+        <v>0.5621853658536585</v>
       </c>
       <c r="G85" s="14" t="n">
-        <v>-129</v>
+        <v>-128</v>
       </c>
       <c r="H85" s="15" t="n">
-        <v>-106</v>
+        <v>-105</v>
       </c>
       <c r="I85" s="13">
         <f>IF($H$85="","",IF($H$85&lt;0,-$H$85/(-$H$85+100),100/($H$85+100)))</f>
@@ -15213,7 +15213,7 @@
       </c>
       <c r="N85" s="19" t="inlineStr">
         <is>
-          <t>Model 56.3% (fair -129). Your call.</t>
+          <t>Model 56.2% (fair -128). Your call.</t>
         </is>
       </c>
       <c r="O85" s="15" t="n"/>
@@ -15249,10 +15249,10 @@
         </is>
       </c>
       <c r="F86" s="13" t="n">
-        <v>0.43725</v>
+        <v>0.43785</v>
       </c>
       <c r="G86" s="14" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H86" s="15" t="n">
         <v>100</v>
@@ -15279,7 +15279,7 @@
       </c>
       <c r="N86" s="19" t="inlineStr">
         <is>
-          <t>Model 43.7% (fair +129). Your call.</t>
+          <t>Model 43.8% (fair +128). Your call.</t>
         </is>
       </c>
       <c r="O86" s="15" t="n"/>
@@ -15315,10 +15315,10 @@
         </is>
       </c>
       <c r="F87" s="13" t="n">
-        <v>0.3350367647058824</v>
+        <v>0.3390441176470589</v>
       </c>
       <c r="G87" s="14" t="n">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="H87" s="15" t="n">
         <v>172</v>
@@ -15345,7 +15345,7 @@
       </c>
       <c r="N87" s="19" t="inlineStr">
         <is>
-          <t>Model 33.5% (fair +198). Your call.</t>
+          <t>Model 33.9% (fair +195). Your call.</t>
         </is>
       </c>
       <c r="O87" s="15" t="n"/>
@@ -15381,13 +15381,13 @@
         </is>
       </c>
       <c r="F88" s="13" t="n">
-        <v>0.6649393442622951</v>
+        <v>0.6609368421052632</v>
       </c>
       <c r="G88" s="14" t="n">
-        <v>-198</v>
+        <v>-195</v>
       </c>
       <c r="H88" s="15" t="n">
-        <v>-205</v>
+        <v>-185</v>
       </c>
       <c r="I88" s="13">
         <f>IF($H$88="","",IF($H$88&lt;0,-$H$88/(-$H$88+100),100/($H$88+100)))</f>
@@ -15411,7 +15411,7 @@
       </c>
       <c r="N88" s="19" t="inlineStr">
         <is>
-          <t>Model 66.5% (fair -198). Your call.</t>
+          <t>Model 66.1% (fair -195). Your call.</t>
         </is>
       </c>
       <c r="O88" s="15" t="n"/>
@@ -15447,13 +15447,13 @@
         </is>
       </c>
       <c r="F89" s="13" t="n">
-        <v>0.5364207373271889</v>
+        <v>0.5359756756756757</v>
       </c>
       <c r="G89" s="14" t="n">
         <v>-116</v>
       </c>
       <c r="H89" s="15" t="n">
-        <v>-117</v>
+        <v>-122</v>
       </c>
       <c r="I89" s="13">
         <f>IF($H$89="","",IF($H$89&lt;0,-$H$89/(-$H$89+100),100/($H$89+100)))</f>
@@ -15513,13 +15513,13 @@
         </is>
       </c>
       <c r="F90" s="13" t="n">
-        <v>0.4636036036036036</v>
+        <v>0.4640552995391705</v>
       </c>
       <c r="G90" s="14" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H90" s="15" t="n">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="I90" s="13">
         <f>IF($H$90="","",IF($H$90&lt;0,-$H$90/(-$H$90+100),100/($H$90+100)))</f>
@@ -15543,7 +15543,7 @@
       </c>
       <c r="N90" s="19" t="inlineStr">
         <is>
-          <t>Model 46.4% (fair +116). Your call.</t>
+          <t>Model 46.4% (fair +115). Your call.</t>
         </is>
       </c>
       <c r="O90" s="15" t="n"/>
@@ -15560,7 +15560,7 @@
       </c>
       <c r="B91" s="12" t="inlineStr">
         <is>
-          <t>Seattle Mariners @ Cleveland Guardians</t>
+          <t>Houston Astros @ Detroit Tigers</t>
         </is>
       </c>
       <c r="C91" s="12" t="inlineStr">
@@ -15570,22 +15570,22 @@
       </c>
       <c r="D91" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E91" s="12" t="inlineStr">
         <is>
-          <t>Seattle Mariners</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F91" s="13" t="n">
-        <v>0.5461764705882354</v>
+        <v>0.6435</v>
       </c>
       <c r="G91" s="14" t="n">
-        <v>-120</v>
+        <v>-181</v>
       </c>
       <c r="H91" s="15" t="n">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I91" s="13">
         <f>IF($H$91="","",IF($H$91&lt;0,-$H$91/(-$H$91+100),100/($H$91+100)))</f>
@@ -15609,7 +15609,7 @@
       </c>
       <c r="N91" s="19" t="inlineStr">
         <is>
-          <t>Model 54.6% (fair -120). Your call.</t>
+          <t>Model 64.3% (fair -181). Your call.</t>
         </is>
       </c>
       <c r="O91" s="15" t="n"/>
@@ -15626,7 +15626,7 @@
       </c>
       <c r="B92" s="20" t="inlineStr">
         <is>
-          <t>Seattle Mariners @ Cleveland Guardians</t>
+          <t>Houston Astros @ Detroit Tigers</t>
         </is>
       </c>
       <c r="C92" s="20" t="inlineStr">
@@ -15636,22 +15636,22 @@
       </c>
       <c r="D92" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E92" s="20" t="inlineStr">
         <is>
-          <t>Cleveland Guardians</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F92" s="13" t="n">
-        <v>0.45385</v>
+        <v>0.3565</v>
       </c>
       <c r="G92" s="14" t="n">
-        <v>120</v>
+        <v>181</v>
       </c>
       <c r="H92" s="15" t="n">
-        <v>100</v>
+        <v>245</v>
       </c>
       <c r="I92" s="13">
         <f>IF($H$92="","",IF($H$92&lt;0,-$H$92/(-$H$92+100),100/($H$92+100)))</f>
@@ -15675,7 +15675,7 @@
       </c>
       <c r="N92" s="19" t="inlineStr">
         <is>
-          <t>Model 45.4% (fair +120). Your call.</t>
+          <t>Model 35.7% (fair +181). Your call.</t>
         </is>
       </c>
       <c r="O92" s="15" t="n"/>
@@ -15692,7 +15692,7 @@
       </c>
       <c r="B93" s="12" t="inlineStr">
         <is>
-          <t>Seattle Mariners @ Cleveland Guardians</t>
+          <t>Houston Astros @ Detroit Tigers</t>
         </is>
       </c>
       <c r="C93" s="12" t="inlineStr">
@@ -15702,22 +15702,22 @@
       </c>
       <c r="D93" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E93" s="12" t="inlineStr">
         <is>
-          <t>Over 7.5</t>
+          <t>Detroit Tigers +1.5</t>
         </is>
       </c>
       <c r="F93" s="13" t="n">
-        <v>0.5025272727272727</v>
+        <v>0.6226745098039216</v>
       </c>
       <c r="G93" s="14" t="n">
-        <v>-101</v>
+        <v>-165</v>
       </c>
       <c r="H93" s="15" t="n">
-        <v>-120</v>
+        <v>-155</v>
       </c>
       <c r="I93" s="13">
         <f>IF($H$93="","",IF($H$93&lt;0,-$H$93/(-$H$93+100),100/($H$93+100)))</f>
@@ -15741,7 +15741,7 @@
       </c>
       <c r="N93" s="19" t="inlineStr">
         <is>
-          <t>Model 50.3% (fair -101). Your call.</t>
+          <t>Model 62.3% (fair -165). Your call.</t>
         </is>
       </c>
       <c r="O93" s="15" t="n"/>
@@ -15758,7 +15758,7 @@
       </c>
       <c r="B94" s="20" t="inlineStr">
         <is>
-          <t>Seattle Mariners @ Cleveland Guardians</t>
+          <t>Houston Astros @ Detroit Tigers</t>
         </is>
       </c>
       <c r="C94" s="20" t="inlineStr">
@@ -15768,22 +15768,22 @@
       </c>
       <c r="D94" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E94" s="20" t="inlineStr">
         <is>
-          <t>Under 7.5</t>
+          <t>Houston Astros -1.5</t>
         </is>
       </c>
       <c r="F94" s="13" t="n">
-        <v>0.49745</v>
+        <v>0.3773333333333334</v>
       </c>
       <c r="G94" s="14" t="n">
-        <v>101</v>
+        <v>165</v>
       </c>
       <c r="H94" s="15" t="n">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="I94" s="13">
         <f>IF($H$94="","",IF($H$94&lt;0,-$H$94/(-$H$94+100),100/($H$94+100)))</f>
@@ -15807,7 +15807,7 @@
       </c>
       <c r="N94" s="19" t="inlineStr">
         <is>
-          <t>Model 49.7% (fair +101). Your call.</t>
+          <t>Model 37.7% (fair +165). Your call.</t>
         </is>
       </c>
       <c r="O94" s="15" t="n"/>
@@ -15834,22 +15834,22 @@
       </c>
       <c r="D95" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E95" s="12" t="inlineStr">
         <is>
-          <t>Cleveland Guardians +1.5</t>
+          <t>Seattle Mariners</t>
         </is>
       </c>
       <c r="F95" s="13" t="n">
-        <v>0.6207610169491526</v>
+        <v>0.54865</v>
       </c>
       <c r="G95" s="14" t="n">
-        <v>-164</v>
+        <v>-122</v>
       </c>
       <c r="H95" s="15" t="n">
-        <v>-195</v>
+        <v>100</v>
       </c>
       <c r="I95" s="13">
         <f>IF($H$95="","",IF($H$95&lt;0,-$H$95/(-$H$95+100),100/($H$95+100)))</f>
@@ -15873,7 +15873,7 @@
       </c>
       <c r="N95" s="19" t="inlineStr">
         <is>
-          <t>Model 62.1% (fair -164). Your call.</t>
+          <t>Model 54.9% (fair -122). Your call.</t>
         </is>
       </c>
       <c r="O95" s="15" t="n"/>
@@ -15900,22 +15900,22 @@
       </c>
       <c r="D96" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E96" s="20" t="inlineStr">
         <is>
-          <t>Seattle Mariners -1.5</t>
+          <t>Cleveland Guardians</t>
         </is>
       </c>
       <c r="F96" s="13" t="n">
-        <v>0.3792307692307692</v>
+        <v>0.45135</v>
       </c>
       <c r="G96" s="14" t="n">
-        <v>164</v>
+        <v>122</v>
       </c>
       <c r="H96" s="15" t="n">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="I96" s="13">
         <f>IF($H$96="","",IF($H$96&lt;0,-$H$96/(-$H$96+100),100/($H$96+100)))</f>
@@ -15939,7 +15939,7 @@
       </c>
       <c r="N96" s="19" t="inlineStr">
         <is>
-          <t>Model 37.9% (fair +164). Your call.</t>
+          <t>Model 45.1% (fair +122). Your call.</t>
         </is>
       </c>
       <c r="O96" s="15" t="n"/>
@@ -15956,7 +15956,7 @@
       </c>
       <c r="B97" s="12" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks @ Tampa Bay Rays</t>
+          <t>Seattle Mariners @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C97" s="12" t="inlineStr">
@@ -15966,22 +15966,22 @@
       </c>
       <c r="D97" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E97" s="12" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F97" s="13" t="n">
-        <v>0.4006</v>
+        <v>0.49165</v>
       </c>
       <c r="G97" s="14" t="n">
-        <v>150</v>
+        <v>103</v>
       </c>
       <c r="H97" s="15" t="n">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="I97" s="13">
         <f>IF($H$97="","",IF($H$97&lt;0,-$H$97/(-$H$97+100),100/($H$97+100)))</f>
@@ -16005,7 +16005,7 @@
       </c>
       <c r="N97" s="19" t="inlineStr">
         <is>
-          <t>Model 40.1% (fair +150). Your call.</t>
+          <t>Model 49.2% (fair +103). Your call.</t>
         </is>
       </c>
       <c r="O97" s="15" t="n"/>
@@ -16022,7 +16022,7 @@
       </c>
       <c r="B98" s="20" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks @ Tampa Bay Rays</t>
+          <t>Seattle Mariners @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C98" s="20" t="inlineStr">
@@ -16032,22 +16032,22 @@
       </c>
       <c r="D98" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E98" s="20" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays</t>
+          <t>Under 7.5</t>
         </is>
       </c>
       <c r="F98" s="13" t="n">
-        <v>0.5994</v>
+        <v>0.50835</v>
       </c>
       <c r="G98" s="14" t="n">
-        <v>-150</v>
+        <v>-103</v>
       </c>
       <c r="H98" s="15" t="n">
-        <v>-144</v>
+        <v>100</v>
       </c>
       <c r="I98" s="13">
         <f>IF($H$98="","",IF($H$98&lt;0,-$H$98/(-$H$98+100),100/($H$98+100)))</f>
@@ -16071,7 +16071,7 @@
       </c>
       <c r="N98" s="19" t="inlineStr">
         <is>
-          <t>Model 59.9% (fair -150). Your call.</t>
+          <t>Model 50.8% (fair -103). Your call.</t>
         </is>
       </c>
       <c r="O98" s="15" t="n"/>
@@ -16088,7 +16088,7 @@
       </c>
       <c r="B99" s="12" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks @ Tampa Bay Rays</t>
+          <t>Seattle Mariners @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C99" s="12" t="inlineStr">
@@ -16098,22 +16098,22 @@
       </c>
       <c r="D99" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E99" s="12" t="inlineStr">
         <is>
-          <t>Over 7.5</t>
+          <t>Cleveland Guardians +1.5</t>
         </is>
       </c>
       <c r="F99" s="13" t="n">
-        <v>0.5879976744186046</v>
+        <v>0.6207610169491526</v>
       </c>
       <c r="G99" s="14" t="n">
-        <v>-143</v>
+        <v>-164</v>
       </c>
       <c r="H99" s="15" t="n">
-        <v>-115</v>
+        <v>-195</v>
       </c>
       <c r="I99" s="13">
         <f>IF($H$99="","",IF($H$99&lt;0,-$H$99/(-$H$99+100),100/($H$99+100)))</f>
@@ -16137,7 +16137,7 @@
       </c>
       <c r="N99" s="19" t="inlineStr">
         <is>
-          <t>Model 58.8% (fair -143). Your call.</t>
+          <t>Model 62.1% (fair -164). Your call.</t>
         </is>
       </c>
       <c r="O99" s="15" t="n"/>
@@ -16154,7 +16154,7 @@
       </c>
       <c r="B100" s="20" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks @ Tampa Bay Rays</t>
+          <t>Seattle Mariners @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C100" s="20" t="inlineStr">
@@ -16164,22 +16164,22 @@
       </c>
       <c r="D100" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E100" s="20" t="inlineStr">
         <is>
-          <t>Under 7.5</t>
+          <t>Seattle Mariners -1.5</t>
         </is>
       </c>
       <c r="F100" s="13" t="n">
-        <v>0.412</v>
+        <v>0.3792307692307692</v>
       </c>
       <c r="G100" s="14" t="n">
-        <v>143</v>
+        <v>164</v>
       </c>
       <c r="H100" s="15" t="n">
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="I100" s="13">
         <f>IF($H$100="","",IF($H$100&lt;0,-$H$100/(-$H$100+100),100/($H$100+100)))</f>
@@ -16203,7 +16203,7 @@
       </c>
       <c r="N100" s="19" t="inlineStr">
         <is>
-          <t>Model 41.2% (fair +143). Your call.</t>
+          <t>Model 37.9% (fair +164). Your call.</t>
         </is>
       </c>
       <c r="O100" s="15" t="n"/>
@@ -16230,22 +16230,22 @@
       </c>
       <c r="D101" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E101" s="12" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays -1.5</t>
+          <t>Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="F101" s="13" t="n">
-        <v>0.4269469026548673</v>
+        <v>0.3937692307692308</v>
       </c>
       <c r="G101" s="14" t="n">
-        <v>134</v>
+        <v>154</v>
       </c>
       <c r="H101" s="15" t="n">
-        <v>126</v>
+        <v>160</v>
       </c>
       <c r="I101" s="13">
         <f>IF($H$101="","",IF($H$101&lt;0,-$H$101/(-$H$101+100),100/($H$101+100)))</f>
@@ -16269,7 +16269,7 @@
       </c>
       <c r="N101" s="19" t="inlineStr">
         <is>
-          <t>Model 42.7% (fair +134). Your call.</t>
+          <t>Model 39.4% (fair +154). Your call.</t>
         </is>
       </c>
       <c r="O101" s="15" t="n"/>
@@ -16296,22 +16296,22 @@
       </c>
       <c r="D102" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E102" s="20" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks +1.5</t>
+          <t>Tampa Bay Rays</t>
         </is>
       </c>
       <c r="F102" s="13" t="n">
-        <v>0.5730555555555555</v>
+        <v>0.6062062500000001</v>
       </c>
       <c r="G102" s="14" t="n">
-        <v>-134</v>
+        <v>-154</v>
       </c>
       <c r="H102" s="15" t="n">
-        <v>-125</v>
+        <v>-156</v>
       </c>
       <c r="I102" s="13">
         <f>IF($H$102="","",IF($H$102&lt;0,-$H$102/(-$H$102+100),100/($H$102+100)))</f>
@@ -16335,7 +16335,7 @@
       </c>
       <c r="N102" s="19" t="inlineStr">
         <is>
-          <t>Model 57.3% (fair -134). Your call.</t>
+          <t>Model 60.6% (fair -154). Your call.</t>
         </is>
       </c>
       <c r="O102" s="15" t="n"/>
@@ -16352,7 +16352,7 @@
       </c>
       <c r="B103" s="12" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies @ New York Mets</t>
+          <t>Arizona Diamondbacks @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C103" s="12" t="inlineStr">
@@ -16362,22 +16362,22 @@
       </c>
       <c r="D103" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E103" s="12" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F103" s="13" t="n">
-        <v>0.5891233480176211</v>
+        <v>0.5958069767441861</v>
       </c>
       <c r="G103" s="14" t="n">
-        <v>-143</v>
+        <v>-147</v>
       </c>
       <c r="H103" s="15" t="n">
-        <v>-127</v>
+        <v>-115</v>
       </c>
       <c r="I103" s="13">
         <f>IF($H$103="","",IF($H$103&lt;0,-$H$103/(-$H$103+100),100/($H$103+100)))</f>
@@ -16401,7 +16401,7 @@
       </c>
       <c r="N103" s="19" t="inlineStr">
         <is>
-          <t>Model 58.9% (fair -143). Your call.</t>
+          <t>Model 59.6% (fair -147). Your call.</t>
         </is>
       </c>
       <c r="O103" s="15" t="n"/>
@@ -16418,7 +16418,7 @@
       </c>
       <c r="B104" s="20" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies @ New York Mets</t>
+          <t>Arizona Diamondbacks @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C104" s="20" t="inlineStr">
@@ -16428,22 +16428,22 @@
       </c>
       <c r="D104" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E104" s="20" t="inlineStr">
         <is>
-          <t>New York Mets</t>
+          <t>Under 7.5</t>
         </is>
       </c>
       <c r="F104" s="13" t="n">
-        <v>0.4108810572687224</v>
+        <v>0.4041784037558686</v>
       </c>
       <c r="G104" s="14" t="n">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="H104" s="15" t="n">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="I104" s="13">
         <f>IF($H$104="","",IF($H$104&lt;0,-$H$104/(-$H$104+100),100/($H$104+100)))</f>
@@ -16467,7 +16467,7 @@
       </c>
       <c r="N104" s="19" t="inlineStr">
         <is>
-          <t>Model 41.1% (fair +143). Your call.</t>
+          <t>Model 40.4% (fair +147). Your call.</t>
         </is>
       </c>
       <c r="O104" s="15" t="n"/>
@@ -16484,32 +16484,32 @@
       </c>
       <c r="B105" s="12" t="inlineStr">
         <is>
-          <t>Colorado Rockies @ Minnesota Twins</t>
+          <t>Arizona Diamondbacks @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C105" s="12" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D105" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E105" s="12" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>Tampa Bay Rays -1.5</t>
         </is>
       </c>
       <c r="F105" s="13" t="n">
-        <v>0.4225210084033614</v>
+        <v>0.4248230088495575</v>
       </c>
       <c r="G105" s="14" t="n">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="H105" s="15" t="n">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="I105" s="13">
         <f>IF($H$105="","",IF($H$105&lt;0,-$H$105/(-$H$105+100),100/($H$105+100)))</f>
@@ -16533,7 +16533,7 @@
       </c>
       <c r="N105" s="19" t="inlineStr">
         <is>
-          <t>Model 42.3% (fair +137). Your call.</t>
+          <t>Model 42.5% (fair +135). Your call.</t>
         </is>
       </c>
       <c r="O105" s="15" t="n"/>
@@ -16550,32 +16550,32 @@
       </c>
       <c r="B106" s="20" t="inlineStr">
         <is>
-          <t>Colorado Rockies @ Minnesota Twins</t>
+          <t>Arizona Diamondbacks @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C106" s="20" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D106" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E106" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>Arizona Diamondbacks +1.5</t>
         </is>
       </c>
       <c r="F106" s="13" t="n">
-        <v>0.5774546218487394</v>
+        <v>0.5751652173913044</v>
       </c>
       <c r="G106" s="14" t="n">
-        <v>-137</v>
+        <v>-135</v>
       </c>
       <c r="H106" s="15" t="n">
-        <v>-138</v>
+        <v>-130</v>
       </c>
       <c r="I106" s="13">
         <f>IF($H$106="","",IF($H$106&lt;0,-$H$106/(-$H$106+100),100/($H$106+100)))</f>
@@ -16599,7 +16599,7 @@
       </c>
       <c r="N106" s="19" t="inlineStr">
         <is>
-          <t>Model 57.7% (fair -137). Your call.</t>
+          <t>Model 57.5% (fair -135). Your call.</t>
         </is>
       </c>
       <c r="O106" s="15" t="n"/>
@@ -16616,32 +16616,32 @@
       </c>
       <c r="B107" s="12" t="inlineStr">
         <is>
-          <t>Colorado Rockies @ Minnesota Twins</t>
+          <t>Philadelphia Phillies @ New York Mets</t>
         </is>
       </c>
       <c r="C107" s="12" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D107" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E107" s="12" t="inlineStr">
         <is>
-          <t>Over 9.5</t>
+          <t>Philadelphia Phillies</t>
         </is>
       </c>
       <c r="F107" s="13" t="n">
-        <v>0.5382666666666667</v>
+        <v>0.5891233480176211</v>
       </c>
       <c r="G107" s="14" t="n">
-        <v>-117</v>
+        <v>-143</v>
       </c>
       <c r="H107" s="15" t="n">
-        <v>-110</v>
+        <v>-127</v>
       </c>
       <c r="I107" s="13">
         <f>IF($H$107="","",IF($H$107&lt;0,-$H$107/(-$H$107+100),100/($H$107+100)))</f>
@@ -16665,7 +16665,7 @@
       </c>
       <c r="N107" s="19" t="inlineStr">
         <is>
-          <t>Model 53.8% (fair -117). Your call.</t>
+          <t>Model 58.9% (fair -143). Your call.</t>
         </is>
       </c>
       <c r="O107" s="15" t="n"/>
@@ -16682,32 +16682,32 @@
       </c>
       <c r="B108" s="20" t="inlineStr">
         <is>
-          <t>Colorado Rockies @ Minnesota Twins</t>
+          <t>Philadelphia Phillies @ New York Mets</t>
         </is>
       </c>
       <c r="C108" s="20" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D108" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E108" s="20" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>New York Mets</t>
         </is>
       </c>
       <c r="F108" s="13" t="n">
-        <v>0.4617380952380952</v>
+        <v>0.4108810572687224</v>
       </c>
       <c r="G108" s="14" t="n">
-        <v>117</v>
+        <v>143</v>
       </c>
       <c r="H108" s="15" t="n">
-        <v>-110</v>
+        <v>127</v>
       </c>
       <c r="I108" s="13">
         <f>IF($H$108="","",IF($H$108&lt;0,-$H$108/(-$H$108+100),100/($H$108+100)))</f>
@@ -16731,7 +16731,7 @@
       </c>
       <c r="N108" s="19" t="inlineStr">
         <is>
-          <t>Model 46.2% (fair +117). Your call.</t>
+          <t>Model 41.1% (fair +143). Your call.</t>
         </is>
       </c>
       <c r="O108" s="15" t="n"/>
@@ -16758,22 +16758,22 @@
       </c>
       <c r="D109" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E109" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins -1.5</t>
+          <t>Colorado Rockies</t>
         </is>
       </c>
       <c r="F109" s="13" t="n">
-        <v>0.4167272727272727</v>
+        <v>0.4225210084033614</v>
       </c>
       <c r="G109" s="14" t="n">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="H109" s="15" t="n">
-        <v>120</v>
+        <v>138</v>
       </c>
       <c r="I109" s="13">
         <f>IF($H$109="","",IF($H$109&lt;0,-$H$109/(-$H$109+100),100/($H$109+100)))</f>
@@ -16797,7 +16797,7 @@
       </c>
       <c r="N109" s="19" t="inlineStr">
         <is>
-          <t>Model 41.7% (fair +140). Your call.</t>
+          <t>Model 42.3% (fair +137). Your call.</t>
         </is>
       </c>
       <c r="O109" s="15" t="n"/>
@@ -16824,22 +16824,22 @@
       </c>
       <c r="D110" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E110" s="20" t="inlineStr">
         <is>
-          <t>Colorado Rockies +1.5</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="F110" s="13" t="n">
-        <v>0.5832551020408163</v>
+        <v>0.5774546218487394</v>
       </c>
       <c r="G110" s="14" t="n">
-        <v>-140</v>
+        <v>-137</v>
       </c>
       <c r="H110" s="15" t="n">
-        <v>-145</v>
+        <v>-138</v>
       </c>
       <c r="I110" s="13">
         <f>IF($H$110="","",IF($H$110&lt;0,-$H$110/(-$H$110+100),100/($H$110+100)))</f>
@@ -16863,7 +16863,7 @@
       </c>
       <c r="N110" s="19" t="inlineStr">
         <is>
-          <t>Model 58.3% (fair -140). Your call.</t>
+          <t>Model 57.7% (fair -137). Your call.</t>
         </is>
       </c>
       <c r="O110" s="15" t="n"/>
@@ -16880,7 +16880,7 @@
       </c>
       <c r="B111" s="12" t="inlineStr">
         <is>
-          <t>Kansas City Royals @ Chicago White Sox</t>
+          <t>Colorado Rockies @ Minnesota Twins</t>
         </is>
       </c>
       <c r="C111" s="12" t="inlineStr">
@@ -16890,22 +16890,22 @@
       </c>
       <c r="D111" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E111" s="12" t="inlineStr">
         <is>
-          <t>Kansas City Royals</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F111" s="13" t="n">
-        <v>0.406431718061674</v>
+        <v>0.52885</v>
       </c>
       <c r="G111" s="14" t="n">
-        <v>146</v>
+        <v>-112</v>
       </c>
       <c r="H111" s="15" t="n">
-        <v>127</v>
+        <v>100</v>
       </c>
       <c r="I111" s="13">
         <f>IF($H$111="","",IF($H$111&lt;0,-$H$111/(-$H$111+100),100/($H$111+100)))</f>
@@ -16929,7 +16929,7 @@
       </c>
       <c r="N111" s="19" t="inlineStr">
         <is>
-          <t>Model 40.6% (fair +146). Your call.</t>
+          <t>Model 52.9% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O111" s="15" t="n"/>
@@ -16946,7 +16946,7 @@
       </c>
       <c r="B112" s="20" t="inlineStr">
         <is>
-          <t>Kansas City Royals @ Chicago White Sox</t>
+          <t>Colorado Rockies @ Minnesota Twins</t>
         </is>
       </c>
       <c r="C112" s="20" t="inlineStr">
@@ -16956,22 +16956,22 @@
       </c>
       <c r="D112" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E112" s="20" t="inlineStr">
         <is>
-          <t>Chicago White Sox</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F112" s="13" t="n">
-        <v>0.5935991189427313</v>
+        <v>0.4711271889400921</v>
       </c>
       <c r="G112" s="14" t="n">
-        <v>-146</v>
+        <v>112</v>
       </c>
       <c r="H112" s="15" t="n">
-        <v>-127</v>
+        <v>-117</v>
       </c>
       <c r="I112" s="13">
         <f>IF($H$112="","",IF($H$112&lt;0,-$H$112/(-$H$112+100),100/($H$112+100)))</f>
@@ -16995,7 +16995,7 @@
       </c>
       <c r="N112" s="19" t="inlineStr">
         <is>
-          <t>Model 59.4% (fair -146). Your call.</t>
+          <t>Model 47.1% (fair +112). Your call.</t>
         </is>
       </c>
       <c r="O112" s="15" t="n"/>
@@ -17012,7 +17012,7 @@
       </c>
       <c r="B113" s="12" t="inlineStr">
         <is>
-          <t>Kansas City Royals @ Chicago White Sox</t>
+          <t>Colorado Rockies @ Minnesota Twins</t>
         </is>
       </c>
       <c r="C113" s="12" t="inlineStr">
@@ -17022,22 +17022,22 @@
       </c>
       <c r="D113" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E113" s="12" t="inlineStr">
         <is>
-          <t>Over 8</t>
+          <t>Minnesota Twins -1.5</t>
         </is>
       </c>
       <c r="F113" s="13" t="n">
-        <v>0.646390243902439</v>
+        <v>0.4123111111111111</v>
       </c>
       <c r="G113" s="14" t="n">
-        <v>-183</v>
+        <v>143</v>
       </c>
       <c r="H113" s="15" t="n">
-        <v>-105</v>
+        <v>125</v>
       </c>
       <c r="I113" s="13">
         <f>IF($H$113="","",IF($H$113&lt;0,-$H$113/(-$H$113+100),100/($H$113+100)))</f>
@@ -17061,7 +17061,7 @@
       </c>
       <c r="N113" s="19" t="inlineStr">
         <is>
-          <t>Model 64.6% (fair -183). Your call.</t>
+          <t>Model 41.2% (fair +143). Your call.</t>
         </is>
       </c>
       <c r="O113" s="15" t="n"/>
@@ -17078,7 +17078,7 @@
       </c>
       <c r="B114" s="20" t="inlineStr">
         <is>
-          <t>Kansas City Royals @ Chicago White Sox</t>
+          <t>Colorado Rockies @ Minnesota Twins</t>
         </is>
       </c>
       <c r="C114" s="20" t="inlineStr">
@@ -17088,22 +17088,22 @@
       </c>
       <c r="D114" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E114" s="20" t="inlineStr">
         <is>
-          <t>Under 8</t>
+          <t>Colorado Rockies +1.5</t>
         </is>
       </c>
       <c r="F114" s="13" t="n">
-        <v>0.3536</v>
+        <v>0.5877000000000001</v>
       </c>
       <c r="G114" s="14" t="n">
-        <v>183</v>
+        <v>-143</v>
       </c>
       <c r="H114" s="15" t="n">
-        <v>100</v>
+        <v>-150</v>
       </c>
       <c r="I114" s="13">
         <f>IF($H$114="","",IF($H$114&lt;0,-$H$114/(-$H$114+100),100/($H$114+100)))</f>
@@ -17127,7 +17127,7 @@
       </c>
       <c r="N114" s="19" t="inlineStr">
         <is>
-          <t>Model 35.4% (fair +183). Your call.</t>
+          <t>Model 58.8% (fair -143). Your call.</t>
         </is>
       </c>
       <c r="O114" s="15" t="n"/>
@@ -17154,22 +17154,22 @@
       </c>
       <c r="D115" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E115" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox -1.5</t>
+          <t>Kansas City Royals</t>
         </is>
       </c>
       <c r="F115" s="13" t="n">
-        <v>0.4257692307692307</v>
+        <v>0.406431718061674</v>
       </c>
       <c r="G115" s="14" t="n">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="H115" s="15" t="n">
-        <v>160</v>
+        <v>127</v>
       </c>
       <c r="I115" s="13">
         <f>IF($H$115="","",IF($H$115&lt;0,-$H$115/(-$H$115+100),100/($H$115+100)))</f>
@@ -17193,7 +17193,7 @@
       </c>
       <c r="N115" s="19" t="inlineStr">
         <is>
-          <t>Model 42.6% (fair +135). Your call.</t>
+          <t>Model 40.6% (fair +146). Your call.</t>
         </is>
       </c>
       <c r="O115" s="15" t="n"/>
@@ -17220,22 +17220,22 @@
       </c>
       <c r="D116" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E116" s="20" t="inlineStr">
         <is>
-          <t>Kansas City Royals +1.5</t>
+          <t>Chicago White Sox</t>
         </is>
       </c>
       <c r="F116" s="13" t="n">
-        <v>0.57426</v>
+        <v>0.5935991189427313</v>
       </c>
       <c r="G116" s="14" t="n">
-        <v>-135</v>
+        <v>-146</v>
       </c>
       <c r="H116" s="15" t="n">
-        <v>-150</v>
+        <v>-127</v>
       </c>
       <c r="I116" s="13">
         <f>IF($H$116="","",IF($H$116&lt;0,-$H$116/(-$H$116+100),100/($H$116+100)))</f>
@@ -17259,7 +17259,7 @@
       </c>
       <c r="N116" s="19" t="inlineStr">
         <is>
-          <t>Model 57.4% (fair -135). Your call.</t>
+          <t>Model 59.4% (fair -146). Your call.</t>
         </is>
       </c>
       <c r="O116" s="15" t="n"/>
@@ -17276,7 +17276,7 @@
       </c>
       <c r="B117" s="12" t="inlineStr">
         <is>
-          <t>Chicago Cubs @ Milwaukee Brewers</t>
+          <t>Kansas City Royals @ Chicago White Sox</t>
         </is>
       </c>
       <c r="C117" s="12" t="inlineStr">
@@ -17286,22 +17286,22 @@
       </c>
       <c r="D117" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E117" s="12" t="inlineStr">
         <is>
-          <t>Chicago Cubs</t>
+          <t>Over 9</t>
         </is>
       </c>
       <c r="F117" s="13" t="n">
-        <v>0.3825409836065574</v>
+        <v>0.5817512195121951</v>
       </c>
       <c r="G117" s="14" t="n">
-        <v>161</v>
+        <v>-139</v>
       </c>
       <c r="H117" s="15" t="n">
-        <v>144</v>
+        <v>-105</v>
       </c>
       <c r="I117" s="13">
         <f>IF($H$117="","",IF($H$117&lt;0,-$H$117/(-$H$117+100),100/($H$117+100)))</f>
@@ -17325,7 +17325,7 @@
       </c>
       <c r="N117" s="19" t="inlineStr">
         <is>
-          <t>Model 38.3% (fair +161). Your call.</t>
+          <t>Model 58.2% (fair -139). Your call.</t>
         </is>
       </c>
       <c r="O117" s="15" t="n"/>
@@ -17342,7 +17342,7 @@
       </c>
       <c r="B118" s="20" t="inlineStr">
         <is>
-          <t>Chicago Cubs @ Milwaukee Brewers</t>
+          <t>Kansas City Royals @ Chicago White Sox</t>
         </is>
       </c>
       <c r="C118" s="20" t="inlineStr">
@@ -17352,22 +17352,22 @@
       </c>
       <c r="D118" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E118" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers</t>
+          <t>Under 9</t>
         </is>
       </c>
       <c r="F118" s="13" t="n">
-        <v>0.61746</v>
+        <v>0.41825</v>
       </c>
       <c r="G118" s="14" t="n">
-        <v>-161</v>
+        <v>139</v>
       </c>
       <c r="H118" s="15" t="n">
-        <v>-150</v>
+        <v>100</v>
       </c>
       <c r="I118" s="13">
         <f>IF($H$118="","",IF($H$118&lt;0,-$H$118/(-$H$118+100),100/($H$118+100)))</f>
@@ -17391,7 +17391,7 @@
       </c>
       <c r="N118" s="19" t="inlineStr">
         <is>
-          <t>Model 61.7% (fair -161). Your call.</t>
+          <t>Model 41.8% (fair +139). Your call.</t>
         </is>
       </c>
       <c r="O118" s="15" t="n"/>
@@ -17408,31 +17408,33 @@
       </c>
       <c r="B119" s="12" t="inlineStr">
         <is>
-          <t>Miami Marlins @ St. Louis Cardinals</t>
+          <t>Kansas City Royals @ Chicago White Sox</t>
         </is>
       </c>
       <c r="C119" s="12" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D119" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E119" s="12" t="inlineStr">
         <is>
-          <t>Miami Marlins</t>
+          <t>Chicago White Sox -1.5</t>
         </is>
       </c>
       <c r="F119" s="13" t="n">
-        <v>0.4869</v>
+        <v>0.4223529411764706</v>
       </c>
       <c r="G119" s="14" t="n">
-        <v>105</v>
-      </c>
-      <c r="H119" s="15" t="n"/>
+        <v>137</v>
+      </c>
+      <c r="H119" s="15" t="n">
+        <v>155</v>
+      </c>
       <c r="I119" s="13">
         <f>IF($H$119="","",IF($H$119&lt;0,-$H$119/(-$H$119+100),100/($H$119+100)))</f>
         <v/>
@@ -17455,7 +17457,7 @@
       </c>
       <c r="N119" s="19" t="inlineStr">
         <is>
-          <t>Model 48.7% (fair +105). Your call.</t>
+          <t>Model 42.2% (fair +137). Your call.</t>
         </is>
       </c>
       <c r="O119" s="15" t="n"/>
@@ -17472,31 +17474,33 @@
       </c>
       <c r="B120" s="20" t="inlineStr">
         <is>
-          <t>Miami Marlins @ St. Louis Cardinals</t>
+          <t>Kansas City Royals @ Chicago White Sox</t>
         </is>
       </c>
       <c r="C120" s="20" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D120" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E120" s="20" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals</t>
+          <t>Kansas City Royals +1.5</t>
         </is>
       </c>
       <c r="F120" s="13" t="n">
-        <v>0.5131</v>
+        <v>0.5776222222222221</v>
       </c>
       <c r="G120" s="14" t="n">
-        <v>-105</v>
-      </c>
-      <c r="H120" s="15" t="n"/>
+        <v>-137</v>
+      </c>
+      <c r="H120" s="15" t="n">
+        <v>-170</v>
+      </c>
       <c r="I120" s="13">
         <f>IF($H$120="","",IF($H$120&lt;0,-$H$120/(-$H$120+100),100/($H$120+100)))</f>
         <v/>
@@ -17519,7 +17523,7 @@
       </c>
       <c r="N120" s="19" t="inlineStr">
         <is>
-          <t>Model 51.3% (fair -105). Your call.</t>
+          <t>Model 57.8% (fair -137). Your call.</t>
         </is>
       </c>
       <c r="O120" s="15" t="n"/>
@@ -17536,12 +17540,12 @@
       </c>
       <c r="B121" s="12" t="inlineStr">
         <is>
-          <t>Athletics @ Los Angeles Angels</t>
+          <t>Chicago Cubs @ Milwaukee Brewers</t>
         </is>
       </c>
       <c r="C121" s="12" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D121" s="12" t="inlineStr">
@@ -17551,16 +17555,18 @@
       </c>
       <c r="E121" s="12" t="inlineStr">
         <is>
-          <t>Athletics</t>
+          <t>Chicago Cubs</t>
         </is>
       </c>
       <c r="F121" s="13" t="n">
-        <v>0.4265</v>
+        <v>0.3825409836065574</v>
       </c>
       <c r="G121" s="14" t="n">
-        <v>134</v>
-      </c>
-      <c r="H121" s="15" t="n"/>
+        <v>161</v>
+      </c>
+      <c r="H121" s="15" t="n">
+        <v>144</v>
+      </c>
       <c r="I121" s="13">
         <f>IF($H$121="","",IF($H$121&lt;0,-$H$121/(-$H$121+100),100/($H$121+100)))</f>
         <v/>
@@ -17583,7 +17589,7 @@
       </c>
       <c r="N121" s="19" t="inlineStr">
         <is>
-          <t>Model 42.6% (fair +134). Your call.</t>
+          <t>Model 38.3% (fair +161). Your call.</t>
         </is>
       </c>
       <c r="O121" s="15" t="n"/>
@@ -17600,12 +17606,12 @@
       </c>
       <c r="B122" s="20" t="inlineStr">
         <is>
-          <t>Athletics @ Los Angeles Angels</t>
+          <t>Chicago Cubs @ Milwaukee Brewers</t>
         </is>
       </c>
       <c r="C122" s="20" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D122" s="20" t="inlineStr">
@@ -17615,16 +17621,18 @@
       </c>
       <c r="E122" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Angels</t>
+          <t>Milwaukee Brewers</t>
         </is>
       </c>
       <c r="F122" s="13" t="n">
-        <v>0.5735</v>
+        <v>0.61746</v>
       </c>
       <c r="G122" s="14" t="n">
-        <v>-134</v>
-      </c>
-      <c r="H122" s="15" t="n"/>
+        <v>-161</v>
+      </c>
+      <c r="H122" s="15" t="n">
+        <v>-150</v>
+      </c>
       <c r="I122" s="13">
         <f>IF($H$122="","",IF($H$122&lt;0,-$H$122/(-$H$122+100),100/($H$122+100)))</f>
         <v/>
@@ -17647,7 +17655,7 @@
       </c>
       <c r="N122" s="19" t="inlineStr">
         <is>
-          <t>Model 57.4% (fair -134). Your call.</t>
+          <t>Model 61.7% (fair -161). Your call.</t>
         </is>
       </c>
       <c r="O122" s="15" t="n"/>
@@ -17664,12 +17672,12 @@
       </c>
       <c r="B123" s="12" t="inlineStr">
         <is>
-          <t>Atlanta Braves @ San Francisco Giants</t>
+          <t>Miami Marlins @ St. Louis Cardinals</t>
         </is>
       </c>
       <c r="C123" s="12" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="D123" s="12" t="inlineStr">
@@ -17679,14 +17687,14 @@
       </c>
       <c r="E123" s="12" t="inlineStr">
         <is>
-          <t>Atlanta Braves</t>
+          <t>Miami Marlins</t>
         </is>
       </c>
       <c r="F123" s="13" t="n">
-        <v>0.5389</v>
+        <v>0.4869</v>
       </c>
       <c r="G123" s="14" t="n">
-        <v>-117</v>
+        <v>105</v>
       </c>
       <c r="H123" s="15" t="n"/>
       <c r="I123" s="13">
@@ -17711,7 +17719,7 @@
       </c>
       <c r="N123" s="19" t="inlineStr">
         <is>
-          <t>Model 53.9% (fair -117). Your call.</t>
+          <t>Model 48.7% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O123" s="15" t="n"/>
@@ -17728,12 +17736,12 @@
       </c>
       <c r="B124" s="20" t="inlineStr">
         <is>
-          <t>Atlanta Braves @ San Francisco Giants</t>
+          <t>Miami Marlins @ St. Louis Cardinals</t>
         </is>
       </c>
       <c r="C124" s="20" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="D124" s="20" t="inlineStr">
@@ -17743,14 +17751,14 @@
       </c>
       <c r="E124" s="20" t="inlineStr">
         <is>
-          <t>San Francisco Giants</t>
+          <t>St. Louis Cardinals</t>
         </is>
       </c>
       <c r="F124" s="13" t="n">
-        <v>0.4612</v>
+        <v>0.5131</v>
       </c>
       <c r="G124" s="14" t="n">
-        <v>117</v>
+        <v>-105</v>
       </c>
       <c r="H124" s="15" t="n"/>
       <c r="I124" s="13">
@@ -17775,7 +17783,7 @@
       </c>
       <c r="N124" s="19" t="inlineStr">
         <is>
-          <t>Model 46.1% (fair +117). Your call.</t>
+          <t>Model 51.3% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O124" s="15" t="n"/>
@@ -17792,33 +17800,31 @@
       </c>
       <c r="B125" s="12" t="inlineStr">
         <is>
-          <t>Atlanta Braves @ San Francisco Giants</t>
+          <t>Athletics @ Los Angeles Angels</t>
         </is>
       </c>
       <c r="C125" s="12" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="D125" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E125" s="12" t="inlineStr">
         <is>
-          <t>Over 7.5</t>
+          <t>Athletics</t>
         </is>
       </c>
       <c r="F125" s="13" t="n">
-        <v>0.5612</v>
+        <v>0.4265</v>
       </c>
       <c r="G125" s="14" t="n">
-        <v>-128</v>
-      </c>
-      <c r="H125" s="15" t="n">
-        <v>-115</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="H125" s="15" t="n"/>
       <c r="I125" s="13">
         <f>IF($H$125="","",IF($H$125&lt;0,-$H$125/(-$H$125+100),100/($H$125+100)))</f>
         <v/>
@@ -17841,7 +17847,7 @@
       </c>
       <c r="N125" s="19" t="inlineStr">
         <is>
-          <t>Model 56.1% (fair -128). Your call.</t>
+          <t>Model 42.6% (fair +134). Your call.</t>
         </is>
       </c>
       <c r="O125" s="15" t="n"/>
@@ -17858,33 +17864,31 @@
       </c>
       <c r="B126" s="20" t="inlineStr">
         <is>
-          <t>Atlanta Braves @ San Francisco Giants</t>
+          <t>Athletics @ Los Angeles Angels</t>
         </is>
       </c>
       <c r="C126" s="20" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="D126" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E126" s="20" t="inlineStr">
         <is>
-          <t>Under 7.5</t>
+          <t>Los Angeles Angels</t>
         </is>
       </c>
       <c r="F126" s="13" t="n">
-        <v>0.4387975609756098</v>
+        <v>0.5735</v>
       </c>
       <c r="G126" s="14" t="n">
-        <v>128</v>
-      </c>
-      <c r="H126" s="15" t="n">
-        <v>-105</v>
-      </c>
+        <v>-134</v>
+      </c>
+      <c r="H126" s="15" t="n"/>
       <c r="I126" s="13">
         <f>IF($H$126="","",IF($H$126&lt;0,-$H$126/(-$H$126+100),100/($H$126+100)))</f>
         <v/>
@@ -17907,7 +17911,7 @@
       </c>
       <c r="N126" s="19" t="inlineStr">
         <is>
-          <t>Model 43.9% (fair +128). Your call.</t>
+          <t>Model 57.4% (fair -134). Your call.</t>
         </is>
       </c>
       <c r="O126" s="15" t="n"/>
@@ -17934,23 +17938,21 @@
       </c>
       <c r="D127" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E127" s="12" t="inlineStr">
         <is>
-          <t>San Francisco Giants +1.5</t>
+          <t>Atlanta Braves</t>
         </is>
       </c>
       <c r="F127" s="13" t="n">
-        <v>0.6076</v>
+        <v>0.5389</v>
       </c>
       <c r="G127" s="14" t="n">
-        <v>-155</v>
-      </c>
-      <c r="H127" s="15" t="n">
-        <v>-140</v>
-      </c>
+        <v>-117</v>
+      </c>
+      <c r="H127" s="15" t="n"/>
       <c r="I127" s="13">
         <f>IF($H$127="","",IF($H$127&lt;0,-$H$127/(-$H$127+100),100/($H$127+100)))</f>
         <v/>
@@ -17973,7 +17975,7 @@
       </c>
       <c r="N127" s="19" t="inlineStr">
         <is>
-          <t>Model 60.8% (fair -155). Your call.</t>
+          <t>Model 53.9% (fair -117). Your call.</t>
         </is>
       </c>
       <c r="O127" s="15" t="n"/>
@@ -18000,23 +18002,21 @@
       </c>
       <c r="D128" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E128" s="20" t="inlineStr">
         <is>
-          <t>Atlanta Braves -1.5</t>
+          <t>San Francisco Giants</t>
         </is>
       </c>
       <c r="F128" s="13" t="n">
-        <v>0.3923720930232558</v>
+        <v>0.4612</v>
       </c>
       <c r="G128" s="14" t="n">
-        <v>155</v>
-      </c>
-      <c r="H128" s="15" t="n">
-        <v>115</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="H128" s="15" t="n"/>
       <c r="I128" s="13">
         <f>IF($H$128="","",IF($H$128&lt;0,-$H$128/(-$H$128+100),100/($H$128+100)))</f>
         <v/>
@@ -18039,7 +18039,7 @@
       </c>
       <c r="N128" s="19" t="inlineStr">
         <is>
-          <t>Model 39.2% (fair +155). Your call.</t>
+          <t>Model 46.1% (fair +117). Your call.</t>
         </is>
       </c>
       <c r="O128" s="15" t="n"/>
@@ -18056,31 +18056,33 @@
       </c>
       <c r="B129" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers @ San Diego Padres</t>
+          <t>Atlanta Braves @ San Francisco Giants</t>
         </is>
       </c>
       <c r="C129" s="12" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="D129" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E129" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F129" s="13" t="n">
-        <v>0.5423</v>
+        <v>0.5612634146341464</v>
       </c>
       <c r="G129" s="14" t="n">
-        <v>-118</v>
-      </c>
-      <c r="H129" s="15" t="n"/>
+        <v>-128</v>
+      </c>
+      <c r="H129" s="15" t="n">
+        <v>-105</v>
+      </c>
       <c r="I129" s="13">
         <f>IF($H$129="","",IF($H$129&lt;0,-$H$129/(-$H$129+100),100/($H$129+100)))</f>
         <v/>
@@ -18103,7 +18105,7 @@
       </c>
       <c r="N129" s="19" t="inlineStr">
         <is>
-          <t>Model 54.2% (fair -118). Your call.</t>
+          <t>Model 56.1% (fair -128). Your call.</t>
         </is>
       </c>
       <c r="O129" s="15" t="n"/>
@@ -18120,31 +18122,33 @@
       </c>
       <c r="B130" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers @ San Diego Padres</t>
+          <t>Atlanta Braves @ San Francisco Giants</t>
         </is>
       </c>
       <c r="C130" s="20" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="D130" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E130" s="20" t="inlineStr">
         <is>
-          <t>San Diego Padres</t>
+          <t>Under 7.5</t>
         </is>
       </c>
       <c r="F130" s="13" t="n">
-        <v>0.4577</v>
+        <v>0.4387254901960784</v>
       </c>
       <c r="G130" s="14" t="n">
-        <v>118</v>
-      </c>
-      <c r="H130" s="15" t="n"/>
+        <v>128</v>
+      </c>
+      <c r="H130" s="15" t="n">
+        <v>104</v>
+      </c>
       <c r="I130" s="13">
         <f>IF($H$130="","",IF($H$130&lt;0,-$H$130/(-$H$130+100),100/($H$130+100)))</f>
         <v/>
@@ -18167,7 +18171,7 @@
       </c>
       <c r="N130" s="19" t="inlineStr">
         <is>
-          <t>Model 45.8% (fair +118). Your call.</t>
+          <t>Model 43.9% (fair +128). Your call.</t>
         </is>
       </c>
       <c r="O130" s="15" t="n"/>
@@ -18184,32 +18188,32 @@
       </c>
       <c r="B131" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers @ San Diego Padres</t>
+          <t>Atlanta Braves @ San Francisco Giants</t>
         </is>
       </c>
       <c r="C131" s="12" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="D131" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E131" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>San Francisco Giants +1.5</t>
         </is>
       </c>
       <c r="F131" s="13" t="n">
-        <v>0.4798243902439024</v>
+        <v>0.6019565217391304</v>
       </c>
       <c r="G131" s="14" t="n">
-        <v>108</v>
+        <v>-151</v>
       </c>
       <c r="H131" s="15" t="n">
-        <v>-105</v>
+        <v>-130</v>
       </c>
       <c r="I131" s="13">
         <f>IF($H$131="","",IF($H$131&lt;0,-$H$131/(-$H$131+100),100/($H$131+100)))</f>
@@ -18233,7 +18237,7 @@
       </c>
       <c r="N131" s="19" t="inlineStr">
         <is>
-          <t>Model 48.0% (fair +108). Your call.</t>
+          <t>Model 60.2% (fair -151). Your call.</t>
         </is>
       </c>
       <c r="O131" s="15" t="n"/>
@@ -18250,32 +18254,32 @@
       </c>
       <c r="B132" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers @ San Diego Padres</t>
+          <t>Atlanta Braves @ San Francisco Giants</t>
         </is>
       </c>
       <c r="C132" s="20" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="D132" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E132" s="20" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>Atlanta Braves -1.5</t>
         </is>
       </c>
       <c r="F132" s="13" t="n">
-        <v>0.5201744186046512</v>
+        <v>0.3980188679245283</v>
       </c>
       <c r="G132" s="14" t="n">
-        <v>-108</v>
+        <v>151</v>
       </c>
       <c r="H132" s="15" t="n">
-        <v>-115</v>
+        <v>112</v>
       </c>
       <c r="I132" s="13">
         <f>IF($H$132="","",IF($H$132&lt;0,-$H$132/(-$H$132+100),100/($H$132+100)))</f>
@@ -18299,7 +18303,7 @@
       </c>
       <c r="N132" s="19" t="inlineStr">
         <is>
-          <t>Model 52.0% (fair -108). Your call.</t>
+          <t>Model 39.8% (fair +151). Your call.</t>
         </is>
       </c>
       <c r="O132" s="15" t="n"/>
@@ -18326,23 +18330,21 @@
       </c>
       <c r="D133" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E133" s="12" t="inlineStr">
         <is>
-          <t>San Diego Padres +1.5</t>
+          <t>Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="F133" s="13" t="n">
-        <v>0.6143400000000001</v>
+        <v>0.5423</v>
       </c>
       <c r="G133" s="14" t="n">
-        <v>-159</v>
-      </c>
-      <c r="H133" s="15" t="n">
-        <v>-150</v>
-      </c>
+        <v>-118</v>
+      </c>
+      <c r="H133" s="15" t="n"/>
       <c r="I133" s="13">
         <f>IF($H$133="","",IF($H$133&lt;0,-$H$133/(-$H$133+100),100/($H$133+100)))</f>
         <v/>
@@ -18365,7 +18367,7 @@
       </c>
       <c r="N133" s="19" t="inlineStr">
         <is>
-          <t>Model 61.4% (fair -159). Your call.</t>
+          <t>Model 54.2% (fair -118). Your call.</t>
         </is>
       </c>
       <c r="O133" s="15" t="n"/>
@@ -18392,23 +18394,21 @@
       </c>
       <c r="D134" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E134" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers -1.5</t>
+          <t>San Diego Padres</t>
         </is>
       </c>
       <c r="F134" s="13" t="n">
-        <v>0.3856444444444445</v>
+        <v>0.4577</v>
       </c>
       <c r="G134" s="14" t="n">
-        <v>159</v>
-      </c>
-      <c r="H134" s="15" t="n">
-        <v>125</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="H134" s="15" t="n"/>
       <c r="I134" s="13">
         <f>IF($H$134="","",IF($H$134&lt;0,-$H$134/(-$H$134+100),100/($H$134+100)))</f>
         <v/>
@@ -18431,7 +18431,7 @@
       </c>
       <c r="N134" s="19" t="inlineStr">
         <is>
-          <t>Model 38.6% (fair +159). Your call.</t>
+          <t>Model 45.8% (fair +118). Your call.</t>
         </is>
       </c>
       <c r="O134" s="15" t="n"/>
@@ -18448,31 +18448,33 @@
       </c>
       <c r="B135" s="12" t="inlineStr">
         <is>
-          <t>New York Yankees @ Boston Red Sox</t>
+          <t>Los Angeles Dodgers @ San Diego Padres</t>
         </is>
       </c>
       <c r="C135" s="12" t="inlineStr">
         <is>
-          <t>23:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="D135" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E135" s="12" t="inlineStr">
         <is>
-          <t>New York Yankees</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F135" s="13" t="n">
-        <v>0.5516</v>
+        <v>0.4704</v>
       </c>
       <c r="G135" s="14" t="n">
-        <v>-123</v>
-      </c>
-      <c r="H135" s="15" t="n"/>
+        <v>113</v>
+      </c>
+      <c r="H135" s="15" t="n">
+        <v>117</v>
+      </c>
       <c r="I135" s="13">
         <f>IF($H$135="","",IF($H$135&lt;0,-$H$135/(-$H$135+100),100/($H$135+100)))</f>
         <v/>
@@ -18495,7 +18497,7 @@
       </c>
       <c r="N135" s="19" t="inlineStr">
         <is>
-          <t>Model 55.2% (fair -123). Your call.</t>
+          <t>Model 47.0% (fair +113). Your call.</t>
         </is>
       </c>
       <c r="O135" s="15" t="n"/>
@@ -18512,32 +18514,32 @@
       </c>
       <c r="B136" s="20" t="inlineStr">
         <is>
-          <t>New York Yankees @ Boston Red Sox</t>
+          <t>Los Angeles Dodgers @ San Diego Padres</t>
         </is>
       </c>
       <c r="C136" s="20" t="inlineStr">
         <is>
-          <t>23:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="D136" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E136" s="20" t="inlineStr">
         <is>
-          <t>Boston Red Sox</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F136" s="13" t="n">
-        <v>0.4484162995594714</v>
+        <v>0.5296000000000001</v>
       </c>
       <c r="G136" s="14" t="n">
-        <v>123</v>
+        <v>-113</v>
       </c>
       <c r="H136" s="15" t="n">
-        <v>-127</v>
+        <v>105</v>
       </c>
       <c r="I136" s="13">
         <f>IF($H$136="","",IF($H$136&lt;0,-$H$136/(-$H$136+100),100/($H$136+100)))</f>
@@ -18561,7 +18563,7 @@
       </c>
       <c r="N136" s="19" t="inlineStr">
         <is>
-          <t>Model 44.8% (fair +123). Your call.</t>
+          <t>Model 53.0% (fair -113). Your call.</t>
         </is>
       </c>
       <c r="O136" s="15" t="n"/>
@@ -18578,32 +18580,32 @@
       </c>
       <c r="B137" s="12" t="inlineStr">
         <is>
-          <t>New York Yankees @ Boston Red Sox</t>
+          <t>Los Angeles Dodgers @ San Diego Padres</t>
         </is>
       </c>
       <c r="C137" s="12" t="inlineStr">
         <is>
-          <t>23:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="D137" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E137" s="12" t="inlineStr">
         <is>
-          <t>Over 8</t>
+          <t>San Diego Padres +1.5</t>
         </is>
       </c>
       <c r="F137" s="13" t="n">
-        <v>0.5584463414634147</v>
+        <v>0.6081249999999999</v>
       </c>
       <c r="G137" s="14" t="n">
-        <v>-126</v>
+        <v>-155</v>
       </c>
       <c r="H137" s="15" t="n">
-        <v>-105</v>
+        <v>-140</v>
       </c>
       <c r="I137" s="13">
         <f>IF($H$137="","",IF($H$137&lt;0,-$H$137/(-$H$137+100),100/($H$137+100)))</f>
@@ -18627,7 +18629,7 @@
       </c>
       <c r="N137" s="19" t="inlineStr">
         <is>
-          <t>Model 55.8% (fair -126). Your call.</t>
+          <t>Model 60.8% (fair -155). Your call.</t>
         </is>
       </c>
       <c r="O137" s="15" t="n"/>
@@ -18644,32 +18646,32 @@
       </c>
       <c r="B138" s="20" t="inlineStr">
         <is>
-          <t>New York Yankees @ Boston Red Sox</t>
+          <t>Los Angeles Dodgers @ San Diego Padres</t>
         </is>
       </c>
       <c r="C138" s="20" t="inlineStr">
         <is>
-          <t>23:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="D138" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E138" s="20" t="inlineStr">
         <is>
-          <t>Under 8</t>
+          <t>Los Angeles Dodgers -1.5</t>
         </is>
       </c>
       <c r="F138" s="13" t="n">
-        <v>0.44155</v>
+        <v>0.3918636363636363</v>
       </c>
       <c r="G138" s="14" t="n">
-        <v>126</v>
+        <v>155</v>
       </c>
       <c r="H138" s="15" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="I138" s="13">
         <f>IF($H$138="","",IF($H$138&lt;0,-$H$138/(-$H$138+100),100/($H$138+100)))</f>
@@ -18693,7 +18695,7 @@
       </c>
       <c r="N138" s="19" t="inlineStr">
         <is>
-          <t>Model 44.2% (fair +126). Your call.</t>
+          <t>Model 39.2% (fair +155). Your call.</t>
         </is>
       </c>
       <c r="O138" s="15" t="n"/>
@@ -18720,23 +18722,21 @@
       </c>
       <c r="D139" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E139" s="12" t="inlineStr">
         <is>
-          <t>Boston Red Sox -1.5</t>
+          <t>New York Yankees</t>
         </is>
       </c>
       <c r="F139" s="13" t="n">
-        <v>0.3221153846153846</v>
+        <v>0.5516</v>
       </c>
       <c r="G139" s="14" t="n">
-        <v>210</v>
-      </c>
-      <c r="H139" s="15" t="n">
-        <v>160</v>
-      </c>
+        <v>-123</v>
+      </c>
+      <c r="H139" s="15" t="n"/>
       <c r="I139" s="13">
         <f>IF($H$139="","",IF($H$139&lt;0,-$H$139/(-$H$139+100),100/($H$139+100)))</f>
         <v/>
@@ -18759,7 +18759,7 @@
       </c>
       <c r="N139" s="19" t="inlineStr">
         <is>
-          <t>Model 32.2% (fair +210). Your call.</t>
+          <t>Model 55.2% (fair -123). Your call.</t>
         </is>
       </c>
       <c r="O139" s="15" t="n"/>
@@ -18786,22 +18786,22 @@
       </c>
       <c r="D140" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E140" s="20" t="inlineStr">
         <is>
-          <t>New York Yankees +1.5</t>
+          <t>Boston Red Sox</t>
         </is>
       </c>
       <c r="F140" s="13" t="n">
-        <v>0.6778728813559323</v>
+        <v>0.4484162995594714</v>
       </c>
       <c r="G140" s="14" t="n">
-        <v>-210</v>
+        <v>123</v>
       </c>
       <c r="H140" s="15" t="n">
-        <v>-195</v>
+        <v>-127</v>
       </c>
       <c r="I140" s="13">
         <f>IF($H$140="","",IF($H$140&lt;0,-$H$140/(-$H$140+100),100/($H$140+100)))</f>
@@ -18825,7 +18825,7 @@
       </c>
       <c r="N140" s="19" t="inlineStr">
         <is>
-          <t>Model 67.8% (fair -210). Your call.</t>
+          <t>Model 44.8% (fair +123). Your call.</t>
         </is>
       </c>
       <c r="O140" s="15" t="n"/>
@@ -18834,9 +18834,271 @@
         <v/>
       </c>
     </row>
+    <row r="141">
+      <c r="A141" s="12" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B141" s="12" t="inlineStr">
+        <is>
+          <t>New York Yankees @ Boston Red Sox</t>
+        </is>
+      </c>
+      <c r="C141" s="12" t="inlineStr">
+        <is>
+          <t>23:20</t>
+        </is>
+      </c>
+      <c r="D141" s="12" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E141" s="12" t="inlineStr">
+        <is>
+          <t>Over 9</t>
+        </is>
+      </c>
+      <c r="F141" s="13" t="n">
+        <v>0.4769048780487805</v>
+      </c>
+      <c r="G141" s="14" t="n">
+        <v>110</v>
+      </c>
+      <c r="H141" s="15" t="n">
+        <v>-105</v>
+      </c>
+      <c r="I141" s="13">
+        <f>IF($H$141="","",IF($H$141&lt;0,-$H$141/(-$H$141+100),100/($H$141+100)))</f>
+        <v/>
+      </c>
+      <c r="J141" s="16">
+        <f>IF($H$141="","",$F$141*IF($H$141&lt;0,-100/$H$141,$H$141/100)-(1-$F$141))</f>
+        <v/>
+      </c>
+      <c r="K141" s="17">
+        <f>IF($H$141="","",MAX(0,($F$141*IF($H$141&lt;0,-100/$H$141,$H$141/100)-(1-$F$141))/IF($H$141&lt;0,-100/$H$141,$H$141/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L141" s="18">
+        <f>IF($H$141="","",ROUND(MIN($K$141,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M141" s="12">
+        <f>IF($J$141="","",IF($J$141&lt;0,"Pass",IF($J$141&lt;'Settings'!$B$4,"Thin",IF($J$141&lt;0.06,"✅ Sharp band",IF($J$141&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N141" s="19" t="inlineStr">
+        <is>
+          <t>Model 47.7% (fair +110). Your call.</t>
+        </is>
+      </c>
+      <c r="O141" s="15" t="n"/>
+      <c r="P141" s="16">
+        <f>IF(OR($H$141="",$O$141=""),"",(1+IF($H$141&lt;0,-100/$H$141,$H$141/100))/(1+IF($O$141&lt;0,-100/$O$141,$O$141/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B142" s="20" t="inlineStr">
+        <is>
+          <t>New York Yankees @ Boston Red Sox</t>
+        </is>
+      </c>
+      <c r="C142" s="20" t="inlineStr">
+        <is>
+          <t>23:20</t>
+        </is>
+      </c>
+      <c r="D142" s="20" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E142" s="20" t="inlineStr">
+        <is>
+          <t>Under 9</t>
+        </is>
+      </c>
+      <c r="F142" s="13" t="n">
+        <v>0.5231</v>
+      </c>
+      <c r="G142" s="14" t="n">
+        <v>-110</v>
+      </c>
+      <c r="H142" s="15" t="n">
+        <v>100</v>
+      </c>
+      <c r="I142" s="13">
+        <f>IF($H$142="","",IF($H$142&lt;0,-$H$142/(-$H$142+100),100/($H$142+100)))</f>
+        <v/>
+      </c>
+      <c r="J142" s="16">
+        <f>IF($H$142="","",$F$142*IF($H$142&lt;0,-100/$H$142,$H$142/100)-(1-$F$142))</f>
+        <v/>
+      </c>
+      <c r="K142" s="17">
+        <f>IF($H$142="","",MAX(0,($F$142*IF($H$142&lt;0,-100/$H$142,$H$142/100)-(1-$F$142))/IF($H$142&lt;0,-100/$H$142,$H$142/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L142" s="18">
+        <f>IF($H$142="","",ROUND(MIN($K$142,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M142" s="12">
+        <f>IF($J$142="","",IF($J$142&lt;0,"Pass",IF($J$142&lt;'Settings'!$B$4,"Thin",IF($J$142&lt;0.06,"✅ Sharp band",IF($J$142&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N142" s="19" t="inlineStr">
+        <is>
+          <t>Model 52.3% (fair -110). Your call.</t>
+        </is>
+      </c>
+      <c r="O142" s="15" t="n"/>
+      <c r="P142" s="16">
+        <f>IF(OR($H$142="",$O$142=""),"",(1+IF($H$142&lt;0,-100/$H$142,$H$142/100))/(1+IF($O$142&lt;0,-100/$O$142,$O$142/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="12" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B143" s="12" t="inlineStr">
+        <is>
+          <t>New York Yankees @ Boston Red Sox</t>
+        </is>
+      </c>
+      <c r="C143" s="12" t="inlineStr">
+        <is>
+          <t>23:20</t>
+        </is>
+      </c>
+      <c r="D143" s="12" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E143" s="12" t="inlineStr">
+        <is>
+          <t>Boston Red Sox -1.5</t>
+        </is>
+      </c>
+      <c r="F143" s="13" t="n">
+        <v>0.2763921568627451</v>
+      </c>
+      <c r="G143" s="14" t="n">
+        <v>262</v>
+      </c>
+      <c r="H143" s="15" t="n">
+        <v>155</v>
+      </c>
+      <c r="I143" s="13">
+        <f>IF($H$143="","",IF($H$143&lt;0,-$H$143/(-$H$143+100),100/($H$143+100)))</f>
+        <v/>
+      </c>
+      <c r="J143" s="16">
+        <f>IF($H$143="","",$F$143*IF($H$143&lt;0,-100/$H$143,$H$143/100)-(1-$F$143))</f>
+        <v/>
+      </c>
+      <c r="K143" s="17">
+        <f>IF($H$143="","",MAX(0,($F$143*IF($H$143&lt;0,-100/$H$143,$H$143/100)-(1-$F$143))/IF($H$143&lt;0,-100/$H$143,$H$143/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L143" s="18">
+        <f>IF($H$143="","",ROUND(MIN($K$143,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M143" s="12">
+        <f>IF($J$143="","",IF($J$143&lt;0,"Pass",IF($J$143&lt;'Settings'!$B$4,"Thin",IF($J$143&lt;0.06,"✅ Sharp band",IF($J$143&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N143" s="19" t="inlineStr">
+        <is>
+          <t>Model 27.6% (fair +262). Your call.</t>
+        </is>
+      </c>
+      <c r="O143" s="15" t="n"/>
+      <c r="P143" s="16">
+        <f>IF(OR($H$143="",$O$143=""),"",(1+IF($H$143&lt;0,-100/$H$143,$H$143/100))/(1+IF($O$143&lt;0,-100/$O$143,$O$143/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B144" s="20" t="inlineStr">
+        <is>
+          <t>New York Yankees @ Boston Red Sox</t>
+        </is>
+      </c>
+      <c r="C144" s="20" t="inlineStr">
+        <is>
+          <t>23:20</t>
+        </is>
+      </c>
+      <c r="D144" s="20" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E144" s="20" t="inlineStr">
+        <is>
+          <t>New York Yankees +1.5</t>
+        </is>
+      </c>
+      <c r="F144" s="13" t="n">
+        <v>0.7236</v>
+      </c>
+      <c r="G144" s="14" t="n">
+        <v>-262</v>
+      </c>
+      <c r="H144" s="15" t="n"/>
+      <c r="I144" s="13">
+        <f>IF($H$144="","",IF($H$144&lt;0,-$H$144/(-$H$144+100),100/($H$144+100)))</f>
+        <v/>
+      </c>
+      <c r="J144" s="16">
+        <f>IF($H$144="","",$F$144*IF($H$144&lt;0,-100/$H$144,$H$144/100)-(1-$F$144))</f>
+        <v/>
+      </c>
+      <c r="K144" s="17">
+        <f>IF($H$144="","",MAX(0,($F$144*IF($H$144&lt;0,-100/$H$144,$H$144/100)-(1-$F$144))/IF($H$144&lt;0,-100/$H$144,$H$144/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L144" s="18">
+        <f>IF($H$144="","",ROUND(MIN($K$144,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M144" s="12">
+        <f>IF($J$144="","",IF($J$144&lt;0,"Pass",IF($J$144&lt;'Settings'!$B$4,"Thin",IF($J$144&lt;0.06,"✅ Sharp band",IF($J$144&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N144" s="19" t="inlineStr">
+        <is>
+          <t>Model 72.4% (fair -262). Your call.</t>
+        </is>
+      </c>
+      <c r="O144" s="15" t="n"/>
+      <c r="P144" s="16">
+        <f>IF(OR($H$144="",$O$144=""),"",(1+IF($H$144&lt;0,-100/$H$144,$H$144/100))/(1+IF($O$144&lt;0,-100/$O$144,$O$144/100))-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="CE4B"/>
-  <conditionalFormatting sqref="J5:J140">
+  <conditionalFormatting sqref="J5:J144">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-0.05"/>
@@ -19262,17 +19524,17 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Toronto Tempo -7.5</t>
+          <t>Toronto Tempo -6.5</t>
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.4358</v>
+        <v>0.4702</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>129</v>
+        <v>113</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -19296,7 +19558,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 43.6% (fair +129). Your call.</t>
+          <t>Model 47.0% (fair +113). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -19328,14 +19590,14 @@
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>Phoenix Mercury +7.5</t>
+          <t>Phoenix Mercury +6.5</t>
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.5642</v>
+        <v>0.5298</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-129</v>
+        <v>-113</v>
       </c>
       <c r="H10" s="15" t="n">
         <v>111</v>
@@ -19362,7 +19624,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 56.4% (fair -129). Your call.</t>
+          <t>Model 53.0% (fair -113). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -19398,10 +19660,10 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.2906666666666666</v>
+        <v>0.2901159420289854</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H11" s="15" t="n">
         <v>245</v>
@@ -19428,7 +19690,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 29.1% (fair +244). Your call.</t>
+          <t>Model 29.0% (fair +245). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -19464,13 +19726,13 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.7092857142857143</v>
+        <v>0.7099056338028169</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>-244</v>
+        <v>-245</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>-250</v>
+        <v>-255</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -19494,7 +19756,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 70.9% (fair -244). Your call.</t>
+          <t>Model 71.0% (fair -245). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -19536,7 +19798,7 @@
         <v>-251</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>100</v>
+        <v>-104</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -19602,7 +19864,7 @@
         <v>251</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>100</v>
+        <v>-104</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -19658,14 +19920,14 @@
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Indiana Fever -7.5</t>
+          <t>Indiana Fever -6.5</t>
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.4933463414634147</v>
+        <v>0.510709756097561</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>103</v>
+        <v>-104</v>
       </c>
       <c r="H15" s="15" t="n">
         <v>-105</v>
@@ -19692,7 +19954,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 49.3% (fair +103). Your call.</t>
+          <t>Model 51.1% (fair -104). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -19724,14 +19986,14 @@
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Sparks +7.5</t>
+          <t>Los Angeles Sparks +6.5</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.5066666666666667</v>
+        <v>0.4893137254901961</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>-103</v>
+        <v>104</v>
       </c>
       <c r="H16" s="15" t="n">
         <v>104</v>
@@ -19758,7 +20020,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 50.7% (fair -103). Your call.</t>
+          <t>Model 48.9% (fair +104). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -19794,10 +20056,10 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.762675</v>
+        <v>0.7608</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>-321</v>
+        <v>-318</v>
       </c>
       <c r="H17" s="15" t="n">
         <v>-300</v>
@@ -19824,7 +20086,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 76.3% (fair -321). Your call.</t>
+          <t>Model 76.1% (fair -318). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -19860,13 +20122,13 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.2373529411764706</v>
+        <v>0.2392</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -19890,7 +20152,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 23.7% (fair +321). Your call.</t>
+          <t>Model 23.9% (fair +318). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -20054,17 +20316,17 @@
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Seattle Storm +7.5</t>
+          <t>Seattle Storm -4.5</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.5591</v>
+        <v>0.1855</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>-127</v>
+        <v>439</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>113</v>
+        <v>430</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -20088,7 +20350,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 55.9% (fair -127). Your call.</t>
+          <t>Model 18.6% (fair +439). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -20120,14 +20382,14 @@
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>Atlanta Dream -7.5</t>
+          <t>Atlanta Dream +4.5</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.4409</v>
+        <v>0.8145</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>127</v>
+        <v>-439</v>
       </c>
       <c r="H22" s="15" t="n">
         <v>108</v>
@@ -20154,7 +20416,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 44.1% (fair +127). Your call.</t>
+          <t>Model 81.5% (fair -439). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -20190,13 +20452,13 @@
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.6240117647058824</v>
+        <v>0.6243046875</v>
       </c>
       <c r="G23" s="14" t="n">
         <v>-166</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>-155</v>
+        <v>-156</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -20256,7 +20518,7 @@
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.376015625</v>
+        <v>0.375703125</v>
       </c>
       <c r="G24" s="14" t="n">
         <v>166</v>
@@ -20322,13 +20584,13 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.4100862745098039</v>
+        <v>0.4101</v>
       </c>
       <c r="G25" s="14" t="n">
         <v>144</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>-104</v>
+        <v>100</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -20394,7 +20656,7 @@
         <v>-144</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>-104</v>
+        <v>100</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -20460,7 +20722,7 @@
         <v>-102</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>-104</v>
+        <v>113</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -20526,7 +20788,7 @@
         <v>102</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -20586,13 +20848,13 @@
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.3086</v>
+        <v>0.3017117117117117</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -20616,7 +20878,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 30.9% (fair +224). Your call.</t>
+          <t>Model 30.2% (fair +231). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -20652,13 +20914,13 @@
         </is>
       </c>
       <c r="F30" s="13" t="n">
-        <v>0.6914</v>
+        <v>0.698269014084507</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>-224</v>
+        <v>-231</v>
       </c>
       <c r="H30" s="15" t="n">
-        <v>-210</v>
+        <v>-255</v>
       </c>
       <c r="I30" s="13">
         <f>IF($H$30="","",IF($H$30&lt;0,-$H$30/(-$H$30+100),100/($H$30+100)))</f>
@@ -20682,7 +20944,7 @@
       </c>
       <c r="N30" s="19" t="inlineStr">
         <is>
-          <t>Model 69.1% (fair -224). Your call.</t>
+          <t>Model 69.8% (fair -231). Your call.</t>
         </is>
       </c>
       <c r="O30" s="15" t="n"/>
@@ -20714,17 +20976,17 @@
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>Over 164.5</t>
+          <t>Over 165.5</t>
         </is>
       </c>
       <c r="F31" s="13" t="n">
-        <v>0.6287809523809523</v>
+        <v>0.6033500000000001</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>-169</v>
+        <v>-152</v>
       </c>
       <c r="H31" s="15" t="n">
-        <v>-110</v>
+        <v>100</v>
       </c>
       <c r="I31" s="13">
         <f>IF($H$31="","",IF($H$31&lt;0,-$H$31/(-$H$31+100),100/($H$31+100)))</f>
@@ -20748,7 +21010,7 @@
       </c>
       <c r="N31" s="19" t="inlineStr">
         <is>
-          <t>Model 62.9% (fair -169). Your call.</t>
+          <t>Model 60.3% (fair -152). Your call.</t>
         </is>
       </c>
       <c r="O31" s="15" t="n"/>
@@ -20780,17 +21042,17 @@
       </c>
       <c r="E32" s="20" t="inlineStr">
         <is>
-          <t>Under 164.5</t>
+          <t>Under 165.5</t>
         </is>
       </c>
       <c r="F32" s="13" t="n">
-        <v>0.3712</v>
+        <v>0.3967000000000001</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>169</v>
+        <v>152</v>
       </c>
       <c r="H32" s="15" t="n">
-        <v>-110</v>
+        <v>100</v>
       </c>
       <c r="I32" s="13">
         <f>IF($H$32="","",IF($H$32&lt;0,-$H$32/(-$H$32+100),100/($H$32+100)))</f>
@@ -20814,7 +21076,7 @@
       </c>
       <c r="N32" s="19" t="inlineStr">
         <is>
-          <t>Model 37.1% (fair +169). Your call.</t>
+          <t>Model 39.7% (fair +152). Your call.</t>
         </is>
       </c>
       <c r="O32" s="15" t="n"/>
@@ -20846,17 +21108,17 @@
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t>Washington Mystics -5.5</t>
+          <t>Washington Mystics -6.5</t>
         </is>
       </c>
       <c r="F33" s="13" t="n">
-        <v>0.4981952380952381</v>
+        <v>0.4811529411764706</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="H33" s="15" t="n">
-        <v>-110</v>
+        <v>-104</v>
       </c>
       <c r="I33" s="13">
         <f>IF($H$33="","",IF($H$33&lt;0,-$H$33/(-$H$33+100),100/($H$33+100)))</f>
@@ -20880,7 +21142,7 @@
       </c>
       <c r="N33" s="19" t="inlineStr">
         <is>
-          <t>Model 49.8% (fair +101). Your call.</t>
+          <t>Model 48.1% (fair +108). Your call.</t>
         </is>
       </c>
       <c r="O33" s="15" t="n"/>
@@ -20912,17 +21174,17 @@
       </c>
       <c r="E34" s="20" t="inlineStr">
         <is>
-          <t>Portland Fire +5.5</t>
+          <t>Portland Fire +6.5</t>
         </is>
       </c>
       <c r="F34" s="13" t="n">
-        <v>0.5017999999999999</v>
+        <v>0.5188118811881188</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>-101</v>
+        <v>-108</v>
       </c>
       <c r="H34" s="15" t="n">
-        <v>-104</v>
+        <v>102</v>
       </c>
       <c r="I34" s="13">
         <f>IF($H$34="","",IF($H$34&lt;0,-$H$34/(-$H$34+100),100/($H$34+100)))</f>
@@ -20946,7 +21208,7 @@
       </c>
       <c r="N34" s="19" t="inlineStr">
         <is>
-          <t>Model 50.2% (fair -101). Your call.</t>
+          <t>Model 51.9% (fair -108). Your call.</t>
         </is>
       </c>
       <c r="O34" s="15" t="n"/>
@@ -20982,13 +21244,13 @@
         </is>
       </c>
       <c r="F35" s="13" t="n">
-        <v>0.753225</v>
+        <v>0.7489948979591837</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>-305</v>
+        <v>-298</v>
       </c>
       <c r="H35" s="15" t="n">
-        <v>-300</v>
+        <v>-292</v>
       </c>
       <c r="I35" s="13">
         <f>IF($H$35="","",IF($H$35&lt;0,-$H$35/(-$H$35+100),100/($H$35+100)))</f>
@@ -21012,7 +21274,7 @@
       </c>
       <c r="N35" s="19" t="inlineStr">
         <is>
-          <t>Model 75.3% (fair -305). Your call.</t>
+          <t>Model 74.9% (fair -298). Your call.</t>
         </is>
       </c>
       <c r="O35" s="15" t="n"/>
@@ -21048,13 +21310,13 @@
         </is>
       </c>
       <c r="F36" s="13" t="n">
-        <v>0.24675</v>
+        <v>0.251012987012987</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="H36" s="15" t="n">
-        <v>300</v>
+        <v>285</v>
       </c>
       <c r="I36" s="13">
         <f>IF($H$36="","",IF($H$36&lt;0,-$H$36/(-$H$36+100),100/($H$36+100)))</f>
@@ -21078,7 +21340,7 @@
       </c>
       <c r="N36" s="19" t="inlineStr">
         <is>
-          <t>Model 24.7% (fair +305). Your call.</t>
+          <t>Model 25.1% (fair +298). Your call.</t>
         </is>
       </c>
       <c r="O36" s="15" t="n"/>
@@ -21114,13 +21376,13 @@
         </is>
       </c>
       <c r="F37" s="13" t="n">
-        <v>0.5527730769230769</v>
+        <v>0.55275</v>
       </c>
       <c r="G37" s="14" t="n">
         <v>-124</v>
       </c>
       <c r="H37" s="15" t="n">
-        <v>-108</v>
+        <v>100</v>
       </c>
       <c r="I37" s="13">
         <f>IF($H$37="","",IF($H$37&lt;0,-$H$37/(-$H$37+100),100/($H$37+100)))</f>
@@ -21186,7 +21448,7 @@
         <v>124</v>
       </c>
       <c r="H38" s="15" t="n">
-        <v>-108</v>
+        <v>100</v>
       </c>
       <c r="I38" s="13">
         <f>IF($H$38="","",IF($H$38&lt;0,-$H$38/(-$H$38+100),100/($H$38+100)))</f>
@@ -21378,13 +21640,13 @@
         </is>
       </c>
       <c r="F41" s="13" t="n">
-        <v>0.429</v>
+        <v>0.4216826923076923</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="H41" s="15" t="n">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="I41" s="13">
         <f>IF($H$41="","",IF($H$41&lt;0,-$H$41/(-$H$41+100),100/($H$41+100)))</f>
@@ -21408,7 +21670,7 @@
       </c>
       <c r="N41" s="19" t="inlineStr">
         <is>
-          <t>Model 42.9% (fair +133). Your call.</t>
+          <t>Model 42.2% (fair +137). Your call.</t>
         </is>
       </c>
       <c r="O41" s="15" t="n"/>
@@ -21444,13 +21706,13 @@
         </is>
       </c>
       <c r="F42" s="13" t="n">
-        <v>0.571</v>
+        <v>0.578321568627451</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>-133</v>
+        <v>-137</v>
       </c>
       <c r="H42" s="15" t="n">
-        <v>100</v>
+        <v>-104</v>
       </c>
       <c r="I42" s="13">
         <f>IF($H$42="","",IF($H$42&lt;0,-$H$42/(-$H$42+100),100/($H$42+100)))</f>
@@ -21474,7 +21736,7 @@
       </c>
       <c r="N42" s="19" t="inlineStr">
         <is>
-          <t>Model 57.1% (fair -133). Your call.</t>
+          <t>Model 57.8% (fair -137). Your call.</t>
         </is>
       </c>
       <c r="O42" s="15" t="n"/>
@@ -21638,17 +21900,17 @@
       </c>
       <c r="E45" s="12" t="inlineStr">
         <is>
-          <t>Golden State Valkyries +1</t>
+          <t>Golden State Valkyries +1.5</t>
         </is>
       </c>
       <c r="F45" s="13" t="n">
-        <v>0.5716857142857142</v>
+        <v>0.576435294117647</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>-133</v>
+        <v>-136</v>
       </c>
       <c r="H45" s="15" t="n">
-        <v>-110</v>
+        <v>-104</v>
       </c>
       <c r="I45" s="13">
         <f>IF($H$45="","",IF($H$45&lt;0,-$H$45/(-$H$45+100),100/($H$45+100)))</f>
@@ -21672,7 +21934,7 @@
       </c>
       <c r="N45" s="19" t="inlineStr">
         <is>
-          <t>Model 57.2% (fair -133). Your call.</t>
+          <t>Model 57.6% (fair -136). Your call.</t>
         </is>
       </c>
       <c r="O45" s="15" t="n"/>
@@ -21704,14 +21966,14 @@
       </c>
       <c r="E46" s="20" t="inlineStr">
         <is>
-          <t>New York Liberty -1</t>
+          <t>New York Liberty -1.5</t>
         </is>
       </c>
       <c r="F46" s="13" t="n">
-        <v>0.4283</v>
+        <v>0.42355</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H46" s="15" t="n">
         <v>100</v>
@@ -21738,7 +22000,7 @@
       </c>
       <c r="N46" s="19" t="inlineStr">
         <is>
-          <t>Model 42.8% (fair +133). Your call.</t>
+          <t>Model 42.4% (fair +136). Your call.</t>
         </is>
       </c>
       <c r="O46" s="15" t="n"/>

--- a/data/output/workbook/2026-06-27.xlsx
+++ b/data/output/workbook/2026-06-27.xlsx
@@ -954,7 +954,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-06-27 15:33</t>
+          <t>2026-06-27 17:03</t>
         </is>
       </c>
     </row>
@@ -8240,37 +8240,37 @@
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>Phoenix Mercury @ Toronto Tempo</t>
+          <t>Cincinnati Reds @ Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Over 179.5</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.6043749999999999</v>
+        <v>0.6714396396396396</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-153</v>
+        <v>-204</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>108</v>
+        <v>-122</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 60.4% (fair -153). Your call.</t>
+          <t>Model 67.1% (fair -204). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -8311,7 +8311,7 @@
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>Cincinnati Reds @ Pittsburgh Pirates</t>
+          <t>Washington Nationals @ Baltimore Orioles</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -8321,22 +8321,22 @@
       </c>
       <c r="D8" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.6685819819819819</v>
+        <v>0.5857560975609757</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>-202</v>
+        <v>-141</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>-122</v>
+        <v>105</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 66.9% (fair -202). Your call.</t>
+          <t>Model 58.6% (fair -141). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -8392,17 +8392,17 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Over 165.5</t>
+          <t>Over 166.5</t>
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.6033500000000001</v>
+        <v>0.5774509803921568</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>-152</v>
+        <v>-137</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -8426,7 +8426,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 60.3% (fair -152). Your call.</t>
+          <t>Model 57.7% (fair -137). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -8443,12 +8443,12 @@
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>Washington Nationals @ Baltimore Orioles</t>
+          <t>Houston Astros @ Detroit Tigers</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -8458,17 +8458,17 @@
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>Over 9.5</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.5857560975609757</v>
+        <v>0.5746</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-141</v>
+        <v>-135</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -8492,7 +8492,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 58.6% (fair -141). Your call.</t>
+          <t>Model 57.5% (fair -135). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -8504,37 +8504,37 @@
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>Cincinnati Reds @ Pittsburgh Pirates</t>
+          <t>Kansas City Royals @ Chicago White Sox</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>Over 9</t>
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.559656862745098</v>
+        <v>0.5866682926829269</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>-127</v>
+        <v>-142</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>104</v>
+        <v>-105</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -8558,7 +8558,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 56.0% (fair -127). Your call.</t>
+          <t>Model 58.7% (fair -142). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -8570,37 +8570,37 @@
     <row r="12">
       <c r="A12" s="20" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>Kansas City Royals @ Chicago White Sox</t>
+          <t>Cincinnati Reds @ Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
         <is>
-          <t>Over 9</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.5817512195121951</v>
+        <v>0.5560194174757281</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>-139</v>
+        <v>-125</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>-105</v>
+        <v>106</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -8624,7 +8624,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 58.2% (fair -139). Your call.</t>
+          <t>Model 55.6% (fair -125). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -8651,19 +8651,19 @@
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Golden State Valkyries</t>
+          <t>Golden State Valkyries +1.5</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.578321568627451</v>
+        <v>0.5795450980392156</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>-137</v>
+        <v>-138</v>
       </c>
       <c r="H13" s="15" t="n">
         <v>-104</v>
@@ -8690,7 +8690,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 57.8% (fair -137). Your call.</t>
+          <t>Model 58.0% (fair -138). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -8717,19 +8717,19 @@
       </c>
       <c r="D14" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Golden State Valkyries +1.5</t>
+          <t>Golden State Valkyries</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.576435294117647</v>
+        <v>0.578321568627451</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>-136</v>
+        <v>-137</v>
       </c>
       <c r="H14" s="15" t="n">
         <v>-104</v>
@@ -8756,7 +8756,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 57.6% (fair -136). Your call.</t>
+          <t>Model 57.8% (fair -137). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -8773,7 +8773,7 @@
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks @ Tampa Bay Rays</t>
+          <t>Seattle Mariners @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
@@ -8783,22 +8783,22 @@
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Over 7.5</t>
+          <t>Seattle Mariners</t>
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.5958069767441861</v>
+        <v>0.54375</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>-147</v>
+        <v>-119</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>-115</v>
+        <v>108</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -8822,7 +8822,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 59.6% (fair -147). Your call.</t>
+          <t>Model 54.4% (fair -119). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -8839,32 +8839,32 @@
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>Las Vegas Aces @ Chicago Sky</t>
+          <t>Arizona Diamondbacks @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>Chicago Sky +7.5</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.5767615384615384</v>
+        <v>0.5958069767441861</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>-136</v>
+        <v>-147</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>-108</v>
+        <v>-115</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -8888,7 +8888,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 57.7% (fair -136). Your call.</t>
+          <t>Model 59.6% (fair -147). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -8905,12 +8905,12 @@
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Washington Nationals @ Baltimore Orioles</t>
+          <t>Las Vegas Aces @ Chicago Sky</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
@@ -8920,17 +8920,17 @@
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Baltimore Orioles -1.5</t>
+          <t>Chicago Sky +7.5</t>
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.5273809523809523</v>
+        <v>0.5767615384615384</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>-112</v>
+        <v>-136</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>110</v>
+        <v>-108</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 52.7% (fair -112). Your call.</t>
+          <t>Model 57.7% (fair -136). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -8981,22 +8981,22 @@
       </c>
       <c r="D18" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
         <is>
-          <t>Baltimore Orioles</t>
+          <t>Baltimore Orioles -1.5</t>
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.6854057034220533</v>
+        <v>0.5273809523809523</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>-218</v>
+        <v>-112</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>-163</v>
+        <v>110</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -9020,7 +9020,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 68.5% (fair -218). Your call.</t>
+          <t>Model 52.7% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -9037,32 +9037,32 @@
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Las Vegas Aces @ Chicago Sky</t>
+          <t>Washington Nationals @ Baltimore Orioles</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Over 178.5</t>
+          <t>Baltimore Orioles</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.55275</v>
+        <v>0.6854057034220533</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>-124</v>
+        <v>-218</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>100</v>
+        <v>-163</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -9086,7 +9086,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 55.3% (fair -124). Your call.</t>
+          <t>Model 68.5% (fair -218). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -9103,12 +9103,12 @@
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>New York Liberty @ Golden State Valkyries</t>
+          <t>Las Vegas Aces @ Chicago Sky</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -9118,17 +9118,17 @@
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Over 163.5</t>
+          <t>Over 178.5</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.5769238095238095</v>
+        <v>0.55275</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>-136</v>
+        <v>-124</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>-110</v>
+        <v>100</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -9152,7 +9152,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 57.7% (fair -136). Your call.</t>
+          <t>Model 55.3% (fair -124). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -9188,13 +9188,13 @@
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.5621853658536585</v>
+        <v>0.55175</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>-128</v>
+        <v>-123</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>-105</v>
+        <v>100</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -9218,7 +9218,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 56.2% (fair -128). Your call.</t>
+          <t>Model 55.2% (fair -123). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -9235,32 +9235,32 @@
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>Seattle Mariners @ Cleveland Guardians</t>
+          <t>New York Liberty @ Golden State Valkyries</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>Seattle Mariners</t>
+          <t>Over 163.5</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.54865</v>
+        <v>0.5769238095238095</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-122</v>
+        <v>-136</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>100</v>
+        <v>-110</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -9284,7 +9284,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 54.9% (fair -122). Your call.</t>
+          <t>Model 57.7% (fair -136). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -9320,10 +9320,10 @@
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.5612634146341464</v>
+        <v>0.5636707317073171</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>-128</v>
+        <v>-129</v>
       </c>
       <c r="H23" s="15" t="n">
         <v>-105</v>
@@ -9350,7 +9350,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 56.1% (fair -128). Your call.</t>
+          <t>Model 56.4% (fair -129). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -9386,7 +9386,7 @@
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.5517098039215687</v>
+        <v>0.5510470588235293</v>
       </c>
       <c r="G24" s="14" t="n">
         <v>-123</v>
@@ -9416,7 +9416,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 55.2% (fair -123). Your call.</t>
+          <t>Model 55.1% (fair -123). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -9560,37 +9560,37 @@
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>Seattle Mariners @ Cleveland Guardians</t>
+          <t>New York Yankees @ Boston Red Sox</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>23:20</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>Seattle Mariners</t>
+          <t>Under 9</t>
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.6186806722689074</v>
+        <v>0.5172596153846154</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>-162</v>
+        <v>-107</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>-138</v>
+        <v>108</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -9614,7 +9614,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 61.9% (fair -162). Your call.</t>
+          <t>Model 51.7% (fair -107). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -9631,32 +9631,32 @@
       </c>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>Atlanta Braves @ San Francisco Giants</t>
+          <t>Colorado Rockies @ Minnesota Twins</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
         <is>
-          <t>San Francisco Giants +1.5</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.6019565217391304</v>
+        <v>0.53585</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>-151</v>
+        <v>-115</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>-130</v>
+        <v>100</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -9680,7 +9680,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 60.2% (fair -151). Your call.</t>
+          <t>Model 53.6% (fair -115). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -9692,17 +9692,17 @@
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>Kansas City Royals @ Chicago White Sox</t>
+          <t>Chicago Cubs @ Milwaukee Brewers</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
@@ -9712,17 +9712,17 @@
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox</t>
+          <t>Milwaukee Brewers</t>
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.5935991189427313</v>
+        <v>0.6324196721311476</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>-146</v>
+        <v>-172</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>-127</v>
+        <v>-144</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 59.4% (fair -146). Your call.</t>
+          <t>Model 63.2% (fair -172). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -9923,10 +9923,10 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.4448878923766816</v>
+        <v>0.4398206278026906</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H5" s="15" t="n">
         <v>123</v>
@@ -9953,7 +9953,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 44.5% (fair +125). Your call.</t>
+          <t>Model 44.0% (fair +127). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -9989,10 +9989,10 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.5551074889867842</v>
+        <v>0.560198678414097</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>-125</v>
+        <v>-127</v>
       </c>
       <c r="H6" s="15" t="n">
         <v>-127</v>
@@ -10019,7 +10019,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 55.5% (fair -125). Your call.</t>
+          <t>Model 56.0% (fair -127). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -10055,10 +10055,10 @@
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.5043</v>
+        <v>0.5093</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-102</v>
+        <v>-104</v>
       </c>
       <c r="H7" s="15" t="n">
         <v>125</v>
@@ -10085,7 +10085,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 50.4% (fair -102). Your call.</t>
+          <t>Model 50.9% (fair -104). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -10121,10 +10121,10 @@
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.4957</v>
+        <v>0.4907</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H8" s="15" t="n">
         <v>100</v>
@@ -10151,7 +10151,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 49.6% (fair +102). Your call.</t>
+          <t>Model 49.1% (fair +104). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -10187,10 +10187,10 @@
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.3795769230769231</v>
+        <v>0.3830384615384615</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="H9" s="15" t="n">
         <v>160</v>
@@ -10217,7 +10217,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 38.0% (fair +163). Your call.</t>
+          <t>Model 38.3% (fair +161). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -10253,10 +10253,10 @@
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.6204536121673004</v>
+        <v>0.6169828897338403</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-163</v>
+        <v>-161</v>
       </c>
       <c r="H10" s="15" t="n">
         <v>-163</v>
@@ -10283,7 +10283,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 62.0% (fair -163). Your call.</t>
+          <t>Model 61.7% (fair -161). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -10319,10 +10319,10 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.5328980392156862</v>
+        <v>0.5287686274509803</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>-114</v>
+        <v>-112</v>
       </c>
       <c r="H11" s="15" t="n">
         <v>-104</v>
@@ -10349,7 +10349,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 53.3% (fair -114). Your call.</t>
+          <t>Model 52.9% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -10385,10 +10385,10 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.4671078431372549</v>
+        <v>0.4712254901960785</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H12" s="15" t="n">
         <v>104</v>
@@ -10415,7 +10415,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 46.7% (fair +114). Your call.</t>
+          <t>Model 47.1% (fair +112). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -10451,10 +10451,10 @@
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.5877</v>
+        <v>0.5897</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>-143</v>
+        <v>-144</v>
       </c>
       <c r="H13" s="15" t="n">
         <v>117</v>
@@ -10481,7 +10481,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 58.8% (fair -143). Your call.</t>
+          <t>Model 59.0% (fair -144). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -10517,10 +10517,10 @@
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.4123</v>
+        <v>0.4103</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H14" s="15" t="n">
         <v>111</v>
@@ -10547,7 +10547,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 41.2% (fair +143). Your call.</t>
+          <t>Model 41.0% (fair +144). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -10583,10 +10583,10 @@
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.2686</v>
+        <v>0.2759</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="H15" s="15" t="n">
         <v>172</v>
@@ -10613,7 +10613,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 26.9% (fair +272). Your call.</t>
+          <t>Model 27.6% (fair +262). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -10649,10 +10649,10 @@
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.7314000000000001</v>
+        <v>0.7241</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>-272</v>
+        <v>-262</v>
       </c>
       <c r="H16" s="15" t="n">
         <v>156</v>
@@ -10679,7 +10679,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 73.1% (fair -272). Your call.</t>
+          <t>Model 72.4% (fair -262). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -11051,7 +11051,7 @@
         <v>-139</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>170</v>
+        <v>126</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -11111,13 +11111,13 @@
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.44035</v>
+        <v>0.4439882352941176</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>100</v>
+        <v>-104</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -11141,7 +11141,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 44.0% (fair +127). Your call.</t>
+          <t>Model 44.4% (fair +125). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -11177,13 +11177,13 @@
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.559656862745098</v>
+        <v>0.5560194174757281</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>-127</v>
+        <v>-125</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -11207,7 +11207,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 56.0% (fair -127). Your call.</t>
+          <t>Model 55.6% (fair -125). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -11315,7 +11315,7 @@
         <v>189</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -11375,13 +11375,13 @@
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.4883870967741936</v>
+        <v>0.4857272727272727</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -11405,7 +11405,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 48.8% (fair +105). Your call.</t>
+          <t>Model 48.6% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -11441,13 +11441,13 @@
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.5116363636363636</v>
+        <v>0.5142684684684684</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>-105</v>
+        <v>-106</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>-120</v>
+        <v>-122</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -11471,7 +11471,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 51.2% (fair -105). Your call.</t>
+          <t>Model 51.4% (fair -106). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -11513,7 +11513,7 @@
         <v>217</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -11579,7 +11579,7 @@
         <v>-217</v>
       </c>
       <c r="H30" s="15" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I30" s="13">
         <f>IF($H$30="","",IF($H$30&lt;0,-$H$30/(-$H$30+100),100/($H$30+100)))</f>
@@ -11711,7 +11711,7 @@
         <v>-240</v>
       </c>
       <c r="H32" s="15" t="n">
-        <v>-124</v>
+        <v>-129</v>
       </c>
       <c r="I32" s="13">
         <f>IF($H$32="","",IF($H$32&lt;0,-$H$32/(-$H$32+100),100/($H$32+100)))</f>
@@ -11777,7 +11777,7 @@
         <v>186</v>
       </c>
       <c r="H33" s="15" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I33" s="13">
         <f>IF($H$33="","",IF($H$33&lt;0,-$H$33/(-$H$33+100),100/($H$33+100)))</f>
@@ -12107,7 +12107,7 @@
         <v>-115</v>
       </c>
       <c r="H38" s="15" t="n">
-        <v>-126</v>
+        <v>-130</v>
       </c>
       <c r="I38" s="13">
         <f>IF($H$38="","",IF($H$38&lt;0,-$H$38/(-$H$38+100),100/($H$38+100)))</f>
@@ -12299,10 +12299,10 @@
         </is>
       </c>
       <c r="F41" s="13" t="n">
-        <v>0.4975490196078431</v>
+        <v>0.5026</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>101</v>
+        <v>-101</v>
       </c>
       <c r="H41" s="15" t="n">
         <v>104</v>
@@ -12329,7 +12329,7 @@
       </c>
       <c r="N41" s="19" t="inlineStr">
         <is>
-          <t>Model 49.8% (fair +101). Your call.</t>
+          <t>Model 50.3% (fair -101). Your call.</t>
         </is>
       </c>
       <c r="O41" s="15" t="n"/>
@@ -12365,13 +12365,13 @@
         </is>
       </c>
       <c r="F42" s="13" t="n">
-        <v>0.5024257425742574</v>
+        <v>0.4974</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>-101</v>
+        <v>101</v>
       </c>
       <c r="H42" s="15" t="n">
-        <v>-102</v>
+        <v>116</v>
       </c>
       <c r="I42" s="13">
         <f>IF($H$42="","",IF($H$42&lt;0,-$H$42/(-$H$42+100),100/($H$42+100)))</f>
@@ -12395,7 +12395,7 @@
       </c>
       <c r="N42" s="19" t="inlineStr">
         <is>
-          <t>Model 50.2% (fair -101). Your call.</t>
+          <t>Model 49.7% (fair +101). Your call.</t>
         </is>
       </c>
       <c r="O42" s="15" t="n"/>
@@ -12563,13 +12563,13 @@
         </is>
       </c>
       <c r="F45" s="13" t="n">
-        <v>0.4483251231527093</v>
+        <v>0.4489108910891089</v>
       </c>
       <c r="G45" s="14" t="n">
         <v>123</v>
       </c>
       <c r="H45" s="15" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I45" s="13">
         <f>IF($H$45="","",IF($H$45&lt;0,-$H$45/(-$H$45+100),100/($H$45+100)))</f>
@@ -12593,7 +12593,7 @@
       </c>
       <c r="N45" s="19" t="inlineStr">
         <is>
-          <t>Model 44.8% (fair +123). Your call.</t>
+          <t>Model 44.9% (fair +123). Your call.</t>
         </is>
       </c>
       <c r="O45" s="15" t="n"/>
@@ -12629,7 +12629,7 @@
         </is>
       </c>
       <c r="F46" s="13" t="n">
-        <v>0.5517098039215687</v>
+        <v>0.5510470588235293</v>
       </c>
       <c r="G46" s="14" t="n">
         <v>-123</v>
@@ -12659,7 +12659,7 @@
       </c>
       <c r="N46" s="19" t="inlineStr">
         <is>
-          <t>Model 55.2% (fair -123). Your call.</t>
+          <t>Model 55.1% (fair -123). Your call.</t>
         </is>
       </c>
       <c r="O46" s="15" t="n"/>
@@ -12959,10 +12959,10 @@
         </is>
       </c>
       <c r="F51" s="13" t="n">
-        <v>0.6186806722689074</v>
+        <v>0.6197243697478991</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>-162</v>
+        <v>-163</v>
       </c>
       <c r="H51" s="15" t="n">
         <v>-138</v>
@@ -12989,7 +12989,7 @@
       </c>
       <c r="N51" s="19" t="inlineStr">
         <is>
-          <t>Model 61.9% (fair -162). Your call.</t>
+          <t>Model 62.0% (fair -163). Your call.</t>
         </is>
       </c>
       <c r="O51" s="15" t="n"/>
@@ -13025,13 +13025,13 @@
         </is>
       </c>
       <c r="F52" s="13" t="n">
-        <v>0.3813304721030042</v>
+        <v>0.3802978723404255</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H52" s="15" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="I52" s="13">
         <f>IF($H$52="","",IF($H$52&lt;0,-$H$52/(-$H$52+100),100/($H$52+100)))</f>
@@ -13055,7 +13055,7 @@
       </c>
       <c r="N52" s="19" t="inlineStr">
         <is>
-          <t>Model 38.1% (fair +162). Your call.</t>
+          <t>Model 38.0% (fair +163). Your call.</t>
         </is>
       </c>
       <c r="O52" s="15" t="n"/>
@@ -13097,7 +13097,7 @@
         <v>-121</v>
       </c>
       <c r="H53" s="15" t="n">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="I53" s="13">
         <f>IF($H$53="","",IF($H$53&lt;0,-$H$53/(-$H$53+100),100/($H$53+100)))</f>
@@ -13163,7 +13163,7 @@
         <v>121</v>
       </c>
       <c r="H54" s="15" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="I54" s="13">
         <f>IF($H$54="","",IF($H$54&lt;0,-$H$54/(-$H$54+100),100/($H$54+100)))</f>
@@ -13351,10 +13351,10 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>0.3656</v>
+        <v>0.3676</v>
       </c>
       <c r="G57" s="14" t="n">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H57" s="15" t="n">
         <v>150</v>
@@ -13381,7 +13381,7 @@
       </c>
       <c r="N57" s="19" t="inlineStr">
         <is>
-          <t>Model 36.6% (fair +174). Your call.</t>
+          <t>Model 36.8% (fair +172). Your call.</t>
         </is>
       </c>
       <c r="O57" s="15" t="n"/>
@@ -13417,13 +13417,13 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>0.6343800000000001</v>
+        <v>0.6324196721311476</v>
       </c>
       <c r="G58" s="14" t="n">
-        <v>-174</v>
+        <v>-172</v>
       </c>
       <c r="H58" s="15" t="n">
-        <v>-150</v>
+        <v>-144</v>
       </c>
       <c r="I58" s="13">
         <f>IF($H$58="","",IF($H$58&lt;0,-$H$58/(-$H$58+100),100/($H$58+100)))</f>
@@ -13447,7 +13447,7 @@
       </c>
       <c r="N58" s="19" t="inlineStr">
         <is>
-          <t>Model 63.4% (fair -174). Your call.</t>
+          <t>Model 63.2% (fair -172). Your call.</t>
         </is>
       </c>
       <c r="O58" s="15" t="n"/>
@@ -13555,7 +13555,7 @@
         <v>167</v>
       </c>
       <c r="H60" s="15" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I60" s="13">
         <f>IF($H$60="","",IF($H$60&lt;0,-$H$60/(-$H$60+100),100/($H$60+100)))</f>
@@ -13621,7 +13621,7 @@
         <v>106</v>
       </c>
       <c r="H61" s="15" t="n">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="I61" s="13">
         <f>IF($H$61="","",IF($H$61&lt;0,-$H$61/(-$H$61+100),100/($H$61+100)))</f>
@@ -13687,7 +13687,7 @@
         <v>-106</v>
       </c>
       <c r="H62" s="15" t="n">
-        <v>103</v>
+        <v>-104</v>
       </c>
       <c r="I62" s="13">
         <f>IF($H$62="","",IF($H$62&lt;0,-$H$62/(-$H$62+100),100/($H$62+100)))</f>
@@ -13875,10 +13875,10 @@
         </is>
       </c>
       <c r="F65" s="13" t="n">
-        <v>0.6417</v>
+        <v>0.6282</v>
       </c>
       <c r="G65" s="14" t="n">
-        <v>-179</v>
+        <v>-169</v>
       </c>
       <c r="H65" s="15" t="n"/>
       <c r="I65" s="13">
@@ -13903,7 +13903,7 @@
       </c>
       <c r="N65" s="19" t="inlineStr">
         <is>
-          <t>Model 64.2% (fair -179). Your call.</t>
+          <t>Model 62.8% (fair -169). Your call.</t>
         </is>
       </c>
       <c r="O65" s="15" t="n"/>
@@ -13939,10 +13939,10 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>0.3584</v>
+        <v>0.3718</v>
       </c>
       <c r="G66" s="14" t="n">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="H66" s="15" t="n"/>
       <c r="I66" s="13">
@@ -13967,7 +13967,7 @@
       </c>
       <c r="N66" s="19" t="inlineStr">
         <is>
-          <t>Model 35.8% (fair +179). Your call.</t>
+          <t>Model 37.2% (fair +169). Your call.</t>
         </is>
       </c>
       <c r="O66" s="15" t="n"/>
@@ -14655,13 +14655,13 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>0.3313824884792627</v>
+        <v>0.3285585585585586</v>
       </c>
       <c r="G77" s="14" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="H77" s="15" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="I77" s="13">
         <f>IF($H$77="","",IF($H$77&lt;0,-$H$77/(-$H$77+100),100/($H$77+100)))</f>
@@ -14685,7 +14685,7 @@
       </c>
       <c r="N77" s="19" t="inlineStr">
         <is>
-          <t>Model 33.1% (fair +202). Your call.</t>
+          <t>Model 32.9% (fair +204). Your call.</t>
         </is>
       </c>
       <c r="O77" s="15" t="n"/>
@@ -14721,10 +14721,10 @@
         </is>
       </c>
       <c r="F78" s="13" t="n">
-        <v>0.6685819819819819</v>
+        <v>0.6714396396396396</v>
       </c>
       <c r="G78" s="14" t="n">
-        <v>-202</v>
+        <v>-204</v>
       </c>
       <c r="H78" s="15" t="n">
         <v>-122</v>
@@ -14751,7 +14751,7 @@
       </c>
       <c r="N78" s="19" t="inlineStr">
         <is>
-          <t>Model 66.9% (fair -202). Your call.</t>
+          <t>Model 67.1% (fair -204). Your call.</t>
         </is>
       </c>
       <c r="O78" s="15" t="n"/>
@@ -14793,7 +14793,7 @@
         <v>-139</v>
       </c>
       <c r="H79" s="15" t="n">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="I79" s="13">
         <f>IF($H$79="","",IF($H$79&lt;0,-$H$79/(-$H$79+100),100/($H$79+100)))</f>
@@ -15183,13 +15183,13 @@
         </is>
       </c>
       <c r="F85" s="13" t="n">
-        <v>0.5621853658536585</v>
+        <v>0.55175</v>
       </c>
       <c r="G85" s="14" t="n">
-        <v>-128</v>
+        <v>-123</v>
       </c>
       <c r="H85" s="15" t="n">
-        <v>-105</v>
+        <v>100</v>
       </c>
       <c r="I85" s="13">
         <f>IF($H$85="","",IF($H$85&lt;0,-$H$85/(-$H$85+100),100/($H$85+100)))</f>
@@ -15213,7 +15213,7 @@
       </c>
       <c r="N85" s="19" t="inlineStr">
         <is>
-          <t>Model 56.2% (fair -128). Your call.</t>
+          <t>Model 55.2% (fair -123). Your call.</t>
         </is>
       </c>
       <c r="O85" s="15" t="n"/>
@@ -15249,13 +15249,13 @@
         </is>
       </c>
       <c r="F86" s="13" t="n">
-        <v>0.43785</v>
+        <v>0.4482333333333333</v>
       </c>
       <c r="G86" s="14" t="n">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="H86" s="15" t="n">
-        <v>100</v>
+        <v>-113</v>
       </c>
       <c r="I86" s="13">
         <f>IF($H$86="","",IF($H$86&lt;0,-$H$86/(-$H$86+100),100/($H$86+100)))</f>
@@ -15279,7 +15279,7 @@
       </c>
       <c r="N86" s="19" t="inlineStr">
         <is>
-          <t>Model 43.8% (fair +128). Your call.</t>
+          <t>Model 44.8% (fair +123). Your call.</t>
         </is>
       </c>
       <c r="O86" s="15" t="n"/>
@@ -15447,10 +15447,10 @@
         </is>
       </c>
       <c r="F89" s="13" t="n">
-        <v>0.5359756756756757</v>
+        <v>0.5276774774774774</v>
       </c>
       <c r="G89" s="14" t="n">
-        <v>-116</v>
+        <v>-112</v>
       </c>
       <c r="H89" s="15" t="n">
         <v>-122</v>
@@ -15477,7 +15477,7 @@
       </c>
       <c r="N89" s="19" t="inlineStr">
         <is>
-          <t>Model 53.6% (fair -116). Your call.</t>
+          <t>Model 52.8% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O89" s="15" t="n"/>
@@ -15513,10 +15513,10 @@
         </is>
       </c>
       <c r="F90" s="13" t="n">
-        <v>0.4640552995391705</v>
+        <v>0.4723502304147465</v>
       </c>
       <c r="G90" s="14" t="n">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="H90" s="15" t="n">
         <v>117</v>
@@ -15543,7 +15543,7 @@
       </c>
       <c r="N90" s="19" t="inlineStr">
         <is>
-          <t>Model 46.4% (fair +115). Your call.</t>
+          <t>Model 47.2% (fair +112). Your call.</t>
         </is>
       </c>
       <c r="O90" s="15" t="n"/>
@@ -15579,10 +15579,10 @@
         </is>
       </c>
       <c r="F91" s="13" t="n">
-        <v>0.6435</v>
+        <v>0.5746</v>
       </c>
       <c r="G91" s="14" t="n">
-        <v>-181</v>
+        <v>-135</v>
       </c>
       <c r="H91" s="15" t="n">
         <v>100</v>
@@ -15609,7 +15609,7 @@
       </c>
       <c r="N91" s="19" t="inlineStr">
         <is>
-          <t>Model 64.3% (fair -181). Your call.</t>
+          <t>Model 57.5% (fair -135). Your call.</t>
         </is>
       </c>
       <c r="O91" s="15" t="n"/>
@@ -15645,13 +15645,13 @@
         </is>
       </c>
       <c r="F92" s="13" t="n">
-        <v>0.3565</v>
+        <v>0.4253658536585366</v>
       </c>
       <c r="G92" s="14" t="n">
-        <v>181</v>
+        <v>135</v>
       </c>
       <c r="H92" s="15" t="n">
-        <v>245</v>
+        <v>105</v>
       </c>
       <c r="I92" s="13">
         <f>IF($H$92="","",IF($H$92&lt;0,-$H$92/(-$H$92+100),100/($H$92+100)))</f>
@@ -15675,7 +15675,7 @@
       </c>
       <c r="N92" s="19" t="inlineStr">
         <is>
-          <t>Model 35.7% (fair +181). Your call.</t>
+          <t>Model 42.5% (fair +135). Your call.</t>
         </is>
       </c>
       <c r="O92" s="15" t="n"/>
@@ -15711,10 +15711,10 @@
         </is>
       </c>
       <c r="F93" s="13" t="n">
-        <v>0.6226745098039216</v>
+        <v>0.6312450980392157</v>
       </c>
       <c r="G93" s="14" t="n">
-        <v>-165</v>
+        <v>-171</v>
       </c>
       <c r="H93" s="15" t="n">
         <v>-155</v>
@@ -15741,7 +15741,7 @@
       </c>
       <c r="N93" s="19" t="inlineStr">
         <is>
-          <t>Model 62.3% (fair -165). Your call.</t>
+          <t>Model 63.1% (fair -171). Your call.</t>
         </is>
       </c>
       <c r="O93" s="15" t="n"/>
@@ -15777,10 +15777,10 @@
         </is>
       </c>
       <c r="F94" s="13" t="n">
-        <v>0.3773333333333334</v>
+        <v>0.3687916666666667</v>
       </c>
       <c r="G94" s="14" t="n">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="H94" s="15" t="n">
         <v>140</v>
@@ -15807,7 +15807,7 @@
       </c>
       <c r="N94" s="19" t="inlineStr">
         <is>
-          <t>Model 37.7% (fair +165). Your call.</t>
+          <t>Model 36.9% (fair +171). Your call.</t>
         </is>
       </c>
       <c r="O94" s="15" t="n"/>
@@ -15843,13 +15843,13 @@
         </is>
       </c>
       <c r="F95" s="13" t="n">
-        <v>0.54865</v>
+        <v>0.54375</v>
       </c>
       <c r="G95" s="14" t="n">
-        <v>-122</v>
+        <v>-119</v>
       </c>
       <c r="H95" s="15" t="n">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="I95" s="13">
         <f>IF($H$95="","",IF($H$95&lt;0,-$H$95/(-$H$95+100),100/($H$95+100)))</f>
@@ -15873,7 +15873,7 @@
       </c>
       <c r="N95" s="19" t="inlineStr">
         <is>
-          <t>Model 54.9% (fair -122). Your call.</t>
+          <t>Model 54.4% (fair -119). Your call.</t>
         </is>
       </c>
       <c r="O95" s="15" t="n"/>
@@ -15909,10 +15909,10 @@
         </is>
       </c>
       <c r="F96" s="13" t="n">
-        <v>0.45135</v>
+        <v>0.45625</v>
       </c>
       <c r="G96" s="14" t="n">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="H96" s="15" t="n">
         <v>100</v>
@@ -15939,7 +15939,7 @@
       </c>
       <c r="N96" s="19" t="inlineStr">
         <is>
-          <t>Model 45.1% (fair +122). Your call.</t>
+          <t>Model 45.6% (fair +119). Your call.</t>
         </is>
       </c>
       <c r="O96" s="15" t="n"/>
@@ -15975,13 +15975,13 @@
         </is>
       </c>
       <c r="F97" s="13" t="n">
-        <v>0.49165</v>
+        <v>0.4867788461538461</v>
       </c>
       <c r="G97" s="14" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="H97" s="15" t="n">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="I97" s="13">
         <f>IF($H$97="","",IF($H$97&lt;0,-$H$97/(-$H$97+100),100/($H$97+100)))</f>
@@ -16005,7 +16005,7 @@
       </c>
       <c r="N97" s="19" t="inlineStr">
         <is>
-          <t>Model 49.2% (fair +103). Your call.</t>
+          <t>Model 48.7% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O97" s="15" t="n"/>
@@ -16041,10 +16041,10 @@
         </is>
       </c>
       <c r="F98" s="13" t="n">
-        <v>0.50835</v>
+        <v>0.51325</v>
       </c>
       <c r="G98" s="14" t="n">
-        <v>-103</v>
+        <v>-105</v>
       </c>
       <c r="H98" s="15" t="n">
         <v>100</v>
@@ -16071,7 +16071,7 @@
       </c>
       <c r="N98" s="19" t="inlineStr">
         <is>
-          <t>Model 50.8% (fair -103). Your call.</t>
+          <t>Model 51.3% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O98" s="15" t="n"/>
@@ -16899,10 +16899,10 @@
         </is>
       </c>
       <c r="F111" s="13" t="n">
-        <v>0.52885</v>
+        <v>0.53585</v>
       </c>
       <c r="G111" s="14" t="n">
-        <v>-112</v>
+        <v>-115</v>
       </c>
       <c r="H111" s="15" t="n">
         <v>100</v>
@@ -16929,7 +16929,7 @@
       </c>
       <c r="N111" s="19" t="inlineStr">
         <is>
-          <t>Model 52.9% (fair -112). Your call.</t>
+          <t>Model 53.6% (fair -115). Your call.</t>
         </is>
       </c>
       <c r="O111" s="15" t="n"/>
@@ -16965,13 +16965,13 @@
         </is>
       </c>
       <c r="F112" s="13" t="n">
-        <v>0.4711271889400921</v>
+        <v>0.4641764705882352</v>
       </c>
       <c r="G112" s="14" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="H112" s="15" t="n">
-        <v>-117</v>
+        <v>-104</v>
       </c>
       <c r="I112" s="13">
         <f>IF($H$112="","",IF($H$112&lt;0,-$H$112/(-$H$112+100),100/($H$112+100)))</f>
@@ -16995,7 +16995,7 @@
       </c>
       <c r="N112" s="19" t="inlineStr">
         <is>
-          <t>Model 47.1% (fair +112). Your call.</t>
+          <t>Model 46.4% (fair +115). Your call.</t>
         </is>
       </c>
       <c r="O112" s="15" t="n"/>
@@ -17295,10 +17295,10 @@
         </is>
       </c>
       <c r="F117" s="13" t="n">
-        <v>0.5817512195121951</v>
+        <v>0.5866682926829269</v>
       </c>
       <c r="G117" s="14" t="n">
-        <v>-139</v>
+        <v>-142</v>
       </c>
       <c r="H117" s="15" t="n">
         <v>-105</v>
@@ -17325,7 +17325,7 @@
       </c>
       <c r="N117" s="19" t="inlineStr">
         <is>
-          <t>Model 58.2% (fair -139). Your call.</t>
+          <t>Model 58.7% (fair -142). Your call.</t>
         </is>
       </c>
       <c r="O117" s="15" t="n"/>
@@ -17361,13 +17361,13 @@
         </is>
       </c>
       <c r="F118" s="13" t="n">
-        <v>0.41825</v>
+        <v>0.4133173076923077</v>
       </c>
       <c r="G118" s="14" t="n">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="H118" s="15" t="n">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="I118" s="13">
         <f>IF($H$118="","",IF($H$118&lt;0,-$H$118/(-$H$118+100),100/($H$118+100)))</f>
@@ -17391,7 +17391,7 @@
       </c>
       <c r="N118" s="19" t="inlineStr">
         <is>
-          <t>Model 41.8% (fair +139). Your call.</t>
+          <t>Model 41.3% (fair +142). Your call.</t>
         </is>
       </c>
       <c r="O118" s="15" t="n"/>
@@ -18075,10 +18075,10 @@
         </is>
       </c>
       <c r="F129" s="13" t="n">
-        <v>0.5612634146341464</v>
+        <v>0.5636707317073171</v>
       </c>
       <c r="G129" s="14" t="n">
-        <v>-128</v>
+        <v>-129</v>
       </c>
       <c r="H129" s="15" t="n">
         <v>-105</v>
@@ -18105,7 +18105,7 @@
       </c>
       <c r="N129" s="19" t="inlineStr">
         <is>
-          <t>Model 56.1% (fair -128). Your call.</t>
+          <t>Model 56.4% (fair -129). Your call.</t>
         </is>
       </c>
       <c r="O129" s="15" t="n"/>
@@ -18141,13 +18141,13 @@
         </is>
       </c>
       <c r="F130" s="13" t="n">
-        <v>0.4387254901960784</v>
+        <v>0.4362980769230769</v>
       </c>
       <c r="G130" s="14" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H130" s="15" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="I130" s="13">
         <f>IF($H$130="","",IF($H$130&lt;0,-$H$130/(-$H$130+100),100/($H$130+100)))</f>
@@ -18171,7 +18171,7 @@
       </c>
       <c r="N130" s="19" t="inlineStr">
         <is>
-          <t>Model 43.9% (fair +128). Your call.</t>
+          <t>Model 43.6% (fair +129). Your call.</t>
         </is>
       </c>
       <c r="O130" s="15" t="n"/>
@@ -18473,7 +18473,7 @@
         <v>113</v>
       </c>
       <c r="H135" s="15" t="n">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I135" s="13">
         <f>IF($H$135="","",IF($H$135&lt;0,-$H$135/(-$H$135+100),100/($H$135+100)))</f>
@@ -18731,10 +18731,10 @@
         </is>
       </c>
       <c r="F139" s="13" t="n">
-        <v>0.5516</v>
+        <v>0.5442</v>
       </c>
       <c r="G139" s="14" t="n">
-        <v>-123</v>
+        <v>-119</v>
       </c>
       <c r="H139" s="15" t="n"/>
       <c r="I139" s="13">
@@ -18759,7 +18759,7 @@
       </c>
       <c r="N139" s="19" t="inlineStr">
         <is>
-          <t>Model 55.2% (fair -123). Your call.</t>
+          <t>Model 54.4% (fair -119). Your call.</t>
         </is>
       </c>
       <c r="O139" s="15" t="n"/>
@@ -18795,10 +18795,10 @@
         </is>
       </c>
       <c r="F140" s="13" t="n">
-        <v>0.4484162995594714</v>
+        <v>0.4558013215859031</v>
       </c>
       <c r="G140" s="14" t="n">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="H140" s="15" t="n">
         <v>-127</v>
@@ -18825,7 +18825,7 @@
       </c>
       <c r="N140" s="19" t="inlineStr">
         <is>
-          <t>Model 44.8% (fair +123). Your call.</t>
+          <t>Model 45.6% (fair +119). Your call.</t>
         </is>
       </c>
       <c r="O140" s="15" t="n"/>
@@ -18861,10 +18861,10 @@
         </is>
       </c>
       <c r="F141" s="13" t="n">
-        <v>0.4769048780487805</v>
+        <v>0.4827439024390244</v>
       </c>
       <c r="G141" s="14" t="n">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H141" s="15" t="n">
         <v>-105</v>
@@ -18891,7 +18891,7 @@
       </c>
       <c r="N141" s="19" t="inlineStr">
         <is>
-          <t>Model 47.7% (fair +110). Your call.</t>
+          <t>Model 48.3% (fair +107). Your call.</t>
         </is>
       </c>
       <c r="O141" s="15" t="n"/>
@@ -18927,13 +18927,13 @@
         </is>
       </c>
       <c r="F142" s="13" t="n">
-        <v>0.5231</v>
+        <v>0.5172596153846154</v>
       </c>
       <c r="G142" s="14" t="n">
-        <v>-110</v>
+        <v>-107</v>
       </c>
       <c r="H142" s="15" t="n">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="I142" s="13">
         <f>IF($H$142="","",IF($H$142&lt;0,-$H$142/(-$H$142+100),100/($H$142+100)))</f>
@@ -18957,7 +18957,7 @@
       </c>
       <c r="N142" s="19" t="inlineStr">
         <is>
-          <t>Model 52.3% (fair -110). Your call.</t>
+          <t>Model 51.7% (fair -107). Your call.</t>
         </is>
       </c>
       <c r="O142" s="15" t="n"/>
@@ -18993,10 +18993,10 @@
         </is>
       </c>
       <c r="F143" s="13" t="n">
-        <v>0.2763921568627451</v>
+        <v>0.2867058823529413</v>
       </c>
       <c r="G143" s="14" t="n">
-        <v>262</v>
+        <v>249</v>
       </c>
       <c r="H143" s="15" t="n">
         <v>155</v>
@@ -19023,7 +19023,7 @@
       </c>
       <c r="N143" s="19" t="inlineStr">
         <is>
-          <t>Model 27.6% (fair +262). Your call.</t>
+          <t>Model 28.7% (fair +249). Your call.</t>
         </is>
       </c>
       <c r="O143" s="15" t="n"/>
@@ -19059,10 +19059,10 @@
         </is>
       </c>
       <c r="F144" s="13" t="n">
-        <v>0.7236</v>
+        <v>0.7133</v>
       </c>
       <c r="G144" s="14" t="n">
-        <v>-262</v>
+        <v>-249</v>
       </c>
       <c r="H144" s="15" t="n"/>
       <c r="I144" s="13">
@@ -19087,7 +19087,7 @@
       </c>
       <c r="N144" s="19" t="inlineStr">
         <is>
-          <t>Model 72.4% (fair -262). Your call.</t>
+          <t>Model 71.3% (fair -249). Your call.</t>
         </is>
       </c>
       <c r="O144" s="15" t="n"/>
@@ -19120,7 +19120,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P46"/>
+  <dimension ref="A1:P40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -19245,12 +19245,12 @@
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>Phoenix Mercury @ Toronto Tempo</t>
+          <t>Los Angeles Sparks @ Indiana Fever</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
@@ -19260,17 +19260,17 @@
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>Phoenix Mercury</t>
+          <t>Los Angeles Sparks</t>
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.3492079207920792</v>
+        <v>0.2905507246376811</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>186</v>
+        <v>244</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>203</v>
+        <v>245</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -19294,7 +19294,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 34.9% (fair +186). Your call.</t>
+          <t>Model 29.1% (fair +244). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -19311,12 +19311,12 @@
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>Phoenix Mercury @ Toronto Tempo</t>
+          <t>Los Angeles Sparks @ Indiana Fever</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -19326,17 +19326,17 @@
       </c>
       <c r="E6" s="20" t="inlineStr">
         <is>
-          <t>Toronto Tempo</t>
+          <t>Indiana Fever</t>
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.6508238095238095</v>
+        <v>0.7094504273504273</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>-186</v>
+        <v>-244</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>-194</v>
+        <v>-251</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -19360,7 +19360,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 65.1% (fair -186). Your call.</t>
+          <t>Model 70.9% (fair -244). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -19377,12 +19377,12 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>Phoenix Mercury @ Toronto Tempo</t>
+          <t>Los Angeles Sparks @ Indiana Fever</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
@@ -19396,13 +19396,13 @@
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.6043749999999999</v>
+        <v>0.715</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-153</v>
+        <v>-251</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>108</v>
+        <v>-104</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -19426,7 +19426,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 60.4% (fair -153). Your call.</t>
+          <t>Model 71.5% (fair -251). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -19443,12 +19443,12 @@
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>Phoenix Mercury @ Toronto Tempo</t>
+          <t>Los Angeles Sparks @ Indiana Fever</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -19462,13 +19462,13 @@
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.3956</v>
+        <v>0.285</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>153</v>
+        <v>251</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>108</v>
+        <v>-104</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -19492,7 +19492,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 39.6% (fair +153). Your call.</t>
+          <t>Model 28.5% (fair +251). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -19509,12 +19509,12 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>Phoenix Mercury @ Toronto Tempo</t>
+          <t>Los Angeles Sparks @ Indiana Fever</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
@@ -19524,17 +19524,17 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Toronto Tempo -6.5</t>
+          <t>Indiana Fever -6.5</t>
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.4702</v>
+        <v>0.513</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>113</v>
+        <v>-105</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>113</v>
+        <v>-108</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -19558,7 +19558,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 47.0% (fair +113). Your call.</t>
+          <t>Model 51.3% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -19575,12 +19575,12 @@
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>Phoenix Mercury @ Toronto Tempo</t>
+          <t>Los Angeles Sparks @ Indiana Fever</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -19590,17 +19590,17 @@
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>Phoenix Mercury +6.5</t>
+          <t>Los Angeles Sparks +6.5</t>
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.5298</v>
+        <v>0.4869756097560976</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-113</v>
+        <v>105</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -19624,7 +19624,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 53.0% (fair -113). Your call.</t>
+          <t>Model 48.7% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -19641,12 +19641,12 @@
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Sparks @ Indiana Fever</t>
+          <t>Atlanta Dream @ Seattle Storm</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
@@ -19656,17 +19656,17 @@
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Sparks</t>
+          <t>Atlanta Dream</t>
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.2901159420289854</v>
+        <v>0.7612197530864198</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>245</v>
+        <v>-319</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>245</v>
+        <v>-305</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -19690,7 +19690,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 29.0% (fair +245). Your call.</t>
+          <t>Model 76.1% (fair -319). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -19707,12 +19707,12 @@
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Sparks @ Indiana Fever</t>
+          <t>Atlanta Dream @ Seattle Storm</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -19722,17 +19722,17 @@
       </c>
       <c r="E12" s="20" t="inlineStr">
         <is>
-          <t>Indiana Fever</t>
+          <t>Seattle Storm</t>
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.7099056338028169</v>
+        <v>0.238825</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>-245</v>
+        <v>319</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>-255</v>
+        <v>300</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -19756,7 +19756,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 71.0% (fair -245). Your call.</t>
+          <t>Model 23.9% (fair +319). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -19773,12 +19773,12 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Sparks @ Indiana Fever</t>
+          <t>Atlanta Dream @ Seattle Storm</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
@@ -19792,13 +19792,13 @@
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.715</v>
+        <v>0.2606730769230769</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>-251</v>
+        <v>284</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>-104</v>
+        <v>108</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -19822,7 +19822,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 71.5% (fair -251). Your call.</t>
+          <t>Model 26.1% (fair +284). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -19839,12 +19839,12 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Sparks @ Indiana Fever</t>
+          <t>Atlanta Dream @ Seattle Storm</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -19858,13 +19858,13 @@
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.285</v>
+        <v>0.7393000000000001</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>251</v>
+        <v>-284</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>-104</v>
+        <v>108</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -19888,7 +19888,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 28.5% (fair +251). Your call.</t>
+          <t>Model 73.9% (fair -284). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -19905,12 +19905,12 @@
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Sparks @ Indiana Fever</t>
+          <t>Atlanta Dream @ Seattle Storm</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
@@ -19920,17 +19920,17 @@
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Indiana Fever -6.5</t>
+          <t>Seattle Storm -4.5</t>
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.510709756097561</v>
+        <v>0.1855</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>-104</v>
+        <v>439</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>-105</v>
+        <v>410</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -19954,7 +19954,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 51.1% (fair -104). Your call.</t>
+          <t>Model 18.6% (fair +439). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -19971,12 +19971,12 @@
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Sparks @ Indiana Fever</t>
+          <t>Atlanta Dream @ Seattle Storm</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -19986,17 +19986,17 @@
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Sparks +6.5</t>
+          <t>Atlanta Dream +4.5</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.4893137254901961</v>
+        <v>0.8145</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>104</v>
+        <v>-439</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -20020,7 +20020,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 48.9% (fair +104). Your call.</t>
+          <t>Model 81.5% (fair -439). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -20032,17 +20032,17 @@
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Atlanta Dream @ Seattle Storm</t>
+          <t>Minnesota Lynx @ Dallas Wings</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
@@ -20052,17 +20052,17 @@
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Atlanta Dream</t>
+          <t>Minnesota Lynx</t>
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.7608</v>
+        <v>0.6274734375000001</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>-318</v>
+        <v>-168</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>-300</v>
+        <v>-156</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -20086,7 +20086,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 76.1% (fair -318). Your call.</t>
+          <t>Model 62.7% (fair -168). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -20098,17 +20098,17 @@
     <row r="18">
       <c r="A18" s="20" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>Atlanta Dream @ Seattle Storm</t>
+          <t>Minnesota Lynx @ Dallas Wings</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -20118,17 +20118,17 @@
       </c>
       <c r="E18" s="20" t="inlineStr">
         <is>
-          <t>Seattle Storm</t>
+          <t>Dallas Wings</t>
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.2392</v>
+        <v>0.3725095057034221</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>318</v>
+        <v>168</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>300</v>
+        <v>163</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -20152,7 +20152,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 23.9% (fair +318). Your call.</t>
+          <t>Model 37.3% (fair +168). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -20164,17 +20164,17 @@
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Atlanta Dream @ Seattle Storm</t>
+          <t>Minnesota Lynx @ Dallas Wings</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -20184,17 +20184,17 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Over 179.5</t>
+          <t>Over 177.5</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.2606730769230769</v>
+        <v>0.4101</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>284</v>
+        <v>144</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -20218,7 +20218,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 26.1% (fair +284). Your call.</t>
+          <t>Model 41.0% (fair +144). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -20230,17 +20230,17 @@
     <row r="20">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>Atlanta Dream @ Seattle Storm</t>
+          <t>Minnesota Lynx @ Dallas Wings</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -20250,17 +20250,17 @@
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Under 179.5</t>
+          <t>Under 177.5</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.7393000000000001</v>
+        <v>0.5899</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>-284</v>
+        <v>-144</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -20284,7 +20284,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 73.9% (fair -284). Your call.</t>
+          <t>Model 59.0% (fair -144). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -20296,17 +20296,17 @@
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Atlanta Dream @ Seattle Storm</t>
+          <t>Minnesota Lynx @ Dallas Wings</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -20316,17 +20316,17 @@
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Seattle Storm -4.5</t>
+          <t>Dallas Wings +3.5</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.1855</v>
+        <v>0.5042</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>439</v>
+        <v>-102</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>430</v>
+        <v>113</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -20350,7 +20350,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 18.6% (fair +439). Your call.</t>
+          <t>Model 50.4% (fair -102). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -20362,17 +20362,17 @@
     <row r="22">
       <c r="A22" s="20" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>Atlanta Dream @ Seattle Storm</t>
+          <t>Minnesota Lynx @ Dallas Wings</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -20382,14 +20382,14 @@
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>Atlanta Dream +4.5</t>
+          <t>Minnesota Lynx -3.5</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.8145</v>
+        <v>0.4958</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-439</v>
+        <v>102</v>
       </c>
       <c r="H22" s="15" t="n">
         <v>108</v>
@@ -20416,7 +20416,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 81.5% (fair -439). Your call.</t>
+          <t>Model 49.6% (fair +102). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -20433,12 +20433,12 @@
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Lynx @ Dallas Wings</t>
+          <t>Portland Fire @ Washington Mystics</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
@@ -20448,17 +20448,17 @@
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Lynx</t>
+          <t>Portland Fire</t>
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.6243046875</v>
+        <v>0.3029129129129129</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>-166</v>
+        <v>230</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>-156</v>
+        <v>233</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -20482,7 +20482,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 62.4% (fair -166). Your call.</t>
+          <t>Model 30.3% (fair +230). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -20499,12 +20499,12 @@
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Lynx @ Dallas Wings</t>
+          <t>Portland Fire @ Washington Mystics</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -20514,17 +20514,17 @@
       </c>
       <c r="E24" s="20" t="inlineStr">
         <is>
-          <t>Dallas Wings</t>
+          <t>Washington Mystics</t>
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.375703125</v>
+        <v>0.6970782608695653</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>166</v>
+        <v>-230</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>156</v>
+        <v>-245</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -20548,7 +20548,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 37.6% (fair +166). Your call.</t>
+          <t>Model 69.7% (fair -230). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -20565,12 +20565,12 @@
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Lynx @ Dallas Wings</t>
+          <t>Portland Fire @ Washington Mystics</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
@@ -20580,17 +20580,17 @@
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Over 177.5</t>
+          <t>Over 166.5</t>
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.4101</v>
+        <v>0.5774509803921568</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>144</v>
+        <v>-137</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 41.0% (fair +144). Your call.</t>
+          <t>Model 57.7% (fair -137). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -20631,12 +20631,12 @@
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Lynx @ Dallas Wings</t>
+          <t>Portland Fire @ Washington Mystics</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -20646,17 +20646,17 @@
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
-          <t>Under 177.5</t>
+          <t>Under 166.5</t>
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.5899</v>
+        <v>0.4226</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>-144</v>
+        <v>137</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -20680,7 +20680,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 59.0% (fair -144). Your call.</t>
+          <t>Model 42.3% (fair +137). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -20697,12 +20697,12 @@
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Lynx @ Dallas Wings</t>
+          <t>Portland Fire @ Washington Mystics</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
@@ -20712,17 +20712,17 @@
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>Dallas Wings +3.5</t>
+          <t>Washington Mystics -6.5</t>
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.5042</v>
+        <v>0.47875</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>-102</v>
+        <v>109</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -20746,7 +20746,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 50.4% (fair -102). Your call.</t>
+          <t>Model 47.9% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -20763,12 +20763,12 @@
       </c>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Lynx @ Dallas Wings</t>
+          <t>Portland Fire @ Washington Mystics</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -20778,17 +20778,17 @@
       </c>
       <c r="E28" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Lynx -3.5</t>
+          <t>Portland Fire +6.5</t>
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.4958</v>
+        <v>0.5212376237623763</v>
       </c>
       <c r="G28" s="14" t="n">
+        <v>-109</v>
+      </c>
+      <c r="H28" s="15" t="n">
         <v>102</v>
-      </c>
-      <c r="H28" s="15" t="n">
-        <v>104</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -20812,7 +20812,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 49.6% (fair +102). Your call.</t>
+          <t>Model 52.1% (fair -109). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -20829,12 +20829,12 @@
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>Portland Fire @ Washington Mystics</t>
+          <t>Las Vegas Aces @ Chicago Sky</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
@@ -20844,17 +20844,17 @@
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>Portland Fire</t>
+          <t>Las Vegas Aces</t>
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.3017117117117117</v>
+        <v>0.7520298701298702</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>231</v>
+        <v>-303</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>233</v>
+        <v>-285</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -20878,7 +20878,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 30.2% (fair +231). Your call.</t>
+          <t>Model 75.2% (fair -303). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -20895,12 +20895,12 @@
       </c>
       <c r="B30" s="20" t="inlineStr">
         <is>
-          <t>Portland Fire @ Washington Mystics</t>
+          <t>Las Vegas Aces @ Chicago Sky</t>
         </is>
       </c>
       <c r="C30" s="20" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="D30" s="20" t="inlineStr">
@@ -20910,17 +20910,17 @@
       </c>
       <c r="E30" s="20" t="inlineStr">
         <is>
-          <t>Washington Mystics</t>
+          <t>Chicago Sky</t>
         </is>
       </c>
       <c r="F30" s="13" t="n">
-        <v>0.698269014084507</v>
+        <v>0.247975</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>-231</v>
+        <v>303</v>
       </c>
       <c r="H30" s="15" t="n">
-        <v>-255</v>
+        <v>300</v>
       </c>
       <c r="I30" s="13">
         <f>IF($H$30="","",IF($H$30&lt;0,-$H$30/(-$H$30+100),100/($H$30+100)))</f>
@@ -20944,7 +20944,7 @@
       </c>
       <c r="N30" s="19" t="inlineStr">
         <is>
-          <t>Model 69.8% (fair -231). Your call.</t>
+          <t>Model 24.8% (fair +303). Your call.</t>
         </is>
       </c>
       <c r="O30" s="15" t="n"/>
@@ -20961,12 +20961,12 @@
       </c>
       <c r="B31" s="12" t="inlineStr">
         <is>
-          <t>Portland Fire @ Washington Mystics</t>
+          <t>Las Vegas Aces @ Chicago Sky</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
@@ -20976,14 +20976,14 @@
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>Over 165.5</t>
+          <t>Over 178.5</t>
         </is>
       </c>
       <c r="F31" s="13" t="n">
-        <v>0.6033500000000001</v>
+        <v>0.55275</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>-152</v>
+        <v>-124</v>
       </c>
       <c r="H31" s="15" t="n">
         <v>100</v>
@@ -21010,7 +21010,7 @@
       </c>
       <c r="N31" s="19" t="inlineStr">
         <is>
-          <t>Model 60.3% (fair -152). Your call.</t>
+          <t>Model 55.3% (fair -124). Your call.</t>
         </is>
       </c>
       <c r="O31" s="15" t="n"/>
@@ -21027,12 +21027,12 @@
       </c>
       <c r="B32" s="20" t="inlineStr">
         <is>
-          <t>Portland Fire @ Washington Mystics</t>
+          <t>Las Vegas Aces @ Chicago Sky</t>
         </is>
       </c>
       <c r="C32" s="20" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="D32" s="20" t="inlineStr">
@@ -21042,14 +21042,14 @@
       </c>
       <c r="E32" s="20" t="inlineStr">
         <is>
-          <t>Under 165.5</t>
+          <t>Under 178.5</t>
         </is>
       </c>
       <c r="F32" s="13" t="n">
-        <v>0.3967000000000001</v>
+        <v>0.4472</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>152</v>
+        <v>124</v>
       </c>
       <c r="H32" s="15" t="n">
         <v>100</v>
@@ -21076,7 +21076,7 @@
       </c>
       <c r="N32" s="19" t="inlineStr">
         <is>
-          <t>Model 39.7% (fair +152). Your call.</t>
+          <t>Model 44.7% (fair +124). Your call.</t>
         </is>
       </c>
       <c r="O32" s="15" t="n"/>
@@ -21093,12 +21093,12 @@
       </c>
       <c r="B33" s="12" t="inlineStr">
         <is>
-          <t>Portland Fire @ Washington Mystics</t>
+          <t>Las Vegas Aces @ Chicago Sky</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
@@ -21108,17 +21108,17 @@
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t>Washington Mystics -6.5</t>
+          <t>Chicago Sky +7.5</t>
         </is>
       </c>
       <c r="F33" s="13" t="n">
-        <v>0.4811529411764706</v>
+        <v>0.5767615384615384</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>108</v>
+        <v>-136</v>
       </c>
       <c r="H33" s="15" t="n">
-        <v>-104</v>
+        <v>-108</v>
       </c>
       <c r="I33" s="13">
         <f>IF($H$33="","",IF($H$33&lt;0,-$H$33/(-$H$33+100),100/($H$33+100)))</f>
@@ -21142,7 +21142,7 @@
       </c>
       <c r="N33" s="19" t="inlineStr">
         <is>
-          <t>Model 48.1% (fair +108). Your call.</t>
+          <t>Model 57.7% (fair -136). Your call.</t>
         </is>
       </c>
       <c r="O33" s="15" t="n"/>
@@ -21159,12 +21159,12 @@
       </c>
       <c r="B34" s="20" t="inlineStr">
         <is>
-          <t>Portland Fire @ Washington Mystics</t>
+          <t>Las Vegas Aces @ Chicago Sky</t>
         </is>
       </c>
       <c r="C34" s="20" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="D34" s="20" t="inlineStr">
@@ -21174,17 +21174,17 @@
       </c>
       <c r="E34" s="20" t="inlineStr">
         <is>
-          <t>Portland Fire +6.5</t>
+          <t>Las Vegas Aces -7.5</t>
         </is>
       </c>
       <c r="F34" s="13" t="n">
-        <v>0.5188118811881188</v>
+        <v>0.4232380952380952</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>-108</v>
+        <v>136</v>
       </c>
       <c r="H34" s="15" t="n">
-        <v>102</v>
+        <v>-110</v>
       </c>
       <c r="I34" s="13">
         <f>IF($H$34="","",IF($H$34&lt;0,-$H$34/(-$H$34+100),100/($H$34+100)))</f>
@@ -21208,7 +21208,7 @@
       </c>
       <c r="N34" s="19" t="inlineStr">
         <is>
-          <t>Model 51.9% (fair -108). Your call.</t>
+          <t>Model 42.3% (fair +136). Your call.</t>
         </is>
       </c>
       <c r="O34" s="15" t="n"/>
@@ -21225,12 +21225,12 @@
       </c>
       <c r="B35" s="12" t="inlineStr">
         <is>
-          <t>Las Vegas Aces @ Chicago Sky</t>
+          <t>New York Liberty @ Golden State Valkyries</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
@@ -21240,17 +21240,17 @@
       </c>
       <c r="E35" s="12" t="inlineStr">
         <is>
-          <t>Las Vegas Aces</t>
+          <t>New York Liberty</t>
         </is>
       </c>
       <c r="F35" s="13" t="n">
-        <v>0.7489948979591837</v>
+        <v>0.4216826923076923</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>-298</v>
+        <v>137</v>
       </c>
       <c r="H35" s="15" t="n">
-        <v>-292</v>
+        <v>108</v>
       </c>
       <c r="I35" s="13">
         <f>IF($H$35="","",IF($H$35&lt;0,-$H$35/(-$H$35+100),100/($H$35+100)))</f>
@@ -21274,7 +21274,7 @@
       </c>
       <c r="N35" s="19" t="inlineStr">
         <is>
-          <t>Model 74.9% (fair -298). Your call.</t>
+          <t>Model 42.2% (fair +137). Your call.</t>
         </is>
       </c>
       <c r="O35" s="15" t="n"/>
@@ -21291,12 +21291,12 @@
       </c>
       <c r="B36" s="20" t="inlineStr">
         <is>
-          <t>Las Vegas Aces @ Chicago Sky</t>
+          <t>New York Liberty @ Golden State Valkyries</t>
         </is>
       </c>
       <c r="C36" s="20" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D36" s="20" t="inlineStr">
@@ -21306,17 +21306,17 @@
       </c>
       <c r="E36" s="20" t="inlineStr">
         <is>
-          <t>Chicago Sky</t>
+          <t>Golden State Valkyries</t>
         </is>
       </c>
       <c r="F36" s="13" t="n">
-        <v>0.251012987012987</v>
+        <v>0.578321568627451</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>298</v>
+        <v>-137</v>
       </c>
       <c r="H36" s="15" t="n">
-        <v>285</v>
+        <v>-104</v>
       </c>
       <c r="I36" s="13">
         <f>IF($H$36="","",IF($H$36&lt;0,-$H$36/(-$H$36+100),100/($H$36+100)))</f>
@@ -21340,7 +21340,7 @@
       </c>
       <c r="N36" s="19" t="inlineStr">
         <is>
-          <t>Model 25.1% (fair +298). Your call.</t>
+          <t>Model 57.8% (fair -137). Your call.</t>
         </is>
       </c>
       <c r="O36" s="15" t="n"/>
@@ -21357,12 +21357,12 @@
       </c>
       <c r="B37" s="12" t="inlineStr">
         <is>
-          <t>Las Vegas Aces @ Chicago Sky</t>
+          <t>New York Liberty @ Golden State Valkyries</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
@@ -21372,17 +21372,17 @@
       </c>
       <c r="E37" s="12" t="inlineStr">
         <is>
-          <t>Over 178.5</t>
+          <t>Over 163.5</t>
         </is>
       </c>
       <c r="F37" s="13" t="n">
-        <v>0.55275</v>
+        <v>0.5769238095238095</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>-124</v>
+        <v>-136</v>
       </c>
       <c r="H37" s="15" t="n">
-        <v>100</v>
+        <v>-110</v>
       </c>
       <c r="I37" s="13">
         <f>IF($H$37="","",IF($H$37&lt;0,-$H$37/(-$H$37+100),100/($H$37+100)))</f>
@@ -21406,7 +21406,7 @@
       </c>
       <c r="N37" s="19" t="inlineStr">
         <is>
-          <t>Model 55.3% (fair -124). Your call.</t>
+          <t>Model 57.7% (fair -136). Your call.</t>
         </is>
       </c>
       <c r="O37" s="15" t="n"/>
@@ -21423,12 +21423,12 @@
       </c>
       <c r="B38" s="20" t="inlineStr">
         <is>
-          <t>Las Vegas Aces @ Chicago Sky</t>
+          <t>New York Liberty @ Golden State Valkyries</t>
         </is>
       </c>
       <c r="C38" s="20" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D38" s="20" t="inlineStr">
@@ -21438,17 +21438,17 @@
       </c>
       <c r="E38" s="20" t="inlineStr">
         <is>
-          <t>Under 178.5</t>
+          <t>Under 163.5</t>
         </is>
       </c>
       <c r="F38" s="13" t="n">
-        <v>0.4472</v>
+        <v>0.4231</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="H38" s="15" t="n">
-        <v>100</v>
+        <v>-110</v>
       </c>
       <c r="I38" s="13">
         <f>IF($H$38="","",IF($H$38&lt;0,-$H$38/(-$H$38+100),100/($H$38+100)))</f>
@@ -21472,7 +21472,7 @@
       </c>
       <c r="N38" s="19" t="inlineStr">
         <is>
-          <t>Model 44.7% (fair +124). Your call.</t>
+          <t>Model 42.3% (fair +136). Your call.</t>
         </is>
       </c>
       <c r="O38" s="15" t="n"/>
@@ -21489,12 +21489,12 @@
       </c>
       <c r="B39" s="12" t="inlineStr">
         <is>
-          <t>Las Vegas Aces @ Chicago Sky</t>
+          <t>New York Liberty @ Golden State Valkyries</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr">
@@ -21504,17 +21504,17 @@
       </c>
       <c r="E39" s="12" t="inlineStr">
         <is>
-          <t>Chicago Sky +7.5</t>
+          <t>Golden State Valkyries +1.5</t>
         </is>
       </c>
       <c r="F39" s="13" t="n">
-        <v>0.5767615384615384</v>
+        <v>0.5795450980392156</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>-136</v>
+        <v>-138</v>
       </c>
       <c r="H39" s="15" t="n">
-        <v>-108</v>
+        <v>-104</v>
       </c>
       <c r="I39" s="13">
         <f>IF($H$39="","",IF($H$39&lt;0,-$H$39/(-$H$39+100),100/($H$39+100)))</f>
@@ -21538,7 +21538,7 @@
       </c>
       <c r="N39" s="19" t="inlineStr">
         <is>
-          <t>Model 57.7% (fair -136). Your call.</t>
+          <t>Model 58.0% (fair -138). Your call.</t>
         </is>
       </c>
       <c r="O39" s="15" t="n"/>
@@ -21555,12 +21555,12 @@
       </c>
       <c r="B40" s="20" t="inlineStr">
         <is>
-          <t>Las Vegas Aces @ Chicago Sky</t>
+          <t>New York Liberty @ Golden State Valkyries</t>
         </is>
       </c>
       <c r="C40" s="20" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D40" s="20" t="inlineStr">
@@ -21570,17 +21570,17 @@
       </c>
       <c r="E40" s="20" t="inlineStr">
         <is>
-          <t>Las Vegas Aces -7.5</t>
+          <t>New York Liberty -1.5</t>
         </is>
       </c>
       <c r="F40" s="13" t="n">
-        <v>0.4232380952380952</v>
+        <v>0.4204878048780488</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H40" s="15" t="n">
-        <v>-110</v>
+        <v>105</v>
       </c>
       <c r="I40" s="13">
         <f>IF($H$40="","",IF($H$40&lt;0,-$H$40/(-$H$40+100),100/($H$40+100)))</f>
@@ -21604,7 +21604,7 @@
       </c>
       <c r="N40" s="19" t="inlineStr">
         <is>
-          <t>Model 42.3% (fair +136). Your call.</t>
+          <t>Model 42.0% (fair +138). Your call.</t>
         </is>
       </c>
       <c r="O40" s="15" t="n"/>
@@ -21613,405 +21613,9 @@
         <v/>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="12" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B41" s="12" t="inlineStr">
-        <is>
-          <t>New York Liberty @ Golden State Valkyries</t>
-        </is>
-      </c>
-      <c r="C41" s="12" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="D41" s="12" t="inlineStr">
-        <is>
-          <t>Moneyline</t>
-        </is>
-      </c>
-      <c r="E41" s="12" t="inlineStr">
-        <is>
-          <t>New York Liberty</t>
-        </is>
-      </c>
-      <c r="F41" s="13" t="n">
-        <v>0.4216826923076923</v>
-      </c>
-      <c r="G41" s="14" t="n">
-        <v>137</v>
-      </c>
-      <c r="H41" s="15" t="n">
-        <v>108</v>
-      </c>
-      <c r="I41" s="13">
-        <f>IF($H$41="","",IF($H$41&lt;0,-$H$41/(-$H$41+100),100/($H$41+100)))</f>
-        <v/>
-      </c>
-      <c r="J41" s="16">
-        <f>IF($H$41="","",$F$41*IF($H$41&lt;0,-100/$H$41,$H$41/100)-(1-$F$41))</f>
-        <v/>
-      </c>
-      <c r="K41" s="17">
-        <f>IF($H$41="","",MAX(0,($F$41*IF($H$41&lt;0,-100/$H$41,$H$41/100)-(1-$F$41))/IF($H$41&lt;0,-100/$H$41,$H$41/100))*'Settings'!$B$3)</f>
-        <v/>
-      </c>
-      <c r="L41" s="18">
-        <f>IF($H$41="","",ROUND(MIN($K$41,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
-        <v/>
-      </c>
-      <c r="M41" s="12">
-        <f>IF($J$41="","",IF($J$41&lt;0,"Pass",IF($J$41&lt;'Settings'!$B$4,"Thin",IF($J$41&lt;0.06,"✅ Sharp band",IF($J$41&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
-        <v/>
-      </c>
-      <c r="N41" s="19" t="inlineStr">
-        <is>
-          <t>Model 42.2% (fair +137). Your call.</t>
-        </is>
-      </c>
-      <c r="O41" s="15" t="n"/>
-      <c r="P41" s="16">
-        <f>IF(OR($H$41="",$O$41=""),"",(1+IF($H$41&lt;0,-100/$H$41,$H$41/100))/(1+IF($O$41&lt;0,-100/$O$41,$O$41/100))-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="20" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B42" s="20" t="inlineStr">
-        <is>
-          <t>New York Liberty @ Golden State Valkyries</t>
-        </is>
-      </c>
-      <c r="C42" s="20" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="D42" s="20" t="inlineStr">
-        <is>
-          <t>Moneyline</t>
-        </is>
-      </c>
-      <c r="E42" s="20" t="inlineStr">
-        <is>
-          <t>Golden State Valkyries</t>
-        </is>
-      </c>
-      <c r="F42" s="13" t="n">
-        <v>0.578321568627451</v>
-      </c>
-      <c r="G42" s="14" t="n">
-        <v>-137</v>
-      </c>
-      <c r="H42" s="15" t="n">
-        <v>-104</v>
-      </c>
-      <c r="I42" s="13">
-        <f>IF($H$42="","",IF($H$42&lt;0,-$H$42/(-$H$42+100),100/($H$42+100)))</f>
-        <v/>
-      </c>
-      <c r="J42" s="16">
-        <f>IF($H$42="","",$F$42*IF($H$42&lt;0,-100/$H$42,$H$42/100)-(1-$F$42))</f>
-        <v/>
-      </c>
-      <c r="K42" s="17">
-        <f>IF($H$42="","",MAX(0,($F$42*IF($H$42&lt;0,-100/$H$42,$H$42/100)-(1-$F$42))/IF($H$42&lt;0,-100/$H$42,$H$42/100))*'Settings'!$B$3)</f>
-        <v/>
-      </c>
-      <c r="L42" s="18">
-        <f>IF($H$42="","",ROUND(MIN($K$42,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
-        <v/>
-      </c>
-      <c r="M42" s="12">
-        <f>IF($J$42="","",IF($J$42&lt;0,"Pass",IF($J$42&lt;'Settings'!$B$4,"Thin",IF($J$42&lt;0.06,"✅ Sharp band",IF($J$42&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
-        <v/>
-      </c>
-      <c r="N42" s="19" t="inlineStr">
-        <is>
-          <t>Model 57.8% (fair -137). Your call.</t>
-        </is>
-      </c>
-      <c r="O42" s="15" t="n"/>
-      <c r="P42" s="16">
-        <f>IF(OR($H$42="",$O$42=""),"",(1+IF($H$42&lt;0,-100/$H$42,$H$42/100))/(1+IF($O$42&lt;0,-100/$O$42,$O$42/100))-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="12" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B43" s="12" t="inlineStr">
-        <is>
-          <t>New York Liberty @ Golden State Valkyries</t>
-        </is>
-      </c>
-      <c r="C43" s="12" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="D43" s="12" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="E43" s="12" t="inlineStr">
-        <is>
-          <t>Over 163.5</t>
-        </is>
-      </c>
-      <c r="F43" s="13" t="n">
-        <v>0.5769238095238095</v>
-      </c>
-      <c r="G43" s="14" t="n">
-        <v>-136</v>
-      </c>
-      <c r="H43" s="15" t="n">
-        <v>-110</v>
-      </c>
-      <c r="I43" s="13">
-        <f>IF($H$43="","",IF($H$43&lt;0,-$H$43/(-$H$43+100),100/($H$43+100)))</f>
-        <v/>
-      </c>
-      <c r="J43" s="16">
-        <f>IF($H$43="","",$F$43*IF($H$43&lt;0,-100/$H$43,$H$43/100)-(1-$F$43))</f>
-        <v/>
-      </c>
-      <c r="K43" s="17">
-        <f>IF($H$43="","",MAX(0,($F$43*IF($H$43&lt;0,-100/$H$43,$H$43/100)-(1-$F$43))/IF($H$43&lt;0,-100/$H$43,$H$43/100))*'Settings'!$B$3)</f>
-        <v/>
-      </c>
-      <c r="L43" s="18">
-        <f>IF($H$43="","",ROUND(MIN($K$43,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
-        <v/>
-      </c>
-      <c r="M43" s="12">
-        <f>IF($J$43="","",IF($J$43&lt;0,"Pass",IF($J$43&lt;'Settings'!$B$4,"Thin",IF($J$43&lt;0.06,"✅ Sharp band",IF($J$43&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
-        <v/>
-      </c>
-      <c r="N43" s="19" t="inlineStr">
-        <is>
-          <t>Model 57.7% (fair -136). Your call.</t>
-        </is>
-      </c>
-      <c r="O43" s="15" t="n"/>
-      <c r="P43" s="16">
-        <f>IF(OR($H$43="",$O$43=""),"",(1+IF($H$43&lt;0,-100/$H$43,$H$43/100))/(1+IF($O$43&lt;0,-100/$O$43,$O$43/100))-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="20" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B44" s="20" t="inlineStr">
-        <is>
-          <t>New York Liberty @ Golden State Valkyries</t>
-        </is>
-      </c>
-      <c r="C44" s="20" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="D44" s="20" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="E44" s="20" t="inlineStr">
-        <is>
-          <t>Under 163.5</t>
-        </is>
-      </c>
-      <c r="F44" s="13" t="n">
-        <v>0.4231</v>
-      </c>
-      <c r="G44" s="14" t="n">
-        <v>136</v>
-      </c>
-      <c r="H44" s="15" t="n">
-        <v>-110</v>
-      </c>
-      <c r="I44" s="13">
-        <f>IF($H$44="","",IF($H$44&lt;0,-$H$44/(-$H$44+100),100/($H$44+100)))</f>
-        <v/>
-      </c>
-      <c r="J44" s="16">
-        <f>IF($H$44="","",$F$44*IF($H$44&lt;0,-100/$H$44,$H$44/100)-(1-$F$44))</f>
-        <v/>
-      </c>
-      <c r="K44" s="17">
-        <f>IF($H$44="","",MAX(0,($F$44*IF($H$44&lt;0,-100/$H$44,$H$44/100)-(1-$F$44))/IF($H$44&lt;0,-100/$H$44,$H$44/100))*'Settings'!$B$3)</f>
-        <v/>
-      </c>
-      <c r="L44" s="18">
-        <f>IF($H$44="","",ROUND(MIN($K$44,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
-        <v/>
-      </c>
-      <c r="M44" s="12">
-        <f>IF($J$44="","",IF($J$44&lt;0,"Pass",IF($J$44&lt;'Settings'!$B$4,"Thin",IF($J$44&lt;0.06,"✅ Sharp band",IF($J$44&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
-        <v/>
-      </c>
-      <c r="N44" s="19" t="inlineStr">
-        <is>
-          <t>Model 42.3% (fair +136). Your call.</t>
-        </is>
-      </c>
-      <c r="O44" s="15" t="n"/>
-      <c r="P44" s="16">
-        <f>IF(OR($H$44="",$O$44=""),"",(1+IF($H$44&lt;0,-100/$H$44,$H$44/100))/(1+IF($O$44&lt;0,-100/$O$44,$O$44/100))-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="12" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B45" s="12" t="inlineStr">
-        <is>
-          <t>New York Liberty @ Golden State Valkyries</t>
-        </is>
-      </c>
-      <c r="C45" s="12" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="D45" s="12" t="inlineStr">
-        <is>
-          <t>Spread</t>
-        </is>
-      </c>
-      <c r="E45" s="12" t="inlineStr">
-        <is>
-          <t>Golden State Valkyries +1.5</t>
-        </is>
-      </c>
-      <c r="F45" s="13" t="n">
-        <v>0.576435294117647</v>
-      </c>
-      <c r="G45" s="14" t="n">
-        <v>-136</v>
-      </c>
-      <c r="H45" s="15" t="n">
-        <v>-104</v>
-      </c>
-      <c r="I45" s="13">
-        <f>IF($H$45="","",IF($H$45&lt;0,-$H$45/(-$H$45+100),100/($H$45+100)))</f>
-        <v/>
-      </c>
-      <c r="J45" s="16">
-        <f>IF($H$45="","",$F$45*IF($H$45&lt;0,-100/$H$45,$H$45/100)-(1-$F$45))</f>
-        <v/>
-      </c>
-      <c r="K45" s="17">
-        <f>IF($H$45="","",MAX(0,($F$45*IF($H$45&lt;0,-100/$H$45,$H$45/100)-(1-$F$45))/IF($H$45&lt;0,-100/$H$45,$H$45/100))*'Settings'!$B$3)</f>
-        <v/>
-      </c>
-      <c r="L45" s="18">
-        <f>IF($H$45="","",ROUND(MIN($K$45,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
-        <v/>
-      </c>
-      <c r="M45" s="12">
-        <f>IF($J$45="","",IF($J$45&lt;0,"Pass",IF($J$45&lt;'Settings'!$B$4,"Thin",IF($J$45&lt;0.06,"✅ Sharp band",IF($J$45&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
-        <v/>
-      </c>
-      <c r="N45" s="19" t="inlineStr">
-        <is>
-          <t>Model 57.6% (fair -136). Your call.</t>
-        </is>
-      </c>
-      <c r="O45" s="15" t="n"/>
-      <c r="P45" s="16">
-        <f>IF(OR($H$45="",$O$45=""),"",(1+IF($H$45&lt;0,-100/$H$45,$H$45/100))/(1+IF($O$45&lt;0,-100/$O$45,$O$45/100))-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="20" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B46" s="20" t="inlineStr">
-        <is>
-          <t>New York Liberty @ Golden State Valkyries</t>
-        </is>
-      </c>
-      <c r="C46" s="20" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="D46" s="20" t="inlineStr">
-        <is>
-          <t>Spread</t>
-        </is>
-      </c>
-      <c r="E46" s="20" t="inlineStr">
-        <is>
-          <t>New York Liberty -1.5</t>
-        </is>
-      </c>
-      <c r="F46" s="13" t="n">
-        <v>0.42355</v>
-      </c>
-      <c r="G46" s="14" t="n">
-        <v>136</v>
-      </c>
-      <c r="H46" s="15" t="n">
-        <v>100</v>
-      </c>
-      <c r="I46" s="13">
-        <f>IF($H$46="","",IF($H$46&lt;0,-$H$46/(-$H$46+100),100/($H$46+100)))</f>
-        <v/>
-      </c>
-      <c r="J46" s="16">
-        <f>IF($H$46="","",$F$46*IF($H$46&lt;0,-100/$H$46,$H$46/100)-(1-$F$46))</f>
-        <v/>
-      </c>
-      <c r="K46" s="17">
-        <f>IF($H$46="","",MAX(0,($F$46*IF($H$46&lt;0,-100/$H$46,$H$46/100)-(1-$F$46))/IF($H$46&lt;0,-100/$H$46,$H$46/100))*'Settings'!$B$3)</f>
-        <v/>
-      </c>
-      <c r="L46" s="18">
-        <f>IF($H$46="","",ROUND(MIN($K$46,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
-        <v/>
-      </c>
-      <c r="M46" s="12">
-        <f>IF($J$46="","",IF($J$46&lt;0,"Pass",IF($J$46&lt;'Settings'!$B$4,"Thin",IF($J$46&lt;0.06,"✅ Sharp band",IF($J$46&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
-        <v/>
-      </c>
-      <c r="N46" s="19" t="inlineStr">
-        <is>
-          <t>Model 42.4% (fair +136). Your call.</t>
-        </is>
-      </c>
-      <c r="O46" s="15" t="n"/>
-      <c r="P46" s="16">
-        <f>IF(OR($H$46="",$O$46=""),"",(1+IF($H$46&lt;0,-100/$H$46,$H$46/100))/(1+IF($O$46&lt;0,-100/$O$46,$O$46/100))-1)</f>
-        <v/>
-      </c>
-    </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="CE4B"/>
-  <conditionalFormatting sqref="J5:J46">
+  <conditionalFormatting sqref="J5:J40">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-0.05"/>
@@ -22115,28 +21719,28 @@
         </is>
       </c>
       <c r="B5" s="21" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C5" s="22" t="n">
-        <v>0.2503</v>
+        <v>0.2508</v>
       </c>
       <c r="D5" s="21" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E5" s="13" t="n">
-        <v>0.4639</v>
+        <v>0.4611</v>
       </c>
       <c r="F5" s="23" t="n">
-        <v>0.53</v>
+        <v>-0.47</v>
       </c>
       <c r="G5" s="24" t="n">
-        <v>0.32</v>
+        <v>-0.28</v>
       </c>
       <c r="H5" s="24" t="n">
-        <v>2.72</v>
+        <v>2.28</v>
       </c>
       <c r="I5" s="13" t="n">
-        <v>0.5068</v>
+        <v>0.5034</v>
       </c>
     </row>
     <row r="6">
@@ -22146,28 +21750,28 @@
         </is>
       </c>
       <c r="B6" s="21" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C6" s="22" t="n">
-        <v>0.2507</v>
+        <v>0.2512</v>
       </c>
       <c r="D6" s="21" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E6" s="13" t="n">
-        <v>0.5</v>
+        <v>0.4962</v>
       </c>
       <c r="F6" s="23" t="n">
-        <v>5.78</v>
+        <v>4.78</v>
       </c>
       <c r="G6" s="24" t="n">
-        <v>4.45</v>
+        <v>3.65</v>
       </c>
       <c r="H6" s="24" t="n">
-        <v>4.17</v>
+        <v>3.61</v>
       </c>
       <c r="I6" s="13" t="n">
-        <v>0.5339</v>
+        <v>0.5294</v>
       </c>
     </row>
     <row r="7">
@@ -22250,7 +21854,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>When the model said X%, how often it actually happened (n=191, ECE 0.069 — lower is better; a calibrated model's bars sit on the diagonal).</t>
+          <t>When the model said X%, how often it actually happened (n=193, ECE 0.063 — lower is better; a calibrated model's bars sit on the diagonal).</t>
         </is>
       </c>
     </row>
@@ -22345,16 +21949,16 @@
         </is>
       </c>
       <c r="B20" s="21" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C20" s="13" t="n">
         <v>0.4543</v>
       </c>
       <c r="D20" s="13" t="n">
-        <v>0.4444</v>
+        <v>0.4531</v>
       </c>
       <c r="E20" s="26" t="n">
-        <v>-0.009900000000000001</v>
+        <v>-0.0012</v>
       </c>
     </row>
     <row r="21">
@@ -22364,16 +21968,16 @@
         </is>
       </c>
       <c r="B21" s="21" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C21" s="13" t="n">
-        <v>0.5431</v>
+        <v>0.5434</v>
       </c>
       <c r="D21" s="13" t="n">
-        <v>0.5735</v>
+        <v>0.5652</v>
       </c>
       <c r="E21" s="26" t="n">
-        <v>0.0304</v>
+        <v>0.0218</v>
       </c>
     </row>
     <row r="22">

--- a/data/output/workbook/2026-06-27.xlsx
+++ b/data/output/workbook/2026-06-27.xlsx
@@ -551,7 +551,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="9896475"/>
+    <ext cx="10125075" cy="9477375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -954,7 +954,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-06-27 17:03</t>
+          <t>2026-06-27 18:07</t>
         </is>
       </c>
     </row>
@@ -4530,7 +4530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q77"/>
+  <dimension ref="A1:Q75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4547,823 +4547,823 @@
         </is>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" s="29" t="inlineStr">
+        <is>
+          <t>Arizona Diamondbacks offense vs Tampa Bay Rays defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B62" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C62" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D62" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E62" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F62" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G62" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H62" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I62" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J62" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K62" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L62" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M62" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N62" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O62" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P62" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q62" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
     <row r="63">
-      <c r="A63" s="29" t="inlineStr">
-        <is>
-          <t>Arizona Diamondbacks offense vs Tampa Bay Rays defense</t>
+      <c r="A63" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B63" s="32" t="n">
+        <v>4.976</v>
+      </c>
+      <c r="C63" s="32" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="D63" s="32" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="E63" s="32" t="n">
+        <v>4.467</v>
+      </c>
+      <c r="F63" s="32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="G63" s="32" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H63" s="36" t="inlineStr">
+        <is>
+          <t>25th</t>
+        </is>
+      </c>
+      <c r="I63" s="32" t="inlineStr"/>
+      <c r="J63" s="36" t="inlineStr">
+        <is>
+          <t>26th</t>
+        </is>
+      </c>
+      <c r="K63" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="L63" s="32" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="M63" s="32" t="n">
+        <v>4.867</v>
+      </c>
+      <c r="N63" s="32" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O63" s="32" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="P63" s="32" t="n">
+        <v>4.234</v>
+      </c>
+      <c r="Q63" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B64" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C64" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D64" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E64" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F64" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G64" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H64" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I64" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J64" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K64" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L64" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M64" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N64" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O64" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P64" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q64" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A64" s="31" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B64" s="32" t="n">
+        <v>8.688000000000001</v>
+      </c>
+      <c r="C64" s="32" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="D64" s="32" t="n">
+        <v>8.85</v>
+      </c>
+      <c r="E64" s="32" t="n">
+        <v>9</v>
+      </c>
+      <c r="F64" s="32" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="G64" s="32" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="H64" s="34" t="inlineStr">
+        <is>
+          <t>12th</t>
+        </is>
+      </c>
+      <c r="I64" s="32" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="J64" s="34" t="inlineStr">
+        <is>
+          <t>17th</t>
+        </is>
+      </c>
+      <c r="K64" s="32" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="L64" s="32" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="M64" s="32" t="n">
+        <v>8.067</v>
+      </c>
+      <c r="N64" s="32" t="n">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="O64" s="32" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="P64" s="32" t="n">
+        <v>7.868</v>
+      </c>
+      <c r="Q64" s="35" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B65" s="32" t="n">
-        <v>4.976</v>
+        <v>1.329</v>
       </c>
       <c r="C65" s="32" t="n">
-        <v>4.7</v>
+        <v>1.033</v>
       </c>
       <c r="D65" s="32" t="n">
-        <v>4.45</v>
+        <v>0.85</v>
       </c>
       <c r="E65" s="32" t="n">
-        <v>4.467</v>
+        <v>1</v>
       </c>
       <c r="F65" s="32" t="n">
-        <v>3.4</v>
+        <v>0.9</v>
       </c>
       <c r="G65" s="32" t="n">
-        <v>2.6</v>
+        <v>0.8</v>
       </c>
       <c r="H65" s="36" t="inlineStr">
         <is>
-          <t>25th</t>
+          <t>22nd</t>
         </is>
       </c>
       <c r="I65" s="32" t="inlineStr"/>
-      <c r="J65" s="36" t="inlineStr">
-        <is>
-          <t>26th</t>
-        </is>
-      </c>
-      <c r="K65" s="32" t="n">
-        <v>6</v>
-      </c>
-      <c r="L65" s="32" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="M65" s="32" t="n">
-        <v>4.867</v>
-      </c>
-      <c r="N65" s="32" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="O65" s="32" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="P65" s="32" t="n">
-        <v>4.234</v>
+      <c r="J65" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K65" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L65" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M65" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N65" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O65" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P65" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Q65" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B66" s="32" t="n">
-        <v>8.688000000000001</v>
+        <v>8.265000000000001</v>
       </c>
       <c r="C66" s="32" t="n">
+        <v>8.467000000000001</v>
+      </c>
+      <c r="D66" s="32" t="n">
+        <v>8.35</v>
+      </c>
+      <c r="E66" s="32" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="F66" s="32" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="G66" s="32" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="H66" s="36" t="inlineStr">
+        <is>
+          <t>23rd</t>
+        </is>
+      </c>
+      <c r="I66" s="32" t="inlineStr"/>
+      <c r="J66" s="34" t="inlineStr">
+        <is>
+          <t>15th</t>
+        </is>
+      </c>
+      <c r="K66" s="32" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="L66" s="32" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="D66" s="32" t="n">
-        <v>8.85</v>
-      </c>
-      <c r="E66" s="32" t="n">
-        <v>9</v>
-      </c>
-      <c r="F66" s="32" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="G66" s="32" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="H66" s="34" t="inlineStr">
-        <is>
-          <t>12th</t>
-        </is>
-      </c>
-      <c r="I66" s="32" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J66" s="34" t="inlineStr">
-        <is>
-          <t>17th</t>
-        </is>
-      </c>
-      <c r="K66" s="32" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="L66" s="32" t="n">
-        <v>8.4</v>
-      </c>
       <c r="M66" s="32" t="n">
-        <v>8.067</v>
+        <v>8.333</v>
       </c>
       <c r="N66" s="32" t="n">
-        <v>8.050000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O66" s="32" t="n">
-        <v>7.8</v>
+        <v>9.5</v>
       </c>
       <c r="P66" s="32" t="n">
-        <v>7.868</v>
+        <v>8.737</v>
       </c>
       <c r="Q66" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B67" s="32" t="n">
-        <v>1.329</v>
+        <v>0.612</v>
       </c>
       <c r="C67" s="32" t="n">
-        <v>1.033</v>
+        <v>0.467</v>
       </c>
       <c r="D67" s="32" t="n">
-        <v>0.85</v>
+        <v>0.5</v>
       </c>
       <c r="E67" s="32" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="F67" s="32" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="G67" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H67" s="33" t="inlineStr">
+        <is>
+          <t>10th</t>
+        </is>
+      </c>
+      <c r="I67" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J67" s="36" t="inlineStr">
+        <is>
+          <t>25th</t>
+        </is>
+      </c>
+      <c r="K67" s="32" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L67" s="32" t="n">
         <v>0.8</v>
       </c>
-      <c r="H67" s="36" t="inlineStr">
-        <is>
-          <t>22nd</t>
-        </is>
-      </c>
-      <c r="I67" s="32" t="inlineStr"/>
-      <c r="J67" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K67" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L67" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M67" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N67" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O67" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P67" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="M67" s="32" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="N67" s="32" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="O67" s="32" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="P67" s="32" t="n">
+        <v>0.473</v>
       </c>
       <c r="Q67" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="31" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B68" s="32" t="n">
-        <v>8.265000000000001</v>
-      </c>
-      <c r="C68" s="32" t="n">
-        <v>8.467000000000001</v>
-      </c>
-      <c r="D68" s="32" t="n">
-        <v>8.35</v>
-      </c>
-      <c r="E68" s="32" t="n">
+          <t>Opp 1st Inn R/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="29" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays offense vs Arizona Diamondbacks defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B70" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C70" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D70" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E70" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F70" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G70" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H70" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I70" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J70" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K70" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L70" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M70" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N70" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O70" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P70" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q70" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B71" s="32" t="n">
+        <v>4.437</v>
+      </c>
+      <c r="C71" s="32" t="n">
+        <v>4.033</v>
+      </c>
+      <c r="D71" s="32" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="E71" s="32" t="n">
+        <v>3.667</v>
+      </c>
+      <c r="F71" s="32" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="G71" s="32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H71" s="34" t="inlineStr">
+        <is>
+          <t>14th</t>
+        </is>
+      </c>
+      <c r="I71" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J71" s="36" t="inlineStr">
+        <is>
+          <t>30th</t>
+        </is>
+      </c>
+      <c r="K71" s="32" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="L71" s="32" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="M71" s="32" t="n">
+        <v>5.333</v>
+      </c>
+      <c r="N71" s="32" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="O71" s="32" t="n">
+        <v>4.767</v>
+      </c>
+      <c r="P71" s="32" t="n">
+        <v>4.847</v>
+      </c>
+      <c r="Q71" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="31" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B72" s="32" t="n">
+        <v>8.521000000000001</v>
+      </c>
+      <c r="C72" s="32" t="n">
         <v>8.4</v>
       </c>
-      <c r="F68" s="32" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="G68" s="32" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="H68" s="36" t="inlineStr">
-        <is>
-          <t>23rd</t>
-        </is>
-      </c>
-      <c r="I68" s="32" t="inlineStr"/>
-      <c r="J68" s="34" t="inlineStr">
-        <is>
-          <t>15th</t>
-        </is>
-      </c>
-      <c r="K68" s="32" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="L68" s="32" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="M68" s="32" t="n">
-        <v>8.333</v>
-      </c>
-      <c r="N68" s="32" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="O68" s="32" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="P68" s="32" t="n">
-        <v>8.737</v>
-      </c>
-      <c r="Q68" s="35" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B69" s="32" t="n">
-        <v>0.612</v>
-      </c>
-      <c r="C69" s="32" t="n">
-        <v>0.467</v>
-      </c>
-      <c r="D69" s="32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E69" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="F69" s="32" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="G69" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H69" s="33" t="inlineStr">
-        <is>
-          <t>10th</t>
-        </is>
-      </c>
-      <c r="I69" s="32" t="inlineStr">
+      <c r="D72" s="32" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="E72" s="32" t="n">
+        <v>8.667</v>
+      </c>
+      <c r="F72" s="32" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G72" s="32" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="H72" s="33" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="I72" s="32" t="inlineStr">
         <is>
           <t>★★★</t>
         </is>
       </c>
-      <c r="J69" s="36" t="inlineStr">
-        <is>
-          <t>25th</t>
-        </is>
-      </c>
-      <c r="K69" s="32" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="L69" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="M69" s="32" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="N69" s="32" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="O69" s="32" t="n">
-        <v>0.467</v>
-      </c>
-      <c r="P69" s="32" t="n">
-        <v>0.473</v>
-      </c>
-      <c r="Q69" s="35" t="inlineStr">
-        <is>
-          <t>Opp 1st Inn R/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="29" t="inlineStr">
-        <is>
-          <t>Tampa Bay Rays offense vs Arizona Diamondbacks defense</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B72" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C72" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D72" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E72" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F72" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G72" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H72" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I72" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J72" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K72" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L72" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M72" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N72" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O72" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P72" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q72" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="J72" s="36" t="inlineStr">
+        <is>
+          <t>27th</t>
+        </is>
+      </c>
+      <c r="K72" s="32" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="L72" s="32" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="M72" s="32" t="n">
+        <v>9.132999999999999</v>
+      </c>
+      <c r="N72" s="32" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="O72" s="32" t="n">
+        <v>8.567</v>
+      </c>
+      <c r="P72" s="32" t="n">
+        <v>8.840999999999999</v>
+      </c>
+      <c r="Q72" s="35" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B73" s="32" t="n">
-        <v>4.437</v>
+        <v>1.114</v>
       </c>
       <c r="C73" s="32" t="n">
-        <v>4.033</v>
+        <v>1.133</v>
       </c>
       <c r="D73" s="32" t="n">
-        <v>3.55</v>
+        <v>1.15</v>
       </c>
       <c r="E73" s="32" t="n">
-        <v>3.667</v>
+        <v>1</v>
       </c>
       <c r="F73" s="32" t="n">
-        <v>3.9</v>
+        <v>1</v>
       </c>
       <c r="G73" s="32" t="n">
-        <v>3.6</v>
+        <v>1</v>
       </c>
       <c r="H73" s="34" t="inlineStr">
         <is>
-          <t>14th</t>
-        </is>
-      </c>
-      <c r="I73" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J73" s="36" t="inlineStr">
-        <is>
-          <t>30th</t>
-        </is>
-      </c>
-      <c r="K73" s="32" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="L73" s="32" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="M73" s="32" t="n">
-        <v>5.333</v>
-      </c>
-      <c r="N73" s="32" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="O73" s="32" t="n">
-        <v>4.767</v>
-      </c>
-      <c r="P73" s="32" t="n">
-        <v>4.847</v>
+          <t>17th</t>
+        </is>
+      </c>
+      <c r="I73" s="32" t="inlineStr"/>
+      <c r="J73" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Q73" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B74" s="32" t="n">
-        <v>8.521000000000001</v>
+        <v>8.611000000000001</v>
       </c>
       <c r="C74" s="32" t="n">
-        <v>8.4</v>
+        <v>8.967000000000001</v>
       </c>
       <c r="D74" s="32" t="n">
-        <v>8.300000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="E74" s="32" t="n">
-        <v>8.667</v>
+        <v>9.667</v>
       </c>
       <c r="F74" s="32" t="n">
-        <v>8.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G74" s="32" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="H74" s="33" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="I74" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J74" s="36" t="inlineStr">
-        <is>
-          <t>27th</t>
+        <v>10.2</v>
+      </c>
+      <c r="H74" s="34" t="inlineStr">
+        <is>
+          <t>18th</t>
+        </is>
+      </c>
+      <c r="I74" s="32" t="inlineStr"/>
+      <c r="J74" s="34" t="inlineStr">
+        <is>
+          <t>16th</t>
         </is>
       </c>
       <c r="K74" s="32" t="n">
-        <v>10.4</v>
+        <v>9.4</v>
       </c>
       <c r="L74" s="32" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="M74" s="32" t="n">
-        <v>9.132999999999999</v>
+        <v>8.333</v>
       </c>
       <c r="N74" s="32" t="n">
-        <v>8.75</v>
+        <v>7.9</v>
       </c>
       <c r="O74" s="32" t="n">
-        <v>8.567</v>
+        <v>7.8</v>
       </c>
       <c r="P74" s="32" t="n">
-        <v>8.840999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q74" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B75" s="32" t="n">
-        <v>1.114</v>
+        <v>0.587</v>
       </c>
       <c r="C75" s="32" t="n">
-        <v>1.133</v>
+        <v>0.867</v>
       </c>
       <c r="D75" s="32" t="n">
-        <v>1.15</v>
+        <v>0.7</v>
       </c>
       <c r="E75" s="32" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="F75" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G75" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H75" s="34" t="inlineStr">
+        <is>
+          <t>16th</t>
+        </is>
+      </c>
+      <c r="I75" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J75" s="36" t="inlineStr">
+        <is>
+          <t>29th</t>
+        </is>
+      </c>
+      <c r="K75" s="32" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L75" s="32" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M75" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="F75" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="G75" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="H75" s="34" t="inlineStr">
-        <is>
-          <t>17th</t>
-        </is>
-      </c>
-      <c r="I75" s="32" t="inlineStr"/>
-      <c r="J75" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="N75" s="32" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="O75" s="32" t="n">
+        <v>0.733</v>
+      </c>
+      <c r="P75" s="32" t="n">
+        <v>0.641</v>
       </c>
       <c r="Q75" s="35" t="inlineStr">
-        <is>
-          <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="31" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B76" s="32" t="n">
-        <v>8.611000000000001</v>
-      </c>
-      <c r="C76" s="32" t="n">
-        <v>8.967000000000001</v>
-      </c>
-      <c r="D76" s="32" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="E76" s="32" t="n">
-        <v>9.667</v>
-      </c>
-      <c r="F76" s="32" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="G76" s="32" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="H76" s="34" t="inlineStr">
-        <is>
-          <t>18th</t>
-        </is>
-      </c>
-      <c r="I76" s="32" t="inlineStr"/>
-      <c r="J76" s="34" t="inlineStr">
-        <is>
-          <t>16th</t>
-        </is>
-      </c>
-      <c r="K76" s="32" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="L76" s="32" t="n">
-        <v>9</v>
-      </c>
-      <c r="M76" s="32" t="n">
-        <v>8.333</v>
-      </c>
-      <c r="N76" s="32" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="O76" s="32" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="P76" s="32" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Q76" s="35" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B77" s="32" t="n">
-        <v>0.587</v>
-      </c>
-      <c r="C77" s="32" t="n">
-        <v>0.867</v>
-      </c>
-      <c r="D77" s="32" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E77" s="32" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="F77" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="G77" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H77" s="34" t="inlineStr">
-        <is>
-          <t>16th</t>
-        </is>
-      </c>
-      <c r="I77" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J77" s="36" t="inlineStr">
-        <is>
-          <t>29th</t>
-        </is>
-      </c>
-      <c r="K77" s="32" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="L77" s="32" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="M77" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="N77" s="32" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="O77" s="32" t="n">
-        <v>0.733</v>
-      </c>
-      <c r="P77" s="32" t="n">
-        <v>0.641</v>
-      </c>
-      <c r="Q77" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -8108,37 +8108,37 @@
     <row r="5">
       <c r="A5" s="12" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Sparks @ Indiana Fever</t>
+          <t>Cincinnati Reds @ Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>Over 179.5</t>
+          <t>Pittsburgh Pirates -1.5</t>
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.715</v>
+        <v>0.5008208955223882</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>-251</v>
+        <v>-100</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>-104</v>
+        <v>168</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -8162,7 +8162,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 71.5% (fair -251). Your call.</t>
+          <t>Model 50.1% (fair -100). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -8174,37 +8174,37 @@
     <row r="6">
       <c r="A6" s="20" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>Cincinnati Reds @ Pittsburgh Pirates</t>
+          <t>Los Angeles Sparks @ Indiana Fever</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates -1.5</t>
+          <t>Over 181.5</t>
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.4966544117647059</v>
+        <v>0.6680980392156862</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>101</v>
+        <v>-201</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>172</v>
+        <v>-104</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -8228,7 +8228,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 49.7% (fair +101). Your call.</t>
+          <t>Model 66.8% (fair -201). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -8311,12 +8311,12 @@
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>Washington Nationals @ Baltimore Orioles</t>
+          <t>Portland Fire @ Washington Mystics</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -8326,17 +8326,17 @@
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>Over 9.5</t>
+          <t>Over 166.5</t>
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.5857560975609757</v>
+        <v>0.5774509803921568</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>-141</v>
+        <v>-137</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 58.6% (fair -141). Your call.</t>
+          <t>Model 57.7% (fair -137). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -8377,12 +8377,12 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>Portland Fire @ Washington Mystics</t>
+          <t>Houston Astros @ Detroit Tigers</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
@@ -8392,17 +8392,17 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Over 166.5</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.5774509803921568</v>
+        <v>0.5749</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>-137</v>
+        <v>-135</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -8426,7 +8426,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 57.7% (fair -137). Your call.</t>
+          <t>Model 57.5% (fair -135). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -8438,37 +8438,37 @@
     <row r="10">
       <c r="A10" s="20" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>Houston Astros @ Detroit Tigers</t>
+          <t>Cincinnati Reds @ Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.5746</v>
+        <v>0.5560194174757281</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-135</v>
+        <v>-125</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -8492,7 +8492,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 57.5% (fair -135). Your call.</t>
+          <t>Model 55.6% (fair -125). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -8509,32 +8509,32 @@
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>Kansas City Royals @ Chicago White Sox</t>
+          <t>New York Liberty @ Golden State Valkyries</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>Over 9</t>
+          <t>Golden State Valkyries</t>
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.5866682926829269</v>
+        <v>0.578321568627451</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>-142</v>
+        <v>-137</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>-105</v>
+        <v>-104</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -8558,7 +8558,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 58.7% (fair -142). Your call.</t>
+          <t>Model 57.8% (fair -137). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -8570,37 +8570,37 @@
     <row r="12">
       <c r="A12" s="20" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>Cincinnati Reds @ Pittsburgh Pirates</t>
+          <t>Washington Nationals @ Baltimore Orioles</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>Baltimore Orioles -1.5</t>
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.5560194174757281</v>
+        <v>0.5262264150943395</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>-125</v>
+        <v>-111</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -8624,7 +8624,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 55.6% (fair -125). Your call.</t>
+          <t>Model 52.6% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -8641,32 +8641,32 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>New York Liberty @ Golden State Valkyries</t>
+          <t>Arizona Diamondbacks @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Golden State Valkyries +1.5</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.5795450980392156</v>
+        <v>0.5958069767441861</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>-138</v>
+        <v>-147</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>-104</v>
+        <v>-115</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -8690,7 +8690,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 58.0% (fair -138). Your call.</t>
+          <t>Model 59.6% (fair -147). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -8707,12 +8707,12 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>New York Liberty @ Golden State Valkyries</t>
+          <t>Washington Nationals @ Baltimore Orioles</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -8722,17 +8722,17 @@
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Golden State Valkyries</t>
+          <t>Baltimore Orioles</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.578321568627451</v>
+        <v>0.6854057034220533</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>-137</v>
+        <v>-218</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>-104</v>
+        <v>-163</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -8756,7 +8756,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 57.8% (fair -137). Your call.</t>
+          <t>Model 68.5% (fair -218). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -8773,32 +8773,32 @@
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Seattle Mariners @ Cleveland Guardians</t>
+          <t>Las Vegas Aces @ Chicago Sky</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Seattle Mariners</t>
+          <t>Over 178.5</t>
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.54375</v>
+        <v>0.55275</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>-119</v>
+        <v>-124</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -8822,7 +8822,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 54.4% (fair -119). Your call.</t>
+          <t>Model 55.3% (fair -124). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -8839,12 +8839,12 @@
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks @ Tampa Bay Rays</t>
+          <t>Texas Rangers @ Toronto Blue Jays</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -8854,17 +8854,17 @@
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>Over 7.5</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.5958069767441861</v>
+        <v>0.55175</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>-147</v>
+        <v>-123</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>-115</v>
+        <v>100</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -8888,7 +8888,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 59.6% (fair -147). Your call.</t>
+          <t>Model 55.2% (fair -123). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -8924,13 +8924,13 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.5767615384615384</v>
+        <v>0.5778666666666666</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>-136</v>
+        <v>-137</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>-108</v>
+        <v>-110</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 57.7% (fair -136). Your call.</t>
+          <t>Model 57.8% (fair -137). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -8971,32 +8971,32 @@
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>Washington Nationals @ Baltimore Orioles</t>
+          <t>New York Liberty @ Golden State Valkyries</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
         <is>
-          <t>Baltimore Orioles -1.5</t>
+          <t>Over 163.5</t>
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.5273809523809523</v>
+        <v>0.5769238095238095</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>-112</v>
+        <v>-136</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>110</v>
+        <v>-110</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -9020,7 +9020,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 52.7% (fair -112). Your call.</t>
+          <t>Model 57.7% (fair -136). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -9037,32 +9037,32 @@
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Washington Nationals @ Baltimore Orioles</t>
+          <t>Atlanta Braves @ San Francisco Giants</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Baltimore Orioles</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.6854057034220533</v>
+        <v>0.5606823529411765</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>-218</v>
+        <v>-128</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>-163</v>
+        <v>-104</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -9086,7 +9086,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 68.5% (fair -218). Your call.</t>
+          <t>Model 56.1% (fair -128). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -9103,29 +9103,29 @@
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>Las Vegas Aces @ Chicago Sky</t>
+          <t>Seattle Mariners @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Over 178.5</t>
+          <t>Seattle Mariners</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.55275</v>
+        <v>0.54865</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>-124</v>
+        <v>-122</v>
       </c>
       <c r="H20" s="15" t="n">
         <v>100</v>
@@ -9152,7 +9152,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 55.3% (fair -124). Your call.</t>
+          <t>Model 54.9% (fair -122). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -9164,37 +9164,37 @@
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Texas Rangers @ Toronto Blue Jays</t>
+          <t>Washington Nationals @ Baltimore Orioles</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>23:05</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Baltimore Orioles</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.55175</v>
+        <v>0.5517098039215687</v>
       </c>
       <c r="G21" s="14" t="n">
         <v>-123</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>100</v>
+        <v>-104</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -9230,37 +9230,37 @@
     <row r="22">
       <c r="A22" s="20" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>New York Liberty @ Golden State Valkyries</t>
+          <t>Chicago Cubs @ Milwaukee Brewers</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>Over 163.5</t>
+          <t>Milwaukee Brewers</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.5769238095238095</v>
+        <v>0.6313406639004149</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-136</v>
+        <v>-171</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>-110</v>
+        <v>-141</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -9284,7 +9284,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 57.7% (fair -136). Your call.</t>
+          <t>Model 63.1% (fair -171). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -9296,37 +9296,37 @@
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>Atlanta Braves @ San Francisco Giants</t>
+          <t>Seattle Mariners @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Over 7.5</t>
+          <t>Seattle Mariners</t>
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.5636707317073171</v>
+        <v>0.6175531914893617</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>-129</v>
+        <v>-161</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>-105</v>
+        <v>-135</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -9350,7 +9350,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 56.4% (fair -129). Your call.</t>
+          <t>Model 61.8% (fair -161). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -9367,12 +9367,12 @@
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>Washington Nationals @ Baltimore Orioles</t>
+          <t>Arizona Diamondbacks @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>23:05</t>
+          <t>22:10</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -9382,17 +9382,17 @@
       </c>
       <c r="E24" s="20" t="inlineStr">
         <is>
-          <t>Baltimore Orioles</t>
+          <t>Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.5510470588235293</v>
+        <v>0.4763555555555556</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>-123</v>
+        <v>110</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>-104</v>
+        <v>125</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -9416,7 +9416,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 55.1% (fair -123). Your call.</t>
+          <t>Model 47.6% (fair +110). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -9428,37 +9428,37 @@
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks @ Tampa Bay Rays</t>
+          <t>Colorado Rockies @ Minnesota Twins</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>22:10</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks</t>
+          <t>Over 9</t>
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.4752863436123348</v>
+        <v>0.53585</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>110</v>
+        <v>-115</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>127</v>
+        <v>100</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -9482,7 +9482,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 47.5% (fair +110). Your call.</t>
+          <t>Model 53.6% (fair -115). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -9499,12 +9499,12 @@
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>Kansas City Royals @ Chicago White Sox</t>
+          <t>Atlanta Braves @ San Francisco Giants</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -9514,17 +9514,17 @@
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
-          <t>Chicago White Sox -1.5</t>
+          <t>San Francisco Giants +1.5</t>
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.4223529411764706</v>
+        <v>0.6048391304347827</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>137</v>
+        <v>-153</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>155</v>
+        <v>-130</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 42.2% (fair +137). Your call.</t>
+          <t>Model 60.5% (fair -153). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -9565,32 +9565,32 @@
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>New York Yankees @ Boston Red Sox</t>
+          <t>New York Liberty @ Golden State Valkyries</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>23:20</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>Under 9</t>
+          <t>Golden State Valkyries -1.5</t>
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.5172596153846154</v>
+        <v>0.5218536585365855</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>-107</v>
+        <v>-109</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -9614,7 +9614,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 51.7% (fair -107). Your call.</t>
+          <t>Model 52.2% (fair -109). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -9626,37 +9626,37 @@
     <row r="28">
       <c r="A28" s="20" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>Colorado Rockies @ Minnesota Twins</t>
+          <t>Philadelphia Phillies @ New York Mets</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
         <is>
-          <t>Over 9.5</t>
+          <t>Philadelphia Phillies</t>
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.53585</v>
+        <v>0.4857272727272727</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>-115</v>
+        <v>106</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -9680,7 +9680,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 53.6% (fair -115). Your call.</t>
+          <t>Model 48.6% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -9692,17 +9692,17 @@
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>Chicago Cubs @ Milwaukee Brewers</t>
+          <t>Philadelphia Phillies @ New York Mets</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
@@ -9712,17 +9712,17 @@
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers</t>
+          <t>Philadelphia Phillies</t>
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.6324196721311476</v>
+        <v>0.5869189189189189</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>-172</v>
+        <v>-142</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>-144</v>
+        <v>-122</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 63.2% (fair -172). Your call.</t>
+          <t>Model 58.7% (fair -142). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -9923,10 +9923,10 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.4398206278026906</v>
+        <v>0.435695067264574</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="H5" s="15" t="n">
         <v>123</v>
@@ -9953,7 +9953,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 44.0% (fair +127). Your call.</t>
+          <t>Model 43.6% (fair +130). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -9989,10 +9989,10 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.560198678414097</v>
+        <v>0.5642828193832599</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>-127</v>
+        <v>-130</v>
       </c>
       <c r="H6" s="15" t="n">
         <v>-127</v>
@@ -10019,7 +10019,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 56.0% (fair -127). Your call.</t>
+          <t>Model 56.4% (fair -130). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -10055,10 +10055,10 @@
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.5093</v>
+        <v>0.5256</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-104</v>
+        <v>-111</v>
       </c>
       <c r="H7" s="15" t="n">
         <v>125</v>
@@ -10085,7 +10085,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 50.9% (fair -104). Your call.</t>
+          <t>Model 52.6% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -10121,10 +10121,10 @@
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.4907</v>
+        <v>0.4744</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="H8" s="15" t="n">
         <v>100</v>
@@ -10151,7 +10151,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 49.1% (fair +104). Your call.</t>
+          <t>Model 47.4% (fair +111). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -10187,10 +10187,10 @@
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.3830384615384615</v>
+        <v>0.3895</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="H9" s="15" t="n">
         <v>160</v>
@@ -10217,7 +10217,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 38.3% (fair +161). Your call.</t>
+          <t>Model 38.9% (fair +157). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -10253,10 +10253,10 @@
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.6169828897338403</v>
+        <v>0.6105372623574145</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-161</v>
+        <v>-157</v>
       </c>
       <c r="H10" s="15" t="n">
         <v>-163</v>
@@ -10283,7 +10283,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 61.7% (fair -161). Your call.</t>
+          <t>Model 61.1% (fair -157). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -10319,10 +10319,10 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.5287686274509803</v>
+        <v>0.5245882352941176</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>-112</v>
+        <v>-110</v>
       </c>
       <c r="H11" s="15" t="n">
         <v>-104</v>
@@ -10349,7 +10349,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 52.9% (fair -112). Your call.</t>
+          <t>Model 52.5% (fair -110). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -10385,10 +10385,10 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.4712254901960785</v>
+        <v>0.4753921568627451</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="H12" s="15" t="n">
         <v>104</v>
@@ -10415,7 +10415,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 47.1% (fair +112). Your call.</t>
+          <t>Model 47.5% (fair +110). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -10451,10 +10451,10 @@
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.5897</v>
+        <v>0.6208</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>-144</v>
+        <v>-164</v>
       </c>
       <c r="H13" s="15" t="n">
         <v>117</v>
@@ -10481,7 +10481,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 59.0% (fair -144). Your call.</t>
+          <t>Model 62.1% (fair -164). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -10517,10 +10517,10 @@
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.4103</v>
+        <v>0.3792</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>144</v>
+        <v>164</v>
       </c>
       <c r="H14" s="15" t="n">
         <v>111</v>
@@ -10547,7 +10547,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 41.0% (fair +144). Your call.</t>
+          <t>Model 37.9% (fair +164). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -10583,10 +10583,10 @@
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.2759</v>
+        <v>0.2883</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>262</v>
+        <v>247</v>
       </c>
       <c r="H15" s="15" t="n">
         <v>172</v>
@@ -10613,7 +10613,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 27.6% (fair +262). Your call.</t>
+          <t>Model 28.8% (fair +247). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -10649,10 +10649,10 @@
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.7241</v>
+        <v>0.7117</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>-262</v>
+        <v>-247</v>
       </c>
       <c r="H16" s="15" t="n">
         <v>156</v>
@@ -10679,7 +10679,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 72.4% (fair -262). Your call.</t>
+          <t>Model 71.2% (fair -247). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -12167,13 +12167,13 @@
         </is>
       </c>
       <c r="F39" s="13" t="n">
-        <v>0.4752863436123348</v>
+        <v>0.4763555555555556</v>
       </c>
       <c r="G39" s="14" t="n">
         <v>110</v>
       </c>
       <c r="H39" s="15" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="I39" s="13">
         <f>IF($H$39="","",IF($H$39&lt;0,-$H$39/(-$H$39+100),100/($H$39+100)))</f>
@@ -12197,7 +12197,7 @@
       </c>
       <c r="N39" s="19" t="inlineStr">
         <is>
-          <t>Model 47.5% (fair +110). Your call.</t>
+          <t>Model 47.6% (fair +110). Your call.</t>
         </is>
       </c>
       <c r="O39" s="15" t="n"/>
@@ -12233,7 +12233,7 @@
         </is>
       </c>
       <c r="F40" s="13" t="n">
-        <v>0.5247281938325992</v>
+        <v>0.5236651982378855</v>
       </c>
       <c r="G40" s="14" t="n">
         <v>-110</v>
@@ -12263,7 +12263,7 @@
       </c>
       <c r="N40" s="19" t="inlineStr">
         <is>
-          <t>Model 52.5% (fair -110). Your call.</t>
+          <t>Model 52.4% (fair -110). Your call.</t>
         </is>
       </c>
       <c r="O40" s="15" t="n"/>
@@ -12299,13 +12299,13 @@
         </is>
       </c>
       <c r="F41" s="13" t="n">
-        <v>0.5026</v>
+        <v>0.5031270935960591</v>
       </c>
       <c r="G41" s="14" t="n">
         <v>-101</v>
       </c>
       <c r="H41" s="15" t="n">
-        <v>104</v>
+        <v>-103</v>
       </c>
       <c r="I41" s="13">
         <f>IF($H$41="","",IF($H$41&lt;0,-$H$41/(-$H$41+100),100/($H$41+100)))</f>
@@ -12365,13 +12365,13 @@
         </is>
       </c>
       <c r="F42" s="13" t="n">
-        <v>0.4974</v>
+        <v>0.4969</v>
       </c>
       <c r="G42" s="14" t="n">
         <v>101</v>
       </c>
       <c r="H42" s="15" t="n">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="I42" s="13">
         <f>IF($H$42="","",IF($H$42&lt;0,-$H$42/(-$H$42+100),100/($H$42+100)))</f>
@@ -12503,7 +12503,7 @@
         <v>-232</v>
       </c>
       <c r="H44" s="15" t="n">
-        <v>-117</v>
+        <v>-118</v>
       </c>
       <c r="I44" s="13">
         <f>IF($H$44="","",IF($H$44&lt;0,-$H$44/(-$H$44+100),100/($H$44+100)))</f>
@@ -12563,13 +12563,13 @@
         </is>
       </c>
       <c r="F45" s="13" t="n">
-        <v>0.4489108910891089</v>
+        <v>0.4483251231527093</v>
       </c>
       <c r="G45" s="14" t="n">
         <v>123</v>
       </c>
       <c r="H45" s="15" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I45" s="13">
         <f>IF($H$45="","",IF($H$45&lt;0,-$H$45/(-$H$45+100),100/($H$45+100)))</f>
@@ -12593,7 +12593,7 @@
       </c>
       <c r="N45" s="19" t="inlineStr">
         <is>
-          <t>Model 44.9% (fair +123). Your call.</t>
+          <t>Model 44.8% (fair +123). Your call.</t>
         </is>
       </c>
       <c r="O45" s="15" t="n"/>
@@ -12629,7 +12629,7 @@
         </is>
       </c>
       <c r="F46" s="13" t="n">
-        <v>0.5510470588235293</v>
+        <v>0.5517098039215687</v>
       </c>
       <c r="G46" s="14" t="n">
         <v>-123</v>
@@ -12659,7 +12659,7 @@
       </c>
       <c r="N46" s="19" t="inlineStr">
         <is>
-          <t>Model 55.1% (fair -123). Your call.</t>
+          <t>Model 55.2% (fair -123). Your call.</t>
         </is>
       </c>
       <c r="O46" s="15" t="n"/>
@@ -12701,7 +12701,7 @@
         <v>-146</v>
       </c>
       <c r="H47" s="15" t="n">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="I47" s="13">
         <f>IF($H$47="","",IF($H$47&lt;0,-$H$47/(-$H$47+100),100/($H$47+100)))</f>
@@ -12959,13 +12959,13 @@
         </is>
       </c>
       <c r="F51" s="13" t="n">
-        <v>0.6197243697478991</v>
+        <v>0.6175531914893617</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>-163</v>
+        <v>-161</v>
       </c>
       <c r="H51" s="15" t="n">
-        <v>-138</v>
+        <v>-135</v>
       </c>
       <c r="I51" s="13">
         <f>IF($H$51="","",IF($H$51&lt;0,-$H$51/(-$H$51+100),100/($H$51+100)))</f>
@@ -12989,7 +12989,7 @@
       </c>
       <c r="N51" s="19" t="inlineStr">
         <is>
-          <t>Model 62.0% (fair -163). Your call.</t>
+          <t>Model 61.8% (fair -161). Your call.</t>
         </is>
       </c>
       <c r="O51" s="15" t="n"/>
@@ -13025,13 +13025,13 @@
         </is>
       </c>
       <c r="F52" s="13" t="n">
-        <v>0.3802978723404255</v>
+        <v>0.3824463519313305</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="H52" s="15" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I52" s="13">
         <f>IF($H$52="","",IF($H$52&lt;0,-$H$52/(-$H$52+100),100/($H$52+100)))</f>
@@ -13055,7 +13055,7 @@
       </c>
       <c r="N52" s="19" t="inlineStr">
         <is>
-          <t>Model 38.0% (fair +163). Your call.</t>
+          <t>Model 38.2% (fair +161). Your call.</t>
         </is>
       </c>
       <c r="O52" s="15" t="n"/>
@@ -13087,17 +13087,17 @@
       </c>
       <c r="E53" s="12" t="inlineStr">
         <is>
-          <t>Over 7.5</t>
+          <t>Over 8</t>
         </is>
       </c>
       <c r="F53" s="13" t="n">
-        <v>0.5473</v>
+        <v>0.4363</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>-121</v>
+        <v>129</v>
       </c>
       <c r="H53" s="15" t="n">
-        <v>108</v>
+        <v>127</v>
       </c>
       <c r="I53" s="13">
         <f>IF($H$53="","",IF($H$53&lt;0,-$H$53/(-$H$53+100),100/($H$53+100)))</f>
@@ -13121,7 +13121,7 @@
       </c>
       <c r="N53" s="19" t="inlineStr">
         <is>
-          <t>Model 54.7% (fair -121). Your call.</t>
+          <t>Model 43.6% (fair +129). Your call.</t>
         </is>
       </c>
       <c r="O53" s="15" t="n"/>
@@ -13153,17 +13153,17 @@
       </c>
       <c r="E54" s="20" t="inlineStr">
         <is>
-          <t>Under 7.5</t>
+          <t>Under 8</t>
         </is>
       </c>
       <c r="F54" s="13" t="n">
-        <v>0.4527</v>
+        <v>0.5637</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>121</v>
+        <v>-129</v>
       </c>
       <c r="H54" s="15" t="n">
-        <v>119</v>
+        <v>-108</v>
       </c>
       <c r="I54" s="13">
         <f>IF($H$54="","",IF($H$54&lt;0,-$H$54/(-$H$54+100),100/($H$54+100)))</f>
@@ -13187,7 +13187,7 @@
       </c>
       <c r="N54" s="19" t="inlineStr">
         <is>
-          <t>Model 45.3% (fair +121). Your call.</t>
+          <t>Model 56.4% (fair -129). Your call.</t>
         </is>
       </c>
       <c r="O54" s="15" t="n"/>
@@ -13351,10 +13351,10 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>0.3676</v>
+        <v>0.36864</v>
       </c>
       <c r="G57" s="14" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H57" s="15" t="n">
         <v>150</v>
@@ -13381,7 +13381,7 @@
       </c>
       <c r="N57" s="19" t="inlineStr">
         <is>
-          <t>Model 36.8% (fair +172). Your call.</t>
+          <t>Model 36.9% (fair +171). Your call.</t>
         </is>
       </c>
       <c r="O57" s="15" t="n"/>
@@ -13417,13 +13417,13 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>0.6324196721311476</v>
+        <v>0.6313406639004149</v>
       </c>
       <c r="G58" s="14" t="n">
-        <v>-172</v>
+        <v>-171</v>
       </c>
       <c r="H58" s="15" t="n">
-        <v>-144</v>
+        <v>-141</v>
       </c>
       <c r="I58" s="13">
         <f>IF($H$58="","",IF($H$58&lt;0,-$H$58/(-$H$58+100),100/($H$58+100)))</f>
@@ -13447,7 +13447,7 @@
       </c>
       <c r="N58" s="19" t="inlineStr">
         <is>
-          <t>Model 63.2% (fair -172). Your call.</t>
+          <t>Model 63.1% (fair -171). Your call.</t>
         </is>
       </c>
       <c r="O58" s="15" t="n"/>
@@ -13555,7 +13555,7 @@
         <v>167</v>
       </c>
       <c r="H60" s="15" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="I60" s="13">
         <f>IF($H$60="","",IF($H$60&lt;0,-$H$60/(-$H$60+100),100/($H$60+100)))</f>
@@ -13621,7 +13621,7 @@
         <v>106</v>
       </c>
       <c r="H61" s="15" t="n">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I61" s="13">
         <f>IF($H$61="","",IF($H$61&lt;0,-$H$61/(-$H$61+100),100/($H$61+100)))</f>
@@ -13687,7 +13687,7 @@
         <v>-106</v>
       </c>
       <c r="H62" s="15" t="n">
-        <v>-104</v>
+        <v>-102</v>
       </c>
       <c r="I62" s="13">
         <f>IF($H$62="","",IF($H$62&lt;0,-$H$62/(-$H$62+100),100/($H$62+100)))</f>
@@ -14391,13 +14391,13 @@
         </is>
       </c>
       <c r="F73" s="13" t="n">
-        <v>0.5857560975609757</v>
+        <v>0.6837</v>
       </c>
       <c r="G73" s="14" t="n">
-        <v>-141</v>
+        <v>-216</v>
       </c>
       <c r="H73" s="15" t="n">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="I73" s="13">
         <f>IF($H$73="","",IF($H$73&lt;0,-$H$73/(-$H$73+100),100/($H$73+100)))</f>
@@ -14421,7 +14421,7 @@
       </c>
       <c r="N73" s="19" t="inlineStr">
         <is>
-          <t>Model 58.6% (fair -141). Your call.</t>
+          <t>Model 68.4% (fair -216). Your call.</t>
         </is>
       </c>
       <c r="O73" s="15" t="n"/>
@@ -14457,13 +14457,13 @@
         </is>
       </c>
       <c r="F74" s="13" t="n">
-        <v>0.4142634146341463</v>
+        <v>0.3163</v>
       </c>
       <c r="G74" s="14" t="n">
-        <v>141</v>
+        <v>216</v>
       </c>
       <c r="H74" s="15" t="n">
-        <v>-105</v>
+        <v>105</v>
       </c>
       <c r="I74" s="13">
         <f>IF($H$74="","",IF($H$74&lt;0,-$H$74/(-$H$74+100),100/($H$74+100)))</f>
@@ -14487,7 +14487,7 @@
       </c>
       <c r="N74" s="19" t="inlineStr">
         <is>
-          <t>Model 41.4% (fair +141). Your call.</t>
+          <t>Model 31.6% (fair +216). Your call.</t>
         </is>
       </c>
       <c r="O74" s="15" t="n"/>
@@ -14523,13 +14523,13 @@
         </is>
       </c>
       <c r="F75" s="13" t="n">
-        <v>0.5273809523809523</v>
+        <v>0.5262264150943395</v>
       </c>
       <c r="G75" s="14" t="n">
-        <v>-112</v>
+        <v>-111</v>
       </c>
       <c r="H75" s="15" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="I75" s="13">
         <f>IF($H$75="","",IF($H$75&lt;0,-$H$75/(-$H$75+100),100/($H$75+100)))</f>
@@ -14553,7 +14553,7 @@
       </c>
       <c r="N75" s="19" t="inlineStr">
         <is>
-          <t>Model 52.7% (fair -112). Your call.</t>
+          <t>Model 52.6% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O75" s="15" t="n"/>
@@ -14589,10 +14589,10 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>0.4725818181818182</v>
+        <v>0.4737818181818181</v>
       </c>
       <c r="G76" s="14" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H76" s="15" t="n">
         <v>-120</v>
@@ -14619,7 +14619,7 @@
       </c>
       <c r="N76" s="19" t="inlineStr">
         <is>
-          <t>Model 47.3% (fair +112). Your call.</t>
+          <t>Model 47.4% (fair +111). Your call.</t>
         </is>
       </c>
       <c r="O76" s="15" t="n"/>
@@ -14859,7 +14859,7 @@
         <v>139</v>
       </c>
       <c r="H80" s="15" t="n">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="I80" s="13">
         <f>IF($H$80="","",IF($H$80&lt;0,-$H$80/(-$H$80+100),100/($H$80+100)))</f>
@@ -14919,13 +14919,13 @@
         </is>
       </c>
       <c r="F81" s="13" t="n">
-        <v>0.4966544117647059</v>
+        <v>0.5008208955223882</v>
       </c>
       <c r="G81" s="14" t="n">
-        <v>101</v>
+        <v>-100</v>
       </c>
       <c r="H81" s="15" t="n">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="I81" s="13">
         <f>IF($H$81="","",IF($H$81&lt;0,-$H$81/(-$H$81+100),100/($H$81+100)))</f>
@@ -14949,7 +14949,7 @@
       </c>
       <c r="N81" s="19" t="inlineStr">
         <is>
-          <t>Model 49.7% (fair +101). Your call.</t>
+          <t>Model 50.1% (fair -100). Your call.</t>
         </is>
       </c>
       <c r="O81" s="15" t="n"/>
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="F82" s="13" t="n">
-        <v>0.5033571428571428</v>
+        <v>0.4991703703703703</v>
       </c>
       <c r="G82" s="14" t="n">
-        <v>-101</v>
+        <v>100</v>
       </c>
       <c r="H82" s="15" t="n">
-        <v>-180</v>
+        <v>-170</v>
       </c>
       <c r="I82" s="13">
         <f>IF($H$82="","",IF($H$82&lt;0,-$H$82/(-$H$82+100),100/($H$82+100)))</f>
@@ -15015,7 +15015,7 @@
       </c>
       <c r="N82" s="19" t="inlineStr">
         <is>
-          <t>Model 50.3% (fair -101). Your call.</t>
+          <t>Model 49.9% (fair +100). Your call.</t>
         </is>
       </c>
       <c r="O82" s="15" t="n"/>
@@ -15051,10 +15051,10 @@
         </is>
       </c>
       <c r="F83" s="13" t="n">
-        <v>0.4761711711711712</v>
+        <v>0.4748198198198199</v>
       </c>
       <c r="G83" s="14" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H83" s="15" t="n">
         <v>122</v>
@@ -15081,7 +15081,7 @@
       </c>
       <c r="N83" s="19" t="inlineStr">
         <is>
-          <t>Model 47.6% (fair +110). Your call.</t>
+          <t>Model 47.5% (fair +111). Your call.</t>
         </is>
       </c>
       <c r="O83" s="15" t="n"/>
@@ -15117,13 +15117,13 @@
         </is>
       </c>
       <c r="F84" s="13" t="n">
-        <v>0.5238306306306306</v>
+        <v>0.5251666666666667</v>
       </c>
       <c r="G84" s="14" t="n">
-        <v>-110</v>
+        <v>-111</v>
       </c>
       <c r="H84" s="15" t="n">
-        <v>-122</v>
+        <v>-125</v>
       </c>
       <c r="I84" s="13">
         <f>IF($H$84="","",IF($H$84&lt;0,-$H$84/(-$H$84+100),100/($H$84+100)))</f>
@@ -15147,7 +15147,7 @@
       </c>
       <c r="N84" s="19" t="inlineStr">
         <is>
-          <t>Model 52.4% (fair -110). Your call.</t>
+          <t>Model 52.5% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O84" s="15" t="n"/>
@@ -15315,13 +15315,13 @@
         </is>
       </c>
       <c r="F87" s="13" t="n">
-        <v>0.3390441176470589</v>
+        <v>0.3357142857142857</v>
       </c>
       <c r="G87" s="14" t="n">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="H87" s="15" t="n">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="I87" s="13">
         <f>IF($H$87="","",IF($H$87&lt;0,-$H$87/(-$H$87+100),100/($H$87+100)))</f>
@@ -15345,7 +15345,7 @@
       </c>
       <c r="N87" s="19" t="inlineStr">
         <is>
-          <t>Model 33.9% (fair +195). Your call.</t>
+          <t>Model 33.6% (fair +198). Your call.</t>
         </is>
       </c>
       <c r="O87" s="15" t="n"/>
@@ -15381,10 +15381,10 @@
         </is>
       </c>
       <c r="F88" s="13" t="n">
-        <v>0.6609368421052632</v>
+        <v>0.6643122807017544</v>
       </c>
       <c r="G88" s="14" t="n">
-        <v>-195</v>
+        <v>-198</v>
       </c>
       <c r="H88" s="15" t="n">
         <v>-185</v>
@@ -15411,7 +15411,7 @@
       </c>
       <c r="N88" s="19" t="inlineStr">
         <is>
-          <t>Model 66.1% (fair -195). Your call.</t>
+          <t>Model 66.4% (fair -198). Your call.</t>
         </is>
       </c>
       <c r="O88" s="15" t="n"/>
@@ -15447,7 +15447,7 @@
         </is>
       </c>
       <c r="F89" s="13" t="n">
-        <v>0.5276774774774774</v>
+        <v>0.528281981981982</v>
       </c>
       <c r="G89" s="14" t="n">
         <v>-112</v>
@@ -15513,7 +15513,7 @@
         </is>
       </c>
       <c r="F90" s="13" t="n">
-        <v>0.4723502304147465</v>
+        <v>0.471705069124424</v>
       </c>
       <c r="G90" s="14" t="n">
         <v>112</v>
@@ -15579,7 +15579,7 @@
         </is>
       </c>
       <c r="F91" s="13" t="n">
-        <v>0.5746</v>
+        <v>0.5749</v>
       </c>
       <c r="G91" s="14" t="n">
         <v>-135</v>
@@ -15645,7 +15645,7 @@
         </is>
       </c>
       <c r="F92" s="13" t="n">
-        <v>0.4253658536585366</v>
+        <v>0.4250731707317073</v>
       </c>
       <c r="G92" s="14" t="n">
         <v>135</v>
@@ -15711,10 +15711,10 @@
         </is>
       </c>
       <c r="F93" s="13" t="n">
-        <v>0.6312450980392157</v>
+        <v>0.6276588235294118</v>
       </c>
       <c r="G93" s="14" t="n">
-        <v>-171</v>
+        <v>-169</v>
       </c>
       <c r="H93" s="15" t="n">
         <v>-155</v>
@@ -15741,7 +15741,7 @@
       </c>
       <c r="N93" s="19" t="inlineStr">
         <is>
-          <t>Model 63.1% (fair -171). Your call.</t>
+          <t>Model 62.8% (fair -169). Your call.</t>
         </is>
       </c>
       <c r="O93" s="15" t="n"/>
@@ -15777,13 +15777,13 @@
         </is>
       </c>
       <c r="F94" s="13" t="n">
-        <v>0.3687916666666667</v>
+        <v>0.3723529411764706</v>
       </c>
       <c r="G94" s="14" t="n">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H94" s="15" t="n">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I94" s="13">
         <f>IF($H$94="","",IF($H$94&lt;0,-$H$94/(-$H$94+100),100/($H$94+100)))</f>
@@ -15807,7 +15807,7 @@
       </c>
       <c r="N94" s="19" t="inlineStr">
         <is>
-          <t>Model 36.9% (fair +171). Your call.</t>
+          <t>Model 37.2% (fair +169). Your call.</t>
         </is>
       </c>
       <c r="O94" s="15" t="n"/>
@@ -15843,13 +15843,13 @@
         </is>
       </c>
       <c r="F95" s="13" t="n">
-        <v>0.54375</v>
+        <v>0.54865</v>
       </c>
       <c r="G95" s="14" t="n">
-        <v>-119</v>
+        <v>-122</v>
       </c>
       <c r="H95" s="15" t="n">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="I95" s="13">
         <f>IF($H$95="","",IF($H$95&lt;0,-$H$95/(-$H$95+100),100/($H$95+100)))</f>
@@ -15873,7 +15873,7 @@
       </c>
       <c r="N95" s="19" t="inlineStr">
         <is>
-          <t>Model 54.4% (fair -119). Your call.</t>
+          <t>Model 54.9% (fair -122). Your call.</t>
         </is>
       </c>
       <c r="O95" s="15" t="n"/>
@@ -15909,10 +15909,10 @@
         </is>
       </c>
       <c r="F96" s="13" t="n">
-        <v>0.45625</v>
+        <v>0.45135</v>
       </c>
       <c r="G96" s="14" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="H96" s="15" t="n">
         <v>100</v>
@@ -15939,7 +15939,7 @@
       </c>
       <c r="N96" s="19" t="inlineStr">
         <is>
-          <t>Model 45.6% (fair +119). Your call.</t>
+          <t>Model 45.1% (fair +122). Your call.</t>
         </is>
       </c>
       <c r="O96" s="15" t="n"/>
@@ -15975,13 +15975,13 @@
         </is>
       </c>
       <c r="F97" s="13" t="n">
-        <v>0.4867788461538461</v>
+        <v>0.4844607843137255</v>
       </c>
       <c r="G97" s="14" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H97" s="15" t="n">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="I97" s="13">
         <f>IF($H$97="","",IF($H$97&lt;0,-$H$97/(-$H$97+100),100/($H$97+100)))</f>
@@ -16005,7 +16005,7 @@
       </c>
       <c r="N97" s="19" t="inlineStr">
         <is>
-          <t>Model 48.7% (fair +105). Your call.</t>
+          <t>Model 48.4% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O97" s="15" t="n"/>
@@ -16041,13 +16041,13 @@
         </is>
       </c>
       <c r="F98" s="13" t="n">
-        <v>0.51325</v>
+        <v>0.5154923076923077</v>
       </c>
       <c r="G98" s="14" t="n">
-        <v>-105</v>
+        <v>-106</v>
       </c>
       <c r="H98" s="15" t="n">
-        <v>100</v>
+        <v>-108</v>
       </c>
       <c r="I98" s="13">
         <f>IF($H$98="","",IF($H$98&lt;0,-$H$98/(-$H$98+100),100/($H$98+100)))</f>
@@ -16071,7 +16071,7 @@
       </c>
       <c r="N98" s="19" t="inlineStr">
         <is>
-          <t>Model 51.3% (fair -105). Your call.</t>
+          <t>Model 51.5% (fair -106). Your call.</t>
         </is>
       </c>
       <c r="O98" s="15" t="n"/>
@@ -16103,17 +16103,17 @@
       </c>
       <c r="E99" s="12" t="inlineStr">
         <is>
-          <t>Cleveland Guardians +1.5</t>
+          <t>Cleveland Guardians -1.5</t>
         </is>
       </c>
       <c r="F99" s="13" t="n">
-        <v>0.6207610169491526</v>
+        <v>0.2262</v>
       </c>
       <c r="G99" s="14" t="n">
-        <v>-164</v>
+        <v>342</v>
       </c>
       <c r="H99" s="15" t="n">
-        <v>-195</v>
+        <v>165</v>
       </c>
       <c r="I99" s="13">
         <f>IF($H$99="","",IF($H$99&lt;0,-$H$99/(-$H$99+100),100/($H$99+100)))</f>
@@ -16137,7 +16137,7 @@
       </c>
       <c r="N99" s="19" t="inlineStr">
         <is>
-          <t>Model 62.1% (fair -164). Your call.</t>
+          <t>Model 22.6% (fair +342). Your call.</t>
         </is>
       </c>
       <c r="O99" s="15" t="n"/>
@@ -16169,17 +16169,17 @@
       </c>
       <c r="E100" s="20" t="inlineStr">
         <is>
-          <t>Seattle Mariners -1.5</t>
+          <t>Seattle Mariners +1.5</t>
         </is>
       </c>
       <c r="F100" s="13" t="n">
-        <v>0.3792307692307692</v>
+        <v>0.7738</v>
       </c>
       <c r="G100" s="14" t="n">
-        <v>164</v>
+        <v>-342</v>
       </c>
       <c r="H100" s="15" t="n">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="I100" s="13">
         <f>IF($H$100="","",IF($H$100&lt;0,-$H$100/(-$H$100+100),100/($H$100+100)))</f>
@@ -16203,7 +16203,7 @@
       </c>
       <c r="N100" s="19" t="inlineStr">
         <is>
-          <t>Model 37.9% (fair +164). Your call.</t>
+          <t>Model 77.4% (fair -342). Your call.</t>
         </is>
       </c>
       <c r="O100" s="15" t="n"/>
@@ -16503,13 +16503,13 @@
         </is>
       </c>
       <c r="F105" s="13" t="n">
-        <v>0.4248230088495575</v>
+        <v>0.4281363636363636</v>
       </c>
       <c r="G105" s="14" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H105" s="15" t="n">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="I105" s="13">
         <f>IF($H$105="","",IF($H$105&lt;0,-$H$105/(-$H$105+100),100/($H$105+100)))</f>
@@ -16533,7 +16533,7 @@
       </c>
       <c r="N105" s="19" t="inlineStr">
         <is>
-          <t>Model 42.5% (fair +135). Your call.</t>
+          <t>Model 42.8% (fair +134). Your call.</t>
         </is>
       </c>
       <c r="O105" s="15" t="n"/>
@@ -16569,10 +16569,10 @@
         </is>
       </c>
       <c r="F106" s="13" t="n">
-        <v>0.5751652173913044</v>
+        <v>0.5718304347826088</v>
       </c>
       <c r="G106" s="14" t="n">
-        <v>-135</v>
+        <v>-134</v>
       </c>
       <c r="H106" s="15" t="n">
         <v>-130</v>
@@ -16599,7 +16599,7 @@
       </c>
       <c r="N106" s="19" t="inlineStr">
         <is>
-          <t>Model 57.5% (fair -135). Your call.</t>
+          <t>Model 57.2% (fair -134). Your call.</t>
         </is>
       </c>
       <c r="O106" s="15" t="n"/>
@@ -16635,13 +16635,13 @@
         </is>
       </c>
       <c r="F107" s="13" t="n">
-        <v>0.5891233480176211</v>
+        <v>0.5869189189189189</v>
       </c>
       <c r="G107" s="14" t="n">
-        <v>-143</v>
+        <v>-142</v>
       </c>
       <c r="H107" s="15" t="n">
-        <v>-127</v>
+        <v>-122</v>
       </c>
       <c r="I107" s="13">
         <f>IF($H$107="","",IF($H$107&lt;0,-$H$107/(-$H$107+100),100/($H$107+100)))</f>
@@ -16665,7 +16665,7 @@
       </c>
       <c r="N107" s="19" t="inlineStr">
         <is>
-          <t>Model 58.9% (fair -143). Your call.</t>
+          <t>Model 58.7% (fair -142). Your call.</t>
         </is>
       </c>
       <c r="O107" s="15" t="n"/>
@@ -16701,10 +16701,10 @@
         </is>
       </c>
       <c r="F108" s="13" t="n">
-        <v>0.4108810572687224</v>
+        <v>0.4130837004405286</v>
       </c>
       <c r="G108" s="14" t="n">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H108" s="15" t="n">
         <v>127</v>
@@ -16731,7 +16731,7 @@
       </c>
       <c r="N108" s="19" t="inlineStr">
         <is>
-          <t>Model 41.1% (fair +143). Your call.</t>
+          <t>Model 41.3% (fair +142). Your call.</t>
         </is>
       </c>
       <c r="O108" s="15" t="n"/>
@@ -16767,10 +16767,10 @@
         </is>
       </c>
       <c r="F109" s="13" t="n">
-        <v>0.4225210084033614</v>
+        <v>0.4236554621848739</v>
       </c>
       <c r="G109" s="14" t="n">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H109" s="15" t="n">
         <v>138</v>
@@ -16797,7 +16797,7 @@
       </c>
       <c r="N109" s="19" t="inlineStr">
         <is>
-          <t>Model 42.3% (fair +137). Your call.</t>
+          <t>Model 42.4% (fair +136). Your call.</t>
         </is>
       </c>
       <c r="O109" s="15" t="n"/>
@@ -16833,13 +16833,13 @@
         </is>
       </c>
       <c r="F110" s="13" t="n">
-        <v>0.5774546218487394</v>
+        <v>0.5763063829787235</v>
       </c>
       <c r="G110" s="14" t="n">
-        <v>-137</v>
+        <v>-136</v>
       </c>
       <c r="H110" s="15" t="n">
-        <v>-138</v>
+        <v>-135</v>
       </c>
       <c r="I110" s="13">
         <f>IF($H$110="","",IF($H$110&lt;0,-$H$110/(-$H$110+100),100/($H$110+100)))</f>
@@ -16863,7 +16863,7 @@
       </c>
       <c r="N110" s="19" t="inlineStr">
         <is>
-          <t>Model 57.7% (fair -137). Your call.</t>
+          <t>Model 57.6% (fair -136). Your call.</t>
         </is>
       </c>
       <c r="O110" s="15" t="n"/>
@@ -16895,7 +16895,7 @@
       </c>
       <c r="E111" s="12" t="inlineStr">
         <is>
-          <t>Over 9.5</t>
+          <t>Over 9</t>
         </is>
       </c>
       <c r="F111" s="13" t="n">
@@ -16961,7 +16961,7 @@
       </c>
       <c r="E112" s="20" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Under 9</t>
         </is>
       </c>
       <c r="F112" s="13" t="n">
@@ -17295,10 +17295,10 @@
         </is>
       </c>
       <c r="F117" s="13" t="n">
-        <v>0.5866682926829269</v>
+        <v>0.6575</v>
       </c>
       <c r="G117" s="14" t="n">
-        <v>-142</v>
+        <v>-192</v>
       </c>
       <c r="H117" s="15" t="n">
         <v>-105</v>
@@ -17325,7 +17325,7 @@
       </c>
       <c r="N117" s="19" t="inlineStr">
         <is>
-          <t>Model 58.7% (fair -142). Your call.</t>
+          <t>Model 65.8% (fair -192). Your call.</t>
         </is>
       </c>
       <c r="O117" s="15" t="n"/>
@@ -17361,13 +17361,13 @@
         </is>
       </c>
       <c r="F118" s="13" t="n">
-        <v>0.4133173076923077</v>
+        <v>0.3425</v>
       </c>
       <c r="G118" s="14" t="n">
-        <v>142</v>
+        <v>192</v>
       </c>
       <c r="H118" s="15" t="n">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="I118" s="13">
         <f>IF($H$118="","",IF($H$118&lt;0,-$H$118/(-$H$118+100),100/($H$118+100)))</f>
@@ -17391,7 +17391,7 @@
       </c>
       <c r="N118" s="19" t="inlineStr">
         <is>
-          <t>Model 41.3% (fair +142). Your call.</t>
+          <t>Model 34.2% (fair +192). Your call.</t>
         </is>
       </c>
       <c r="O118" s="15" t="n"/>
@@ -17427,13 +17427,13 @@
         </is>
       </c>
       <c r="F119" s="13" t="n">
-        <v>0.4223529411764706</v>
+        <v>0.4246800000000001</v>
       </c>
       <c r="G119" s="14" t="n">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="H119" s="15" t="n">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="I119" s="13">
         <f>IF($H$119="","",IF($H$119&lt;0,-$H$119/(-$H$119+100),100/($H$119+100)))</f>
@@ -17457,7 +17457,7 @@
       </c>
       <c r="N119" s="19" t="inlineStr">
         <is>
-          <t>Model 42.2% (fair +137). Your call.</t>
+          <t>Model 42.5% (fair +135). Your call.</t>
         </is>
       </c>
       <c r="O119" s="15" t="n"/>
@@ -17493,10 +17493,10 @@
         </is>
       </c>
       <c r="F120" s="13" t="n">
-        <v>0.5776222222222221</v>
+        <v>0.5752925925925925</v>
       </c>
       <c r="G120" s="14" t="n">
-        <v>-137</v>
+        <v>-135</v>
       </c>
       <c r="H120" s="15" t="n">
         <v>-170</v>
@@ -17523,7 +17523,7 @@
       </c>
       <c r="N120" s="19" t="inlineStr">
         <is>
-          <t>Model 57.8% (fair -137). Your call.</t>
+          <t>Model 57.5% (fair -135). Your call.</t>
         </is>
       </c>
       <c r="O120" s="15" t="n"/>
@@ -18075,13 +18075,13 @@
         </is>
       </c>
       <c r="F129" s="13" t="n">
-        <v>0.5636707317073171</v>
+        <v>0.5606823529411765</v>
       </c>
       <c r="G129" s="14" t="n">
-        <v>-129</v>
+        <v>-128</v>
       </c>
       <c r="H129" s="15" t="n">
-        <v>-105</v>
+        <v>-104</v>
       </c>
       <c r="I129" s="13">
         <f>IF($H$129="","",IF($H$129&lt;0,-$H$129/(-$H$129+100),100/($H$129+100)))</f>
@@ -18105,7 +18105,7 @@
       </c>
       <c r="N129" s="19" t="inlineStr">
         <is>
-          <t>Model 56.4% (fair -129). Your call.</t>
+          <t>Model 56.1% (fair -128). Your call.</t>
         </is>
       </c>
       <c r="O129" s="15" t="n"/>
@@ -18141,13 +18141,13 @@
         </is>
       </c>
       <c r="F130" s="13" t="n">
-        <v>0.4362980769230769</v>
+        <v>0.4393137254901961</v>
       </c>
       <c r="G130" s="14" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H130" s="15" t="n">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="I130" s="13">
         <f>IF($H$130="","",IF($H$130&lt;0,-$H$130/(-$H$130+100),100/($H$130+100)))</f>
@@ -18171,7 +18171,7 @@
       </c>
       <c r="N130" s="19" t="inlineStr">
         <is>
-          <t>Model 43.6% (fair +129). Your call.</t>
+          <t>Model 43.9% (fair +128). Your call.</t>
         </is>
       </c>
       <c r="O130" s="15" t="n"/>
@@ -18207,10 +18207,10 @@
         </is>
       </c>
       <c r="F131" s="13" t="n">
-        <v>0.6019565217391304</v>
+        <v>0.6048391304347827</v>
       </c>
       <c r="G131" s="14" t="n">
-        <v>-151</v>
+        <v>-153</v>
       </c>
       <c r="H131" s="15" t="n">
         <v>-130</v>
@@ -18237,7 +18237,7 @@
       </c>
       <c r="N131" s="19" t="inlineStr">
         <is>
-          <t>Model 60.2% (fair -151). Your call.</t>
+          <t>Model 60.5% (fair -153). Your call.</t>
         </is>
       </c>
       <c r="O131" s="15" t="n"/>
@@ -18273,13 +18273,13 @@
         </is>
       </c>
       <c r="F132" s="13" t="n">
-        <v>0.3980188679245283</v>
+        <v>0.3951612903225807</v>
       </c>
       <c r="G132" s="14" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="H132" s="15" t="n">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="I132" s="13">
         <f>IF($H$132="","",IF($H$132&lt;0,-$H$132/(-$H$132+100),100/($H$132+100)))</f>
@@ -18303,7 +18303,7 @@
       </c>
       <c r="N132" s="19" t="inlineStr">
         <is>
-          <t>Model 39.8% (fair +151). Your call.</t>
+          <t>Model 39.5% (fair +153). Your call.</t>
         </is>
       </c>
       <c r="O132" s="15" t="n"/>
@@ -18599,13 +18599,13 @@
         </is>
       </c>
       <c r="F137" s="13" t="n">
-        <v>0.6081249999999999</v>
+        <v>0.6065484978540773</v>
       </c>
       <c r="G137" s="14" t="n">
-        <v>-155</v>
+        <v>-154</v>
       </c>
       <c r="H137" s="15" t="n">
-        <v>-140</v>
+        <v>-133</v>
       </c>
       <c r="I137" s="13">
         <f>IF($H$137="","",IF($H$137&lt;0,-$H$137/(-$H$137+100),100/($H$137+100)))</f>
@@ -18629,7 +18629,7 @@
       </c>
       <c r="N137" s="19" t="inlineStr">
         <is>
-          <t>Model 60.8% (fair -155). Your call.</t>
+          <t>Model 60.7% (fair -154). Your call.</t>
         </is>
       </c>
       <c r="O137" s="15" t="n"/>
@@ -18665,13 +18665,13 @@
         </is>
       </c>
       <c r="F138" s="13" t="n">
-        <v>0.3918636363636363</v>
+        <v>0.3934234234234235</v>
       </c>
       <c r="G138" s="14" t="n">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H138" s="15" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="I138" s="13">
         <f>IF($H$138="","",IF($H$138&lt;0,-$H$138/(-$H$138+100),100/($H$138+100)))</f>
@@ -18695,7 +18695,7 @@
       </c>
       <c r="N138" s="19" t="inlineStr">
         <is>
-          <t>Model 39.2% (fair +155). Your call.</t>
+          <t>Model 39.3% (fair +154). Your call.</t>
         </is>
       </c>
       <c r="O138" s="15" t="n"/>
@@ -18731,10 +18731,10 @@
         </is>
       </c>
       <c r="F139" s="13" t="n">
-        <v>0.5442</v>
+        <v>0.5396</v>
       </c>
       <c r="G139" s="14" t="n">
-        <v>-119</v>
+        <v>-117</v>
       </c>
       <c r="H139" s="15" t="n"/>
       <c r="I139" s="13">
@@ -18759,7 +18759,7 @@
       </c>
       <c r="N139" s="19" t="inlineStr">
         <is>
-          <t>Model 54.4% (fair -119). Your call.</t>
+          <t>Model 54.0% (fair -117). Your call.</t>
         </is>
       </c>
       <c r="O139" s="15" t="n"/>
@@ -18795,10 +18795,10 @@
         </is>
       </c>
       <c r="F140" s="13" t="n">
-        <v>0.4558013215859031</v>
+        <v>0.460388986784141</v>
       </c>
       <c r="G140" s="14" t="n">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="H140" s="15" t="n">
         <v>-127</v>
@@ -18825,7 +18825,7 @@
       </c>
       <c r="N140" s="19" t="inlineStr">
         <is>
-          <t>Model 45.6% (fair +119). Your call.</t>
+          <t>Model 46.0% (fair +117). Your call.</t>
         </is>
       </c>
       <c r="O140" s="15" t="n"/>
@@ -18861,10 +18861,10 @@
         </is>
       </c>
       <c r="F141" s="13" t="n">
-        <v>0.4827439024390244</v>
+        <v>0.4466</v>
       </c>
       <c r="G141" s="14" t="n">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="H141" s="15" t="n">
         <v>-105</v>
@@ -18891,7 +18891,7 @@
       </c>
       <c r="N141" s="19" t="inlineStr">
         <is>
-          <t>Model 48.3% (fair +107). Your call.</t>
+          <t>Model 44.7% (fair +124). Your call.</t>
         </is>
       </c>
       <c r="O141" s="15" t="n"/>
@@ -18927,13 +18927,13 @@
         </is>
       </c>
       <c r="F142" s="13" t="n">
-        <v>0.5172596153846154</v>
+        <v>0.5534</v>
       </c>
       <c r="G142" s="14" t="n">
-        <v>-107</v>
+        <v>-124</v>
       </c>
       <c r="H142" s="15" t="n">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="I142" s="13">
         <f>IF($H$142="","",IF($H$142&lt;0,-$H$142/(-$H$142+100),100/($H$142+100)))</f>
@@ -18957,7 +18957,7 @@
       </c>
       <c r="N142" s="19" t="inlineStr">
         <is>
-          <t>Model 51.7% (fair -107). Your call.</t>
+          <t>Model 55.3% (fair -124). Your call.</t>
         </is>
       </c>
       <c r="O142" s="15" t="n"/>
@@ -18993,13 +18993,13 @@
         </is>
       </c>
       <c r="F143" s="13" t="n">
-        <v>0.2867058823529413</v>
+        <v>0.2826</v>
       </c>
       <c r="G143" s="14" t="n">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="H143" s="15" t="n">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="I143" s="13">
         <f>IF($H$143="","",IF($H$143&lt;0,-$H$143/(-$H$143+100),100/($H$143+100)))</f>
@@ -19023,7 +19023,7 @@
       </c>
       <c r="N143" s="19" t="inlineStr">
         <is>
-          <t>Model 28.7% (fair +249). Your call.</t>
+          <t>Model 28.3% (fair +254). Your call.</t>
         </is>
       </c>
       <c r="O143" s="15" t="n"/>
@@ -19059,10 +19059,10 @@
         </is>
       </c>
       <c r="F144" s="13" t="n">
-        <v>0.7133</v>
+        <v>0.7174</v>
       </c>
       <c r="G144" s="14" t="n">
-        <v>-249</v>
+        <v>-254</v>
       </c>
       <c r="H144" s="15" t="n"/>
       <c r="I144" s="13">
@@ -19087,7 +19087,7 @@
       </c>
       <c r="N144" s="19" t="inlineStr">
         <is>
-          <t>Model 71.3% (fair -249). Your call.</t>
+          <t>Model 71.7% (fair -254). Your call.</t>
         </is>
       </c>
       <c r="O144" s="15" t="n"/>
@@ -19264,7 +19264,7 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.2905507246376811</v>
+        <v>0.2906666666666666</v>
       </c>
       <c r="G5" s="14" t="n">
         <v>244</v>
@@ -19330,13 +19330,13 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.7094504273504273</v>
+        <v>0.7092857142857143</v>
       </c>
       <c r="G6" s="14" t="n">
         <v>-244</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>-251</v>
+        <v>-250</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -19392,14 +19392,14 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Over 179.5</t>
+          <t>Over 181.5</t>
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.715</v>
+        <v>0.6680980392156862</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-251</v>
+        <v>-201</v>
       </c>
       <c r="H7" s="15" t="n">
         <v>-104</v>
@@ -19426,7 +19426,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 71.5% (fair -251). Your call.</t>
+          <t>Model 66.8% (fair -201). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -19458,14 +19458,14 @@
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>Under 179.5</t>
+          <t>Under 181.5</t>
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.285</v>
+        <v>0.3319</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>251</v>
+        <v>201</v>
       </c>
       <c r="H8" s="15" t="n">
         <v>-104</v>
@@ -19492,7 +19492,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 28.5% (fair +251). Your call.</t>
+          <t>Model 33.2% (fair +201). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -19524,14 +19524,14 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Indiana Fever -6.5</t>
+          <t>Indiana Fever -7.5</t>
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.513</v>
+        <v>0.4974749999999999</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>-105</v>
+        <v>101</v>
       </c>
       <c r="H9" s="15" t="n">
         <v>-108</v>
@@ -19558,7 +19558,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 51.3% (fair -105). Your call.</t>
+          <t>Model 49.7% (fair +101). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -19590,17 +19590,17 @@
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Sparks +6.5</t>
+          <t>Los Angeles Sparks +7.5</t>
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.4869756097560976</v>
+        <v>0.5024999999999999</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>105</v>
+        <v>-101</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -19624,7 +19624,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 48.7% (fair +105). Your call.</t>
+          <t>Model 50.2% (fair -101). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -19660,13 +19660,13 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.7612197530864198</v>
+        <v>0.7708850574712643</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>-319</v>
+        <v>-336</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>-305</v>
+        <v>-335</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -19690,7 +19690,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 76.1% (fair -319). Your call.</t>
+          <t>Model 77.1% (fair -336). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -19726,13 +19726,13 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.238825</v>
+        <v>0.2291494252873564</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>319</v>
+        <v>336</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>300</v>
+        <v>335</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -19756,7 +19756,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 23.9% (fair +319). Your call.</t>
+          <t>Model 22.9% (fair +336). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -19930,7 +19930,7 @@
         <v>439</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>410</v>
+        <v>430</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -19996,7 +19996,7 @@
         <v>-439</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -20056,10 +20056,10 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.6274734375000001</v>
+        <v>0.6261328125000001</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>-168</v>
+        <v>-167</v>
       </c>
       <c r="H17" s="15" t="n">
         <v>-156</v>
@@ -20086,7 +20086,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 62.7% (fair -168). Your call.</t>
+          <t>Model 62.6% (fair -167). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -20122,13 +20122,13 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.3725095057034221</v>
+        <v>0.3738846153846154</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -20152,7 +20152,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 37.3% (fair +168). Your call.</t>
+          <t>Model 37.4% (fair +167). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -20320,13 +20320,13 @@
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.5042</v>
+        <v>0.5099926829268293</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>-102</v>
+        <v>-104</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>113</v>
+        <v>-105</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -20350,7 +20350,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 50.4% (fair -102). Your call.</t>
+          <t>Model 51.0% (fair -104). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -20386,10 +20386,10 @@
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.4958</v>
+        <v>0.49</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H22" s="15" t="n">
         <v>108</v>
@@ -20416,7 +20416,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 49.6% (fair +102). Your call.</t>
+          <t>Model 49.0% (fair +104). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -20452,10 +20452,10 @@
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.3029129129129129</v>
+        <v>0.3044444444444445</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H23" s="15" t="n">
         <v>233</v>
@@ -20482,7 +20482,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 30.3% (fair +230). Your call.</t>
+          <t>Model 30.4% (fair +228). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -20518,13 +20518,13 @@
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.6970782608695653</v>
+        <v>0.6955714714714715</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>-230</v>
+        <v>-228</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>-245</v>
+        <v>-233</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -20548,7 +20548,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 69.7% (fair -230). Your call.</t>
+          <t>Model 69.6% (fair -228). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -20848,10 +20848,10 @@
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.7520298701298702</v>
+        <v>0.7484025974025973</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>-303</v>
+        <v>-297</v>
       </c>
       <c r="H29" s="15" t="n">
         <v>-285</v>
@@ -20878,7 +20878,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 75.2% (fair -303). Your call.</t>
+          <t>Model 74.8% (fair -297). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -20914,13 +20914,13 @@
         </is>
       </c>
       <c r="F30" s="13" t="n">
-        <v>0.247975</v>
+        <v>0.2516103896103896</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="H30" s="15" t="n">
-        <v>300</v>
+        <v>285</v>
       </c>
       <c r="I30" s="13">
         <f>IF($H$30="","",IF($H$30&lt;0,-$H$30/(-$H$30+100),100/($H$30+100)))</f>
@@ -20944,7 +20944,7 @@
       </c>
       <c r="N30" s="19" t="inlineStr">
         <is>
-          <t>Model 24.8% (fair +303). Your call.</t>
+          <t>Model 25.2% (fair +297). Your call.</t>
         </is>
       </c>
       <c r="O30" s="15" t="n"/>
@@ -21112,13 +21112,13 @@
         </is>
       </c>
       <c r="F33" s="13" t="n">
-        <v>0.5767615384615384</v>
+        <v>0.5778666666666666</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>-136</v>
+        <v>-137</v>
       </c>
       <c r="H33" s="15" t="n">
-        <v>-108</v>
+        <v>-110</v>
       </c>
       <c r="I33" s="13">
         <f>IF($H$33="","",IF($H$33&lt;0,-$H$33/(-$H$33+100),100/($H$33+100)))</f>
@@ -21142,7 +21142,7 @@
       </c>
       <c r="N33" s="19" t="inlineStr">
         <is>
-          <t>Model 57.7% (fair -136). Your call.</t>
+          <t>Model 57.8% (fair -137). Your call.</t>
         </is>
       </c>
       <c r="O33" s="15" t="n"/>
@@ -21178,10 +21178,10 @@
         </is>
       </c>
       <c r="F34" s="13" t="n">
-        <v>0.4232380952380952</v>
+        <v>0.4221380952380953</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H34" s="15" t="n">
         <v>-110</v>
@@ -21208,7 +21208,7 @@
       </c>
       <c r="N34" s="19" t="inlineStr">
         <is>
-          <t>Model 42.3% (fair +136). Your call.</t>
+          <t>Model 42.2% (fair +137). Your call.</t>
         </is>
       </c>
       <c r="O34" s="15" t="n"/>
@@ -21504,17 +21504,17 @@
       </c>
       <c r="E39" s="12" t="inlineStr">
         <is>
-          <t>Golden State Valkyries +1.5</t>
+          <t>Golden State Valkyries -1.5</t>
         </is>
       </c>
       <c r="F39" s="13" t="n">
-        <v>0.5795450980392156</v>
+        <v>0.5218536585365855</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>-138</v>
+        <v>-109</v>
       </c>
       <c r="H39" s="15" t="n">
-        <v>-104</v>
+        <v>105</v>
       </c>
       <c r="I39" s="13">
         <f>IF($H$39="","",IF($H$39&lt;0,-$H$39/(-$H$39+100),100/($H$39+100)))</f>
@@ -21538,7 +21538,7 @@
       </c>
       <c r="N39" s="19" t="inlineStr">
         <is>
-          <t>Model 58.0% (fair -138). Your call.</t>
+          <t>Model 52.2% (fair -109). Your call.</t>
         </is>
       </c>
       <c r="O39" s="15" t="n"/>
@@ -21570,17 +21570,17 @@
       </c>
       <c r="E40" s="20" t="inlineStr">
         <is>
-          <t>New York Liberty -1.5</t>
+          <t>New York Liberty +1.5</t>
         </is>
       </c>
       <c r="F40" s="13" t="n">
-        <v>0.4204878048780488</v>
+        <v>0.4781188118811881</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>138</v>
+        <v>109</v>
       </c>
       <c r="H40" s="15" t="n">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="I40" s="13">
         <f>IF($H$40="","",IF($H$40&lt;0,-$H$40/(-$H$40+100),100/($H$40+100)))</f>
@@ -21604,7 +21604,7 @@
       </c>
       <c r="N40" s="19" t="inlineStr">
         <is>
-          <t>Model 42.0% (fair +138). Your call.</t>
+          <t>Model 47.8% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O40" s="15" t="n"/>

--- a/data/output/workbook/2026-06-27.xlsx
+++ b/data/output/workbook/2026-06-27.xlsx
@@ -461,7 +461,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="9467850"/>
+    <ext cx="10125075" cy="9086850"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -551,7 +551,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="9477375"/>
+    <ext cx="10125075" cy="9896475"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -954,7 +954,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-06-27 18:07</t>
+          <t>2026-06-27 20:01</t>
         </is>
       </c>
     </row>
@@ -2006,7 +2006,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q75"/>
+  <dimension ref="A1:Q73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2023,811 +2023,811 @@
         </is>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" s="29" t="inlineStr">
+        <is>
+          <t>Cincinnati Reds offense vs Pittsburgh Pirates defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B60" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C60" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D60" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E60" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F60" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G60" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H60" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I60" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J60" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K60" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L60" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M60" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N60" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O60" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P60" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q60" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
     <row r="61">
-      <c r="A61" s="29" t="inlineStr">
-        <is>
-          <t>Cincinnati Reds offense vs Pittsburgh Pirates defense</t>
+      <c r="A61" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B61" s="32" t="n">
+        <v>4.453</v>
+      </c>
+      <c r="C61" s="32" t="n">
+        <v>4.267</v>
+      </c>
+      <c r="D61" s="32" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="E61" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="F61" s="32" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G61" s="32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H61" s="33" t="inlineStr">
+        <is>
+          <t>9th</t>
+        </is>
+      </c>
+      <c r="I61" s="32" t="inlineStr"/>
+      <c r="J61" s="33" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="K61" s="32" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="L61" s="32" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="M61" s="32" t="n">
+        <v>3.067</v>
+      </c>
+      <c r="N61" s="32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O61" s="32" t="n">
+        <v>3.367</v>
+      </c>
+      <c r="P61" s="32" t="n">
+        <v>3.964</v>
+      </c>
+      <c r="Q61" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B62" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C62" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D62" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E62" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F62" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G62" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H62" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I62" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J62" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K62" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L62" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M62" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N62" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O62" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P62" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q62" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A62" s="31" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B62" s="32" t="n">
+        <v>8.452999999999999</v>
+      </c>
+      <c r="C62" s="32" t="n">
+        <v>7.967</v>
+      </c>
+      <c r="D62" s="32" t="n">
+        <v>7.35</v>
+      </c>
+      <c r="E62" s="32" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="F62" s="32" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="G62" s="32" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="H62" s="34" t="inlineStr">
+        <is>
+          <t>15th</t>
+        </is>
+      </c>
+      <c r="I62" s="32" t="inlineStr"/>
+      <c r="J62" s="34" t="inlineStr">
+        <is>
+          <t>14th</t>
+        </is>
+      </c>
+      <c r="K62" s="32" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="L62" s="32" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M62" s="32" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="N62" s="32" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="O62" s="32" t="n">
+        <v>7.467</v>
+      </c>
+      <c r="P62" s="32" t="n">
+        <v>7.765</v>
+      </c>
+      <c r="Q62" s="35" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B63" s="32" t="n">
-        <v>4.453</v>
+        <v>1.07</v>
       </c>
       <c r="C63" s="32" t="n">
-        <v>4.267</v>
+        <v>1.233</v>
       </c>
       <c r="D63" s="32" t="n">
-        <v>3.75</v>
+        <v>1.2</v>
       </c>
       <c r="E63" s="32" t="n">
-        <v>4</v>
+        <v>1.067</v>
       </c>
       <c r="F63" s="32" t="n">
-        <v>3.5</v>
+        <v>0.9</v>
       </c>
       <c r="G63" s="32" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H63" s="33" t="inlineStr">
-        <is>
-          <t>9th</t>
+        <v>0.6</v>
+      </c>
+      <c r="H63" s="36" t="inlineStr">
+        <is>
+          <t>28th</t>
         </is>
       </c>
       <c r="I63" s="32" t="inlineStr"/>
-      <c r="J63" s="33" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="K63" s="32" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="L63" s="32" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="M63" s="32" t="n">
-        <v>3.067</v>
-      </c>
-      <c r="N63" s="32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="O63" s="32" t="n">
-        <v>3.367</v>
-      </c>
-      <c r="P63" s="32" t="n">
-        <v>3.964</v>
+      <c r="J63" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K63" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L63" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M63" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N63" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O63" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P63" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Q63" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B64" s="32" t="n">
-        <v>8.452999999999999</v>
+        <v>9.081</v>
       </c>
       <c r="C64" s="32" t="n">
-        <v>7.967</v>
+        <v>9.167</v>
       </c>
       <c r="D64" s="32" t="n">
-        <v>7.35</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="E64" s="32" t="n">
-        <v>7.6</v>
+        <v>9.667</v>
       </c>
       <c r="F64" s="32" t="n">
-        <v>7.6</v>
+        <v>10.1</v>
       </c>
       <c r="G64" s="32" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="H64" s="34" t="inlineStr">
-        <is>
-          <t>15th</t>
+        <v>11</v>
+      </c>
+      <c r="H64" s="36" t="inlineStr">
+        <is>
+          <t>24th</t>
         </is>
       </c>
       <c r="I64" s="32" t="inlineStr"/>
-      <c r="J64" s="34" t="inlineStr">
-        <is>
-          <t>14th</t>
+      <c r="J64" s="33" t="inlineStr">
+        <is>
+          <t>10th</t>
         </is>
       </c>
       <c r="K64" s="32" t="n">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="L64" s="32" t="n">
-        <v>6.7</v>
+        <v>9.5</v>
       </c>
       <c r="M64" s="32" t="n">
-        <v>7.2</v>
+        <v>9.4</v>
       </c>
       <c r="N64" s="32" t="n">
-        <v>7.5</v>
+        <v>9.5</v>
       </c>
       <c r="O64" s="32" t="n">
-        <v>7.467</v>
+        <v>9.333</v>
       </c>
       <c r="P64" s="32" t="n">
-        <v>7.765</v>
+        <v>8.114000000000001</v>
       </c>
       <c r="Q64" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B65" s="32" t="n">
-        <v>1.07</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="C65" s="32" t="n">
-        <v>1.233</v>
+        <v>0.333</v>
       </c>
       <c r="D65" s="32" t="n">
-        <v>1.2</v>
+        <v>0.25</v>
       </c>
       <c r="E65" s="32" t="n">
-        <v>1.067</v>
+        <v>0.2</v>
       </c>
       <c r="F65" s="32" t="n">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
       <c r="G65" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H65" s="34" t="inlineStr">
+        <is>
+          <t>17th</t>
+        </is>
+      </c>
+      <c r="I65" s="32" t="inlineStr"/>
+      <c r="J65" s="34" t="inlineStr">
+        <is>
+          <t>19th</t>
+        </is>
+      </c>
+      <c r="K65" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="H65" s="36" t="inlineStr">
-        <is>
-          <t>28th</t>
-        </is>
-      </c>
-      <c r="I65" s="32" t="inlineStr"/>
-      <c r="J65" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K65" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L65" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M65" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N65" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O65" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P65" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="L65" s="32" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M65" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N65" s="32" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="O65" s="32" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="P65" s="32" t="n">
+        <v>0.422</v>
       </c>
       <c r="Q65" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="31" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B66" s="32" t="n">
-        <v>9.081</v>
-      </c>
-      <c r="C66" s="32" t="n">
-        <v>9.167</v>
-      </c>
-      <c r="D66" s="32" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="E66" s="32" t="n">
-        <v>9.667</v>
-      </c>
-      <c r="F66" s="32" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="G66" s="32" t="n">
-        <v>11</v>
-      </c>
-      <c r="H66" s="36" t="inlineStr">
-        <is>
-          <t>24th</t>
-        </is>
-      </c>
-      <c r="I66" s="32" t="inlineStr"/>
-      <c r="J66" s="33" t="inlineStr">
-        <is>
-          <t>10th</t>
-        </is>
-      </c>
-      <c r="K66" s="32" t="n">
-        <v>10</v>
-      </c>
-      <c r="L66" s="32" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="M66" s="32" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="N66" s="32" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="O66" s="32" t="n">
-        <v>9.333</v>
-      </c>
-      <c r="P66" s="32" t="n">
-        <v>8.114000000000001</v>
-      </c>
-      <c r="Q66" s="35" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B67" s="32" t="n">
-        <v>0.5639999999999999</v>
-      </c>
-      <c r="C67" s="32" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="D67" s="32" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E67" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F67" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G67" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H67" s="34" t="inlineStr">
-        <is>
-          <t>17th</t>
-        </is>
-      </c>
-      <c r="I67" s="32" t="inlineStr"/>
-      <c r="J67" s="34" t="inlineStr">
-        <is>
-          <t>19th</t>
-        </is>
-      </c>
-      <c r="K67" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="L67" s="32" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="M67" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="N67" s="32" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="O67" s="32" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="P67" s="32" t="n">
-        <v>0.422</v>
-      </c>
-      <c r="Q67" s="35" t="inlineStr">
-        <is>
-          <t>Opp 1st Inn R/G</t>
+      <c r="A67" s="29" t="inlineStr">
+        <is>
+          <t>Pittsburgh Pirates offense vs Cincinnati Reds defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B68" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C68" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D68" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E68" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F68" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G68" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H68" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I68" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J68" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K68" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L68" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M68" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N68" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O68" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P68" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q68" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="29" t="inlineStr">
-        <is>
-          <t>Pittsburgh Pirates offense vs Cincinnati Reds defense</t>
+      <c r="A69" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B69" s="32" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="C69" s="32" t="n">
+        <v>3.667</v>
+      </c>
+      <c r="D69" s="32" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E69" s="32" t="n">
+        <v>3.733</v>
+      </c>
+      <c r="F69" s="32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G69" s="32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H69" s="34" t="inlineStr">
+        <is>
+          <t>16th</t>
+        </is>
+      </c>
+      <c r="I69" s="32" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="J69" s="34" t="inlineStr">
+        <is>
+          <t>20th</t>
+        </is>
+      </c>
+      <c r="K69" s="32" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="L69" s="32" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="M69" s="32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N69" s="32" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O69" s="32" t="n">
+        <v>4.533</v>
+      </c>
+      <c r="P69" s="32" t="n">
+        <v>4.308</v>
+      </c>
+      <c r="Q69" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B70" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C70" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D70" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E70" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F70" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G70" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H70" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I70" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J70" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K70" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L70" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M70" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N70" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O70" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P70" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q70" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A70" s="31" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B70" s="32" t="n">
+        <v>7.602</v>
+      </c>
+      <c r="C70" s="32" t="n">
+        <v>7.333</v>
+      </c>
+      <c r="D70" s="32" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="E70" s="32" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="F70" s="32" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="G70" s="32" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H70" s="33" t="inlineStr">
+        <is>
+          <t>8th</t>
+        </is>
+      </c>
+      <c r="I70" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J70" s="36" t="inlineStr">
+        <is>
+          <t>23rd</t>
+        </is>
+      </c>
+      <c r="K70" s="32" t="n">
+        <v>9</v>
+      </c>
+      <c r="L70" s="32" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="M70" s="32" t="n">
+        <v>7.467</v>
+      </c>
+      <c r="N70" s="32" t="n">
+        <v>7.45</v>
+      </c>
+      <c r="O70" s="32" t="n">
+        <v>7.933</v>
+      </c>
+      <c r="P70" s="32" t="n">
+        <v>8.244</v>
+      </c>
+      <c r="Q70" s="35" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>3.53</v>
+        <v>0.705</v>
       </c>
       <c r="C71" s="32" t="n">
-        <v>3.667</v>
+        <v>0.7</v>
       </c>
       <c r="D71" s="32" t="n">
-        <v>3.2</v>
+        <v>0.75</v>
       </c>
       <c r="E71" s="32" t="n">
-        <v>3.733</v>
+        <v>0.8</v>
       </c>
       <c r="F71" s="32" t="n">
-        <v>4.2</v>
+        <v>1</v>
       </c>
       <c r="G71" s="32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="H71" s="34" t="inlineStr">
-        <is>
-          <t>16th</t>
-        </is>
-      </c>
-      <c r="I71" s="32" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J71" s="34" t="inlineStr">
-        <is>
-          <t>20th</t>
-        </is>
-      </c>
-      <c r="K71" s="32" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="L71" s="32" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="M71" s="32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N71" s="32" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="O71" s="32" t="n">
-        <v>4.533</v>
-      </c>
-      <c r="P71" s="32" t="n">
-        <v>4.308</v>
+        <v>0.8</v>
+      </c>
+      <c r="H71" s="36" t="inlineStr">
+        <is>
+          <t>26th</t>
+        </is>
+      </c>
+      <c r="I71" s="32" t="inlineStr"/>
+      <c r="J71" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Q71" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B72" s="32" t="n">
-        <v>7.602</v>
+        <v>8.849</v>
       </c>
       <c r="C72" s="32" t="n">
-        <v>7.333</v>
+        <v>9.4</v>
       </c>
       <c r="D72" s="32" t="n">
-        <v>7.15</v>
+        <v>9.35</v>
       </c>
       <c r="E72" s="32" t="n">
-        <v>7.8</v>
+        <v>8.933</v>
       </c>
       <c r="F72" s="32" t="n">
-        <v>8.800000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="G72" s="32" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="H72" s="33" t="inlineStr">
-        <is>
-          <t>8th</t>
-        </is>
-      </c>
-      <c r="I72" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
+        <v>10.2</v>
+      </c>
+      <c r="H72" s="36" t="inlineStr">
+        <is>
+          <t>21st</t>
+        </is>
+      </c>
+      <c r="I72" s="32" t="inlineStr"/>
       <c r="J72" s="36" t="inlineStr">
         <is>
-          <t>23rd</t>
+          <t>21st</t>
         </is>
       </c>
       <c r="K72" s="32" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="L72" s="32" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="M72" s="32" t="n">
+        <v>9.067</v>
+      </c>
+      <c r="N72" s="32" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="O72" s="32" t="n">
         <v>9</v>
       </c>
-      <c r="L72" s="32" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="M72" s="32" t="n">
-        <v>7.467</v>
-      </c>
-      <c r="N72" s="32" t="n">
-        <v>7.45</v>
-      </c>
-      <c r="O72" s="32" t="n">
-        <v>7.933</v>
-      </c>
       <c r="P72" s="32" t="n">
-        <v>8.244</v>
+        <v>8.936</v>
       </c>
       <c r="Q72" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B73" s="32" t="n">
-        <v>0.705</v>
+        <v>0.5</v>
       </c>
       <c r="C73" s="32" t="n">
+        <v>0.867</v>
+      </c>
+      <c r="D73" s="32" t="n">
         <v>0.7</v>
-      </c>
-      <c r="D73" s="32" t="n">
-        <v>0.75</v>
       </c>
       <c r="E73" s="32" t="n">
         <v>0.8</v>
       </c>
       <c r="F73" s="32" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="G73" s="32" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="H73" s="36" t="inlineStr">
         <is>
-          <t>26th</t>
+          <t>29th</t>
         </is>
       </c>
       <c r="I73" s="32" t="inlineStr"/>
-      <c r="J73" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J73" s="33" t="inlineStr">
+        <is>
+          <t>8th</t>
+        </is>
+      </c>
+      <c r="K73" s="32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L73" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M73" s="32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N73" s="32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O73" s="32" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="P73" s="32" t="n">
+        <v>0.436</v>
       </c>
       <c r="Q73" s="35" t="inlineStr">
-        <is>
-          <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="31" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B74" s="32" t="n">
-        <v>8.849</v>
-      </c>
-      <c r="C74" s="32" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="D74" s="32" t="n">
-        <v>9.35</v>
-      </c>
-      <c r="E74" s="32" t="n">
-        <v>8.933</v>
-      </c>
-      <c r="F74" s="32" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="G74" s="32" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="H74" s="36" t="inlineStr">
-        <is>
-          <t>21st</t>
-        </is>
-      </c>
-      <c r="I74" s="32" t="inlineStr"/>
-      <c r="J74" s="36" t="inlineStr">
-        <is>
-          <t>21st</t>
-        </is>
-      </c>
-      <c r="K74" s="32" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="L74" s="32" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="M74" s="32" t="n">
-        <v>9.067</v>
-      </c>
-      <c r="N74" s="32" t="n">
-        <v>8.550000000000001</v>
-      </c>
-      <c r="O74" s="32" t="n">
-        <v>9</v>
-      </c>
-      <c r="P74" s="32" t="n">
-        <v>8.936</v>
-      </c>
-      <c r="Q74" s="35" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B75" s="32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C75" s="32" t="n">
-        <v>0.867</v>
-      </c>
-      <c r="D75" s="32" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E75" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="F75" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="G75" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H75" s="36" t="inlineStr">
-        <is>
-          <t>29th</t>
-        </is>
-      </c>
-      <c r="I75" s="32" t="inlineStr"/>
-      <c r="J75" s="33" t="inlineStr">
-        <is>
-          <t>8th</t>
-        </is>
-      </c>
-      <c r="K75" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="L75" s="32" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="M75" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="N75" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="O75" s="32" t="n">
-        <v>0.467</v>
-      </c>
-      <c r="P75" s="32" t="n">
-        <v>0.436</v>
-      </c>
-      <c r="Q75" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -4530,7 +4530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q75"/>
+  <dimension ref="A1:Q77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4547,823 +4547,823 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="29" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="29" t="inlineStr">
         <is>
           <t>Arizona Diamondbacks offense vs Tampa Bay Rays defense</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="30" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B62" s="30" t="inlineStr">
+      <c r="B64" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C62" s="30" t="inlineStr">
+      <c r="C64" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D62" s="30" t="inlineStr">
+      <c r="D64" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E62" s="30" t="inlineStr">
+      <c r="E64" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F62" s="30" t="inlineStr">
+      <c r="F64" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G62" s="30" t="inlineStr">
+      <c r="G64" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H62" s="30" t="inlineStr">
+      <c r="H64" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I62" s="30" t="inlineStr">
+      <c r="I64" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J62" s="30" t="inlineStr">
+      <c r="J64" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K62" s="30" t="inlineStr">
+      <c r="K64" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L62" s="30" t="inlineStr">
+      <c r="L64" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M62" s="30" t="inlineStr">
+      <c r="M64" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N62" s="30" t="inlineStr">
+      <c r="N64" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O62" s="30" t="inlineStr">
+      <c r="O64" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P62" s="30" t="inlineStr">
+      <c r="P64" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q62" s="30" t="inlineStr">
+      <c r="Q64" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B63" s="32" t="n">
-        <v>4.976</v>
-      </c>
-      <c r="C63" s="32" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="D63" s="32" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="E63" s="32" t="n">
-        <v>4.467</v>
-      </c>
-      <c r="F63" s="32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="G63" s="32" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="H63" s="36" t="inlineStr">
-        <is>
-          <t>25th</t>
-        </is>
-      </c>
-      <c r="I63" s="32" t="inlineStr"/>
-      <c r="J63" s="36" t="inlineStr">
-        <is>
-          <t>26th</t>
-        </is>
-      </c>
-      <c r="K63" s="32" t="n">
-        <v>6</v>
-      </c>
-      <c r="L63" s="32" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="M63" s="32" t="n">
-        <v>4.867</v>
-      </c>
-      <c r="N63" s="32" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="O63" s="32" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="P63" s="32" t="n">
-        <v>4.234</v>
-      </c>
-      <c r="Q63" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="31" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B64" s="32" t="n">
-        <v>8.688000000000001</v>
-      </c>
-      <c r="C64" s="32" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="D64" s="32" t="n">
-        <v>8.85</v>
-      </c>
-      <c r="E64" s="32" t="n">
-        <v>9</v>
-      </c>
-      <c r="F64" s="32" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="G64" s="32" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="H64" s="34" t="inlineStr">
-        <is>
-          <t>12th</t>
-        </is>
-      </c>
-      <c r="I64" s="32" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J64" s="34" t="inlineStr">
-        <is>
-          <t>17th</t>
-        </is>
-      </c>
-      <c r="K64" s="32" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="L64" s="32" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="M64" s="32" t="n">
-        <v>8.067</v>
-      </c>
-      <c r="N64" s="32" t="n">
-        <v>8.050000000000001</v>
-      </c>
-      <c r="O64" s="32" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="P64" s="32" t="n">
-        <v>7.868</v>
-      </c>
-      <c r="Q64" s="35" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B65" s="32" t="n">
-        <v>1.329</v>
+        <v>4.976</v>
       </c>
       <c r="C65" s="32" t="n">
-        <v>1.033</v>
+        <v>4.7</v>
       </c>
       <c r="D65" s="32" t="n">
-        <v>0.85</v>
+        <v>4.45</v>
       </c>
       <c r="E65" s="32" t="n">
-        <v>1</v>
+        <v>4.467</v>
       </c>
       <c r="F65" s="32" t="n">
-        <v>0.9</v>
+        <v>3.4</v>
       </c>
       <c r="G65" s="32" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="H65" s="36" t="inlineStr">
         <is>
-          <t>22nd</t>
+          <t>25th</t>
         </is>
       </c>
       <c r="I65" s="32" t="inlineStr"/>
-      <c r="J65" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K65" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L65" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M65" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N65" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O65" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P65" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J65" s="36" t="inlineStr">
+        <is>
+          <t>26th</t>
+        </is>
+      </c>
+      <c r="K65" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="L65" s="32" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="M65" s="32" t="n">
+        <v>4.867</v>
+      </c>
+      <c r="N65" s="32" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O65" s="32" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="P65" s="32" t="n">
+        <v>4.234</v>
       </c>
       <c r="Q65" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B66" s="32" t="n">
-        <v>8.265000000000001</v>
+        <v>8.688000000000001</v>
       </c>
       <c r="C66" s="32" t="n">
-        <v>8.467000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D66" s="32" t="n">
-        <v>8.35</v>
+        <v>8.85</v>
       </c>
       <c r="E66" s="32" t="n">
+        <v>9</v>
+      </c>
+      <c r="F66" s="32" t="n">
         <v>8.4</v>
       </c>
-      <c r="F66" s="32" t="n">
-        <v>8.6</v>
-      </c>
       <c r="G66" s="32" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="H66" s="36" t="inlineStr">
-        <is>
-          <t>23rd</t>
-        </is>
-      </c>
-      <c r="I66" s="32" t="inlineStr"/>
+        <v>7.6</v>
+      </c>
+      <c r="H66" s="34" t="inlineStr">
+        <is>
+          <t>12th</t>
+        </is>
+      </c>
+      <c r="I66" s="32" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
       <c r="J66" s="34" t="inlineStr">
         <is>
-          <t>15th</t>
+          <t>17th</t>
         </is>
       </c>
       <c r="K66" s="32" t="n">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L66" s="32" t="n">
-        <v>8.699999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="M66" s="32" t="n">
-        <v>8.333</v>
+        <v>8.067</v>
       </c>
       <c r="N66" s="32" t="n">
-        <v>8.800000000000001</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="O66" s="32" t="n">
-        <v>9.5</v>
+        <v>7.8</v>
       </c>
       <c r="P66" s="32" t="n">
-        <v>8.737</v>
+        <v>7.868</v>
       </c>
       <c r="Q66" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="31" t="inlineStr">
         <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B67" s="32" t="n">
+        <v>1.329</v>
+      </c>
+      <c r="C67" s="32" t="n">
+        <v>1.033</v>
+      </c>
+      <c r="D67" s="32" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="E67" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="F67" s="32" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G67" s="32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H67" s="36" t="inlineStr">
+        <is>
+          <t>22nd</t>
+        </is>
+      </c>
+      <c r="I67" s="32" t="inlineStr"/>
+      <c r="J67" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K67" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L67" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M67" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N67" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O67" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P67" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q67" s="35" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="31" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B68" s="32" t="n">
+        <v>8.265000000000001</v>
+      </c>
+      <c r="C68" s="32" t="n">
+        <v>8.467000000000001</v>
+      </c>
+      <c r="D68" s="32" t="n">
+        <v>8.35</v>
+      </c>
+      <c r="E68" s="32" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="F68" s="32" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="G68" s="32" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="H68" s="36" t="inlineStr">
+        <is>
+          <t>23rd</t>
+        </is>
+      </c>
+      <c r="I68" s="32" t="inlineStr"/>
+      <c r="J68" s="34" t="inlineStr">
+        <is>
+          <t>15th</t>
+        </is>
+      </c>
+      <c r="K68" s="32" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="L68" s="32" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M68" s="32" t="n">
+        <v>8.333</v>
+      </c>
+      <c r="N68" s="32" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="O68" s="32" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="P68" s="32" t="n">
+        <v>8.737</v>
+      </c>
+      <c r="Q68" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B67" s="32" t="n">
+      <c r="B69" s="32" t="n">
         <v>0.612</v>
       </c>
-      <c r="C67" s="32" t="n">
+      <c r="C69" s="32" t="n">
         <v>0.467</v>
       </c>
-      <c r="D67" s="32" t="n">
+      <c r="D69" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="E67" s="32" t="n">
+      <c r="E69" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="F67" s="32" t="n">
+      <c r="F69" s="32" t="n">
         <v>0.7</v>
       </c>
-      <c r="G67" s="32" t="n">
+      <c r="G69" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="H67" s="33" t="inlineStr">
+      <c r="H69" s="33" t="inlineStr">
         <is>
           <t>10th</t>
         </is>
       </c>
-      <c r="I67" s="32" t="inlineStr">
+      <c r="I69" s="32" t="inlineStr">
         <is>
           <t>★★★</t>
         </is>
       </c>
-      <c r="J67" s="36" t="inlineStr">
+      <c r="J69" s="36" t="inlineStr">
         <is>
           <t>25th</t>
         </is>
       </c>
-      <c r="K67" s="32" t="n">
+      <c r="K69" s="32" t="n">
         <v>1.2</v>
       </c>
-      <c r="L67" s="32" t="n">
+      <c r="L69" s="32" t="n">
         <v>0.8</v>
       </c>
-      <c r="M67" s="32" t="n">
+      <c r="M69" s="32" t="n">
         <v>0.667</v>
       </c>
-      <c r="N67" s="32" t="n">
+      <c r="N69" s="32" t="n">
         <v>0.65</v>
       </c>
-      <c r="O67" s="32" t="n">
+      <c r="O69" s="32" t="n">
         <v>0.467</v>
       </c>
-      <c r="P67" s="32" t="n">
+      <c r="P69" s="32" t="n">
         <v>0.473</v>
       </c>
-      <c r="Q67" s="35" t="inlineStr">
+      <c r="Q69" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="29" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="29" t="inlineStr">
         <is>
           <t>Tampa Bay Rays offense vs Arizona Diamondbacks defense</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="30" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B70" s="30" t="inlineStr">
+      <c r="B72" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C70" s="30" t="inlineStr">
+      <c r="C72" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D70" s="30" t="inlineStr">
+      <c r="D72" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E70" s="30" t="inlineStr">
+      <c r="E72" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F70" s="30" t="inlineStr">
+      <c r="F72" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G70" s="30" t="inlineStr">
+      <c r="G72" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H70" s="30" t="inlineStr">
+      <c r="H72" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I70" s="30" t="inlineStr">
+      <c r="I72" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J70" s="30" t="inlineStr">
+      <c r="J72" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K70" s="30" t="inlineStr">
+      <c r="K72" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L70" s="30" t="inlineStr">
+      <c r="L72" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M70" s="30" t="inlineStr">
+      <c r="M72" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N70" s="30" t="inlineStr">
+      <c r="N72" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O70" s="30" t="inlineStr">
+      <c r="O72" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P70" s="30" t="inlineStr">
+      <c r="P72" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q70" s="30" t="inlineStr">
+      <c r="Q72" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B71" s="32" t="n">
-        <v>4.437</v>
-      </c>
-      <c r="C71" s="32" t="n">
-        <v>4.033</v>
-      </c>
-      <c r="D71" s="32" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="E71" s="32" t="n">
-        <v>3.667</v>
-      </c>
-      <c r="F71" s="32" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="G71" s="32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="H71" s="34" t="inlineStr">
-        <is>
-          <t>14th</t>
-        </is>
-      </c>
-      <c r="I71" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J71" s="36" t="inlineStr">
-        <is>
-          <t>30th</t>
-        </is>
-      </c>
-      <c r="K71" s="32" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="L71" s="32" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="M71" s="32" t="n">
-        <v>5.333</v>
-      </c>
-      <c r="N71" s="32" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="O71" s="32" t="n">
-        <v>4.767</v>
-      </c>
-      <c r="P71" s="32" t="n">
-        <v>4.847</v>
-      </c>
-      <c r="Q71" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="31" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B72" s="32" t="n">
-        <v>8.521000000000001</v>
-      </c>
-      <c r="C72" s="32" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="D72" s="32" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="E72" s="32" t="n">
-        <v>8.667</v>
-      </c>
-      <c r="F72" s="32" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="G72" s="32" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="H72" s="33" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="I72" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J72" s="36" t="inlineStr">
-        <is>
-          <t>27th</t>
-        </is>
-      </c>
-      <c r="K72" s="32" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="L72" s="32" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="M72" s="32" t="n">
-        <v>9.132999999999999</v>
-      </c>
-      <c r="N72" s="32" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="O72" s="32" t="n">
-        <v>8.567</v>
-      </c>
-      <c r="P72" s="32" t="n">
-        <v>8.840999999999999</v>
-      </c>
-      <c r="Q72" s="35" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B73" s="32" t="n">
-        <v>1.114</v>
+        <v>4.437</v>
       </c>
       <c r="C73" s="32" t="n">
-        <v>1.133</v>
+        <v>4.033</v>
       </c>
       <c r="D73" s="32" t="n">
-        <v>1.15</v>
+        <v>3.55</v>
       </c>
       <c r="E73" s="32" t="n">
-        <v>1</v>
+        <v>3.667</v>
       </c>
       <c r="F73" s="32" t="n">
-        <v>1</v>
+        <v>3.9</v>
       </c>
       <c r="G73" s="32" t="n">
-        <v>1</v>
+        <v>3.6</v>
       </c>
       <c r="H73" s="34" t="inlineStr">
         <is>
-          <t>17th</t>
-        </is>
-      </c>
-      <c r="I73" s="32" t="inlineStr"/>
-      <c r="J73" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>14th</t>
+        </is>
+      </c>
+      <c r="I73" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J73" s="36" t="inlineStr">
+        <is>
+          <t>30th</t>
+        </is>
+      </c>
+      <c r="K73" s="32" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="L73" s="32" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="M73" s="32" t="n">
+        <v>5.333</v>
+      </c>
+      <c r="N73" s="32" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="O73" s="32" t="n">
+        <v>4.767</v>
+      </c>
+      <c r="P73" s="32" t="n">
+        <v>4.847</v>
       </c>
       <c r="Q73" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B74" s="32" t="n">
-        <v>8.611000000000001</v>
+        <v>8.521000000000001</v>
       </c>
       <c r="C74" s="32" t="n">
-        <v>8.967000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="D74" s="32" t="n">
-        <v>9.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E74" s="32" t="n">
-        <v>9.667</v>
+        <v>8.667</v>
       </c>
       <c r="F74" s="32" t="n">
-        <v>9.199999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="G74" s="32" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="H74" s="34" t="inlineStr">
-        <is>
-          <t>18th</t>
-        </is>
-      </c>
-      <c r="I74" s="32" t="inlineStr"/>
-      <c r="J74" s="34" t="inlineStr">
-        <is>
-          <t>16th</t>
+        <v>9.6</v>
+      </c>
+      <c r="H74" s="33" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="I74" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J74" s="36" t="inlineStr">
+        <is>
+          <t>27th</t>
         </is>
       </c>
       <c r="K74" s="32" t="n">
-        <v>9.4</v>
+        <v>10.4</v>
       </c>
       <c r="L74" s="32" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="M74" s="32" t="n">
-        <v>8.333</v>
+        <v>9.132999999999999</v>
       </c>
       <c r="N74" s="32" t="n">
-        <v>7.9</v>
+        <v>8.75</v>
       </c>
       <c r="O74" s="32" t="n">
-        <v>7.8</v>
+        <v>8.567</v>
       </c>
       <c r="P74" s="32" t="n">
-        <v>8.199999999999999</v>
+        <v>8.840999999999999</v>
       </c>
       <c r="Q74" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="31" t="inlineStr">
         <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B75" s="32" t="n">
+        <v>1.114</v>
+      </c>
+      <c r="C75" s="32" t="n">
+        <v>1.133</v>
+      </c>
+      <c r="D75" s="32" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="E75" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="F75" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="H75" s="34" t="inlineStr">
+        <is>
+          <t>17th</t>
+        </is>
+      </c>
+      <c r="I75" s="32" t="inlineStr"/>
+      <c r="J75" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q75" s="35" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="31" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B76" s="32" t="n">
+        <v>8.611000000000001</v>
+      </c>
+      <c r="C76" s="32" t="n">
+        <v>8.967000000000001</v>
+      </c>
+      <c r="D76" s="32" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="E76" s="32" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="F76" s="32" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="G76" s="32" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="H76" s="34" t="inlineStr">
+        <is>
+          <t>18th</t>
+        </is>
+      </c>
+      <c r="I76" s="32" t="inlineStr"/>
+      <c r="J76" s="34" t="inlineStr">
+        <is>
+          <t>16th</t>
+        </is>
+      </c>
+      <c r="K76" s="32" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="L76" s="32" t="n">
+        <v>9</v>
+      </c>
+      <c r="M76" s="32" t="n">
+        <v>8.333</v>
+      </c>
+      <c r="N76" s="32" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="O76" s="32" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="P76" s="32" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Q76" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B75" s="32" t="n">
+      <c r="B77" s="32" t="n">
         <v>0.587</v>
       </c>
-      <c r="C75" s="32" t="n">
+      <c r="C77" s="32" t="n">
         <v>0.867</v>
       </c>
-      <c r="D75" s="32" t="n">
+      <c r="D77" s="32" t="n">
         <v>0.7</v>
       </c>
-      <c r="E75" s="32" t="n">
+      <c r="E77" s="32" t="n">
         <v>0.667</v>
       </c>
-      <c r="F75" s="32" t="n">
+      <c r="F77" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="G75" s="32" t="n">
+      <c r="G77" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="H75" s="34" t="inlineStr">
+      <c r="H77" s="34" t="inlineStr">
         <is>
           <t>16th</t>
         </is>
       </c>
-      <c r="I75" s="32" t="inlineStr">
+      <c r="I77" s="32" t="inlineStr">
         <is>
           <t>★★★</t>
         </is>
       </c>
-      <c r="J75" s="36" t="inlineStr">
+      <c r="J77" s="36" t="inlineStr">
         <is>
           <t>29th</t>
         </is>
       </c>
-      <c r="K75" s="32" t="n">
+      <c r="K77" s="32" t="n">
         <v>1.8</v>
       </c>
-      <c r="L75" s="32" t="n">
+      <c r="L77" s="32" t="n">
         <v>1.1</v>
       </c>
-      <c r="M75" s="32" t="n">
+      <c r="M77" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="N75" s="32" t="n">
+      <c r="N77" s="32" t="n">
         <v>0.9</v>
       </c>
-      <c r="O75" s="32" t="n">
+      <c r="O77" s="32" t="n">
         <v>0.733</v>
       </c>
-      <c r="P75" s="32" t="n">
+      <c r="P77" s="32" t="n">
         <v>0.641</v>
       </c>
-      <c r="Q75" s="35" t="inlineStr">
+      <c r="Q77" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -8132,10 +8132,10 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.5008208955223882</v>
+        <v>0.4944402985074627</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>-100</v>
+        <v>102</v>
       </c>
       <c r="H5" s="15" t="n">
         <v>168</v>
@@ -8162,7 +8162,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 50.1% (fair -100). Your call.</t>
+          <t>Model 49.4% (fair +102). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -8194,17 +8194,17 @@
       </c>
       <c r="E6" s="20" t="inlineStr">
         <is>
-          <t>Over 181.5</t>
+          <t>Over 183</t>
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.6680980392156862</v>
+        <v>0.631044776119403</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>-201</v>
+        <v>-171</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>-104</v>
+        <v>101</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -8228,7 +8228,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 66.8% (fair -201). Your call.</t>
+          <t>Model 63.1% (fair -171). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -8264,10 +8264,10 @@
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.6714396396396396</v>
+        <v>0.6607234234234234</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-204</v>
+        <v>-195</v>
       </c>
       <c r="H7" s="15" t="n">
         <v>-122</v>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 67.1% (fair -204). Your call.</t>
+          <t>Model 66.1% (fair -195). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -8377,12 +8377,12 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>Houston Astros @ Detroit Tigers</t>
+          <t>Texas Rangers @ Toronto Blue Jays</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
@@ -8396,13 +8396,13 @@
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.5749</v>
+        <v>0.5659134615384616</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>-135</v>
+        <v>-130</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -8426,7 +8426,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 57.5% (fair -135). Your call.</t>
+          <t>Model 56.6% (fair -130). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -8438,37 +8438,37 @@
     <row r="10">
       <c r="A10" s="20" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>Cincinnati Reds @ Pittsburgh Pirates</t>
+          <t>Las Vegas Aces @ Chicago Sky</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>Chicago Sky +6.5</t>
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.5560194174757281</v>
+        <v>0.5519711538461538</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-125</v>
+        <v>-123</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -8492,7 +8492,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 55.6% (fair -125). Your call.</t>
+          <t>Model 55.2% (fair -123). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -8504,17 +8504,17 @@
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>New York Liberty @ Golden State Valkyries</t>
+          <t>Atlanta Dream @ Seattle Storm</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
@@ -8524,17 +8524,17 @@
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>Golden State Valkyries</t>
+          <t>Seattle Storm</t>
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.578321568627451</v>
+        <v>0.2729976019184652</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>-137</v>
+        <v>266</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>-104</v>
+        <v>317</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -8558,7 +8558,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 57.8% (fair -137). Your call.</t>
+          <t>Model 27.3% (fair +266). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -8594,13 +8594,13 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.5262264150943395</v>
+        <v>0.5233179723502304</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>-111</v>
+        <v>-110</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -8624,7 +8624,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 52.6% (fair -111). Your call.</t>
+          <t>Model 52.3% (fair -110). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -8641,32 +8641,32 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks @ Tampa Bay Rays</t>
+          <t>New York Liberty @ Golden State Valkyries</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Over 7.5</t>
+          <t>Golden State Valkyries</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.5958069767441861</v>
+        <v>0.578321568627451</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>-147</v>
+        <v>-137</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>-115</v>
+        <v>-104</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -8690,7 +8690,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 59.6% (fair -147). Your call.</t>
+          <t>Model 57.8% (fair -137). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -8707,32 +8707,32 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>Washington Nationals @ Baltimore Orioles</t>
+          <t>Arizona Diamondbacks @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Baltimore Orioles</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.6854057034220533</v>
+        <v>0.5867307692307692</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>-218</v>
+        <v>-142</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>-163</v>
+        <v>-108</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -8756,7 +8756,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 68.5% (fair -218). Your call.</t>
+          <t>Model 58.7% (fair -142). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -8768,37 +8768,37 @@
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Las Vegas Aces @ Chicago Sky</t>
+          <t>Cincinnati Reds @ Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Over 178.5</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.55275</v>
+        <v>0.5467961165048544</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>-124</v>
+        <v>-121</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -8822,7 +8822,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 55.3% (fair -124). Your call.</t>
+          <t>Model 54.7% (fair -121). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -8839,12 +8839,12 @@
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>Texas Rangers @ Toronto Blue Jays</t>
+          <t>Colorado Rockies @ Minnesota Twins</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -8854,17 +8854,17 @@
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.55175</v>
+        <v>0.5172350230414747</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>-123</v>
+        <v>-107</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -8888,7 +8888,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 55.2% (fair -123). Your call.</t>
+          <t>Model 51.7% (fair -107). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -8905,32 +8905,32 @@
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Las Vegas Aces @ Chicago Sky</t>
+          <t>Atlanta Braves @ San Francisco Giants</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Chicago Sky +7.5</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.5778666666666666</v>
+        <v>0.55335</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>-137</v>
+        <v>-124</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>-110</v>
+        <v>100</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 57.8% (fair -137). Your call.</t>
+          <t>Model 55.3% (fair -124). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -8971,12 +8971,12 @@
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>New York Liberty @ Golden State Valkyries</t>
+          <t>Las Vegas Aces @ Chicago Sky</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -8986,17 +8986,17 @@
       </c>
       <c r="E18" s="20" t="inlineStr">
         <is>
-          <t>Over 163.5</t>
+          <t>Over 178.5</t>
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.5769238095238095</v>
+        <v>0.55275</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>-136</v>
+        <v>-124</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>-110</v>
+        <v>100</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -9020,7 +9020,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 57.7% (fair -136). Your call.</t>
+          <t>Model 55.3% (fair -124). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Atlanta Braves @ San Francisco Giants</t>
+          <t>New York Liberty @ Golden State Valkyries</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -9052,17 +9052,17 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Over 7.5</t>
+          <t>Over 163.5</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.5606823529411765</v>
+        <v>0.5769238095238095</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>-128</v>
+        <v>-136</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>-104</v>
+        <v>-110</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -9086,7 +9086,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 56.1% (fair -128). Your call.</t>
+          <t>Model 57.7% (fair -136). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -9164,37 +9164,37 @@
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Washington Nationals @ Baltimore Orioles</t>
+          <t>Kansas City Royals @ Chicago White Sox</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>23:05</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Baltimore Orioles</t>
+          <t>Chicago White Sox -1.5</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.5517098039215687</v>
+        <v>0.4240625</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>-123</v>
+        <v>136</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>-104</v>
+        <v>156</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -9218,7 +9218,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 55.2% (fair -123). Your call.</t>
+          <t>Model 42.4% (fair +136). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -9230,37 +9230,37 @@
     <row r="22">
       <c r="A22" s="20" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>Chicago Cubs @ Milwaukee Brewers</t>
+          <t>Atlanta Braves @ San Francisco Giants</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers</t>
+          <t>San Francisco Giants +1.5</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.6313406639004149</v>
+        <v>0.6052920704845816</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-171</v>
+        <v>-153</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>-141</v>
+        <v>-127</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -9284,7 +9284,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 63.1% (fair -171). Your call.</t>
+          <t>Model 60.5% (fair -153). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -9301,12 +9301,12 @@
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>Seattle Mariners @ Cleveland Guardians</t>
+          <t>Washington Nationals @ Baltimore Orioles</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>23:05</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
@@ -9316,17 +9316,17 @@
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Seattle Mariners</t>
+          <t>Baltimore Orioles</t>
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.6175531914893617</v>
+        <v>0.5510470588235293</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>-161</v>
+        <v>-123</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>-135</v>
+        <v>-104</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -9350,7 +9350,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 61.8% (fair -161). Your call.</t>
+          <t>Model 55.1% (fair -123). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -9362,17 +9362,17 @@
     <row r="24">
       <c r="A24" s="20" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks @ Tampa Bay Rays</t>
+          <t>Washington Nationals @ Baltimore Orioles</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>22:10</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -9382,17 +9382,17 @@
       </c>
       <c r="E24" s="20" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks</t>
+          <t>Baltimore Orioles</t>
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.4763555555555556</v>
+        <v>0.6909345323741006</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>110</v>
+        <v>-224</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>125</v>
+        <v>-178</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -9416,7 +9416,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 47.6% (fair +110). Your call.</t>
+          <t>Model 69.1% (fair -224). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -9428,37 +9428,37 @@
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>Colorado Rockies @ Minnesota Twins</t>
+          <t>Chicago Cubs @ Milwaukee Brewers</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Over 9</t>
+          <t>Milwaukee Brewers</t>
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.53585</v>
+        <v>0.6284153526970954</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>-115</v>
+        <v>-169</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>100</v>
+        <v>-141</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -9482,7 +9482,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 53.6% (fair -115). Your call.</t>
+          <t>Model 62.8% (fair -169). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -9494,37 +9494,37 @@
     <row r="26">
       <c r="A26" s="20" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>Atlanta Braves @ San Francisco Giants</t>
+          <t>Arizona Diamondbacks @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>22:10</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
-          <t>San Francisco Giants +1.5</t>
+          <t>Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.6048391304347827</v>
+        <v>0.4763555555555556</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>-153</v>
+        <v>110</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>-130</v>
+        <v>125</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 60.5% (fair -153). Your call.</t>
+          <t>Model 47.6% (fair +110). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -9560,37 +9560,37 @@
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>New York Liberty @ Golden State Valkyries</t>
+          <t>Seattle Mariners @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>Golden State Valkyries -1.5</t>
+          <t>Seattle Mariners</t>
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.5218536585365855</v>
+        <v>0.6212899159663865</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>-109</v>
+        <v>-164</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>105</v>
+        <v>-138</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -9614,7 +9614,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 52.2% (fair -109). Your call.</t>
+          <t>Model 62.1% (fair -164). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -10715,10 +10715,10 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.3717625899280576</v>
+        <v>0.3762230215827338</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="H17" s="15" t="n">
         <v>178</v>
@@ -10745,7 +10745,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 37.2% (fair +169). Your call.</t>
+          <t>Model 37.6% (fair +166). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -10781,10 +10781,10 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.6282503597122302</v>
+        <v>0.6237683453237409</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>-169</v>
+        <v>-166</v>
       </c>
       <c r="H18" s="15" t="n">
         <v>-178</v>
@@ -10811,7 +10811,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 62.8% (fair -169). Your call.</t>
+          <t>Model 62.4% (fair -166). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -10847,10 +10847,10 @@
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.4846</v>
+        <v>0.5125</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>106</v>
+        <v>-105</v>
       </c>
       <c r="H19" s="15" t="n">
         <v>105</v>
@@ -10877,7 +10877,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 48.5% (fair +106). Your call.</t>
+          <t>Model 51.2% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -10913,10 +10913,10 @@
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.5154000000000001</v>
+        <v>0.4875</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>-106</v>
+        <v>105</v>
       </c>
       <c r="H20" s="15" t="n">
         <v>113</v>
@@ -10943,7 +10943,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 51.5% (fair -106). Your call.</t>
+          <t>Model 48.8% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -10979,10 +10979,10 @@
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.4176</v>
+        <v>0.4012</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="H21" s="15" t="n">
         <v>117</v>
@@ -11009,7 +11009,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 41.8% (fair +139). Your call.</t>
+          <t>Model 40.1% (fair +149). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -11045,10 +11045,10 @@
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.5824</v>
+        <v>0.5988</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-139</v>
+        <v>-149</v>
       </c>
       <c r="H22" s="15" t="n">
         <v>126</v>
@@ -11075,7 +11075,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 58.2% (fair -139). Your call.</t>
+          <t>Model 59.9% (fair -149). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -11111,10 +11111,10 @@
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.4439882352941176</v>
+        <v>0.4532156862745098</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="H23" s="15" t="n">
         <v>-104</v>
@@ -11141,7 +11141,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 44.4% (fair +125). Your call.</t>
+          <t>Model 45.3% (fair +121). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -11177,10 +11177,10 @@
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.5560194174757281</v>
+        <v>0.5467961165048544</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>-125</v>
+        <v>-121</v>
       </c>
       <c r="H24" s="15" t="n">
         <v>106</v>
@@ -11207,7 +11207,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 55.6% (fair -125). Your call.</t>
+          <t>Model 54.7% (fair -121). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -11243,10 +11243,10 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.6534</v>
+        <v>0.6786</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>-189</v>
+        <v>-211</v>
       </c>
       <c r="H25" s="15" t="n">
         <v>117</v>
@@ -11273,7 +11273,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 65.3% (fair -189). Your call.</t>
+          <t>Model 67.9% (fair -211). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -11309,10 +11309,10 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.3466</v>
+        <v>0.3214</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>189</v>
+        <v>211</v>
       </c>
       <c r="H26" s="15" t="n">
         <v>117</v>
@@ -11339,7 +11339,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 34.7% (fair +189). Your call.</t>
+          <t>Model 32.1% (fair +211). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -11771,10 +11771,10 @@
         </is>
       </c>
       <c r="F33" s="13" t="n">
-        <v>0.3497</v>
+        <v>0.3506</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H33" s="15" t="n">
         <v>115</v>
@@ -11801,7 +11801,7 @@
       </c>
       <c r="N33" s="19" t="inlineStr">
         <is>
-          <t>Model 35.0% (fair +186). Your call.</t>
+          <t>Model 35.1% (fair +185). Your call.</t>
         </is>
       </c>
       <c r="O33" s="15" t="n"/>
@@ -11837,10 +11837,10 @@
         </is>
       </c>
       <c r="F34" s="13" t="n">
-        <v>0.6503</v>
+        <v>0.6494</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>-186</v>
+        <v>-185</v>
       </c>
       <c r="H34" s="15" t="n">
         <v>104</v>
@@ -11867,7 +11867,7 @@
       </c>
       <c r="N34" s="19" t="inlineStr">
         <is>
-          <t>Model 65.0% (fair -186). Your call.</t>
+          <t>Model 64.9% (fair -185). Your call.</t>
         </is>
       </c>
       <c r="O34" s="15" t="n"/>
@@ -11903,10 +11903,10 @@
         </is>
       </c>
       <c r="F35" s="13" t="n">
-        <v>0.6626</v>
+        <v>0.6567</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>-196</v>
+        <v>-191</v>
       </c>
       <c r="H35" s="15" t="n">
         <v>117</v>
@@ -11933,7 +11933,7 @@
       </c>
       <c r="N35" s="19" t="inlineStr">
         <is>
-          <t>Model 66.3% (fair -196). Your call.</t>
+          <t>Model 65.7% (fair -191). Your call.</t>
         </is>
       </c>
       <c r="O35" s="15" t="n"/>
@@ -11969,10 +11969,10 @@
         </is>
       </c>
       <c r="F36" s="13" t="n">
-        <v>0.3374</v>
+        <v>0.3433</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="H36" s="15" t="n">
         <v>111</v>
@@ -11999,7 +11999,7 @@
       </c>
       <c r="N36" s="19" t="inlineStr">
         <is>
-          <t>Model 33.7% (fair +196). Your call.</t>
+          <t>Model 34.3% (fair +191). Your call.</t>
         </is>
       </c>
       <c r="O36" s="15" t="n"/>
@@ -12035,7 +12035,7 @@
         </is>
       </c>
       <c r="F37" s="13" t="n">
-        <v>0.4649</v>
+        <v>0.4657</v>
       </c>
       <c r="G37" s="14" t="n">
         <v>115</v>
@@ -12065,7 +12065,7 @@
       </c>
       <c r="N37" s="19" t="inlineStr">
         <is>
-          <t>Model 46.5% (fair +115). Your call.</t>
+          <t>Model 46.6% (fair +115). Your call.</t>
         </is>
       </c>
       <c r="O37" s="15" t="n"/>
@@ -12101,7 +12101,7 @@
         </is>
       </c>
       <c r="F38" s="13" t="n">
-        <v>0.5351</v>
+        <v>0.5343</v>
       </c>
       <c r="G38" s="14" t="n">
         <v>-115</v>
@@ -12131,7 +12131,7 @@
       </c>
       <c r="N38" s="19" t="inlineStr">
         <is>
-          <t>Model 53.5% (fair -115). Your call.</t>
+          <t>Model 53.4% (fair -115). Your call.</t>
         </is>
       </c>
       <c r="O38" s="15" t="n"/>
@@ -12299,13 +12299,13 @@
         </is>
       </c>
       <c r="F41" s="13" t="n">
-        <v>0.5031270935960591</v>
+        <v>0.5050009900990099</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>-101</v>
+        <v>-102</v>
       </c>
       <c r="H41" s="15" t="n">
-        <v>-103</v>
+        <v>-102</v>
       </c>
       <c r="I41" s="13">
         <f>IF($H$41="","",IF($H$41&lt;0,-$H$41/(-$H$41+100),100/($H$41+100)))</f>
@@ -12329,7 +12329,7 @@
       </c>
       <c r="N41" s="19" t="inlineStr">
         <is>
-          <t>Model 50.3% (fair -101). Your call.</t>
+          <t>Model 50.5% (fair -102). Your call.</t>
         </is>
       </c>
       <c r="O41" s="15" t="n"/>
@@ -12365,13 +12365,13 @@
         </is>
       </c>
       <c r="F42" s="13" t="n">
-        <v>0.4969</v>
+        <v>0.495</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H42" s="15" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I42" s="13">
         <f>IF($H$42="","",IF($H$42&lt;0,-$H$42/(-$H$42+100),100/($H$42+100)))</f>
@@ -12395,7 +12395,7 @@
       </c>
       <c r="N42" s="19" t="inlineStr">
         <is>
-          <t>Model 49.7% (fair +101). Your call.</t>
+          <t>Model 49.5% (fair +102). Your call.</t>
         </is>
       </c>
       <c r="O42" s="15" t="n"/>
@@ -12503,7 +12503,7 @@
         <v>-232</v>
       </c>
       <c r="H44" s="15" t="n">
-        <v>-118</v>
+        <v>-117</v>
       </c>
       <c r="I44" s="13">
         <f>IF($H$44="","",IF($H$44&lt;0,-$H$44/(-$H$44+100),100/($H$44+100)))</f>
@@ -12563,13 +12563,13 @@
         </is>
       </c>
       <c r="F45" s="13" t="n">
-        <v>0.4483251231527093</v>
+        <v>0.4489108910891089</v>
       </c>
       <c r="G45" s="14" t="n">
         <v>123</v>
       </c>
       <c r="H45" s="15" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I45" s="13">
         <f>IF($H$45="","",IF($H$45&lt;0,-$H$45/(-$H$45+100),100/($H$45+100)))</f>
@@ -12593,7 +12593,7 @@
       </c>
       <c r="N45" s="19" t="inlineStr">
         <is>
-          <t>Model 44.8% (fair +123). Your call.</t>
+          <t>Model 44.9% (fair +123). Your call.</t>
         </is>
       </c>
       <c r="O45" s="15" t="n"/>
@@ -12629,7 +12629,7 @@
         </is>
       </c>
       <c r="F46" s="13" t="n">
-        <v>0.5517098039215687</v>
+        <v>0.5510470588235293</v>
       </c>
       <c r="G46" s="14" t="n">
         <v>-123</v>
@@ -12659,7 +12659,7 @@
       </c>
       <c r="N46" s="19" t="inlineStr">
         <is>
-          <t>Model 55.2% (fair -123). Your call.</t>
+          <t>Model 55.1% (fair -123). Your call.</t>
         </is>
       </c>
       <c r="O46" s="15" t="n"/>
@@ -12701,7 +12701,7 @@
         <v>-146</v>
       </c>
       <c r="H47" s="15" t="n">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="I47" s="13">
         <f>IF($H$47="","",IF($H$47&lt;0,-$H$47/(-$H$47+100),100/($H$47+100)))</f>
@@ -12959,13 +12959,13 @@
         </is>
       </c>
       <c r="F51" s="13" t="n">
-        <v>0.6175531914893617</v>
+        <v>0.6212899159663865</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>-161</v>
+        <v>-164</v>
       </c>
       <c r="H51" s="15" t="n">
-        <v>-135</v>
+        <v>-138</v>
       </c>
       <c r="I51" s="13">
         <f>IF($H$51="","",IF($H$51&lt;0,-$H$51/(-$H$51+100),100/($H$51+100)))</f>
@@ -12989,7 +12989,7 @@
       </c>
       <c r="N51" s="19" t="inlineStr">
         <is>
-          <t>Model 61.8% (fair -161). Your call.</t>
+          <t>Model 62.1% (fair -164). Your call.</t>
         </is>
       </c>
       <c r="O51" s="15" t="n"/>
@@ -13025,13 +13025,13 @@
         </is>
       </c>
       <c r="F52" s="13" t="n">
-        <v>0.3824463519313305</v>
+        <v>0.3787394957983193</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="H52" s="15" t="n">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="I52" s="13">
         <f>IF($H$52="","",IF($H$52&lt;0,-$H$52/(-$H$52+100),100/($H$52+100)))</f>
@@ -13055,7 +13055,7 @@
       </c>
       <c r="N52" s="19" t="inlineStr">
         <is>
-          <t>Model 38.2% (fair +161). Your call.</t>
+          <t>Model 37.9% (fair +164). Your call.</t>
         </is>
       </c>
       <c r="O52" s="15" t="n"/>
@@ -13097,7 +13097,7 @@
         <v>129</v>
       </c>
       <c r="H53" s="15" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="I53" s="13">
         <f>IF($H$53="","",IF($H$53&lt;0,-$H$53/(-$H$53+100),100/($H$53+100)))</f>
@@ -13351,13 +13351,13 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>0.36864</v>
+        <v>0.3715573770491803</v>
       </c>
       <c r="G57" s="14" t="n">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H57" s="15" t="n">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="I57" s="13">
         <f>IF($H$57="","",IF($H$57&lt;0,-$H$57/(-$H$57+100),100/($H$57+100)))</f>
@@ -13381,7 +13381,7 @@
       </c>
       <c r="N57" s="19" t="inlineStr">
         <is>
-          <t>Model 36.9% (fair +171). Your call.</t>
+          <t>Model 37.2% (fair +169). Your call.</t>
         </is>
       </c>
       <c r="O57" s="15" t="n"/>
@@ -13417,10 +13417,10 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>0.6313406639004149</v>
+        <v>0.6284153526970954</v>
       </c>
       <c r="G58" s="14" t="n">
-        <v>-171</v>
+        <v>-169</v>
       </c>
       <c r="H58" s="15" t="n">
         <v>-141</v>
@@ -13447,7 +13447,7 @@
       </c>
       <c r="N58" s="19" t="inlineStr">
         <is>
-          <t>Model 63.1% (fair -171). Your call.</t>
+          <t>Model 62.8% (fair -169). Your call.</t>
         </is>
       </c>
       <c r="O58" s="15" t="n"/>
@@ -13489,7 +13489,7 @@
         <v>-167</v>
       </c>
       <c r="H59" s="15" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="I59" s="13">
         <f>IF($H$59="","",IF($H$59&lt;0,-$H$59/(-$H$59+100),100/($H$59+100)))</f>
@@ -13555,7 +13555,7 @@
         <v>167</v>
       </c>
       <c r="H60" s="15" t="n">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="I60" s="13">
         <f>IF($H$60="","",IF($H$60&lt;0,-$H$60/(-$H$60+100),100/($H$60+100)))</f>
@@ -14259,13 +14259,13 @@
         </is>
       </c>
       <c r="F71" s="13" t="n">
-        <v>0.3145925925925925</v>
+        <v>0.3090875912408759</v>
       </c>
       <c r="G71" s="14" t="n">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="H71" s="15" t="n">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="I71" s="13">
         <f>IF($H$71="","",IF($H$71&lt;0,-$H$71/(-$H$71+100),100/($H$71+100)))</f>
@@ -14289,7 +14289,7 @@
       </c>
       <c r="N71" s="19" t="inlineStr">
         <is>
-          <t>Model 31.5% (fair +218). Your call.</t>
+          <t>Model 30.9% (fair +224). Your call.</t>
         </is>
       </c>
       <c r="O71" s="15" t="n"/>
@@ -14325,13 +14325,13 @@
         </is>
       </c>
       <c r="F72" s="13" t="n">
-        <v>0.6854057034220533</v>
+        <v>0.6909345323741006</v>
       </c>
       <c r="G72" s="14" t="n">
-        <v>-218</v>
+        <v>-224</v>
       </c>
       <c r="H72" s="15" t="n">
-        <v>-163</v>
+        <v>-178</v>
       </c>
       <c r="I72" s="13">
         <f>IF($H$72="","",IF($H$72&lt;0,-$H$72/(-$H$72+100),100/($H$72+100)))</f>
@@ -14355,7 +14355,7 @@
       </c>
       <c r="N72" s="19" t="inlineStr">
         <is>
-          <t>Model 68.5% (fair -218). Your call.</t>
+          <t>Model 69.1% (fair -224). Your call.</t>
         </is>
       </c>
       <c r="O72" s="15" t="n"/>
@@ -14397,7 +14397,7 @@
         <v>-216</v>
       </c>
       <c r="H73" s="15" t="n">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="I73" s="13">
         <f>IF($H$73="","",IF($H$73&lt;0,-$H$73/(-$H$73+100),100/($H$73+100)))</f>
@@ -14463,7 +14463,7 @@
         <v>216</v>
       </c>
       <c r="H74" s="15" t="n">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="I74" s="13">
         <f>IF($H$74="","",IF($H$74&lt;0,-$H$74/(-$H$74+100),100/($H$74+100)))</f>
@@ -14523,13 +14523,13 @@
         </is>
       </c>
       <c r="F75" s="13" t="n">
-        <v>0.5262264150943395</v>
+        <v>0.5233179723502304</v>
       </c>
       <c r="G75" s="14" t="n">
-        <v>-111</v>
+        <v>-110</v>
       </c>
       <c r="H75" s="15" t="n">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="I75" s="13">
         <f>IF($H$75="","",IF($H$75&lt;0,-$H$75/(-$H$75+100),100/($H$75+100)))</f>
@@ -14553,7 +14553,7 @@
       </c>
       <c r="N75" s="19" t="inlineStr">
         <is>
-          <t>Model 52.6% (fair -111). Your call.</t>
+          <t>Model 52.3% (fair -110). Your call.</t>
         </is>
       </c>
       <c r="O75" s="15" t="n"/>
@@ -14589,10 +14589,10 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>0.4737818181818181</v>
+        <v>0.4766727272727272</v>
       </c>
       <c r="G76" s="14" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H76" s="15" t="n">
         <v>-120</v>
@@ -14619,7 +14619,7 @@
       </c>
       <c r="N76" s="19" t="inlineStr">
         <is>
-          <t>Model 47.4% (fair +111). Your call.</t>
+          <t>Model 47.7% (fair +110). Your call.</t>
         </is>
       </c>
       <c r="O76" s="15" t="n"/>
@@ -14655,13 +14655,13 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>0.3285585585585586</v>
+        <v>0.3393087557603687</v>
       </c>
       <c r="G77" s="14" t="n">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="H77" s="15" t="n">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="I77" s="13">
         <f>IF($H$77="","",IF($H$77&lt;0,-$H$77/(-$H$77+100),100/($H$77+100)))</f>
@@ -14685,7 +14685,7 @@
       </c>
       <c r="N77" s="19" t="inlineStr">
         <is>
-          <t>Model 32.9% (fair +204). Your call.</t>
+          <t>Model 33.9% (fair +195). Your call.</t>
         </is>
       </c>
       <c r="O77" s="15" t="n"/>
@@ -14721,10 +14721,10 @@
         </is>
       </c>
       <c r="F78" s="13" t="n">
-        <v>0.6714396396396396</v>
+        <v>0.6607234234234234</v>
       </c>
       <c r="G78" s="14" t="n">
-        <v>-204</v>
+        <v>-195</v>
       </c>
       <c r="H78" s="15" t="n">
         <v>-122</v>
@@ -14751,7 +14751,7 @@
       </c>
       <c r="N78" s="19" t="inlineStr">
         <is>
-          <t>Model 67.1% (fair -204). Your call.</t>
+          <t>Model 66.1% (fair -195). Your call.</t>
         </is>
       </c>
       <c r="O78" s="15" t="n"/>
@@ -14783,17 +14783,17 @@
       </c>
       <c r="E79" s="12" t="inlineStr">
         <is>
-          <t>Over 9.5</t>
+          <t>Over 9</t>
         </is>
       </c>
       <c r="F79" s="13" t="n">
-        <v>0.5817</v>
+        <v>0.6131</v>
       </c>
       <c r="G79" s="14" t="n">
-        <v>-139</v>
+        <v>-158</v>
       </c>
       <c r="H79" s="15" t="n">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="I79" s="13">
         <f>IF($H$79="","",IF($H$79&lt;0,-$H$79/(-$H$79+100),100/($H$79+100)))</f>
@@ -14817,7 +14817,7 @@
       </c>
       <c r="N79" s="19" t="inlineStr">
         <is>
-          <t>Model 58.2% (fair -139). Your call.</t>
+          <t>Model 61.3% (fair -158). Your call.</t>
         </is>
       </c>
       <c r="O79" s="15" t="n"/>
@@ -14849,17 +14849,17 @@
       </c>
       <c r="E80" s="20" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Under 9</t>
         </is>
       </c>
       <c r="F80" s="13" t="n">
-        <v>0.4183</v>
+        <v>0.3869</v>
       </c>
       <c r="G80" s="14" t="n">
-        <v>139</v>
+        <v>158</v>
       </c>
       <c r="H80" s="15" t="n">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="I80" s="13">
         <f>IF($H$80="","",IF($H$80&lt;0,-$H$80/(-$H$80+100),100/($H$80+100)))</f>
@@ -14883,7 +14883,7 @@
       </c>
       <c r="N80" s="19" t="inlineStr">
         <is>
-          <t>Model 41.8% (fair +139). Your call.</t>
+          <t>Model 38.7% (fair +158). Your call.</t>
         </is>
       </c>
       <c r="O80" s="15" t="n"/>
@@ -14919,10 +14919,10 @@
         </is>
       </c>
       <c r="F81" s="13" t="n">
-        <v>0.5008208955223882</v>
+        <v>0.4944402985074627</v>
       </c>
       <c r="G81" s="14" t="n">
-        <v>-100</v>
+        <v>102</v>
       </c>
       <c r="H81" s="15" t="n">
         <v>168</v>
@@ -14949,7 +14949,7 @@
       </c>
       <c r="N81" s="19" t="inlineStr">
         <is>
-          <t>Model 50.1% (fair -100). Your call.</t>
+          <t>Model 49.4% (fair +102). Your call.</t>
         </is>
       </c>
       <c r="O81" s="15" t="n"/>
@@ -14985,10 +14985,10 @@
         </is>
       </c>
       <c r="F82" s="13" t="n">
-        <v>0.4991703703703703</v>
+        <v>0.5055296296296296</v>
       </c>
       <c r="G82" s="14" t="n">
-        <v>100</v>
+        <v>-102</v>
       </c>
       <c r="H82" s="15" t="n">
         <v>-170</v>
@@ -15015,7 +15015,7 @@
       </c>
       <c r="N82" s="19" t="inlineStr">
         <is>
-          <t>Model 49.9% (fair +100). Your call.</t>
+          <t>Model 50.6% (fair -102). Your call.</t>
         </is>
       </c>
       <c r="O82" s="15" t="n"/>
@@ -15051,13 +15051,13 @@
         </is>
       </c>
       <c r="F83" s="13" t="n">
-        <v>0.4748198198198199</v>
+        <v>0.4845161290322582</v>
       </c>
       <c r="G83" s="14" t="n">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="H83" s="15" t="n">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="I83" s="13">
         <f>IF($H$83="","",IF($H$83&lt;0,-$H$83/(-$H$83+100),100/($H$83+100)))</f>
@@ -15081,7 +15081,7 @@
       </c>
       <c r="N83" s="19" t="inlineStr">
         <is>
-          <t>Model 47.5% (fair +111). Your call.</t>
+          <t>Model 48.5% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O83" s="15" t="n"/>
@@ -15117,13 +15117,13 @@
         </is>
       </c>
       <c r="F84" s="13" t="n">
-        <v>0.5251666666666667</v>
+        <v>0.5154774774774774</v>
       </c>
       <c r="G84" s="14" t="n">
-        <v>-111</v>
+        <v>-106</v>
       </c>
       <c r="H84" s="15" t="n">
-        <v>-125</v>
+        <v>-122</v>
       </c>
       <c r="I84" s="13">
         <f>IF($H$84="","",IF($H$84&lt;0,-$H$84/(-$H$84+100),100/($H$84+100)))</f>
@@ -15147,7 +15147,7 @@
       </c>
       <c r="N84" s="19" t="inlineStr">
         <is>
-          <t>Model 52.5% (fair -111). Your call.</t>
+          <t>Model 51.5% (fair -106). Your call.</t>
         </is>
       </c>
       <c r="O84" s="15" t="n"/>
@@ -15183,13 +15183,13 @@
         </is>
       </c>
       <c r="F85" s="13" t="n">
-        <v>0.55175</v>
+        <v>0.5659134615384616</v>
       </c>
       <c r="G85" s="14" t="n">
-        <v>-123</v>
+        <v>-130</v>
       </c>
       <c r="H85" s="15" t="n">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="I85" s="13">
         <f>IF($H$85="","",IF($H$85&lt;0,-$H$85/(-$H$85+100),100/($H$85+100)))</f>
@@ -15213,7 +15213,7 @@
       </c>
       <c r="N85" s="19" t="inlineStr">
         <is>
-          <t>Model 55.2% (fair -123). Your call.</t>
+          <t>Model 56.6% (fair -130). Your call.</t>
         </is>
       </c>
       <c r="O85" s="15" t="n"/>
@@ -15249,13 +15249,13 @@
         </is>
       </c>
       <c r="F86" s="13" t="n">
-        <v>0.4482333333333333</v>
+        <v>0.434076923076923</v>
       </c>
       <c r="G86" s="14" t="n">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="H86" s="15" t="n">
-        <v>-113</v>
+        <v>-108</v>
       </c>
       <c r="I86" s="13">
         <f>IF($H$86="","",IF($H$86&lt;0,-$H$86/(-$H$86+100),100/($H$86+100)))</f>
@@ -15279,7 +15279,7 @@
       </c>
       <c r="N86" s="19" t="inlineStr">
         <is>
-          <t>Model 44.8% (fair +123). Your call.</t>
+          <t>Model 43.4% (fair +130). Your call.</t>
         </is>
       </c>
       <c r="O86" s="15" t="n"/>
@@ -15315,13 +15315,13 @@
         </is>
       </c>
       <c r="F87" s="13" t="n">
-        <v>0.3357142857142857</v>
+        <v>0.3344604316546762</v>
       </c>
       <c r="G87" s="14" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H87" s="15" t="n">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I87" s="13">
         <f>IF($H$87="","",IF($H$87&lt;0,-$H$87/(-$H$87+100),100/($H$87+100)))</f>
@@ -15345,7 +15345,7 @@
       </c>
       <c r="N87" s="19" t="inlineStr">
         <is>
-          <t>Model 33.6% (fair +198). Your call.</t>
+          <t>Model 33.4% (fair +199). Your call.</t>
         </is>
       </c>
       <c r="O87" s="15" t="n"/>
@@ -15381,13 +15381,13 @@
         </is>
       </c>
       <c r="F88" s="13" t="n">
-        <v>0.6643122807017544</v>
+        <v>0.6655499999999999</v>
       </c>
       <c r="G88" s="14" t="n">
-        <v>-198</v>
+        <v>-199</v>
       </c>
       <c r="H88" s="15" t="n">
-        <v>-185</v>
+        <v>-180</v>
       </c>
       <c r="I88" s="13">
         <f>IF($H$88="","",IF($H$88&lt;0,-$H$88/(-$H$88+100),100/($H$88+100)))</f>
@@ -15411,7 +15411,7 @@
       </c>
       <c r="N88" s="19" t="inlineStr">
         <is>
-          <t>Model 66.4% (fair -198). Your call.</t>
+          <t>Model 66.6% (fair -199). Your call.</t>
         </is>
       </c>
       <c r="O88" s="15" t="n"/>
@@ -15447,13 +15447,13 @@
         </is>
       </c>
       <c r="F89" s="13" t="n">
-        <v>0.528281981981982</v>
+        <v>0.5274</v>
       </c>
       <c r="G89" s="14" t="n">
         <v>-112</v>
       </c>
       <c r="H89" s="15" t="n">
-        <v>-122</v>
+        <v>-120</v>
       </c>
       <c r="I89" s="13">
         <f>IF($H$89="","",IF($H$89&lt;0,-$H$89/(-$H$89+100),100/($H$89+100)))</f>
@@ -15477,7 +15477,7 @@
       </c>
       <c r="N89" s="19" t="inlineStr">
         <is>
-          <t>Model 52.8% (fair -112). Your call.</t>
+          <t>Model 52.7% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O89" s="15" t="n"/>
@@ -15513,7 +15513,7 @@
         </is>
       </c>
       <c r="F90" s="13" t="n">
-        <v>0.471705069124424</v>
+        <v>0.4726267281105991</v>
       </c>
       <c r="G90" s="14" t="n">
         <v>112</v>
@@ -15543,7 +15543,7 @@
       </c>
       <c r="N90" s="19" t="inlineStr">
         <is>
-          <t>Model 47.2% (fair +112). Your call.</t>
+          <t>Model 47.3% (fair +112). Your call.</t>
         </is>
       </c>
       <c r="O90" s="15" t="n"/>
@@ -15579,13 +15579,13 @@
         </is>
       </c>
       <c r="F91" s="13" t="n">
-        <v>0.5749</v>
+        <v>0.6437</v>
       </c>
       <c r="G91" s="14" t="n">
-        <v>-135</v>
+        <v>-181</v>
       </c>
       <c r="H91" s="15" t="n">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="I91" s="13">
         <f>IF($H$91="","",IF($H$91&lt;0,-$H$91/(-$H$91+100),100/($H$91+100)))</f>
@@ -15609,7 +15609,7 @@
       </c>
       <c r="N91" s="19" t="inlineStr">
         <is>
-          <t>Model 57.5% (fair -135). Your call.</t>
+          <t>Model 64.4% (fair -181). Your call.</t>
         </is>
       </c>
       <c r="O91" s="15" t="n"/>
@@ -15645,10 +15645,10 @@
         </is>
       </c>
       <c r="F92" s="13" t="n">
-        <v>0.4250731707317073</v>
+        <v>0.3563</v>
       </c>
       <c r="G92" s="14" t="n">
-        <v>135</v>
+        <v>181</v>
       </c>
       <c r="H92" s="15" t="n">
         <v>105</v>
@@ -15675,7 +15675,7 @@
       </c>
       <c r="N92" s="19" t="inlineStr">
         <is>
-          <t>Model 42.5% (fair +135). Your call.</t>
+          <t>Model 35.6% (fair +181). Your call.</t>
         </is>
       </c>
       <c r="O92" s="15" t="n"/>
@@ -15711,13 +15711,13 @@
         </is>
       </c>
       <c r="F93" s="13" t="n">
-        <v>0.6276588235294118</v>
+        <v>0.6291000000000001</v>
       </c>
       <c r="G93" s="14" t="n">
-        <v>-169</v>
+        <v>-170</v>
       </c>
       <c r="H93" s="15" t="n">
-        <v>-155</v>
+        <v>-150</v>
       </c>
       <c r="I93" s="13">
         <f>IF($H$93="","",IF($H$93&lt;0,-$H$93/(-$H$93+100),100/($H$93+100)))</f>
@@ -15741,7 +15741,7 @@
       </c>
       <c r="N93" s="19" t="inlineStr">
         <is>
-          <t>Model 62.8% (fair -169). Your call.</t>
+          <t>Model 62.9% (fair -170). Your call.</t>
         </is>
       </c>
       <c r="O93" s="15" t="n"/>
@@ -15777,13 +15777,13 @@
         </is>
       </c>
       <c r="F94" s="13" t="n">
-        <v>0.3723529411764706</v>
+        <v>0.3709016393442623</v>
       </c>
       <c r="G94" s="14" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H94" s="15" t="n">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="I94" s="13">
         <f>IF($H$94="","",IF($H$94&lt;0,-$H$94/(-$H$94+100),100/($H$94+100)))</f>
@@ -15807,7 +15807,7 @@
       </c>
       <c r="N94" s="19" t="inlineStr">
         <is>
-          <t>Model 37.2% (fair +169). Your call.</t>
+          <t>Model 37.1% (fair +170). Your call.</t>
         </is>
       </c>
       <c r="O94" s="15" t="n"/>
@@ -15975,10 +15975,10 @@
         </is>
       </c>
       <c r="F97" s="13" t="n">
-        <v>0.4844607843137255</v>
+        <v>0.4867647058823529</v>
       </c>
       <c r="G97" s="14" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H97" s="15" t="n">
         <v>104</v>
@@ -16005,7 +16005,7 @@
       </c>
       <c r="N97" s="19" t="inlineStr">
         <is>
-          <t>Model 48.4% (fair +106). Your call.</t>
+          <t>Model 48.7% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O97" s="15" t="n"/>
@@ -16041,13 +16041,13 @@
         </is>
       </c>
       <c r="F98" s="13" t="n">
-        <v>0.5154923076923077</v>
+        <v>0.5132196078431371</v>
       </c>
       <c r="G98" s="14" t="n">
-        <v>-106</v>
+        <v>-105</v>
       </c>
       <c r="H98" s="15" t="n">
-        <v>-108</v>
+        <v>-104</v>
       </c>
       <c r="I98" s="13">
         <f>IF($H$98="","",IF($H$98&lt;0,-$H$98/(-$H$98+100),100/($H$98+100)))</f>
@@ -16071,7 +16071,7 @@
       </c>
       <c r="N98" s="19" t="inlineStr">
         <is>
-          <t>Model 51.5% (fair -106). Your call.</t>
+          <t>Model 51.3% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O98" s="15" t="n"/>
@@ -16179,7 +16179,7 @@
         <v>-342</v>
       </c>
       <c r="H100" s="15" t="n">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="I100" s="13">
         <f>IF($H$100="","",IF($H$100&lt;0,-$H$100/(-$H$100+100),100/($H$100+100)))</f>
@@ -16239,13 +16239,13 @@
         </is>
       </c>
       <c r="F101" s="13" t="n">
-        <v>0.3937692307692308</v>
+        <v>0.3886516853932585</v>
       </c>
       <c r="G101" s="14" t="n">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="H101" s="15" t="n">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="I101" s="13">
         <f>IF($H$101="","",IF($H$101&lt;0,-$H$101/(-$H$101+100),100/($H$101+100)))</f>
@@ -16269,7 +16269,7 @@
       </c>
       <c r="N101" s="19" t="inlineStr">
         <is>
-          <t>Model 39.4% (fair +154). Your call.</t>
+          <t>Model 38.9% (fair +157). Your call.</t>
         </is>
       </c>
       <c r="O101" s="15" t="n"/>
@@ -16305,13 +16305,13 @@
         </is>
       </c>
       <c r="F102" s="13" t="n">
-        <v>0.6062062500000001</v>
+        <v>0.6113429657794677</v>
       </c>
       <c r="G102" s="14" t="n">
-        <v>-154</v>
+        <v>-157</v>
       </c>
       <c r="H102" s="15" t="n">
-        <v>-156</v>
+        <v>-163</v>
       </c>
       <c r="I102" s="13">
         <f>IF($H$102="","",IF($H$102&lt;0,-$H$102/(-$H$102+100),100/($H$102+100)))</f>
@@ -16335,7 +16335,7 @@
       </c>
       <c r="N102" s="19" t="inlineStr">
         <is>
-          <t>Model 60.6% (fair -154). Your call.</t>
+          <t>Model 61.1% (fair -157). Your call.</t>
         </is>
       </c>
       <c r="O102" s="15" t="n"/>
@@ -16371,13 +16371,13 @@
         </is>
       </c>
       <c r="F103" s="13" t="n">
-        <v>0.5958069767441861</v>
+        <v>0.5867307692307692</v>
       </c>
       <c r="G103" s="14" t="n">
-        <v>-147</v>
+        <v>-142</v>
       </c>
       <c r="H103" s="15" t="n">
-        <v>-115</v>
+        <v>-108</v>
       </c>
       <c r="I103" s="13">
         <f>IF($H$103="","",IF($H$103&lt;0,-$H$103/(-$H$103+100),100/($H$103+100)))</f>
@@ -16401,7 +16401,7 @@
       </c>
       <c r="N103" s="19" t="inlineStr">
         <is>
-          <t>Model 59.6% (fair -147). Your call.</t>
+          <t>Model 58.7% (fair -142). Your call.</t>
         </is>
       </c>
       <c r="O103" s="15" t="n"/>
@@ -16437,13 +16437,13 @@
         </is>
       </c>
       <c r="F104" s="13" t="n">
-        <v>0.4041784037558686</v>
+        <v>0.413235294117647</v>
       </c>
       <c r="G104" s="14" t="n">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="H104" s="15" t="n">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="I104" s="13">
         <f>IF($H$104="","",IF($H$104&lt;0,-$H$104/(-$H$104+100),100/($H$104+100)))</f>
@@ -16467,7 +16467,7 @@
       </c>
       <c r="N104" s="19" t="inlineStr">
         <is>
-          <t>Model 40.4% (fair +147). Your call.</t>
+          <t>Model 41.3% (fair +142). Your call.</t>
         </is>
       </c>
       <c r="O104" s="15" t="n"/>
@@ -16503,13 +16503,13 @@
         </is>
       </c>
       <c r="F105" s="13" t="n">
-        <v>0.4281363636363636</v>
+        <v>0.4282882882882883</v>
       </c>
       <c r="G105" s="14" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H105" s="15" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="I105" s="13">
         <f>IF($H$105="","",IF($H$105&lt;0,-$H$105/(-$H$105+100),100/($H$105+100)))</f>
@@ -16533,7 +16533,7 @@
       </c>
       <c r="N105" s="19" t="inlineStr">
         <is>
-          <t>Model 42.8% (fair +134). Your call.</t>
+          <t>Model 42.8% (fair +133). Your call.</t>
         </is>
       </c>
       <c r="O105" s="15" t="n"/>
@@ -16569,13 +16569,13 @@
         </is>
       </c>
       <c r="F106" s="13" t="n">
-        <v>0.5718304347826088</v>
+        <v>0.5717237885462555</v>
       </c>
       <c r="G106" s="14" t="n">
-        <v>-134</v>
+        <v>-133</v>
       </c>
       <c r="H106" s="15" t="n">
-        <v>-130</v>
+        <v>-127</v>
       </c>
       <c r="I106" s="13">
         <f>IF($H$106="","",IF($H$106&lt;0,-$H$106/(-$H$106+100),100/($H$106+100)))</f>
@@ -16599,7 +16599,7 @@
       </c>
       <c r="N106" s="19" t="inlineStr">
         <is>
-          <t>Model 57.2% (fair -134). Your call.</t>
+          <t>Model 57.2% (fair -133). Your call.</t>
         </is>
       </c>
       <c r="O106" s="15" t="n"/>
@@ -16767,13 +16767,13 @@
         </is>
       </c>
       <c r="F109" s="13" t="n">
-        <v>0.4236554621848739</v>
+        <v>0.4195081967213115</v>
       </c>
       <c r="G109" s="14" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H109" s="15" t="n">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="I109" s="13">
         <f>IF($H$109="","",IF($H$109&lt;0,-$H$109/(-$H$109+100),100/($H$109+100)))</f>
@@ -16797,7 +16797,7 @@
       </c>
       <c r="N109" s="19" t="inlineStr">
         <is>
-          <t>Model 42.4% (fair +136). Your call.</t>
+          <t>Model 42.0% (fair +138). Your call.</t>
         </is>
       </c>
       <c r="O109" s="15" t="n"/>
@@ -16833,13 +16833,13 @@
         </is>
       </c>
       <c r="F110" s="13" t="n">
-        <v>0.5763063829787235</v>
+        <v>0.5804697478991597</v>
       </c>
       <c r="G110" s="14" t="n">
-        <v>-136</v>
+        <v>-138</v>
       </c>
       <c r="H110" s="15" t="n">
-        <v>-135</v>
+        <v>-138</v>
       </c>
       <c r="I110" s="13">
         <f>IF($H$110="","",IF($H$110&lt;0,-$H$110/(-$H$110+100),100/($H$110+100)))</f>
@@ -16863,7 +16863,7 @@
       </c>
       <c r="N110" s="19" t="inlineStr">
         <is>
-          <t>Model 57.6% (fair -136). Your call.</t>
+          <t>Model 58.0% (fair -138). Your call.</t>
         </is>
       </c>
       <c r="O110" s="15" t="n"/>
@@ -16895,17 +16895,17 @@
       </c>
       <c r="E111" s="12" t="inlineStr">
         <is>
-          <t>Over 9</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F111" s="13" t="n">
-        <v>0.53585</v>
+        <v>0.5172350230414747</v>
       </c>
       <c r="G111" s="14" t="n">
-        <v>-115</v>
+        <v>-107</v>
       </c>
       <c r="H111" s="15" t="n">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="I111" s="13">
         <f>IF($H$111="","",IF($H$111&lt;0,-$H$111/(-$H$111+100),100/($H$111+100)))</f>
@@ -16929,7 +16929,7 @@
       </c>
       <c r="N111" s="19" t="inlineStr">
         <is>
-          <t>Model 53.6% (fair -115). Your call.</t>
+          <t>Model 51.7% (fair -107). Your call.</t>
         </is>
       </c>
       <c r="O111" s="15" t="n"/>
@@ -16961,17 +16961,17 @@
       </c>
       <c r="E112" s="20" t="inlineStr">
         <is>
-          <t>Under 9</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F112" s="13" t="n">
-        <v>0.4641764705882352</v>
+        <v>0.4827272727272727</v>
       </c>
       <c r="G112" s="14" t="n">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="H112" s="15" t="n">
-        <v>-104</v>
+        <v>-120</v>
       </c>
       <c r="I112" s="13">
         <f>IF($H$112="","",IF($H$112&lt;0,-$H$112/(-$H$112+100),100/($H$112+100)))</f>
@@ -16995,7 +16995,7 @@
       </c>
       <c r="N112" s="19" t="inlineStr">
         <is>
-          <t>Model 46.4% (fair +115). Your call.</t>
+          <t>Model 48.3% (fair +107). Your call.</t>
         </is>
       </c>
       <c r="O112" s="15" t="n"/>
@@ -17031,13 +17031,13 @@
         </is>
       </c>
       <c r="F113" s="13" t="n">
-        <v>0.4123111111111111</v>
+        <v>0.4080434782608696</v>
       </c>
       <c r="G113" s="14" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H113" s="15" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="I113" s="13">
         <f>IF($H$113="","",IF($H$113&lt;0,-$H$113/(-$H$113+100),100/($H$113+100)))</f>
@@ -17061,7 +17061,7 @@
       </c>
       <c r="N113" s="19" t="inlineStr">
         <is>
-          <t>Model 41.2% (fair +143). Your call.</t>
+          <t>Model 40.8% (fair +145). Your call.</t>
         </is>
       </c>
       <c r="O113" s="15" t="n"/>
@@ -17097,13 +17097,13 @@
         </is>
       </c>
       <c r="F114" s="13" t="n">
-        <v>0.5877000000000001</v>
+        <v>0.591978431372549</v>
       </c>
       <c r="G114" s="14" t="n">
-        <v>-143</v>
+        <v>-145</v>
       </c>
       <c r="H114" s="15" t="n">
-        <v>-150</v>
+        <v>-155</v>
       </c>
       <c r="I114" s="13">
         <f>IF($H$114="","",IF($H$114&lt;0,-$H$114/(-$H$114+100),100/($H$114+100)))</f>
@@ -17127,7 +17127,7 @@
       </c>
       <c r="N114" s="19" t="inlineStr">
         <is>
-          <t>Model 58.8% (fair -143). Your call.</t>
+          <t>Model 59.2% (fair -145). Your call.</t>
         </is>
       </c>
       <c r="O114" s="15" t="n"/>
@@ -17163,10 +17163,10 @@
         </is>
       </c>
       <c r="F115" s="13" t="n">
-        <v>0.406431718061674</v>
+        <v>0.4036563876651982</v>
       </c>
       <c r="G115" s="14" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="H115" s="15" t="n">
         <v>127</v>
@@ -17193,7 +17193,7 @@
       </c>
       <c r="N115" s="19" t="inlineStr">
         <is>
-          <t>Model 40.6% (fair +146). Your call.</t>
+          <t>Model 40.4% (fair +148). Your call.</t>
         </is>
       </c>
       <c r="O115" s="15" t="n"/>
@@ -17229,10 +17229,10 @@
         </is>
       </c>
       <c r="F116" s="13" t="n">
-        <v>0.5935991189427313</v>
+        <v>0.5963405286343613</v>
       </c>
       <c r="G116" s="14" t="n">
-        <v>-146</v>
+        <v>-148</v>
       </c>
       <c r="H116" s="15" t="n">
         <v>-127</v>
@@ -17259,7 +17259,7 @@
       </c>
       <c r="N116" s="19" t="inlineStr">
         <is>
-          <t>Model 59.4% (fair -146). Your call.</t>
+          <t>Model 59.6% (fair -148). Your call.</t>
         </is>
       </c>
       <c r="O116" s="15" t="n"/>
@@ -17295,13 +17295,13 @@
         </is>
       </c>
       <c r="F117" s="13" t="n">
-        <v>0.6575</v>
+        <v>0.6516999999999999</v>
       </c>
       <c r="G117" s="14" t="n">
-        <v>-192</v>
+        <v>-187</v>
       </c>
       <c r="H117" s="15" t="n">
-        <v>-105</v>
+        <v>-103</v>
       </c>
       <c r="I117" s="13">
         <f>IF($H$117="","",IF($H$117&lt;0,-$H$117/(-$H$117+100),100/($H$117+100)))</f>
@@ -17325,7 +17325,7 @@
       </c>
       <c r="N117" s="19" t="inlineStr">
         <is>
-          <t>Model 65.8% (fair -192). Your call.</t>
+          <t>Model 65.2% (fair -187). Your call.</t>
         </is>
       </c>
       <c r="O117" s="15" t="n"/>
@@ -17361,13 +17361,13 @@
         </is>
       </c>
       <c r="F118" s="13" t="n">
-        <v>0.3425</v>
+        <v>0.3483000000000001</v>
       </c>
       <c r="G118" s="14" t="n">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="H118" s="15" t="n">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="I118" s="13">
         <f>IF($H$118="","",IF($H$118&lt;0,-$H$118/(-$H$118+100),100/($H$118+100)))</f>
@@ -17391,7 +17391,7 @@
       </c>
       <c r="N118" s="19" t="inlineStr">
         <is>
-          <t>Model 34.2% (fair +192). Your call.</t>
+          <t>Model 34.8% (fair +187). Your call.</t>
         </is>
       </c>
       <c r="O118" s="15" t="n"/>
@@ -17427,13 +17427,13 @@
         </is>
       </c>
       <c r="F119" s="13" t="n">
-        <v>0.4246800000000001</v>
+        <v>0.4240625</v>
       </c>
       <c r="G119" s="14" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H119" s="15" t="n">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="I119" s="13">
         <f>IF($H$119="","",IF($H$119&lt;0,-$H$119/(-$H$119+100),100/($H$119+100)))</f>
@@ -17457,7 +17457,7 @@
       </c>
       <c r="N119" s="19" t="inlineStr">
         <is>
-          <t>Model 42.5% (fair +135). Your call.</t>
+          <t>Model 42.4% (fair +136). Your call.</t>
         </is>
       </c>
       <c r="O119" s="15" t="n"/>
@@ -17493,13 +17493,13 @@
         </is>
       </c>
       <c r="F120" s="13" t="n">
-        <v>0.5752925925925925</v>
+        <v>0.5759310861423221</v>
       </c>
       <c r="G120" s="14" t="n">
-        <v>-135</v>
+        <v>-136</v>
       </c>
       <c r="H120" s="15" t="n">
-        <v>-170</v>
+        <v>-167</v>
       </c>
       <c r="I120" s="13">
         <f>IF($H$120="","",IF($H$120&lt;0,-$H$120/(-$H$120+100),100/($H$120+100)))</f>
@@ -17523,7 +17523,7 @@
       </c>
       <c r="N120" s="19" t="inlineStr">
         <is>
-          <t>Model 57.5% (fair -135). Your call.</t>
+          <t>Model 57.6% (fair -136). Your call.</t>
         </is>
       </c>
       <c r="O120" s="15" t="n"/>
@@ -18075,13 +18075,13 @@
         </is>
       </c>
       <c r="F129" s="13" t="n">
-        <v>0.5606823529411765</v>
+        <v>0.55335</v>
       </c>
       <c r="G129" s="14" t="n">
-        <v>-128</v>
+        <v>-124</v>
       </c>
       <c r="H129" s="15" t="n">
-        <v>-104</v>
+        <v>100</v>
       </c>
       <c r="I129" s="13">
         <f>IF($H$129="","",IF($H$129&lt;0,-$H$129/(-$H$129+100),100/($H$129+100)))</f>
@@ -18105,7 +18105,7 @@
       </c>
       <c r="N129" s="19" t="inlineStr">
         <is>
-          <t>Model 56.1% (fair -128). Your call.</t>
+          <t>Model 55.3% (fair -124). Your call.</t>
         </is>
       </c>
       <c r="O129" s="15" t="n"/>
@@ -18141,13 +18141,13 @@
         </is>
       </c>
       <c r="F130" s="13" t="n">
-        <v>0.4393137254901961</v>
+        <v>0.4466392156862745</v>
       </c>
       <c r="G130" s="14" t="n">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="H130" s="15" t="n">
-        <v>104</v>
+        <v>-104</v>
       </c>
       <c r="I130" s="13">
         <f>IF($H$130="","",IF($H$130&lt;0,-$H$130/(-$H$130+100),100/($H$130+100)))</f>
@@ -18171,7 +18171,7 @@
       </c>
       <c r="N130" s="19" t="inlineStr">
         <is>
-          <t>Model 43.9% (fair +128). Your call.</t>
+          <t>Model 44.7% (fair +124). Your call.</t>
         </is>
       </c>
       <c r="O130" s="15" t="n"/>
@@ -18207,13 +18207,13 @@
         </is>
       </c>
       <c r="F131" s="13" t="n">
-        <v>0.6048391304347827</v>
+        <v>0.6052920704845816</v>
       </c>
       <c r="G131" s="14" t="n">
         <v>-153</v>
       </c>
       <c r="H131" s="15" t="n">
-        <v>-130</v>
+        <v>-127</v>
       </c>
       <c r="I131" s="13">
         <f>IF($H$131="","",IF($H$131&lt;0,-$H$131/(-$H$131+100),100/($H$131+100)))</f>
@@ -18273,13 +18273,13 @@
         </is>
       </c>
       <c r="F132" s="13" t="n">
-        <v>0.3951612903225807</v>
+        <v>0.3947272727272727</v>
       </c>
       <c r="G132" s="14" t="n">
         <v>153</v>
       </c>
       <c r="H132" s="15" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="I132" s="13">
         <f>IF($H$132="","",IF($H$132&lt;0,-$H$132/(-$H$132+100),100/($H$132+100)))</f>
@@ -18539,7 +18539,7 @@
         <v>-113</v>
       </c>
       <c r="H136" s="15" t="n">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="I136" s="13">
         <f>IF($H$136="","",IF($H$136&lt;0,-$H$136/(-$H$136+100),100/($H$136+100)))</f>
@@ -18599,10 +18599,10 @@
         </is>
       </c>
       <c r="F137" s="13" t="n">
-        <v>0.6065484978540773</v>
+        <v>0.6092884120171673</v>
       </c>
       <c r="G137" s="14" t="n">
-        <v>-154</v>
+        <v>-156</v>
       </c>
       <c r="H137" s="15" t="n">
         <v>-133</v>
@@ -18629,7 +18629,7 @@
       </c>
       <c r="N137" s="19" t="inlineStr">
         <is>
-          <t>Model 60.7% (fair -154). Your call.</t>
+          <t>Model 60.9% (fair -156). Your call.</t>
         </is>
       </c>
       <c r="O137" s="15" t="n"/>
@@ -18665,13 +18665,13 @@
         </is>
       </c>
       <c r="F138" s="13" t="n">
-        <v>0.3934234234234235</v>
+        <v>0.390704845814978</v>
       </c>
       <c r="G138" s="14" t="n">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="H138" s="15" t="n">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="I138" s="13">
         <f>IF($H$138="","",IF($H$138&lt;0,-$H$138/(-$H$138+100),100/($H$138+100)))</f>
@@ -18695,7 +18695,7 @@
       </c>
       <c r="N138" s="19" t="inlineStr">
         <is>
-          <t>Model 39.3% (fair +154). Your call.</t>
+          <t>Model 39.1% (fair +156). Your call.</t>
         </is>
       </c>
       <c r="O138" s="15" t="n"/>
@@ -18867,7 +18867,7 @@
         <v>124</v>
       </c>
       <c r="H141" s="15" t="n">
-        <v>-105</v>
+        <v>-103</v>
       </c>
       <c r="I141" s="13">
         <f>IF($H$141="","",IF($H$141&lt;0,-$H$141/(-$H$141+100),100/($H$141+100)))</f>
@@ -18933,7 +18933,7 @@
         <v>-124</v>
       </c>
       <c r="H142" s="15" t="n">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="I142" s="13">
         <f>IF($H$142="","",IF($H$142&lt;0,-$H$142/(-$H$142+100),100/($H$142+100)))</f>
@@ -18993,13 +18993,13 @@
         </is>
       </c>
       <c r="F143" s="13" t="n">
-        <v>0.2826</v>
+        <v>0.2826171875</v>
       </c>
       <c r="G143" s="14" t="n">
         <v>254</v>
       </c>
       <c r="H143" s="15" t="n">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="I143" s="13">
         <f>IF($H$143="","",IF($H$143&lt;0,-$H$143/(-$H$143+100),100/($H$143+100)))</f>
@@ -19264,10 +19264,10 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.2906666666666666</v>
+        <v>0.2847826086956522</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="H5" s="15" t="n">
         <v>245</v>
@@ -19294,7 +19294,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 29.1% (fair +244). Your call.</t>
+          <t>Model 28.5% (fair +251). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -19330,13 +19330,13 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.7092857142857143</v>
+        <v>0.7152417910447761</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>-244</v>
+        <v>-251</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>-250</v>
+        <v>-235</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -19360,7 +19360,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 70.9% (fair -244). Your call.</t>
+          <t>Model 71.5% (fair -251). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -19392,17 +19392,17 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Over 181.5</t>
+          <t>Over 183</t>
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.6680980392156862</v>
+        <v>0.631044776119403</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-201</v>
+        <v>-171</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>-104</v>
+        <v>101</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -19426,7 +19426,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 66.8% (fair -201). Your call.</t>
+          <t>Model 63.1% (fair -171). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -19458,17 +19458,17 @@
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>Under 181.5</t>
+          <t>Under 183</t>
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.3319</v>
+        <v>0.3689</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>201</v>
+        <v>171</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>-104</v>
+        <v>101</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -19492,7 +19492,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 33.2% (fair +201). Your call.</t>
+          <t>Model 36.9% (fair +171). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -19528,13 +19528,13 @@
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.4974749999999999</v>
+        <v>0.4757</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>-108</v>
+        <v>111</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -19558,7 +19558,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 49.7% (fair +101). Your call.</t>
+          <t>Model 47.6% (fair +110). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -19594,10 +19594,10 @@
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.5024999999999999</v>
+        <v>0.5243</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-101</v>
+        <v>-110</v>
       </c>
       <c r="H10" s="15" t="n">
         <v>108</v>
@@ -19624,7 +19624,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 50.2% (fair -101). Your call.</t>
+          <t>Model 52.4% (fair -110). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -19660,13 +19660,13 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.7708850574712643</v>
+        <v>0.7269953051643192</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>-336</v>
+        <v>-266</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>-335</v>
+        <v>-326</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -19690,7 +19690,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 77.1% (fair -336). Your call.</t>
+          <t>Model 72.7% (fair -266). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -19726,13 +19726,13 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.2291494252873564</v>
+        <v>0.2729976019184652</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>336</v>
+        <v>266</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>335</v>
+        <v>317</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -19756,7 +19756,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 22.9% (fair +336). Your call.</t>
+          <t>Model 27.3% (fair +266). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -19920,14 +19920,14 @@
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Seattle Storm -4.5</t>
+          <t>Seattle Storm -4</t>
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.1855</v>
+        <v>0.1973</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>439</v>
+        <v>407</v>
       </c>
       <c r="H15" s="15" t="n">
         <v>430</v>
@@ -19954,7 +19954,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 18.6% (fair +439). Your call.</t>
+          <t>Model 19.7% (fair +407). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -19986,17 +19986,17 @@
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>Atlanta Dream +4.5</t>
+          <t>Atlanta Dream +4</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.8145</v>
+        <v>0.8027</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>-439</v>
+        <v>-407</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -20020,7 +20020,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 81.5% (fair -439). Your call.</t>
+          <t>Model 80.3% (fair -407). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -20056,10 +20056,10 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.6261328125000001</v>
+        <v>0.6243046875</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>-167</v>
+        <v>-166</v>
       </c>
       <c r="H17" s="15" t="n">
         <v>-156</v>
@@ -20086,7 +20086,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 62.6% (fair -167). Your call.</t>
+          <t>Model 62.4% (fair -166). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -20122,13 +20122,13 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.3738846153846154</v>
+        <v>0.375703125</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -20152,7 +20152,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 37.4% (fair +167). Your call.</t>
+          <t>Model 37.6% (fair +166). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -20316,17 +20316,17 @@
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Dallas Wings +3.5</t>
+          <t>Dallas Wings +2.5</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.5099926829268293</v>
+        <v>0.4695</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>-104</v>
+        <v>113</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>-105</v>
+        <v>113</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -20350,7 +20350,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 51.0% (fair -104). Your call.</t>
+          <t>Model 46.9% (fair +113). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -20382,14 +20382,14 @@
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Lynx -3.5</t>
+          <t>Minnesota Lynx -2.5</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.49</v>
+        <v>0.5305</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>104</v>
+        <v>-113</v>
       </c>
       <c r="H22" s="15" t="n">
         <v>108</v>
@@ -20416,7 +20416,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 49.0% (fair +104). Your call.</t>
+          <t>Model 53.0% (fair -113). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -20452,10 +20452,10 @@
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.3044444444444445</v>
+        <v>0.3029129129129129</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="H23" s="15" t="n">
         <v>233</v>
@@ -20482,7 +20482,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 30.4% (fair +228). Your call.</t>
+          <t>Model 30.3% (fair +230). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -20518,13 +20518,13 @@
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.6955714714714715</v>
+        <v>0.6970782608695653</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>-228</v>
+        <v>-230</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>-233</v>
+        <v>-245</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -20548,7 +20548,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 69.6% (fair -228). Your call.</t>
+          <t>Model 69.7% (fair -230). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -20716,10 +20716,10 @@
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.47875</v>
+        <v>0.47505</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H27" s="15" t="n">
         <v>100</v>
@@ -20746,7 +20746,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 47.9% (fair +109). Your call.</t>
+          <t>Model 47.5% (fair +111). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -20782,13 +20782,13 @@
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.5212376237623763</v>
+        <v>0.5249450980392156</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>-109</v>
+        <v>-111</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>102</v>
+        <v>-104</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -20812,7 +20812,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 52.1% (fair -109). Your call.</t>
+          <t>Model 52.5% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -20848,13 +20848,13 @@
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.7484025974025973</v>
+        <v>0.747679575596817</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>-297</v>
+        <v>-296</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>-285</v>
+        <v>-277</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -20878,7 +20878,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 74.8% (fair -297). Your call.</t>
+          <t>Model 74.8% (fair -296). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -20914,10 +20914,10 @@
         </is>
       </c>
       <c r="F30" s="13" t="n">
-        <v>0.2516103896103896</v>
+        <v>0.2523376623376624</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H30" s="15" t="n">
         <v>285</v>
@@ -20944,7 +20944,7 @@
       </c>
       <c r="N30" s="19" t="inlineStr">
         <is>
-          <t>Model 25.2% (fair +297). Your call.</t>
+          <t>Model 25.2% (fair +296). Your call.</t>
         </is>
       </c>
       <c r="O30" s="15" t="n"/>
@@ -21108,17 +21108,17 @@
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t>Chicago Sky +7.5</t>
+          <t>Chicago Sky +6.5</t>
         </is>
       </c>
       <c r="F33" s="13" t="n">
-        <v>0.5778666666666666</v>
+        <v>0.5519711538461538</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>-137</v>
+        <v>-123</v>
       </c>
       <c r="H33" s="15" t="n">
-        <v>-110</v>
+        <v>108</v>
       </c>
       <c r="I33" s="13">
         <f>IF($H$33="","",IF($H$33&lt;0,-$H$33/(-$H$33+100),100/($H$33+100)))</f>
@@ -21142,7 +21142,7 @@
       </c>
       <c r="N33" s="19" t="inlineStr">
         <is>
-          <t>Model 57.8% (fair -137). Your call.</t>
+          <t>Model 55.2% (fair -123). Your call.</t>
         </is>
       </c>
       <c r="O33" s="15" t="n"/>
@@ -21174,17 +21174,17 @@
       </c>
       <c r="E34" s="20" t="inlineStr">
         <is>
-          <t>Las Vegas Aces -7.5</t>
+          <t>Las Vegas Aces -6.5</t>
         </is>
       </c>
       <c r="F34" s="13" t="n">
-        <v>0.4221380952380953</v>
+        <v>0.4479923076923077</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="H34" s="15" t="n">
-        <v>-110</v>
+        <v>-108</v>
       </c>
       <c r="I34" s="13">
         <f>IF($H$34="","",IF($H$34&lt;0,-$H$34/(-$H$34+100),100/($H$34+100)))</f>
@@ -21208,7 +21208,7 @@
       </c>
       <c r="N34" s="19" t="inlineStr">
         <is>
-          <t>Model 42.2% (fair +137). Your call.</t>
+          <t>Model 44.8% (fair +123). Your call.</t>
         </is>
       </c>
       <c r="O34" s="15" t="n"/>
@@ -21508,13 +21508,13 @@
         </is>
       </c>
       <c r="F39" s="13" t="n">
-        <v>0.5218536585365855</v>
+        <v>0.5274207920792079</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>-109</v>
+        <v>-112</v>
       </c>
       <c r="H39" s="15" t="n">
-        <v>105</v>
+        <v>-102</v>
       </c>
       <c r="I39" s="13">
         <f>IF($H$39="","",IF($H$39&lt;0,-$H$39/(-$H$39+100),100/($H$39+100)))</f>
@@ -21538,7 +21538,7 @@
       </c>
       <c r="N39" s="19" t="inlineStr">
         <is>
-          <t>Model 52.2% (fair -109). Your call.</t>
+          <t>Model 52.7% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O39" s="15" t="n"/>
@@ -21574,13 +21574,13 @@
         </is>
       </c>
       <c r="F40" s="13" t="n">
-        <v>0.4781188118811881</v>
+        <v>0.4725980392156863</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="H40" s="15" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="I40" s="13">
         <f>IF($H$40="","",IF($H$40&lt;0,-$H$40/(-$H$40+100),100/($H$40+100)))</f>
@@ -21604,7 +21604,7 @@
       </c>
       <c r="N40" s="19" t="inlineStr">
         <is>
-          <t>Model 47.8% (fair +109). Your call.</t>
+          <t>Model 47.3% (fair +112). Your call.</t>
         </is>
       </c>
       <c r="O40" s="15" t="n"/>
@@ -21719,25 +21719,25 @@
         </is>
       </c>
       <c r="B5" s="21" t="n">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="C5" s="22" t="n">
-        <v>0.2508</v>
+        <v>0.2513</v>
       </c>
       <c r="D5" s="21" t="n">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E5" s="13" t="n">
-        <v>0.4611</v>
+        <v>0.4615</v>
       </c>
       <c r="F5" s="23" t="n">
-        <v>-0.47</v>
+        <v>0.31</v>
       </c>
       <c r="G5" s="24" t="n">
-        <v>-0.28</v>
+        <v>0.18</v>
       </c>
       <c r="H5" s="24" t="n">
-        <v>2.28</v>
+        <v>2.76</v>
       </c>
       <c r="I5" s="13" t="n">
         <v>0.5034</v>
@@ -21750,28 +21750,28 @@
         </is>
       </c>
       <c r="B6" s="21" t="n">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="C6" s="22" t="n">
-        <v>0.2512</v>
+        <v>0.2518</v>
       </c>
       <c r="D6" s="21" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E6" s="13" t="n">
         <v>0.4962</v>
       </c>
       <c r="F6" s="23" t="n">
-        <v>4.78</v>
+        <v>5.56</v>
       </c>
       <c r="G6" s="24" t="n">
-        <v>3.65</v>
+        <v>4.18</v>
       </c>
       <c r="H6" s="24" t="n">
-        <v>3.61</v>
+        <v>4.17</v>
       </c>
       <c r="I6" s="13" t="n">
-        <v>0.5294</v>
+        <v>0.5289</v>
       </c>
     </row>
     <row r="7">
@@ -21854,7 +21854,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>When the model said X%, how often it actually happened (n=193, ECE 0.063 — lower is better; a calibrated model's bars sit on the diagonal).</t>
+          <t>When the model said X%, how often it actually happened (n=196, ECE 0.066 — lower is better; a calibrated model's bars sit on the diagonal).</t>
         </is>
       </c>
     </row>
@@ -21987,16 +21987,16 @@
         </is>
       </c>
       <c r="B22" s="21" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C22" s="13" t="n">
-        <v>0.6458</v>
+        <v>0.6433</v>
       </c>
       <c r="D22" s="13" t="n">
-        <v>0.5556</v>
+        <v>0.5333</v>
       </c>
       <c r="E22" s="27" t="n">
-        <v>-0.0902</v>
+        <v>-0.11</v>
       </c>
     </row>
     <row r="23">
